--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1368,7 +1368,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm-dd-yy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1378,25 +1378,28 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF0563C1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1599,35 +1602,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1637,14 +1640,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1653,10 +1656,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2108,18 +2112,12 @@
         <f>D8</f>
         <v>0</v>
       </c>
-      <c r="E9" s="10">
-        <f>E8</f>
-        <v>0</v>
-      </c>
+      <c r="E9" s="10"/>
       <c r="F9" s="23">
         <f>F8</f>
         <v>0</v>
       </c>
-      <c r="G9" s="10">
-        <f>G8</f>
-        <v>0</v>
-      </c>
+      <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="J9" s="13"/>
     </row>
@@ -2262,1697 +2260,1697 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:63">
-      <c r="A1" t="s">
+      <c r="A1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AP1" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AQ1" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AT1" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AW1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AX1" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AY1" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AZ1" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BA1" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BB1" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BC1" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BD1" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BE1" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BF1" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BG1" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BH1" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BI1" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BJ1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BK1" s="25" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:63">
-      <c r="A2" t="s">
+      <c r="A2" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z2" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE2" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AG2" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AH2" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AI2" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AK2" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AL2" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AN2" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AO2" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AP2" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AQ2" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AS2" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AT2" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AU2" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AV2" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AW2" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AX2" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AY2" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AZ2" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BA2" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BB2" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BC2" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BD2" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BE2" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BF2" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BG2" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BH2" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BI2" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BJ2" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BK2" s="25" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:63">
-      <c r="A3" t="s">
+      <c r="A3" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="X3" t="s">
+      <c r="X3" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Y3" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="Z3" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AC3" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AD3" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AE3" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AF3" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AG3" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AH3" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AI3" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AJ3" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AK3" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AL3" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AM3" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AN3" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AO3" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="AP3" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="AQ3" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AR3" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AS3" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AT3" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AU3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AV3" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AW3" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="AX3" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="AY3" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="AZ3" t="s">
+      <c r="AZ3" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="BA3" t="s">
+      <c r="BA3" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="BB3" t="s">
+      <c r="BB3" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="BC3" t="s">
+      <c r="BC3" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BD3" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="BE3" t="s">
+      <c r="BE3" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="BF3" t="s">
+      <c r="BF3" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="BG3" t="s">
+      <c r="BG3" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="BH3" t="s">
+      <c r="BH3" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="BI3" t="s">
+      <c r="BI3" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="BJ3" t="s">
+      <c r="BJ3" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="BK3" t="s">
+      <c r="BK3" s="25" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:63">
-      <c r="A4" t="s">
+      <c r="A4" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U4" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="Z4" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AA4" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AD4" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AE4" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AF4" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AG4" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AH4" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AI4" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AJ4" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AK4" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AL4" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AM4" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AN4" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AO4" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AP4" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AQ4" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AR4" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AS4" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AT4" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AW4" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AX4" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AY4" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="AZ4" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BA4" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BB4" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BC4" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BD4" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BE4" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BF4" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BG4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BH4" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BI4" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BJ4" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BK4" s="25" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:63">
-      <c r="A5" t="s">
+      <c r="A5" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="25" t="s">
         <v>249</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R5" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S5" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="T5" t="s">
+      <c r="T5" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U5" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="V5" t="s">
+      <c r="V5" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Y5" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="Z5" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AA5" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AB5" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AC5" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AD5" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AE5" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AF5" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AG5" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AH5" s="25" t="s">
         <v>273</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AI5" s="25" t="s">
         <v>274</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AJ5" s="25" t="s">
         <v>275</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AK5" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AL5" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AM5" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AN5" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AO5" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="AP5" t="s">
+      <c r="AP5" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="AQ5" t="s">
+      <c r="AQ5" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AR5" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AS5" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AT5" s="25" t="s">
         <v>284</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AW5" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AX5" s="25" t="s">
         <v>287</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AY5" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="AZ5" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BA5" s="25" t="s">
         <v>290</v>
       </c>
-      <c r="BB5" t="s">
+      <c r="BB5" s="25" t="s">
         <v>291</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BC5" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="BD5" t="s">
+      <c r="BD5" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BE5" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BF5" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BG5" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="BH5" t="s">
+      <c r="BH5" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="BI5" t="s">
+      <c r="BI5" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="BJ5" t="s">
+      <c r="BJ5" s="25" t="s">
         <v>298</v>
       </c>
-      <c r="BK5" t="s">
+      <c r="BK5" s="25" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:63">
-      <c r="A6" t="s">
+      <c r="A6" s="25" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:63">
-      <c r="A7" t="s">
+      <c r="A7" s="25" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:63">
-      <c r="A8" t="s">
+      <c r="A8" s="25" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:63">
-      <c r="A9" t="s">
+      <c r="A9" s="25" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:63">
-      <c r="A10" t="s">
+      <c r="A10" s="25" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:63">
-      <c r="A11" t="s">
+      <c r="A11" s="25" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:63">
-      <c r="A12" t="s">
+      <c r="A12" s="25" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:63">
-      <c r="A13" t="s">
+      <c r="A13" s="25" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:63">
-      <c r="A14" t="s">
+      <c r="A14" s="25" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:63">
-      <c r="A15" t="s">
+      <c r="A15" s="25" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:63">
-      <c r="A16" t="s">
+      <c r="A16" s="25" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" t="s">
+      <c r="A17" s="25" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" t="s">
+      <c r="A18" s="25" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" t="s">
+      <c r="A19" s="25" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" t="s">
+      <c r="A20" s="25" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" t="s">
+      <c r="A21" s="25" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" t="s">
+      <c r="A22" s="25" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" t="s">
+      <c r="A23" s="25" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" t="s">
+      <c r="A24" s="25" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" t="s">
+      <c r="A25" s="25" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" t="s">
+      <c r="A26" s="25" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" t="s">
+      <c r="A27" s="25" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="s">
+      <c r="A28" s="25" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" t="s">
+      <c r="A29" s="25" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" t="s">
+      <c r="A30" s="25" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" t="s">
+      <c r="A31" s="25" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" t="s">
+      <c r="A32" s="25" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" t="s">
+      <c r="A33" s="25" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" t="s">
+      <c r="A34" s="25" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" t="s">
+      <c r="A35" s="25" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" t="s">
+      <c r="A36" s="25" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" t="s">
+      <c r="A37" s="25" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="s">
+      <c r="A38" s="25" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" t="s">
+      <c r="A39" s="25" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" t="s">
+      <c r="A40" s="25" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" t="s">
+      <c r="A41" s="25" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" t="s">
+      <c r="A42" s="25" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" t="s">
+      <c r="A43" s="25" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" t="s">
+      <c r="A44" s="25" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
+      <c r="A45" s="25" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" t="s">
+      <c r="A46" s="25" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" t="s">
+      <c r="A47" s="25" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" t="s">
+      <c r="A48" s="25" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" t="s">
+      <c r="A49" s="25" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" t="s">
+      <c r="A50" s="25" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
+      <c r="A51" s="25" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" t="s">
+      <c r="A52" s="25" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" t="s">
+      <c r="A53" s="25" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" t="s">
+      <c r="A54" s="25" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
+      <c r="A55" s="25" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" t="s">
+      <c r="A56" s="25" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" t="s">
+      <c r="A57" s="25" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
+      <c r="A58" s="25" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" t="s">
+      <c r="A59" s="25" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" t="s">
+      <c r="A60" s="25" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" t="s">
+      <c r="A61" s="25" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" t="s">
+      <c r="A62" s="25" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" t="s">
+      <c r="A63" s="25" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" t="s">
+      <c r="A64" s="25" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" t="s">
+      <c r="A65" s="25" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" t="s">
+      <c r="A66" s="25" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" t="s">
+      <c r="A67" s="25" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" t="s">
+      <c r="A68" s="25" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" t="s">
+      <c r="A69" s="25" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" t="s">
+      <c r="A70" s="25" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" t="s">
+      <c r="A71" s="25" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" t="s">
+      <c r="A72" s="25" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" t="s">
+      <c r="A73" s="25" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" t="s">
+      <c r="A74" s="25" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" t="s">
+      <c r="A75" s="25" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" t="s">
+      <c r="A76" s="25" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" t="s">
+      <c r="A77" s="25" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" t="s">
+      <c r="A78" s="25" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" t="s">
+      <c r="A79" s="25" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" t="s">
+      <c r="A80" s="25" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" t="s">
+      <c r="A81" s="25" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" t="s">
+      <c r="A82" s="25" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" t="s">
+      <c r="A83" s="25" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" t="s">
+      <c r="A84" s="25" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" t="s">
+      <c r="A85" s="25" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" t="s">
+      <c r="A86" s="25" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" t="s">
+      <c r="A87" s="25" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" t="s">
+      <c r="A88" s="25" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" t="s">
+      <c r="A89" s="25" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" t="s">
+      <c r="A90" s="25" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" t="s">
+      <c r="A91" s="25" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" t="s">
+      <c r="A92" s="25" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" t="s">
+      <c r="A93" s="25" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" t="s">
+      <c r="A94" s="25" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" t="s">
+      <c r="A95" s="25" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" t="s">
+      <c r="A96" s="25" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" t="s">
+      <c r="A97" s="25" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" t="s">
+      <c r="A98" s="25" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" t="s">
+      <c r="A99" s="25" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" t="s">
+      <c r="A100" s="25" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" t="s">
+      <c r="A101" s="25" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" t="s">
+      <c r="A102" s="25" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" t="s">
+      <c r="A103" s="25" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" t="s">
+      <c r="A104" s="25" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" t="s">
+      <c r="A105" s="25" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" t="s">
+      <c r="A106" s="25" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" t="s">
+      <c r="A107" s="25" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" t="s">
+      <c r="A108" s="25" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" t="s">
+      <c r="A109" s="25" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" t="s">
+      <c r="A110" s="25" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" t="s">
+      <c r="A111" s="25" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" t="s">
+      <c r="A112" s="25" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" t="s">
+      <c r="A113" s="25" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" t="s">
+      <c r="A114" s="25" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" t="s">
+      <c r="A115" s="25" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" t="s">
+      <c r="A116" s="25" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" t="s">
+      <c r="A117" s="25" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" t="s">
+      <c r="A118" s="25" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" t="s">
+      <c r="A119" s="25" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" t="s">
+      <c r="A120" s="25" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" t="s">
+      <c r="A121" s="25" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" t="s">
+      <c r="A122" s="25" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" t="s">
+      <c r="A123" s="25" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" t="s">
+      <c r="A124" s="25" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" t="s">
+      <c r="A125" s="25" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" t="s">
+      <c r="A126" s="25" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" t="s">
+      <c r="A127" s="25" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" t="s">
+      <c r="A128" s="25" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" t="s">
+      <c r="A129" s="25" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" t="s">
+      <c r="A130" s="25" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" t="s">
+      <c r="A131" s="25" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" t="s">
+      <c r="A132" s="25" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" t="s">
+      <c r="A133" s="25" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" t="s">
+      <c r="A134" s="25" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" t="s">
+      <c r="A135" s="25" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" t="s">
+      <c r="A136" s="25" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" t="s">
+      <c r="A137" s="25" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" t="s">
+      <c r="A138" s="25" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" t="s">
+      <c r="A139" s="25" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" t="s">
+      <c r="A140" s="25" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" t="s">
+      <c r="A141" s="25" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" t="s">
+      <c r="A142" s="25" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" t="s">
+      <c r="A143" s="25" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" t="s">
+      <c r="A144" s="25" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" t="s">
+      <c r="A145" s="25" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" t="s">
+      <c r="A146" s="25" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" t="s">
+      <c r="A147" s="25" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" t="s">
+      <c r="A148" s="25" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" t="s">
+      <c r="A149" s="25" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" t="s">
+      <c r="A150" s="25" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" t="s">
+      <c r="A151" s="25" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" t="s">
+      <c r="A152" s="25" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" t="s">
+      <c r="A153" s="25" t="s">
         <v>447</v>
       </c>
     </row>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1428,7 +1428,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1505,6 +1505,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1534,20 +1545,7 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -1556,7 +1554,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top/>
@@ -1574,35 +1572,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1631,16 +1605,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1653,13 +1636,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1985,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="J1" s="22">
+      <c r="J1" s="25">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>0</v>
       </c>
@@ -2004,7 +1984,7 @@
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="23" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="5">
@@ -2027,7 +2007,7 @@
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="23">
         <f>IF($E$2="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
@@ -2085,12 +2065,12 @@
         <v>0</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="23">
+      <c r="D8" s="26">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="23">
+      <c r="F8" s="26">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>0</v>
       </c>
@@ -2108,12 +2088,12 @@
         <v>0</v>
       </c>
       <c r="C9" s="7"/>
-      <c r="D9" s="23">
+      <c r="D9" s="26">
         <f>D8</f>
         <v>0</v>
       </c>
       <c r="E9" s="10"/>
-      <c r="F9" s="23">
+      <c r="F9" s="26">
         <f>F8</f>
         <v>0</v>
       </c>
@@ -2123,27 +2103,25 @@
     </row>
     <row r="10" spans="2:22" ht="13.5" customHeight="1"/>
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B11" s="24">
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="16">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="D11" s="14">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="14">
+      <c r="E11" s="17">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="16">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="16">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="18">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>0</v>
       </c>
@@ -2159,67 +2137,67 @@
       <c r="R11" s="1"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="16">
+      <c r="B12" s="19">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="15"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="17">
+      <c r="B13" s="20">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15"/>
-      <c r="L13" s="21">
+      <c r="C13" s="20"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="18"/>
+      <c r="L13" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="21" t="s">
+      <c r="M13" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="21">
+      <c r="N13" s="24">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="21">
+      <c r="O13" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S13" s="21">
+      <c r="S13" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="T13" s="21" t="s">
+      <c r="T13" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="U13" s="21">
+      <c r="U13" s="24">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="21">
+      <c r="V13" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="15"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -2260,1697 +2238,1697 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:63">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="25" t="s">
+      <c r="R1" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="S1" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="T1" s="25" t="s">
+      <c r="T1" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="U1" s="25" t="s">
+      <c r="U1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="25" t="s">
+      <c r="V1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="25" t="s">
+      <c r="W1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="25" t="s">
+      <c r="X1" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="25" t="s">
+      <c r="Y1" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="25" t="s">
+      <c r="Z1" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="25" t="s">
+      <c r="AA1" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="25" t="s">
+      <c r="AB1" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="25" t="s">
+      <c r="AC1" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" s="25" t="s">
+      <c r="AD1" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" s="25" t="s">
+      <c r="AE1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="25" t="s">
+      <c r="AF1" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="25" t="s">
+      <c r="AG1" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="AH1" s="25" t="s">
+      <c r="AH1" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" s="25" t="s">
+      <c r="AI1" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="25" t="s">
+      <c r="AJ1" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" s="25" t="s">
+      <c r="AK1" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="AL1" s="25" t="s">
+      <c r="AL1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" s="25" t="s">
+      <c r="AM1" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="AN1" s="25" t="s">
+      <c r="AN1" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="AO1" s="25" t="s">
+      <c r="AO1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="AP1" s="25" t="s">
+      <c r="AP1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="AQ1" s="25" t="s">
+      <c r="AQ1" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="AR1" s="25" t="s">
+      <c r="AR1" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="AS1" s="25" t="s">
+      <c r="AS1" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="AT1" s="25" t="s">
+      <c r="AT1" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="AU1" s="25" t="s">
+      <c r="AU1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="AV1" s="25" t="s">
+      <c r="AV1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="AW1" s="25" t="s">
+      <c r="AW1" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="AX1" s="25" t="s">
+      <c r="AX1" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="AY1" s="25" t="s">
+      <c r="AY1" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="AZ1" s="25" t="s">
+      <c r="AZ1" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" s="25" t="s">
+      <c r="BA1" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="BB1" s="25" t="s">
+      <c r="BB1" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="BC1" s="25" t="s">
+      <c r="BC1" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="BD1" s="25" t="s">
+      <c r="BD1" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="BE1" s="25" t="s">
+      <c r="BE1" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="BF1" s="25" t="s">
+      <c r="BF1" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="BG1" s="25" t="s">
+      <c r="BG1" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="BH1" s="25" t="s">
+      <c r="BH1" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="BI1" s="25" t="s">
+      <c r="BI1" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="BJ1" s="25" t="s">
+      <c r="BJ1" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="BK1" s="25" t="s">
+      <c r="BK1" s="27" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:63">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="L2" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="Q2" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="R2" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="25" t="s">
+      <c r="S2" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="25" t="s">
+      <c r="T2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="25" t="s">
+      <c r="U2" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="V2" s="25" t="s">
+      <c r="V2" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="W2" s="25" t="s">
+      <c r="W2" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="25" t="s">
+      <c r="X2" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="25" t="s">
+      <c r="Y2" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="25" t="s">
+      <c r="Z2" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="25" t="s">
+      <c r="AA2" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="25" t="s">
+      <c r="AB2" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="AC2" s="25" t="s">
+      <c r="AC2" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="AD2" s="25" t="s">
+      <c r="AD2" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="AE2" s="25" t="s">
+      <c r="AE2" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="25" t="s">
+      <c r="AF2" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="AG2" s="25" t="s">
+      <c r="AG2" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AH2" s="25" t="s">
+      <c r="AH2" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="AI2" s="25" t="s">
+      <c r="AI2" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="AJ2" s="25" t="s">
+      <c r="AJ2" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" s="25" t="s">
+      <c r="AK2" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="AL2" s="25" t="s">
+      <c r="AL2" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="AM2" s="25" t="s">
+      <c r="AM2" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="AN2" s="25" t="s">
+      <c r="AN2" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="AO2" s="25" t="s">
+      <c r="AO2" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="AP2" s="25" t="s">
+      <c r="AP2" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="AQ2" s="25" t="s">
+      <c r="AQ2" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="AR2" s="25" t="s">
+      <c r="AR2" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="AS2" s="25" t="s">
+      <c r="AS2" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="AT2" s="25" t="s">
+      <c r="AT2" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="AU2" s="25" t="s">
+      <c r="AU2" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="AV2" s="25" t="s">
+      <c r="AV2" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="AW2" s="25" t="s">
+      <c r="AW2" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="AX2" s="25" t="s">
+      <c r="AX2" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" s="25" t="s">
+      <c r="AY2" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="AZ2" s="25" t="s">
+      <c r="AZ2" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="BA2" s="25" t="s">
+      <c r="BA2" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="BB2" s="25" t="s">
+      <c r="BB2" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="BC2" s="25" t="s">
+      <c r="BC2" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="BD2" s="25" t="s">
+      <c r="BD2" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="BE2" s="25" t="s">
+      <c r="BE2" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="BF2" s="25" t="s">
+      <c r="BF2" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="BG2" s="25" t="s">
+      <c r="BG2" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="BH2" s="25" t="s">
+      <c r="BH2" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="BI2" s="25" t="s">
+      <c r="BI2" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="BJ2" s="25" t="s">
+      <c r="BJ2" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="BK2" s="25" t="s">
+      <c r="BK2" s="27" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:63">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="M3" s="25" t="s">
+      <c r="M3" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="O3" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="P3" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="Q3" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="R3" s="25" t="s">
+      <c r="R3" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="S3" s="25" t="s">
+      <c r="S3" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="T3" s="25" t="s">
+      <c r="T3" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="U3" s="25" t="s">
+      <c r="U3" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="V3" s="25" t="s">
+      <c r="V3" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="W3" s="25" t="s">
+      <c r="W3" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="X3" s="25" t="s">
+      <c r="X3" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="Y3" s="25" t="s">
+      <c r="Y3" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="Z3" s="25" t="s">
+      <c r="Z3" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="AA3" s="25" t="s">
+      <c r="AA3" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="AB3" s="25" t="s">
+      <c r="AB3" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="AC3" s="25" t="s">
+      <c r="AC3" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="AD3" s="25" t="s">
+      <c r="AD3" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="AE3" s="25" t="s">
+      <c r="AE3" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="AF3" s="25" t="s">
+      <c r="AF3" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="AG3" s="25" t="s">
+      <c r="AG3" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="AH3" s="25" t="s">
+      <c r="AH3" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="AI3" s="25" t="s">
+      <c r="AI3" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="AJ3" s="25" t="s">
+      <c r="AJ3" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="AK3" s="25" t="s">
+      <c r="AK3" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AL3" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="AM3" s="25" t="s">
+      <c r="AM3" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="AN3" s="25" t="s">
+      <c r="AN3" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="AO3" s="25" t="s">
+      <c r="AO3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="AP3" s="25" t="s">
+      <c r="AP3" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="AQ3" s="25" t="s">
+      <c r="AQ3" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="AR3" s="25" t="s">
+      <c r="AR3" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="AS3" s="25" t="s">
+      <c r="AS3" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="AT3" s="25" t="s">
+      <c r="AT3" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="AU3" s="25" t="s">
+      <c r="AU3" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="AV3" s="25" t="s">
+      <c r="AV3" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="AW3" s="25" t="s">
+      <c r="AW3" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="AX3" s="25" t="s">
+      <c r="AX3" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="AY3" s="25" t="s">
+      <c r="AY3" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="AZ3" s="25" t="s">
+      <c r="AZ3" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="BA3" s="25" t="s">
+      <c r="BA3" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="BB3" s="25" t="s">
+      <c r="BB3" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="BC3" s="25" t="s">
+      <c r="BC3" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="BD3" s="25" t="s">
+      <c r="BD3" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="BE3" s="25" t="s">
+      <c r="BE3" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="BF3" s="25" t="s">
+      <c r="BF3" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="BG3" s="25" t="s">
+      <c r="BG3" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="BH3" s="25" t="s">
+      <c r="BH3" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="BI3" s="25" t="s">
+      <c r="BI3" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="BJ3" s="25" t="s">
+      <c r="BJ3" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="BK3" s="25" t="s">
+      <c r="BK3" s="27" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:63">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="I4" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="K4" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="L4" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="M4" s="25" t="s">
+      <c r="M4" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="N4" s="25" t="s">
+      <c r="N4" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="O4" s="25" t="s">
+      <c r="O4" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="P4" s="25" t="s">
+      <c r="P4" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="Q4" s="25" t="s">
+      <c r="Q4" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="R4" s="25" t="s">
+      <c r="R4" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="S4" s="25" t="s">
+      <c r="S4" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="T4" s="25" t="s">
+      <c r="T4" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="U4" s="25" t="s">
+      <c r="U4" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="V4" s="25" t="s">
+      <c r="V4" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="W4" s="25" t="s">
+      <c r="W4" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="X4" s="25" t="s">
+      <c r="X4" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="Y4" s="25" t="s">
+      <c r="Y4" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="Z4" s="25" t="s">
+      <c r="Z4" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="AA4" s="25" t="s">
+      <c r="AA4" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="AB4" s="25" t="s">
+      <c r="AB4" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="AC4" s="25" t="s">
+      <c r="AC4" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="AD4" s="25" t="s">
+      <c r="AD4" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="AE4" s="25" t="s">
+      <c r="AE4" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="AF4" s="25" t="s">
+      <c r="AF4" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="AG4" s="25" t="s">
+      <c r="AG4" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="AH4" s="25" t="s">
+      <c r="AH4" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="AI4" s="25" t="s">
+      <c r="AI4" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="AJ4" s="25" t="s">
+      <c r="AJ4" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="AK4" s="25" t="s">
+      <c r="AK4" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="AL4" s="25" t="s">
+      <c r="AL4" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="AM4" s="25" t="s">
+      <c r="AM4" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="AN4" s="25" t="s">
+      <c r="AN4" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="AO4" s="25" t="s">
+      <c r="AO4" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="AP4" s="25" t="s">
+      <c r="AP4" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="AQ4" s="25" t="s">
+      <c r="AQ4" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="AR4" s="25" t="s">
+      <c r="AR4" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="AS4" s="25" t="s">
+      <c r="AS4" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="AT4" s="25" t="s">
+      <c r="AT4" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="AU4" s="25" t="s">
+      <c r="AU4" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="AV4" s="25" t="s">
+      <c r="AV4" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="AW4" s="25" t="s">
+      <c r="AW4" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="AX4" s="25" t="s">
+      <c r="AX4" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="AY4" s="25" t="s">
+      <c r="AY4" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="AZ4" s="25" t="s">
+      <c r="AZ4" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="BA4" s="25" t="s">
+      <c r="BA4" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="BB4" s="25" t="s">
+      <c r="BB4" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="BC4" s="25" t="s">
+      <c r="BC4" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="BD4" s="25" t="s">
+      <c r="BD4" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="BE4" s="25" t="s">
+      <c r="BE4" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="BF4" s="25" t="s">
+      <c r="BF4" s="27" t="s">
         <v>238</v>
       </c>
-      <c r="BG4" s="25" t="s">
+      <c r="BG4" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="BH4" s="25" t="s">
+      <c r="BH4" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="BI4" s="25" t="s">
+      <c r="BI4" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="BJ4" s="25" t="s">
+      <c r="BJ4" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="BK4" s="25" t="s">
+      <c r="BK4" s="27" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:63">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="I5" s="25" t="s">
+      <c r="I5" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="K5" s="25" t="s">
+      <c r="K5" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="N5" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="O5" s="25" t="s">
+      <c r="O5" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="P5" s="25" t="s">
+      <c r="P5" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="R5" s="25" t="s">
+      <c r="R5" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="S5" s="25" t="s">
+      <c r="S5" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="T5" s="25" t="s">
+      <c r="T5" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="U5" s="25" t="s">
+      <c r="U5" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="V5" s="25" t="s">
+      <c r="V5" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="W5" s="25" t="s">
+      <c r="W5" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="X5" s="25" t="s">
+      <c r="X5" s="27" t="s">
         <v>264</v>
       </c>
-      <c r="Y5" s="25" t="s">
+      <c r="Y5" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="Z5" s="25" t="s">
+      <c r="Z5" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="AA5" s="25" t="s">
+      <c r="AA5" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="AB5" s="25" t="s">
+      <c r="AB5" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="AC5" s="25" t="s">
+      <c r="AC5" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="AD5" s="25" t="s">
+      <c r="AD5" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="AE5" s="25" t="s">
+      <c r="AE5" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="AF5" s="25" t="s">
+      <c r="AF5" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="AG5" s="25" t="s">
+      <c r="AG5" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="AH5" s="25" t="s">
+      <c r="AH5" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="AI5" s="25" t="s">
+      <c r="AI5" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="AJ5" s="25" t="s">
+      <c r="AJ5" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="AK5" s="25" t="s">
+      <c r="AK5" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="AL5" s="25" t="s">
+      <c r="AL5" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="AM5" s="25" t="s">
+      <c r="AM5" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="AN5" s="25" t="s">
+      <c r="AN5" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="AO5" s="25" t="s">
+      <c r="AO5" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="AP5" s="25" t="s">
+      <c r="AP5" s="27" t="s">
         <v>281</v>
       </c>
-      <c r="AQ5" s="25" t="s">
+      <c r="AQ5" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="AR5" s="25" t="s">
+      <c r="AR5" s="27" t="s">
         <v>282</v>
       </c>
-      <c r="AS5" s="25" t="s">
+      <c r="AS5" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="AT5" s="25" t="s">
+      <c r="AT5" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="AU5" s="25" t="s">
+      <c r="AU5" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="AV5" s="25" t="s">
+      <c r="AV5" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="AW5" s="25" t="s">
+      <c r="AW5" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="AX5" s="25" t="s">
+      <c r="AX5" s="27" t="s">
         <v>287</v>
       </c>
-      <c r="AY5" s="25" t="s">
+      <c r="AY5" s="27" t="s">
         <v>288</v>
       </c>
-      <c r="AZ5" s="25" t="s">
+      <c r="AZ5" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="BA5" s="25" t="s">
+      <c r="BA5" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="BB5" s="25" t="s">
+      <c r="BB5" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="BC5" s="25" t="s">
+      <c r="BC5" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="BD5" s="25" t="s">
+      <c r="BD5" s="27" t="s">
         <v>293</v>
       </c>
-      <c r="BE5" s="25" t="s">
+      <c r="BE5" s="27" t="s">
         <v>294</v>
       </c>
-      <c r="BF5" s="25" t="s">
+      <c r="BF5" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="BG5" s="25" t="s">
+      <c r="BG5" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="BH5" s="25" t="s">
+      <c r="BH5" s="27" t="s">
         <v>296</v>
       </c>
-      <c r="BI5" s="25" t="s">
+      <c r="BI5" s="27" t="s">
         <v>297</v>
       </c>
-      <c r="BJ5" s="25" t="s">
+      <c r="BJ5" s="27" t="s">
         <v>298</v>
       </c>
-      <c r="BK5" s="25" t="s">
+      <c r="BK5" s="27" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:63">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="27" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:63">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="27" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:63">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:63">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="27" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:63">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:63">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="27" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:63">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="27" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:63">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="27" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:63">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="27" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:63">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="27" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:63">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="27" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="27" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="27" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="27" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="27" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="27" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="27" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="27" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="27" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="27" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="27" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="27" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="27" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="27" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="27" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="27" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="27" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="27" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="27" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="27" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="27" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="27" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="27" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="27" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="27" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="27" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="27" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="27" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="27" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="27" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="27" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="27" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="25" t="s">
+      <c r="A48" s="27" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="27" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="27" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="27" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="27" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="27" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="27" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="27" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="27" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="25" t="s">
+      <c r="A57" s="27" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="25" t="s">
+      <c r="A58" s="27" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="25" t="s">
+      <c r="A59" s="27" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="25" t="s">
+      <c r="A60" s="27" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="27" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="25" t="s">
+      <c r="A62" s="27" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="25" t="s">
+      <c r="A63" s="27" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="25" t="s">
+      <c r="A64" s="27" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="25" t="s">
+      <c r="A65" s="27" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="25" t="s">
+      <c r="A66" s="27" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="25" t="s">
+      <c r="A67" s="27" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="25" t="s">
+      <c r="A68" s="27" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="25" t="s">
+      <c r="A69" s="27" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="25" t="s">
+      <c r="A70" s="27" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="25" t="s">
+      <c r="A71" s="27" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="25" t="s">
+      <c r="A72" s="27" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="25" t="s">
+      <c r="A73" s="27" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="25" t="s">
+      <c r="A74" s="27" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="25" t="s">
+      <c r="A75" s="27" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="25" t="s">
+      <c r="A76" s="27" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="25" t="s">
+      <c r="A77" s="27" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="25" t="s">
+      <c r="A78" s="27" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="25" t="s">
+      <c r="A79" s="27" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="25" t="s">
+      <c r="A80" s="27" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="25" t="s">
+      <c r="A81" s="27" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="25" t="s">
+      <c r="A82" s="27" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="25" t="s">
+      <c r="A83" s="27" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="25" t="s">
+      <c r="A84" s="27" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="25" t="s">
+      <c r="A85" s="27" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="25" t="s">
+      <c r="A86" s="27" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="25" t="s">
+      <c r="A87" s="27" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="25" t="s">
+      <c r="A88" s="27" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="25" t="s">
+      <c r="A89" s="27" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="25" t="s">
+      <c r="A90" s="27" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="25" t="s">
+      <c r="A91" s="27" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="25" t="s">
+      <c r="A92" s="27" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="25" t="s">
+      <c r="A93" s="27" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="25" t="s">
+      <c r="A94" s="27" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="25" t="s">
+      <c r="A95" s="27" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="25" t="s">
+      <c r="A96" s="27" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="25" t="s">
+      <c r="A97" s="27" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="25" t="s">
+      <c r="A98" s="27" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="25" t="s">
+      <c r="A99" s="27" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="25" t="s">
+      <c r="A100" s="27" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="25" t="s">
+      <c r="A101" s="27" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="25" t="s">
+      <c r="A102" s="27" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="25" t="s">
+      <c r="A103" s="27" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="25" t="s">
+      <c r="A104" s="27" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="25" t="s">
+      <c r="A105" s="27" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="25" t="s">
+      <c r="A106" s="27" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="25" t="s">
+      <c r="A107" s="27" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="25" t="s">
+      <c r="A108" s="27" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="25" t="s">
+      <c r="A109" s="27" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="25" t="s">
+      <c r="A110" s="27" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="25" t="s">
+      <c r="A111" s="27" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="25" t="s">
+      <c r="A112" s="27" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="25" t="s">
+      <c r="A113" s="27" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="25" t="s">
+      <c r="A114" s="27" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="25" t="s">
+      <c r="A115" s="27" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="25" t="s">
+      <c r="A116" s="27" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="25" t="s">
+      <c r="A117" s="27" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="25" t="s">
+      <c r="A118" s="27" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="25" t="s">
+      <c r="A119" s="27" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="25" t="s">
+      <c r="A120" s="27" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="25" t="s">
+      <c r="A121" s="27" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="25" t="s">
+      <c r="A122" s="27" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="25" t="s">
+      <c r="A123" s="27" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="25" t="s">
+      <c r="A124" s="27" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="25" t="s">
+      <c r="A125" s="27" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="25" t="s">
+      <c r="A126" s="27" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="25" t="s">
+      <c r="A127" s="27" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="25" t="s">
+      <c r="A128" s="27" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="25" t="s">
+      <c r="A129" s="27" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="25" t="s">
+      <c r="A130" s="27" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="25" t="s">
+      <c r="A131" s="27" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="25" t="s">
+      <c r="A132" s="27" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="25" t="s">
+      <c r="A133" s="27" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="25" t="s">
+      <c r="A134" s="27" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="25" t="s">
+      <c r="A135" s="27" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="25" t="s">
+      <c r="A136" s="27" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="25" t="s">
+      <c r="A137" s="27" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="25" t="s">
+      <c r="A138" s="27" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="25" t="s">
+      <c r="A139" s="27" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="25" t="s">
+      <c r="A140" s="27" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="25" t="s">
+      <c r="A141" s="27" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="25" t="s">
+      <c r="A142" s="27" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="25" t="s">
+      <c r="A143" s="27" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="25" t="s">
+      <c r="A144" s="27" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="25" t="s">
+      <c r="A145" s="27" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="25" t="s">
+      <c r="A146" s="27" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="25" t="s">
+      <c r="A147" s="27" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="25" t="s">
+      <c r="A148" s="27" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="25" t="s">
+      <c r="A149" s="27" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="25" t="s">
+      <c r="A150" s="27" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="25" t="s">
+      <c r="A151" s="27" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="25" t="s">
+      <c r="A152" s="27" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="25" t="s">
+      <c r="A153" s="27" t="s">
         <v>447</v>
       </c>
     </row>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1365,8 +1365,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm-dd-yy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -1402,7 +1404,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1427,8 +1429,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1516,9 +1524,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1532,6 +1538,19 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -1545,6 +1564,17 @@
       <left style="medium">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -1554,7 +1584,7 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top/>
@@ -1572,11 +1602,99 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1608,29 +1726,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1640,6 +1758,23 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1935,7 +2070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.28515625" customWidth="1"/>
@@ -2018,7 +2153,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="2:22" ht="12.75" customHeight="1">
+    <row r="4" spans="2:22" ht="12" customHeight="1">
       <c r="J4" s="6">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>0</v>
@@ -2029,7 +2164,7 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="2:22" ht="12" customHeight="1">
+    <row r="5" spans="2:22">
       <c r="B5" s="7">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>0</v>
@@ -2199,8 +2334,114 @@
       <c r="G14" s="16"/>
       <c r="H14" s="18"/>
     </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="27">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28">
+        <v>0</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="32"/>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="B16" s="33">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="33"/>
+      <c r="D16" s="28">
+        <v>0</v>
+      </c>
+      <c r="E16" s="29"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="31">
+        <f>IFERROR(F16/D16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="32"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="33">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="33"/>
+      <c r="D17" s="28">
+        <v>0</v>
+      </c>
+      <c r="E17" s="29"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="31">
+        <f>IFERROR(F17/D17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="32"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="33">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="28">
+        <v>0</v>
+      </c>
+      <c r="E18" s="29"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="31">
+        <f>IFERROR(F18/D18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="32"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="33">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="33"/>
+      <c r="D19" s="28">
+        <v>0</v>
+      </c>
+      <c r="E19" s="29"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="31">
+        <f>IFERROR(F19/D19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="32"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="34">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="34"/>
+      <c r="D20" s="35">
+        <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="35">
+        <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="35">
+        <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="36">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="37"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="27">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="J2:O3"/>
@@ -2222,6 +2463,12 @@
     <mergeCell ref="H11:H14"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2">
@@ -2238,1697 +2485,1697 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:63">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="M1" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="27" t="s">
+      <c r="O1" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="P1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="27" t="s">
+      <c r="Q1" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="T1" s="27" t="s">
+      <c r="T1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="U1" s="27" t="s">
+      <c r="U1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="27" t="s">
+      <c r="V1" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="27" t="s">
+      <c r="W1" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="27" t="s">
+      <c r="X1" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="27" t="s">
+      <c r="Y1" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="27" t="s">
+      <c r="Z1" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="27" t="s">
+      <c r="AA1" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="27" t="s">
+      <c r="AB1" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="27" t="s">
+      <c r="AC1" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" s="27" t="s">
+      <c r="AD1" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" s="27" t="s">
+      <c r="AE1" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="27" t="s">
+      <c r="AF1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="27" t="s">
+      <c r="AG1" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AH1" s="27" t="s">
+      <c r="AH1" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" s="27" t="s">
+      <c r="AI1" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="27" t="s">
+      <c r="AJ1" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" s="27" t="s">
+      <c r="AK1" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="AL1" s="27" t="s">
+      <c r="AL1" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" s="27" t="s">
+      <c r="AM1" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="AN1" s="27" t="s">
+      <c r="AN1" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="AO1" s="27" t="s">
+      <c r="AO1" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="AP1" s="27" t="s">
+      <c r="AP1" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="AQ1" s="27" t="s">
+      <c r="AQ1" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="AR1" s="27" t="s">
+      <c r="AR1" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="AS1" s="27" t="s">
+      <c r="AS1" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="AT1" s="27" t="s">
+      <c r="AT1" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="AU1" s="27" t="s">
+      <c r="AU1" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="AV1" s="27" t="s">
+      <c r="AV1" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="AW1" s="27" t="s">
+      <c r="AW1" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="AX1" s="27" t="s">
+      <c r="AX1" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="AY1" s="27" t="s">
+      <c r="AY1" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="AZ1" s="27" t="s">
+      <c r="AZ1" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" s="27" t="s">
+      <c r="BA1" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="BB1" s="27" t="s">
+      <c r="BB1" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="BC1" s="27" t="s">
+      <c r="BC1" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="BD1" s="27" t="s">
+      <c r="BD1" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="BE1" s="27" t="s">
+      <c r="BE1" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="BF1" s="27" t="s">
+      <c r="BF1" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="BG1" s="27" t="s">
+      <c r="BG1" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="BH1" s="27" t="s">
+      <c r="BH1" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="BI1" s="27" t="s">
+      <c r="BI1" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="BJ1" s="27" t="s">
+      <c r="BJ1" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="BK1" s="27" t="s">
+      <c r="BK1" s="38" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:63">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="P2" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="Q2" s="27" t="s">
+      <c r="Q2" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="R2" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="S2" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="T2" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="U2" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="V2" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="W2" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="X2" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="27" t="s">
+      <c r="Y2" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="Z2" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AA2" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AB2" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="AC2" s="27" t="s">
+      <c r="AC2" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="AD2" s="27" t="s">
+      <c r="AD2" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="AE2" s="27" t="s">
+      <c r="AE2" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="27" t="s">
+      <c r="AF2" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="AG2" s="27" t="s">
+      <c r="AG2" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="AH2" s="27" t="s">
+      <c r="AH2" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="AI2" s="27" t="s">
+      <c r="AI2" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="AJ2" s="27" t="s">
+      <c r="AJ2" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" s="27" t="s">
+      <c r="AK2" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="AL2" s="27" t="s">
+      <c r="AL2" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="AM2" s="27" t="s">
+      <c r="AM2" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="AN2" s="27" t="s">
+      <c r="AN2" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="AO2" s="27" t="s">
+      <c r="AO2" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="AP2" s="27" t="s">
+      <c r="AP2" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="AQ2" s="27" t="s">
+      <c r="AQ2" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="AR2" s="27" t="s">
+      <c r="AR2" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="AS2" s="27" t="s">
+      <c r="AS2" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="AT2" s="27" t="s">
+      <c r="AT2" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="AU2" s="27" t="s">
+      <c r="AU2" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="AV2" s="27" t="s">
+      <c r="AV2" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="AW2" s="27" t="s">
+      <c r="AW2" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="AX2" s="27" t="s">
+      <c r="AX2" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" s="27" t="s">
+      <c r="AY2" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="AZ2" s="27" t="s">
+      <c r="AZ2" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="BA2" s="27" t="s">
+      <c r="BA2" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="BB2" s="27" t="s">
+      <c r="BB2" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="BC2" s="27" t="s">
+      <c r="BC2" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="BD2" s="27" t="s">
+      <c r="BD2" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="BE2" s="27" t="s">
+      <c r="BE2" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="BF2" s="27" t="s">
+      <c r="BF2" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="BG2" s="27" t="s">
+      <c r="BG2" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="BH2" s="27" t="s">
+      <c r="BH2" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="BI2" s="27" t="s">
+      <c r="BI2" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="BJ2" s="27" t="s">
+      <c r="BJ2" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="BK2" s="27" t="s">
+      <c r="BK2" s="38" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:63">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="N3" s="27" t="s">
+      <c r="N3" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="O3" s="27" t="s">
+      <c r="O3" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="P3" s="27" t="s">
+      <c r="P3" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="Q3" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="R3" s="27" t="s">
+      <c r="R3" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="S3" s="27" t="s">
+      <c r="S3" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="T3" s="27" t="s">
+      <c r="T3" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="U3" s="27" t="s">
+      <c r="U3" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="V3" s="27" t="s">
+      <c r="V3" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="W3" s="27" t="s">
+      <c r="W3" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="X3" s="27" t="s">
+      <c r="X3" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="Y3" s="27" t="s">
+      <c r="Y3" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="Z3" s="27" t="s">
+      <c r="Z3" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="AA3" s="27" t="s">
+      <c r="AA3" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="AB3" s="27" t="s">
+      <c r="AB3" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="AC3" s="27" t="s">
+      <c r="AC3" s="38" t="s">
         <v>151</v>
       </c>
-      <c r="AD3" s="27" t="s">
+      <c r="AD3" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="AE3" s="27" t="s">
+      <c r="AE3" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="AF3" s="27" t="s">
+      <c r="AF3" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="AG3" s="27" t="s">
+      <c r="AG3" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="AH3" s="27" t="s">
+      <c r="AH3" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="AI3" s="27" t="s">
+      <c r="AI3" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="AJ3" s="27" t="s">
+      <c r="AJ3" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="AK3" s="27" t="s">
+      <c r="AK3" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="AL3" s="27" t="s">
+      <c r="AL3" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="AM3" s="27" t="s">
+      <c r="AM3" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="AN3" s="27" t="s">
+      <c r="AN3" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="AO3" s="27" t="s">
+      <c r="AO3" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="AP3" s="27" t="s">
+      <c r="AP3" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="AQ3" s="27" t="s">
+      <c r="AQ3" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="AR3" s="27" t="s">
+      <c r="AR3" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="AS3" s="27" t="s">
+      <c r="AS3" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="AT3" s="27" t="s">
+      <c r="AT3" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="AU3" s="27" t="s">
+      <c r="AU3" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="AV3" s="27" t="s">
+      <c r="AV3" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="AW3" s="27" t="s">
+      <c r="AW3" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="AX3" s="27" t="s">
+      <c r="AX3" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="AY3" s="27" t="s">
+      <c r="AY3" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="AZ3" s="27" t="s">
+      <c r="AZ3" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="BA3" s="27" t="s">
+      <c r="BA3" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="BB3" s="27" t="s">
+      <c r="BB3" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="BC3" s="27" t="s">
+      <c r="BC3" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="BD3" s="27" t="s">
+      <c r="BD3" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="BE3" s="27" t="s">
+      <c r="BE3" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BF3" s="27" t="s">
+      <c r="BF3" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="BG3" s="27" t="s">
+      <c r="BG3" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="BH3" s="27" t="s">
+      <c r="BH3" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="BI3" s="27" t="s">
+      <c r="BI3" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="BJ3" s="27" t="s">
+      <c r="BJ3" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="BK3" s="27" t="s">
+      <c r="BK3" s="38" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:63">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="K4" s="27" t="s">
+      <c r="K4" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="M4" s="27" t="s">
+      <c r="M4" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="N4" s="27" t="s">
+      <c r="N4" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="O4" s="27" t="s">
+      <c r="O4" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="P4" s="27" t="s">
+      <c r="P4" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="Q4" s="27" t="s">
+      <c r="Q4" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="R4" s="27" t="s">
+      <c r="R4" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="S4" s="27" t="s">
+      <c r="S4" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="T4" s="27" t="s">
+      <c r="T4" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="U4" s="27" t="s">
+      <c r="U4" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="V4" s="27" t="s">
+      <c r="V4" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="W4" s="27" t="s">
+      <c r="W4" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="X4" s="27" t="s">
+      <c r="X4" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="Y4" s="27" t="s">
+      <c r="Y4" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="Z4" s="27" t="s">
+      <c r="Z4" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="AA4" s="27" t="s">
+      <c r="AA4" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="AB4" s="27" t="s">
+      <c r="AB4" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="AC4" s="27" t="s">
+      <c r="AC4" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="AD4" s="27" t="s">
+      <c r="AD4" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="AE4" s="27" t="s">
+      <c r="AE4" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="AF4" s="27" t="s">
+      <c r="AF4" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="AG4" s="27" t="s">
+      <c r="AG4" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="AH4" s="27" t="s">
+      <c r="AH4" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="AI4" s="27" t="s">
+      <c r="AI4" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="AJ4" s="27" t="s">
+      <c r="AJ4" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="AK4" s="27" t="s">
+      <c r="AK4" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="AL4" s="27" t="s">
+      <c r="AL4" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="AM4" s="27" t="s">
+      <c r="AM4" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="AN4" s="27" t="s">
+      <c r="AN4" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="AO4" s="27" t="s">
+      <c r="AO4" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="AP4" s="27" t="s">
+      <c r="AP4" s="38" t="s">
         <v>223</v>
       </c>
-      <c r="AQ4" s="27" t="s">
+      <c r="AQ4" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="AR4" s="27" t="s">
+      <c r="AR4" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="AS4" s="27" t="s">
+      <c r="AS4" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="AT4" s="27" t="s">
+      <c r="AT4" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="AU4" s="27" t="s">
+      <c r="AU4" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="AV4" s="27" t="s">
+      <c r="AV4" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="AW4" s="27" t="s">
+      <c r="AW4" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="AX4" s="27" t="s">
+      <c r="AX4" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="AY4" s="27" t="s">
+      <c r="AY4" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="AZ4" s="27" t="s">
+      <c r="AZ4" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="BA4" s="27" t="s">
+      <c r="BA4" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="BB4" s="27" t="s">
+      <c r="BB4" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="BC4" s="27" t="s">
+      <c r="BC4" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="BD4" s="27" t="s">
+      <c r="BD4" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="BE4" s="27" t="s">
+      <c r="BE4" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="BF4" s="27" t="s">
+      <c r="BF4" s="38" t="s">
         <v>238</v>
       </c>
-      <c r="BG4" s="27" t="s">
+      <c r="BG4" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="BH4" s="27" t="s">
+      <c r="BH4" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="BI4" s="27" t="s">
+      <c r="BI4" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="BJ4" s="27" t="s">
+      <c r="BJ4" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="BK4" s="27" t="s">
+      <c r="BK4" s="38" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:63">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="38" t="s">
         <v>251</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="M5" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="N5" s="27" t="s">
+      <c r="N5" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="O5" s="27" t="s">
+      <c r="O5" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="P5" s="27" t="s">
+      <c r="P5" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="Q5" s="27" t="s">
+      <c r="Q5" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="R5" s="27" t="s">
+      <c r="R5" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="S5" s="27" t="s">
+      <c r="S5" s="38" t="s">
         <v>260</v>
       </c>
-      <c r="T5" s="27" t="s">
+      <c r="T5" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="U5" s="27" t="s">
+      <c r="U5" s="38" t="s">
         <v>262</v>
       </c>
-      <c r="V5" s="27" t="s">
+      <c r="V5" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="W5" s="27" t="s">
+      <c r="W5" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="X5" s="27" t="s">
+      <c r="X5" s="38" t="s">
         <v>264</v>
       </c>
-      <c r="Y5" s="27" t="s">
+      <c r="Y5" s="38" t="s">
         <v>265</v>
       </c>
-      <c r="Z5" s="27" t="s">
+      <c r="Z5" s="38" t="s">
         <v>266</v>
       </c>
-      <c r="AA5" s="27" t="s">
+      <c r="AA5" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="AB5" s="27" t="s">
+      <c r="AB5" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="AC5" s="27" t="s">
+      <c r="AC5" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="AD5" s="27" t="s">
+      <c r="AD5" s="38" t="s">
         <v>269</v>
       </c>
-      <c r="AE5" s="27" t="s">
+      <c r="AE5" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="AF5" s="27" t="s">
+      <c r="AF5" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="AG5" s="27" t="s">
+      <c r="AG5" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="AH5" s="27" t="s">
+      <c r="AH5" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="AI5" s="27" t="s">
+      <c r="AI5" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="AJ5" s="27" t="s">
+      <c r="AJ5" s="38" t="s">
         <v>275</v>
       </c>
-      <c r="AK5" s="27" t="s">
+      <c r="AK5" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="AL5" s="27" t="s">
+      <c r="AL5" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="AM5" s="27" t="s">
+      <c r="AM5" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="AN5" s="27" t="s">
+      <c r="AN5" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="AO5" s="27" t="s">
+      <c r="AO5" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="AP5" s="27" t="s">
+      <c r="AP5" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="AQ5" s="27" t="s">
+      <c r="AQ5" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="AR5" s="27" t="s">
+      <c r="AR5" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="AS5" s="27" t="s">
+      <c r="AS5" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="AT5" s="27" t="s">
+      <c r="AT5" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="AU5" s="27" t="s">
+      <c r="AU5" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="AV5" s="27" t="s">
+      <c r="AV5" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="AW5" s="27" t="s">
+      <c r="AW5" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="AX5" s="27" t="s">
+      <c r="AX5" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="AY5" s="27" t="s">
+      <c r="AY5" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="AZ5" s="27" t="s">
+      <c r="AZ5" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="BA5" s="27" t="s">
+      <c r="BA5" s="38" t="s">
         <v>290</v>
       </c>
-      <c r="BB5" s="27" t="s">
+      <c r="BB5" s="38" t="s">
         <v>291</v>
       </c>
-      <c r="BC5" s="27" t="s">
+      <c r="BC5" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="BD5" s="27" t="s">
+      <c r="BD5" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="BE5" s="27" t="s">
+      <c r="BE5" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="BF5" s="27" t="s">
+      <c r="BF5" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="BG5" s="27" t="s">
+      <c r="BG5" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="BH5" s="27" t="s">
+      <c r="BH5" s="38" t="s">
         <v>296</v>
       </c>
-      <c r="BI5" s="27" t="s">
+      <c r="BI5" s="38" t="s">
         <v>297</v>
       </c>
-      <c r="BJ5" s="27" t="s">
+      <c r="BJ5" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="BK5" s="27" t="s">
+      <c r="BK5" s="38" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:63">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="38" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:63">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="38" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:63">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="38" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:63">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="38" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:63">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="38" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:63">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="38" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:63">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="38" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:63">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="38" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:63">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="38" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:63">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="38" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:63">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="38" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="38" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="38" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="38" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="38" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="38" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="38" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="38" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="38" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="38" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="38" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="38" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="38" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="38" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="38" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="38" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="38" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="38" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="38" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="27" t="s">
+      <c r="A35" s="38" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="38" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="38" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="38" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="38" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="38" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="38" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="38" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="38" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="38" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="38" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="38" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="38" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="38" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="38" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="27" t="s">
+      <c r="A50" s="38" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="38" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="38" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="27" t="s">
+      <c r="A53" s="38" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="38" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="38" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="38" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="38" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="27" t="s">
+      <c r="A58" s="38" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="38" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="27" t="s">
+      <c r="A60" s="38" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="38" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="27" t="s">
+      <c r="A62" s="38" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="38" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="27" t="s">
+      <c r="A64" s="38" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="38" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="27" t="s">
+      <c r="A66" s="38" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="38" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="27" t="s">
+      <c r="A68" s="38" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="38" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="27" t="s">
+      <c r="A70" s="38" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="38" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="27" t="s">
+      <c r="A72" s="38" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="27" t="s">
+      <c r="A73" s="38" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="27" t="s">
+      <c r="A74" s="38" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="27" t="s">
+      <c r="A75" s="38" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="27" t="s">
+      <c r="A76" s="38" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="27" t="s">
+      <c r="A77" s="38" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="27" t="s">
+      <c r="A78" s="38" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="27" t="s">
+      <c r="A79" s="38" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="27" t="s">
+      <c r="A80" s="38" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="27" t="s">
+      <c r="A81" s="38" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="27" t="s">
+      <c r="A82" s="38" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="27" t="s">
+      <c r="A83" s="38" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="27" t="s">
+      <c r="A84" s="38" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="27" t="s">
+      <c r="A85" s="38" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="27" t="s">
+      <c r="A86" s="38" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="27" t="s">
+      <c r="A87" s="38" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="27" t="s">
+      <c r="A88" s="38" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="27" t="s">
+      <c r="A89" s="38" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="27" t="s">
+      <c r="A90" s="38" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="27" t="s">
+      <c r="A91" s="38" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="27" t="s">
+      <c r="A92" s="38" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="27" t="s">
+      <c r="A93" s="38" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="27" t="s">
+      <c r="A94" s="38" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="27" t="s">
+      <c r="A95" s="38" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="27" t="s">
+      <c r="A96" s="38" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="27" t="s">
+      <c r="A97" s="38" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="27" t="s">
+      <c r="A98" s="38" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="27" t="s">
+      <c r="A99" s="38" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="27" t="s">
+      <c r="A100" s="38" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="27" t="s">
+      <c r="A101" s="38" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="27" t="s">
+      <c r="A102" s="38" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="27" t="s">
+      <c r="A103" s="38" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="27" t="s">
+      <c r="A104" s="38" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="27" t="s">
+      <c r="A105" s="38" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="27" t="s">
+      <c r="A106" s="38" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="27" t="s">
+      <c r="A107" s="38" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="27" t="s">
+      <c r="A108" s="38" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="27" t="s">
+      <c r="A109" s="38" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="27" t="s">
+      <c r="A110" s="38" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="27" t="s">
+      <c r="A111" s="38" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="27" t="s">
+      <c r="A112" s="38" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="27" t="s">
+      <c r="A113" s="38" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="27" t="s">
+      <c r="A114" s="38" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="27" t="s">
+      <c r="A115" s="38" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="27" t="s">
+      <c r="A116" s="38" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="27" t="s">
+      <c r="A117" s="38" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="27" t="s">
+      <c r="A118" s="38" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="27" t="s">
+      <c r="A119" s="38" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="27" t="s">
+      <c r="A120" s="38" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="27" t="s">
+      <c r="A121" s="38" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="27" t="s">
+      <c r="A122" s="38" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="27" t="s">
+      <c r="A123" s="38" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="27" t="s">
+      <c r="A124" s="38" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="27" t="s">
+      <c r="A125" s="38" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="27" t="s">
+      <c r="A126" s="38" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="27" t="s">
+      <c r="A127" s="38" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="27" t="s">
+      <c r="A128" s="38" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="27" t="s">
+      <c r="A129" s="38" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="27" t="s">
+      <c r="A130" s="38" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="27" t="s">
+      <c r="A131" s="38" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="27" t="s">
+      <c r="A132" s="38" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="27" t="s">
+      <c r="A133" s="38" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="27" t="s">
+      <c r="A134" s="38" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="27" t="s">
+      <c r="A135" s="38" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="27" t="s">
+      <c r="A136" s="38" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="27" t="s">
+      <c r="A137" s="38" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="27" t="s">
+      <c r="A138" s="38" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="27" t="s">
+      <c r="A139" s="38" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="27" t="s">
+      <c r="A140" s="38" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="27" t="s">
+      <c r="A141" s="38" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="27" t="s">
+      <c r="A142" s="38" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="27" t="s">
+      <c r="A143" s="38" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="27" t="s">
+      <c r="A144" s="38" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="27" t="s">
+      <c r="A145" s="38" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="27" t="s">
+      <c r="A146" s="38" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="27" t="s">
+      <c r="A147" s="38" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="27" t="s">
+      <c r="A148" s="38" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="27" t="s">
+      <c r="A149" s="38" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="27" t="s">
+      <c r="A150" s="38" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="27" t="s">
+      <c r="A151" s="38" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="27" t="s">
+      <c r="A152" s="38" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="27" t="s">
+      <c r="A153" s="38" t="s">
         <v>447</v>
       </c>
     </row>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1387,13 +1387,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1419,6 +1419,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1426,12 +1432,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1445,26 +1445,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1498,6 +1478,91 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="dotted">
         <color auto="1"/>
       </left>
@@ -1535,43 +1600,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1589,6 +1617,51 @@
       </right>
       <top/>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1603,83 +1676,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -1699,83 +1699,83 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2100,37 +2100,37 @@
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="J1" s="25">
+      <c r="J1" s="33">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="3"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="17"/>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="7">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="5">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="3">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
     </row>
     <row r="3" spans="2:22">
       <c r="B3" s="1">
@@ -2138,125 +2138,125 @@
         <v>0</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="30">
         <f>IF($E$2="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="2:22">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="J7" s="11"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="J7" s="19"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="26">
+      <c r="C8" s="5"/>
+      <c r="D8" s="34">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="26">
+      <c r="E8" s="7"/>
+      <c r="F8" s="34">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="J8" s="12"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="J8" s="20"/>
       <c r="K8">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,59,FALSE))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="26">
+      <c r="C9" s="5"/>
+      <c r="D9" s="34">
         <f>D8</f>
         <v>0</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="26">
+      <c r="E9" s="7"/>
+      <c r="F9" s="34">
         <f>F8</f>
         <v>0</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="J9" s="13"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="J9" s="21"/>
     </row>
     <row r="10" spans="2:22" ht="13.5" customHeight="1"/>
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16">
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="8">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="9">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="8">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="8">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="10">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>0</v>
       </c>
@@ -2272,173 +2272,172 @@
       <c r="R11" s="1"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="19">
+      <c r="B12" s="11">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="18"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="10"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="20">
+      <c r="B13" s="12">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="18"/>
-      <c r="L13" s="24">
+      <c r="C13" s="12"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="10"/>
+      <c r="L13" s="31">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="24" t="s">
+      <c r="M13" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="24">
+      <c r="N13" s="31">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="24">
+      <c r="O13" s="31">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S13" s="24">
+      <c r="S13" s="31">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="T13" s="24" t="s">
+      <c r="T13" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="U13" s="24">
+      <c r="U13" s="31">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="24">
+      <c r="V13" s="31">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="18"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="10"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="27">
+      <c r="B15" s="13">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="32"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="32">
+        <v>0</v>
+      </c>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27"/>
+      <c r="H15" s="28"/>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="33">
+      <c r="B16" s="14">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="28">
-        <v>0</v>
-      </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="31">
+      <c r="C16" s="14"/>
+      <c r="D16" s="32">
+        <v>0</v>
+      </c>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="35">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="28"/>
     </row>
     <row r="17" spans="2:8">
-      <c r="B17" s="33">
+      <c r="B17" s="14">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="28">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31">
+      <c r="C17" s="14"/>
+      <c r="D17" s="32">
+        <v>0</v>
+      </c>
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="35">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="28"/>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="33">
+      <c r="B18" s="14">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="28">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="31">
+      <c r="C18" s="14"/>
+      <c r="D18" s="32">
+        <v>0</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="35">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="28"/>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="33">
+      <c r="B19" s="14">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="28">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="31">
+      <c r="C19" s="14"/>
+      <c r="D19" s="32">
+        <v>0</v>
+      </c>
+      <c r="E19" s="26"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="35">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="28"/>
     </row>
     <row r="20" spans="2:8">
-      <c r="B20" s="34">
+      <c r="B20" s="15">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35">
+      <c r="C20" s="15"/>
+      <c r="D20" s="36">
         <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="36">
         <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="36">
         <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="37">
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="37"/>
+      <c r="H20" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1759,6 +1759,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1772,7 +1773,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="J1" s="33">
+      <c r="J1" s="34">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>0</v>
       </c>
@@ -2119,7 +2119,7 @@
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="31" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="3">
@@ -2142,7 +2142,7 @@
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="31">
         <f>IF($E$2="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
@@ -2200,12 +2200,12 @@
         <v>0</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="34">
+      <c r="D8" s="35">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E8" s="7"/>
-      <c r="F8" s="34">
+      <c r="F8" s="35">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>0</v>
       </c>
@@ -2223,12 +2223,12 @@
         <v>0</v>
       </c>
       <c r="C9" s="5"/>
-      <c r="D9" s="34">
+      <c r="D9" s="35">
         <f>D8</f>
         <v>0</v>
       </c>
       <c r="E9" s="7"/>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>F8</f>
         <v>0</v>
       </c>
@@ -2294,33 +2294,33 @@
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="10"/>
-      <c r="L13" s="31">
+      <c r="L13" s="32">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="31" t="s">
+      <c r="M13" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="31">
+      <c r="N13" s="32">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="31">
+      <c r="O13" s="32">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S13" s="31">
+      <c r="S13" s="32">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="T13" s="31" t="s">
+      <c r="T13" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="U13" s="31">
+      <c r="U13" s="32">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="31">
+      <c r="V13" s="32">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
@@ -2340,12 +2340,13 @@
         <v>0</v>
       </c>
       <c r="C15" s="13"/>
-      <c r="D15" s="32">
+      <c r="D15" s="33">
         <v>0</v>
       </c>
       <c r="E15" s="26"/>
       <c r="F15" s="27"/>
-      <c r="H15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="2:22">
       <c r="B16" s="14">
@@ -2353,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="C16" s="14"/>
-      <c r="D16" s="32">
+      <c r="D16" s="33">
         <v>0</v>
       </c>
       <c r="E16" s="26"/>
       <c r="F16" s="27"/>
-      <c r="G16" s="35">
+      <c r="G16" s="28">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="28"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="14">
@@ -2370,16 +2371,16 @@
         <v>0</v>
       </c>
       <c r="C17" s="14"/>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <v>0</v>
       </c>
       <c r="E17" s="26"/>
       <c r="F17" s="27"/>
-      <c r="G17" s="35">
+      <c r="G17" s="28">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="28"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="14">
@@ -2387,16 +2388,16 @@
         <v>0</v>
       </c>
       <c r="C18" s="14"/>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <v>0</v>
       </c>
       <c r="E18" s="26"/>
       <c r="F18" s="27"/>
-      <c r="G18" s="35">
+      <c r="G18" s="28">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="28"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="14">
@@ -2404,16 +2405,16 @@
         <v>0</v>
       </c>
       <c r="C19" s="14"/>
-      <c r="D19" s="32">
+      <c r="D19" s="33">
         <v>0</v>
       </c>
       <c r="E19" s="26"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="35">
+      <c r="G19" s="28">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="28"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="15">
@@ -2437,7 +2438,7 @@
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="29"/>
+      <c r="H20" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1694,29 +1694,143 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1732,47 +1846,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2095,7 +2181,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="1">
+      <c r="B1" s="33">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>0</v>
       </c>
@@ -2115,14 +2201,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="5">
+      <c r="D2" s="35">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="36">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>0</v>
       </c>
@@ -2133,16 +2219,16 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="1">
+      <c r="B3" s="33">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="5">
+      <c r="D3" s="35">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="37">
         <f>IF($E$2="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
@@ -2154,7 +2240,7 @@
       <c r="O3" s="3"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="4">
+      <c r="J4" s="38">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>0</v>
       </c>
@@ -2165,7 +2251,7 @@
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="5">
+      <c r="B5" s="35">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>0</v>
       </c>
@@ -2173,7 +2259,7 @@
       <c r="D5" s="18"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="5">
+      <c r="B6" s="35">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>0</v>
       </c>
@@ -2195,17 +2281,17 @@
       <c r="J7" s="19"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="5">
+      <c r="B8" s="35">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="35">
+      <c r="D8" s="39">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E8" s="7"/>
-      <c r="F8" s="35">
+      <c r="F8" s="39">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>0</v>
       </c>
@@ -2218,17 +2304,17 @@
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="5">
+      <c r="B9" s="35">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C9" s="5"/>
-      <c r="D9" s="35">
+      <c r="D9" s="39">
         <f>D8</f>
         <v>0</v>
       </c>
       <c r="E9" s="7"/>
-      <c r="F9" s="35">
+      <c r="F9" s="39">
         <f>F8</f>
         <v>0</v>
       </c>
@@ -2240,39 +2326,39 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="22"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="8">
+      <c r="D11" s="40">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="41">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="40">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="40">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="33">
         <f>B18</f>
         <v>0</v>
       </c>
       <c r="K11" s="1"/>
-      <c r="Q11" s="1">
+      <c r="Q11" s="33">
         <f>B18</f>
         <v>0</v>
       </c>
       <c r="R11" s="1"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="11">
+      <c r="B12" s="43">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>0</v>
       </c>
@@ -2284,7 +2370,7 @@
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="12">
+      <c r="B13" s="44">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>0</v>
       </c>
@@ -2294,33 +2380,33 @@
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="10"/>
-      <c r="L13" s="32">
+      <c r="L13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="M13" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="32">
+      <c r="N13" s="45">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="32">
+      <c r="O13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S13" s="32">
+      <c r="S13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="T13" s="32" t="s">
+      <c r="T13" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="U13" s="32">
+      <c r="U13" s="45">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="32">
+      <c r="V13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
@@ -2335,110 +2421,110 @@
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="13">
+      <c r="B15" s="46">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C15" s="13"/>
-      <c r="D15" s="33">
+      <c r="D15" s="32">
         <v>0</v>
       </c>
       <c r="E15" s="26"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="28"/>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="14">
+      <c r="B16" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C16" s="14"/>
-      <c r="D16" s="33">
+      <c r="D16" s="32">
         <v>0</v>
       </c>
       <c r="E16" s="26"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="28">
+      <c r="F16" s="26"/>
+      <c r="G16" s="48">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="29"/>
+      <c r="H16" s="28"/>
     </row>
     <row r="17" spans="2:8">
-      <c r="B17" s="14">
+      <c r="B17" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C17" s="14"/>
-      <c r="D17" s="33">
+      <c r="D17" s="32">
         <v>0</v>
       </c>
       <c r="E17" s="26"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28">
+      <c r="F17" s="26"/>
+      <c r="G17" s="48">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="29"/>
+      <c r="H17" s="28"/>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="14">
+      <c r="B18" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C18" s="14"/>
-      <c r="D18" s="33">
+      <c r="D18" s="32">
         <v>0</v>
       </c>
       <c r="E18" s="26"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="28">
+      <c r="F18" s="26"/>
+      <c r="G18" s="48">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="29"/>
+      <c r="H18" s="28"/>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="14">
+      <c r="B19" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C19" s="14"/>
-      <c r="D19" s="33">
+      <c r="D19" s="32">
         <v>0</v>
       </c>
       <c r="E19" s="26"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="28">
+      <c r="F19" s="26"/>
+      <c r="G19" s="48">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="29"/>
+      <c r="H19" s="28"/>
     </row>
     <row r="20" spans="2:8">
-      <c r="B20" s="15">
+      <c r="B20" s="49">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C20" s="15"/>
-      <c r="D20" s="36">
+      <c r="D20" s="50">
         <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="50">
         <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="50">
         <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="51">
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="30"/>
+      <c r="H20" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -2485,1697 +2571,1697 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:63">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="38" t="s">
+      <c r="L1" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="M1" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="N1" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="38" t="s">
+      <c r="P1" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="38" t="s">
+      <c r="R1" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="38" t="s">
+      <c r="S1" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="T1" s="38" t="s">
+      <c r="T1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="U1" s="38" t="s">
+      <c r="U1" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="38" t="s">
+      <c r="V1" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="38" t="s">
+      <c r="W1" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="38" t="s">
+      <c r="X1" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="38" t="s">
+      <c r="Y1" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="38" t="s">
+      <c r="Z1" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="38" t="s">
+      <c r="AA1" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="38" t="s">
+      <c r="AB1" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="38" t="s">
+      <c r="AC1" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" s="38" t="s">
+      <c r="AD1" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" s="38" t="s">
+      <c r="AE1" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="38" t="s">
+      <c r="AF1" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="38" t="s">
+      <c r="AG1" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="AH1" s="38" t="s">
+      <c r="AH1" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" s="38" t="s">
+      <c r="AI1" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="38" t="s">
+      <c r="AJ1" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" s="38" t="s">
+      <c r="AK1" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="AL1" s="38" t="s">
+      <c r="AL1" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" s="38" t="s">
+      <c r="AM1" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="AN1" s="38" t="s">
+      <c r="AN1" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="AO1" s="38" t="s">
+      <c r="AO1" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="AP1" s="38" t="s">
+      <c r="AP1" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="AQ1" s="38" t="s">
+      <c r="AQ1" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="AR1" s="38" t="s">
+      <c r="AR1" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="AS1" s="38" t="s">
+      <c r="AS1" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="AT1" s="38" t="s">
+      <c r="AT1" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="AU1" s="38" t="s">
+      <c r="AU1" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="AV1" s="38" t="s">
+      <c r="AV1" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="AW1" s="38" t="s">
+      <c r="AW1" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="AX1" s="38" t="s">
+      <c r="AX1" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="AY1" s="38" t="s">
+      <c r="AY1" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="AZ1" s="38" t="s">
+      <c r="AZ1" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" s="38" t="s">
+      <c r="BA1" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="BB1" s="38" t="s">
+      <c r="BB1" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="BC1" s="38" t="s">
+      <c r="BC1" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="BD1" s="38" t="s">
+      <c r="BD1" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="BE1" s="38" t="s">
+      <c r="BE1" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="BF1" s="38" t="s">
+      <c r="BF1" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="BG1" s="38" t="s">
+      <c r="BG1" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="BH1" s="38" t="s">
+      <c r="BH1" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="BI1" s="38" t="s">
+      <c r="BI1" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="BJ1" s="38" t="s">
+      <c r="BJ1" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="BK1" s="38" t="s">
+      <c r="BK1" s="52" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:63">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="J2" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="L2" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="38" t="s">
+      <c r="N2" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="O2" s="38" t="s">
+      <c r="O2" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="38" t="s">
+      <c r="P2" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="Q2" s="38" t="s">
+      <c r="Q2" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="38" t="s">
+      <c r="R2" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="38" t="s">
+      <c r="S2" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="38" t="s">
+      <c r="T2" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="38" t="s">
+      <c r="U2" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="V2" s="38" t="s">
+      <c r="V2" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="W2" s="38" t="s">
+      <c r="W2" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="38" t="s">
+      <c r="X2" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="38" t="s">
+      <c r="Y2" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="38" t="s">
+      <c r="Z2" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="38" t="s">
+      <c r="AA2" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="38" t="s">
+      <c r="AB2" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="AC2" s="38" t="s">
+      <c r="AC2" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="AD2" s="38" t="s">
+      <c r="AD2" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="AE2" s="38" t="s">
+      <c r="AE2" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="38" t="s">
+      <c r="AF2" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="AG2" s="38" t="s">
+      <c r="AG2" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="AH2" s="38" t="s">
+      <c r="AH2" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="AI2" s="38" t="s">
+      <c r="AI2" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AJ2" s="38" t="s">
+      <c r="AJ2" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" s="38" t="s">
+      <c r="AK2" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="AL2" s="38" t="s">
+      <c r="AL2" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="AM2" s="38" t="s">
+      <c r="AM2" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="AN2" s="38" t="s">
+      <c r="AN2" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="AO2" s="38" t="s">
+      <c r="AO2" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="AP2" s="38" t="s">
+      <c r="AP2" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="AQ2" s="38" t="s">
+      <c r="AQ2" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="AR2" s="38" t="s">
+      <c r="AR2" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="AS2" s="38" t="s">
+      <c r="AS2" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="AT2" s="38" t="s">
+      <c r="AT2" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="AU2" s="38" t="s">
+      <c r="AU2" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="AV2" s="38" t="s">
+      <c r="AV2" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="AW2" s="38" t="s">
+      <c r="AW2" s="52" t="s">
         <v>110</v>
       </c>
-      <c r="AX2" s="38" t="s">
+      <c r="AX2" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" s="38" t="s">
+      <c r="AY2" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="AZ2" s="38" t="s">
+      <c r="AZ2" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="BA2" s="38" t="s">
+      <c r="BA2" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="BB2" s="38" t="s">
+      <c r="BB2" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="BC2" s="38" t="s">
+      <c r="BC2" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="BD2" s="38" t="s">
+      <c r="BD2" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="BE2" s="38" t="s">
+      <c r="BE2" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="BF2" s="38" t="s">
+      <c r="BF2" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="BG2" s="38" t="s">
+      <c r="BG2" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="BH2" s="38" t="s">
+      <c r="BH2" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="BI2" s="38" t="s">
+      <c r="BI2" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="BJ2" s="38" t="s">
+      <c r="BJ2" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="BK2" s="38" t="s">
+      <c r="BK2" s="52" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:63">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="52" t="s">
         <v>132</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="52" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="52" t="s">
         <v>133</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="52" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="L3" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="N3" s="38" t="s">
+      <c r="N3" s="52" t="s">
         <v>137</v>
       </c>
-      <c r="O3" s="38" t="s">
+      <c r="O3" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="P3" s="38" t="s">
+      <c r="P3" s="52" t="s">
         <v>139</v>
       </c>
-      <c r="Q3" s="38" t="s">
+      <c r="Q3" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="R3" s="38" t="s">
+      <c r="R3" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="S3" s="38" t="s">
+      <c r="S3" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="T3" s="38" t="s">
+      <c r="T3" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="U3" s="38" t="s">
+      <c r="U3" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="V3" s="38" t="s">
+      <c r="V3" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="W3" s="38" t="s">
+      <c r="W3" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="X3" s="38" t="s">
+      <c r="X3" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="Y3" s="38" t="s">
+      <c r="Y3" s="52" t="s">
         <v>147</v>
       </c>
-      <c r="Z3" s="38" t="s">
+      <c r="Z3" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="AA3" s="38" t="s">
+      <c r="AA3" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="AB3" s="38" t="s">
+      <c r="AB3" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="AC3" s="38" t="s">
+      <c r="AC3" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="AD3" s="38" t="s">
+      <c r="AD3" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="AE3" s="38" t="s">
+      <c r="AE3" s="52" t="s">
         <v>153</v>
       </c>
-      <c r="AF3" s="38" t="s">
+      <c r="AF3" s="52" t="s">
         <v>154</v>
       </c>
-      <c r="AG3" s="38" t="s">
+      <c r="AG3" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="AH3" s="38" t="s">
+      <c r="AH3" s="52" t="s">
         <v>156</v>
       </c>
-      <c r="AI3" s="38" t="s">
+      <c r="AI3" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="AJ3" s="38" t="s">
+      <c r="AJ3" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="AK3" s="38" t="s">
+      <c r="AK3" s="52" t="s">
         <v>159</v>
       </c>
-      <c r="AL3" s="38" t="s">
+      <c r="AL3" s="52" t="s">
         <v>160</v>
       </c>
-      <c r="AM3" s="38" t="s">
+      <c r="AM3" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="AN3" s="38" t="s">
+      <c r="AN3" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="AO3" s="38" t="s">
+      <c r="AO3" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="AP3" s="38" t="s">
+      <c r="AP3" s="52" t="s">
         <v>162</v>
       </c>
-      <c r="AQ3" s="38" t="s">
+      <c r="AQ3" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="AR3" s="38" t="s">
+      <c r="AR3" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="AS3" s="38" t="s">
+      <c r="AS3" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AT3" s="38" t="s">
+      <c r="AT3" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="AU3" s="38" t="s">
+      <c r="AU3" s="52" t="s">
         <v>166</v>
       </c>
-      <c r="AV3" s="38" t="s">
+      <c r="AV3" s="52" t="s">
         <v>167</v>
       </c>
-      <c r="AW3" s="38" t="s">
+      <c r="AW3" s="52" t="s">
         <v>168</v>
       </c>
-      <c r="AX3" s="38" t="s">
+      <c r="AX3" s="52" t="s">
         <v>169</v>
       </c>
-      <c r="AY3" s="38" t="s">
+      <c r="AY3" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="AZ3" s="38" t="s">
+      <c r="AZ3" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="BA3" s="38" t="s">
+      <c r="BA3" s="52" t="s">
         <v>172</v>
       </c>
-      <c r="BB3" s="38" t="s">
+      <c r="BB3" s="52" t="s">
         <v>173</v>
       </c>
-      <c r="BC3" s="38" t="s">
+      <c r="BC3" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="BD3" s="38" t="s">
+      <c r="BD3" s="52" t="s">
         <v>175</v>
       </c>
-      <c r="BE3" s="38" t="s">
+      <c r="BE3" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="BF3" s="38" t="s">
+      <c r="BF3" s="52" t="s">
         <v>177</v>
       </c>
-      <c r="BG3" s="38" t="s">
+      <c r="BG3" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="BH3" s="38" t="s">
+      <c r="BH3" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="BI3" s="38" t="s">
+      <c r="BI3" s="52" t="s">
         <v>180</v>
       </c>
-      <c r="BJ3" s="38" t="s">
+      <c r="BJ3" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="BK3" s="38" t="s">
+      <c r="BK3" s="52" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:63">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="52" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="52" t="s">
         <v>188</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="52" t="s">
         <v>191</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="52" t="s">
         <v>193</v>
       </c>
-      <c r="L4" s="38" t="s">
+      <c r="L4" s="52" t="s">
         <v>194</v>
       </c>
-      <c r="M4" s="38" t="s">
+      <c r="M4" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="N4" s="38" t="s">
+      <c r="N4" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="O4" s="38" t="s">
+      <c r="O4" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="P4" s="38" t="s">
+      <c r="P4" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="Q4" s="38" t="s">
+      <c r="Q4" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="R4" s="38" t="s">
+      <c r="R4" s="52" t="s">
         <v>200</v>
       </c>
-      <c r="S4" s="38" t="s">
+      <c r="S4" s="52" t="s">
         <v>201</v>
       </c>
-      <c r="T4" s="38" t="s">
+      <c r="T4" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="U4" s="38" t="s">
+      <c r="U4" s="52" t="s">
         <v>203</v>
       </c>
-      <c r="V4" s="38" t="s">
+      <c r="V4" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="W4" s="38" t="s">
+      <c r="W4" s="52" t="s">
         <v>204</v>
       </c>
-      <c r="X4" s="38" t="s">
+      <c r="X4" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="Y4" s="38" t="s">
+      <c r="Y4" s="52" t="s">
         <v>206</v>
       </c>
-      <c r="Z4" s="38" t="s">
+      <c r="Z4" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="AA4" s="38" t="s">
+      <c r="AA4" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="AB4" s="38" t="s">
+      <c r="AB4" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="AC4" s="38" t="s">
+      <c r="AC4" s="52" t="s">
         <v>210</v>
       </c>
-      <c r="AD4" s="38" t="s">
+      <c r="AD4" s="52" t="s">
         <v>211</v>
       </c>
-      <c r="AE4" s="38" t="s">
+      <c r="AE4" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="AF4" s="38" t="s">
+      <c r="AF4" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="AG4" s="38" t="s">
+      <c r="AG4" s="52" t="s">
         <v>214</v>
       </c>
-      <c r="AH4" s="38" t="s">
+      <c r="AH4" s="52" t="s">
         <v>215</v>
       </c>
-      <c r="AI4" s="38" t="s">
+      <c r="AI4" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="AJ4" s="38" t="s">
+      <c r="AJ4" s="52" t="s">
         <v>217</v>
       </c>
-      <c r="AK4" s="38" t="s">
+      <c r="AK4" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="AL4" s="38" t="s">
+      <c r="AL4" s="52" t="s">
         <v>219</v>
       </c>
-      <c r="AM4" s="38" t="s">
+      <c r="AM4" s="52" t="s">
         <v>220</v>
       </c>
-      <c r="AN4" s="38" t="s">
+      <c r="AN4" s="52" t="s">
         <v>221</v>
       </c>
-      <c r="AO4" s="38" t="s">
+      <c r="AO4" s="52" t="s">
         <v>222</v>
       </c>
-      <c r="AP4" s="38" t="s">
+      <c r="AP4" s="52" t="s">
         <v>223</v>
       </c>
-      <c r="AQ4" s="38" t="s">
+      <c r="AQ4" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="AR4" s="38" t="s">
+      <c r="AR4" s="52" t="s">
         <v>224</v>
       </c>
-      <c r="AS4" s="38" t="s">
+      <c r="AS4" s="52" t="s">
         <v>225</v>
       </c>
-      <c r="AT4" s="38" t="s">
+      <c r="AT4" s="52" t="s">
         <v>226</v>
       </c>
-      <c r="AU4" s="38" t="s">
+      <c r="AU4" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="AV4" s="38" t="s">
+      <c r="AV4" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="AW4" s="38" t="s">
+      <c r="AW4" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="AX4" s="38" t="s">
+      <c r="AX4" s="52" t="s">
         <v>230</v>
       </c>
-      <c r="AY4" s="38" t="s">
+      <c r="AY4" s="52" t="s">
         <v>231</v>
       </c>
-      <c r="AZ4" s="38" t="s">
+      <c r="AZ4" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="BA4" s="38" t="s">
+      <c r="BA4" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="BB4" s="38" t="s">
+      <c r="BB4" s="52" t="s">
         <v>234</v>
       </c>
-      <c r="BC4" s="38" t="s">
+      <c r="BC4" s="52" t="s">
         <v>235</v>
       </c>
-      <c r="BD4" s="38" t="s">
+      <c r="BD4" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="BE4" s="38" t="s">
+      <c r="BE4" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="BF4" s="38" t="s">
+      <c r="BF4" s="52" t="s">
         <v>238</v>
       </c>
-      <c r="BG4" s="38" t="s">
+      <c r="BG4" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="BH4" s="38" t="s">
+      <c r="BH4" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="BI4" s="38" t="s">
+      <c r="BI4" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="BJ4" s="38" t="s">
+      <c r="BJ4" s="52" t="s">
         <v>241</v>
       </c>
-      <c r="BK4" s="38" t="s">
+      <c r="BK4" s="52" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:63">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="52" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="52" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="52" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="52" t="s">
         <v>247</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="52" t="s">
         <v>250</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="52" t="s">
         <v>251</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="52" t="s">
         <v>252</v>
       </c>
-      <c r="L5" s="38" t="s">
+      <c r="L5" s="52" t="s">
         <v>253</v>
       </c>
-      <c r="M5" s="38" t="s">
+      <c r="M5" s="52" t="s">
         <v>254</v>
       </c>
-      <c r="N5" s="38" t="s">
+      <c r="N5" s="52" t="s">
         <v>255</v>
       </c>
-      <c r="O5" s="38" t="s">
+      <c r="O5" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="P5" s="38" t="s">
+      <c r="P5" s="52" t="s">
         <v>257</v>
       </c>
-      <c r="Q5" s="38" t="s">
+      <c r="Q5" s="52" t="s">
         <v>258</v>
       </c>
-      <c r="R5" s="38" t="s">
+      <c r="R5" s="52" t="s">
         <v>259</v>
       </c>
-      <c r="S5" s="38" t="s">
+      <c r="S5" s="52" t="s">
         <v>260</v>
       </c>
-      <c r="T5" s="38" t="s">
+      <c r="T5" s="52" t="s">
         <v>261</v>
       </c>
-      <c r="U5" s="38" t="s">
+      <c r="U5" s="52" t="s">
         <v>262</v>
       </c>
-      <c r="V5" s="38" t="s">
+      <c r="V5" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="W5" s="38" t="s">
+      <c r="W5" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="X5" s="38" t="s">
+      <c r="X5" s="52" t="s">
         <v>264</v>
       </c>
-      <c r="Y5" s="38" t="s">
+      <c r="Y5" s="52" t="s">
         <v>265</v>
       </c>
-      <c r="Z5" s="38" t="s">
+      <c r="Z5" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="AA5" s="38" t="s">
+      <c r="AA5" s="52" t="s">
         <v>267</v>
       </c>
-      <c r="AB5" s="38" t="s">
+      <c r="AB5" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="AC5" s="38" t="s">
+      <c r="AC5" s="52" t="s">
         <v>268</v>
       </c>
-      <c r="AD5" s="38" t="s">
+      <c r="AD5" s="52" t="s">
         <v>269</v>
       </c>
-      <c r="AE5" s="38" t="s">
+      <c r="AE5" s="52" t="s">
         <v>270</v>
       </c>
-      <c r="AF5" s="38" t="s">
+      <c r="AF5" s="52" t="s">
         <v>271</v>
       </c>
-      <c r="AG5" s="38" t="s">
+      <c r="AG5" s="52" t="s">
         <v>272</v>
       </c>
-      <c r="AH5" s="38" t="s">
+      <c r="AH5" s="52" t="s">
         <v>273</v>
       </c>
-      <c r="AI5" s="38" t="s">
+      <c r="AI5" s="52" t="s">
         <v>274</v>
       </c>
-      <c r="AJ5" s="38" t="s">
+      <c r="AJ5" s="52" t="s">
         <v>275</v>
       </c>
-      <c r="AK5" s="38" t="s">
+      <c r="AK5" s="52" t="s">
         <v>276</v>
       </c>
-      <c r="AL5" s="38" t="s">
+      <c r="AL5" s="52" t="s">
         <v>277</v>
       </c>
-      <c r="AM5" s="38" t="s">
+      <c r="AM5" s="52" t="s">
         <v>278</v>
       </c>
-      <c r="AN5" s="38" t="s">
+      <c r="AN5" s="52" t="s">
         <v>279</v>
       </c>
-      <c r="AO5" s="38" t="s">
+      <c r="AO5" s="52" t="s">
         <v>280</v>
       </c>
-      <c r="AP5" s="38" t="s">
+      <c r="AP5" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="AQ5" s="38" t="s">
+      <c r="AQ5" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="AR5" s="38" t="s">
+      <c r="AR5" s="52" t="s">
         <v>282</v>
       </c>
-      <c r="AS5" s="38" t="s">
+      <c r="AS5" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="AT5" s="38" t="s">
+      <c r="AT5" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="AU5" s="38" t="s">
+      <c r="AU5" s="52" t="s">
         <v>285</v>
       </c>
-      <c r="AV5" s="38" t="s">
+      <c r="AV5" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="AW5" s="38" t="s">
+      <c r="AW5" s="52" t="s">
         <v>286</v>
       </c>
-      <c r="AX5" s="38" t="s">
+      <c r="AX5" s="52" t="s">
         <v>287</v>
       </c>
-      <c r="AY5" s="38" t="s">
+      <c r="AY5" s="52" t="s">
         <v>288</v>
       </c>
-      <c r="AZ5" s="38" t="s">
+      <c r="AZ5" s="52" t="s">
         <v>289</v>
       </c>
-      <c r="BA5" s="38" t="s">
+      <c r="BA5" s="52" t="s">
         <v>290</v>
       </c>
-      <c r="BB5" s="38" t="s">
+      <c r="BB5" s="52" t="s">
         <v>291</v>
       </c>
-      <c r="BC5" s="38" t="s">
+      <c r="BC5" s="52" t="s">
         <v>292</v>
       </c>
-      <c r="BD5" s="38" t="s">
+      <c r="BD5" s="52" t="s">
         <v>293</v>
       </c>
-      <c r="BE5" s="38" t="s">
+      <c r="BE5" s="52" t="s">
         <v>294</v>
       </c>
-      <c r="BF5" s="38" t="s">
+      <c r="BF5" s="52" t="s">
         <v>295</v>
       </c>
-      <c r="BG5" s="38" t="s">
+      <c r="BG5" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="BH5" s="38" t="s">
+      <c r="BH5" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="BI5" s="38" t="s">
+      <c r="BI5" s="52" t="s">
         <v>297</v>
       </c>
-      <c r="BJ5" s="38" t="s">
+      <c r="BJ5" s="52" t="s">
         <v>298</v>
       </c>
-      <c r="BK5" s="38" t="s">
+      <c r="BK5" s="52" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:63">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="52" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:63">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="52" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:63">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="52" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:63">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="52" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:63">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="52" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:63">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="52" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:63">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="52" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:63">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="52" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:63">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="52" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:63">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="52" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:63">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="52" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="52" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="52" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="52" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="52" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="52" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="52" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="52" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="52" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="52" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="52" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="38" t="s">
+      <c r="A27" s="52" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="38" t="s">
+      <c r="A28" s="52" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="52" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="52" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="52" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="52" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="52" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="38" t="s">
+      <c r="A34" s="52" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="38" t="s">
+      <c r="A35" s="52" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="52" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="38" t="s">
+      <c r="A37" s="52" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="38" t="s">
+      <c r="A38" s="52" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="38" t="s">
+      <c r="A39" s="52" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="38" t="s">
+      <c r="A40" s="52" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="38" t="s">
+      <c r="A41" s="52" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="38" t="s">
+      <c r="A42" s="52" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="38" t="s">
+      <c r="A43" s="52" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="38" t="s">
+      <c r="A44" s="52" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="38" t="s">
+      <c r="A45" s="52" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="52" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="38" t="s">
+      <c r="A47" s="52" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="52" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="38" t="s">
+      <c r="A49" s="52" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="38" t="s">
+      <c r="A50" s="52" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="38" t="s">
+      <c r="A51" s="52" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="52" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="38" t="s">
+      <c r="A53" s="52" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="52" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="38" t="s">
+      <c r="A55" s="52" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="38" t="s">
+      <c r="A56" s="52" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="38" t="s">
+      <c r="A57" s="52" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="38" t="s">
+      <c r="A58" s="52" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="38" t="s">
+      <c r="A59" s="52" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="38" t="s">
+      <c r="A60" s="52" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="38" t="s">
+      <c r="A61" s="52" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="38" t="s">
+      <c r="A62" s="52" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="38" t="s">
+      <c r="A63" s="52" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="38" t="s">
+      <c r="A64" s="52" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="38" t="s">
+      <c r="A65" s="52" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="38" t="s">
+      <c r="A66" s="52" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="38" t="s">
+      <c r="A67" s="52" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="38" t="s">
+      <c r="A68" s="52" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="38" t="s">
+      <c r="A69" s="52" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="38" t="s">
+      <c r="A70" s="52" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="38" t="s">
+      <c r="A71" s="52" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="38" t="s">
+      <c r="A72" s="52" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="38" t="s">
+      <c r="A73" s="52" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="38" t="s">
+      <c r="A74" s="52" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="38" t="s">
+      <c r="A75" s="52" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="38" t="s">
+      <c r="A76" s="52" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="38" t="s">
+      <c r="A77" s="52" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="38" t="s">
+      <c r="A78" s="52" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="38" t="s">
+      <c r="A79" s="52" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="38" t="s">
+      <c r="A80" s="52" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="38" t="s">
+      <c r="A81" s="52" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="38" t="s">
+      <c r="A82" s="52" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="38" t="s">
+      <c r="A83" s="52" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="38" t="s">
+      <c r="A84" s="52" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="38" t="s">
+      <c r="A85" s="52" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="38" t="s">
+      <c r="A86" s="52" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="38" t="s">
+      <c r="A87" s="52" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="38" t="s">
+      <c r="A88" s="52" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="38" t="s">
+      <c r="A89" s="52" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="38" t="s">
+      <c r="A90" s="52" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="38" t="s">
+      <c r="A91" s="52" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="38" t="s">
+      <c r="A92" s="52" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="38" t="s">
+      <c r="A93" s="52" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="38" t="s">
+      <c r="A94" s="52" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="38" t="s">
+      <c r="A95" s="52" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="38" t="s">
+      <c r="A96" s="52" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="38" t="s">
+      <c r="A97" s="52" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="38" t="s">
+      <c r="A98" s="52" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="38" t="s">
+      <c r="A99" s="52" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="38" t="s">
+      <c r="A100" s="52" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="38" t="s">
+      <c r="A101" s="52" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="38" t="s">
+      <c r="A102" s="52" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="38" t="s">
+      <c r="A103" s="52" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="38" t="s">
+      <c r="A104" s="52" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="38" t="s">
+      <c r="A105" s="52" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="38" t="s">
+      <c r="A106" s="52" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="38" t="s">
+      <c r="A107" s="52" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="38" t="s">
+      <c r="A108" s="52" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="38" t="s">
+      <c r="A109" s="52" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="38" t="s">
+      <c r="A110" s="52" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="38" t="s">
+      <c r="A111" s="52" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="38" t="s">
+      <c r="A112" s="52" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="38" t="s">
+      <c r="A113" s="52" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="38" t="s">
+      <c r="A114" s="52" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="38" t="s">
+      <c r="A115" s="52" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="38" t="s">
+      <c r="A116" s="52" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="38" t="s">
+      <c r="A117" s="52" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="38" t="s">
+      <c r="A118" s="52" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="38" t="s">
+      <c r="A119" s="52" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="38" t="s">
+      <c r="A120" s="52" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="38" t="s">
+      <c r="A121" s="52" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="38" t="s">
+      <c r="A122" s="52" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="38" t="s">
+      <c r="A123" s="52" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="38" t="s">
+      <c r="A124" s="52" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="38" t="s">
+      <c r="A125" s="52" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="38" t="s">
+      <c r="A126" s="52" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="38" t="s">
+      <c r="A127" s="52" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="38" t="s">
+      <c r="A128" s="52" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="38" t="s">
+      <c r="A129" s="52" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="38" t="s">
+      <c r="A130" s="52" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="38" t="s">
+      <c r="A131" s="52" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="38" t="s">
+      <c r="A132" s="52" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="38" t="s">
+      <c r="A133" s="52" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="38" t="s">
+      <c r="A134" s="52" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="38" t="s">
+      <c r="A135" s="52" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="38" t="s">
+      <c r="A136" s="52" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="38" t="s">
+      <c r="A137" s="52" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="38" t="s">
+      <c r="A138" s="52" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="38" t="s">
+      <c r="A139" s="52" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="38" t="s">
+      <c r="A140" s="52" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="38" t="s">
+      <c r="A141" s="52" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="38" t="s">
+      <c r="A142" s="52" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="38" t="s">
+      <c r="A143" s="52" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="38" t="s">
+      <c r="A144" s="52" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="38" t="s">
+      <c r="A145" s="52" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="38" t="s">
+      <c r="A146" s="52" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="38" t="s">
+      <c r="A147" s="52" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="38" t="s">
+      <c r="A148" s="52" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="38" t="s">
+      <c r="A149" s="52" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="38" t="s">
+      <c r="A150" s="52" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="38" t="s">
+      <c r="A151" s="52" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="38" t="s">
+      <c r="A152" s="52" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="38" t="s">
+      <c r="A153" s="52" t="s">
         <v>447</v>
       </c>
     </row>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1379,6 +1379,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
@@ -1388,12 +1394,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1694,174 +1694,177 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2156,381 +2159,379 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:ALL20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" customWidth="1"/>
-    <col min="3" max="3" width="56.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" customWidth="1"/>
-    <col min="17" max="17" width="4.7109375" customWidth="1"/>
-    <col min="18" max="18" width="19.85546875" customWidth="1"/>
-    <col min="19" max="19" width="11.5703125" customWidth="1"/>
-    <col min="20" max="22" width="15.7109375" customWidth="1"/>
-    <col min="23" max="23" width="4.7109375" customWidth="1"/>
-    <col min="24" max="24" width="37.42578125" customWidth="1"/>
-    <col min="25" max="25" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="56.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="1" customWidth="1"/>
+    <col min="5" max="6" width="18.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="9" max="10" width="4.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="15" width="15.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19.85546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5703125" style="1" customWidth="1"/>
+    <col min="20" max="22" width="15.7109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="4.7109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="37.42578125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="11.5703125" style="1" customWidth="1"/>
+    <col min="26" max="1000" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="33">
+      <c r="B1" s="34">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="J1" s="34">
+      <c r="C1" s="2"/>
+      <c r="J1" s="35">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="18"/>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="35">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="36">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="36">
+      <c r="J2" s="37">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="33">
+      <c r="B3" s="34">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="35">
+      <c r="C3" s="2"/>
+      <c r="D3" s="36">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="38">
         <f>IF($E$2="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="38">
+      <c r="J4" s="39">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="35">
+      <c r="B5" s="36">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="18"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="19"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="35">
+      <c r="B6" s="36">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="2:22">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="J7" s="19"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="J7" s="20"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="35">
+      <c r="B8" s="36">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="39">
+      <c r="C8" s="6"/>
+      <c r="D8" s="40">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="39">
+      <c r="E8" s="8"/>
+      <c r="F8" s="40">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="J8" s="20"/>
-      <c r="K8">
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="1">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,59,FALSE))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="39">
+      <c r="C9" s="6"/>
+      <c r="D9" s="40">
         <f>D8</f>
         <v>0</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="39">
+      <c r="E9" s="8"/>
+      <c r="F9" s="40">
         <f>F8</f>
         <v>0</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="J9" s="21"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="J9" s="22"/>
     </row>
     <row r="10" spans="2:22" ht="13.5" customHeight="1"/>
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="40">
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="41">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="41">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="41">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="43">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="34">
         <f>B18</f>
         <v>0</v>
       </c>
-      <c r="K11" s="1"/>
-      <c r="Q11" s="33">
+      <c r="K11" s="2"/>
+      <c r="Q11" s="34">
         <f>B18</f>
         <v>0</v>
       </c>
-      <c r="R11" s="1"/>
+      <c r="R11" s="2"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="43">
+      <c r="B12" s="44">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="10"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="11"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="44">
+      <c r="B13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="10"/>
-      <c r="L13" s="45">
+      <c r="C13" s="13"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="11"/>
+      <c r="L13" s="46">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="31" t="s">
+      <c r="M13" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="45">
+      <c r="N13" s="46">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="45">
+      <c r="O13" s="46">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S13" s="45">
+      <c r="S13" s="46">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="T13" s="31" t="s">
+      <c r="T13" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="U13" s="45">
+      <c r="U13" s="46">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="45">
+      <c r="V13" s="46">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="24"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="10"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="11"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="46">
+      <c r="B15" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="32">
-        <v>0</v>
-      </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="28"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="33">
+        <v>0</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="47">
+      <c r="B16" s="48">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="32">
-        <v>0</v>
-      </c>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="48">
+      <c r="C16" s="15"/>
+      <c r="D16" s="33">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="49">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="28"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="2:8">
-      <c r="B17" s="47">
+      <c r="B17" s="48">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="32">
-        <v>0</v>
-      </c>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="48">
+      <c r="C17" s="15"/>
+      <c r="D17" s="33">
+        <v>0</v>
+      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="49">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="28"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="47">
+      <c r="B18" s="48">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="32">
-        <v>0</v>
-      </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="48">
+      <c r="C18" s="15"/>
+      <c r="D18" s="33">
+        <v>0</v>
+      </c>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="49">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="28"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="47">
+      <c r="B19" s="48">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="32">
-        <v>0</v>
-      </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="48">
+      <c r="C19" s="15"/>
+      <c r="D19" s="33">
+        <v>0</v>
+      </c>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="49">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="28"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" spans="2:8">
-      <c r="B20" s="49">
+      <c r="B20" s="50">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="50">
+      <c r="C20" s="16"/>
+      <c r="D20" s="51">
         <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="51">
         <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="51">
         <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="52">
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="29"/>
+      <c r="H20" s="30"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <protectedRanges>
-    <protectedRange sqref="A1:NTP10000" name="Range1"/>
-  </protectedRanges>
   <mergeCells count="27">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
@@ -2575,1697 +2576,1697 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:63">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="H1" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="52" t="s">
+      <c r="I1" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="J1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="52" t="s">
+      <c r="K1" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="52" t="s">
+      <c r="L1" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="52" t="s">
+      <c r="M1" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="52" t="s">
+      <c r="N1" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="52" t="s">
+      <c r="O1" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="52" t="s">
+      <c r="P1" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="52" t="s">
+      <c r="Q1" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="52" t="s">
+      <c r="R1" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="52" t="s">
+      <c r="S1" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="T1" s="52" t="s">
+      <c r="T1" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="U1" s="52" t="s">
+      <c r="U1" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="52" t="s">
+      <c r="V1" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="52" t="s">
+      <c r="W1" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="52" t="s">
+      <c r="X1" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="52" t="s">
+      <c r="Y1" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="52" t="s">
+      <c r="Z1" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="52" t="s">
+      <c r="AA1" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="52" t="s">
+      <c r="AB1" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="52" t="s">
+      <c r="AC1" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" s="52" t="s">
+      <c r="AD1" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" s="52" t="s">
+      <c r="AE1" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="52" t="s">
+      <c r="AF1" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="52" t="s">
+      <c r="AG1" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="AH1" s="52" t="s">
+      <c r="AH1" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" s="52" t="s">
+      <c r="AI1" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="52" t="s">
+      <c r="AJ1" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" s="52" t="s">
+      <c r="AK1" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="AL1" s="52" t="s">
+      <c r="AL1" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" s="52" t="s">
+      <c r="AM1" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="AN1" s="52" t="s">
+      <c r="AN1" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="AO1" s="52" t="s">
+      <c r="AO1" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="AP1" s="52" t="s">
+      <c r="AP1" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="AQ1" s="52" t="s">
+      <c r="AQ1" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AR1" s="52" t="s">
+      <c r="AR1" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="AS1" s="52" t="s">
+      <c r="AS1" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="AT1" s="52" t="s">
+      <c r="AT1" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="AU1" s="52" t="s">
+      <c r="AU1" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="AV1" s="52" t="s">
+      <c r="AV1" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="AW1" s="52" t="s">
+      <c r="AW1" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="AX1" s="52" t="s">
+      <c r="AX1" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="AY1" s="52" t="s">
+      <c r="AY1" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="AZ1" s="52" t="s">
+      <c r="AZ1" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" s="52" t="s">
+      <c r="BA1" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="BB1" s="52" t="s">
+      <c r="BB1" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="BC1" s="52" t="s">
+      <c r="BC1" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="BD1" s="52" t="s">
+      <c r="BD1" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="BE1" s="52" t="s">
+      <c r="BE1" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="BF1" s="52" t="s">
+      <c r="BF1" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="BG1" s="52" t="s">
+      <c r="BG1" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="BH1" s="52" t="s">
+      <c r="BH1" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="BI1" s="52" t="s">
+      <c r="BI1" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="BJ1" s="52" t="s">
+      <c r="BJ1" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="BK1" s="52" t="s">
+      <c r="BK1" s="53" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:63">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="52" t="s">
+      <c r="G2" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="52" t="s">
+      <c r="J2" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="52" t="s">
+      <c r="K2" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="L2" s="52" t="s">
+      <c r="L2" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="52" t="s">
+      <c r="M2" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="52" t="s">
+      <c r="N2" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="O2" s="52" t="s">
+      <c r="O2" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="52" t="s">
+      <c r="P2" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="Q2" s="52" t="s">
+      <c r="Q2" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="52" t="s">
+      <c r="R2" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="52" t="s">
+      <c r="S2" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="52" t="s">
+      <c r="T2" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="52" t="s">
+      <c r="U2" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="V2" s="52" t="s">
+      <c r="V2" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="W2" s="52" t="s">
+      <c r="W2" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="52" t="s">
+      <c r="X2" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="52" t="s">
+      <c r="Y2" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="52" t="s">
+      <c r="Z2" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="52" t="s">
+      <c r="AA2" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="52" t="s">
+      <c r="AB2" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="AC2" s="52" t="s">
+      <c r="AC2" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="AD2" s="52" t="s">
+      <c r="AD2" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="AE2" s="52" t="s">
+      <c r="AE2" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="52" t="s">
+      <c r="AF2" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="AG2" s="52" t="s">
+      <c r="AG2" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="AH2" s="52" t="s">
+      <c r="AH2" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="AI2" s="52" t="s">
+      <c r="AI2" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="AJ2" s="52" t="s">
+      <c r="AJ2" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" s="52" t="s">
+      <c r="AK2" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="AL2" s="52" t="s">
+      <c r="AL2" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="AM2" s="52" t="s">
+      <c r="AM2" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="AN2" s="52" t="s">
+      <c r="AN2" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="AO2" s="52" t="s">
+      <c r="AO2" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="AP2" s="52" t="s">
+      <c r="AP2" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="AQ2" s="52" t="s">
+      <c r="AQ2" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="AR2" s="52" t="s">
+      <c r="AR2" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="AS2" s="52" t="s">
+      <c r="AS2" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="AT2" s="52" t="s">
+      <c r="AT2" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="AU2" s="52" t="s">
+      <c r="AU2" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="AV2" s="52" t="s">
+      <c r="AV2" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="AW2" s="52" t="s">
+      <c r="AW2" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="AX2" s="52" t="s">
+      <c r="AX2" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" s="52" t="s">
+      <c r="AY2" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="AZ2" s="52" t="s">
+      <c r="AZ2" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="BA2" s="52" t="s">
+      <c r="BA2" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="BB2" s="52" t="s">
+      <c r="BB2" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="BC2" s="52" t="s">
+      <c r="BC2" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="BD2" s="52" t="s">
+      <c r="BD2" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="BE2" s="52" t="s">
+      <c r="BE2" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="BF2" s="52" t="s">
+      <c r="BF2" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="BG2" s="52" t="s">
+      <c r="BG2" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="BH2" s="52" t="s">
+      <c r="BH2" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="BI2" s="52" t="s">
+      <c r="BI2" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="BJ2" s="52" t="s">
+      <c r="BJ2" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="BK2" s="52" t="s">
+      <c r="BK2" s="53" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:63">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="52" t="s">
+      <c r="H3" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="I3" s="52" t="s">
+      <c r="I3" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="52" t="s">
+      <c r="J3" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="K3" s="52" t="s">
+      <c r="K3" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="52" t="s">
+      <c r="L3" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="M3" s="52" t="s">
+      <c r="M3" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="N3" s="52" t="s">
+      <c r="N3" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="O3" s="52" t="s">
+      <c r="O3" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="P3" s="52" t="s">
+      <c r="P3" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="Q3" s="52" t="s">
+      <c r="Q3" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="R3" s="52" t="s">
+      <c r="R3" s="53" t="s">
         <v>141</v>
       </c>
-      <c r="S3" s="52" t="s">
+      <c r="S3" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="T3" s="52" t="s">
+      <c r="T3" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="U3" s="52" t="s">
+      <c r="U3" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="V3" s="52" t="s">
+      <c r="V3" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="W3" s="52" t="s">
+      <c r="W3" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="X3" s="52" t="s">
+      <c r="X3" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="Y3" s="52" t="s">
+      <c r="Y3" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="Z3" s="52" t="s">
+      <c r="Z3" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="AA3" s="52" t="s">
+      <c r="AA3" s="53" t="s">
         <v>149</v>
       </c>
-      <c r="AB3" s="52" t="s">
+      <c r="AB3" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="AC3" s="52" t="s">
+      <c r="AC3" s="53" t="s">
         <v>151</v>
       </c>
-      <c r="AD3" s="52" t="s">
+      <c r="AD3" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="AE3" s="52" t="s">
+      <c r="AE3" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="AF3" s="52" t="s">
+      <c r="AF3" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="AG3" s="52" t="s">
+      <c r="AG3" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="AH3" s="52" t="s">
+      <c r="AH3" s="53" t="s">
         <v>156</v>
       </c>
-      <c r="AI3" s="52" t="s">
+      <c r="AI3" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="AJ3" s="52" t="s">
+      <c r="AJ3" s="53" t="s">
         <v>158</v>
       </c>
-      <c r="AK3" s="52" t="s">
+      <c r="AK3" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="AL3" s="52" t="s">
+      <c r="AL3" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="AM3" s="52" t="s">
+      <c r="AM3" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="AN3" s="52" t="s">
+      <c r="AN3" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="AO3" s="52" t="s">
+      <c r="AO3" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="AP3" s="52" t="s">
+      <c r="AP3" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="AQ3" s="52" t="s">
+      <c r="AQ3" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="AR3" s="52" t="s">
+      <c r="AR3" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="AS3" s="52" t="s">
+      <c r="AS3" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="AT3" s="52" t="s">
+      <c r="AT3" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="AU3" s="52" t="s">
+      <c r="AU3" s="53" t="s">
         <v>166</v>
       </c>
-      <c r="AV3" s="52" t="s">
+      <c r="AV3" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="AW3" s="52" t="s">
+      <c r="AW3" s="53" t="s">
         <v>168</v>
       </c>
-      <c r="AX3" s="52" t="s">
+      <c r="AX3" s="53" t="s">
         <v>169</v>
       </c>
-      <c r="AY3" s="52" t="s">
+      <c r="AY3" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="AZ3" s="52" t="s">
+      <c r="AZ3" s="53" t="s">
         <v>171</v>
       </c>
-      <c r="BA3" s="52" t="s">
+      <c r="BA3" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="BB3" s="52" t="s">
+      <c r="BB3" s="53" t="s">
         <v>173</v>
       </c>
-      <c r="BC3" s="52" t="s">
+      <c r="BC3" s="53" t="s">
         <v>174</v>
       </c>
-      <c r="BD3" s="52" t="s">
+      <c r="BD3" s="53" t="s">
         <v>175</v>
       </c>
-      <c r="BE3" s="52" t="s">
+      <c r="BE3" s="53" t="s">
         <v>176</v>
       </c>
-      <c r="BF3" s="52" t="s">
+      <c r="BF3" s="53" t="s">
         <v>177</v>
       </c>
-      <c r="BG3" s="52" t="s">
+      <c r="BG3" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="BH3" s="52" t="s">
+      <c r="BH3" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="BI3" s="52" t="s">
+      <c r="BI3" s="53" t="s">
         <v>180</v>
       </c>
-      <c r="BJ3" s="52" t="s">
+      <c r="BJ3" s="53" t="s">
         <v>181</v>
       </c>
-      <c r="BK3" s="52" t="s">
+      <c r="BK3" s="53" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:63">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="53" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="53" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="53" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="53" t="s">
         <v>187</v>
       </c>
-      <c r="F4" s="52" t="s">
+      <c r="F4" s="53" t="s">
         <v>188</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="53" t="s">
         <v>189</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="I4" s="52" t="s">
+      <c r="I4" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="J4" s="52" t="s">
+      <c r="J4" s="53" t="s">
         <v>192</v>
       </c>
-      <c r="K4" s="52" t="s">
+      <c r="K4" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="L4" s="52" t="s">
+      <c r="L4" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="M4" s="52" t="s">
+      <c r="M4" s="53" t="s">
         <v>195</v>
       </c>
-      <c r="N4" s="52" t="s">
+      <c r="N4" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="O4" s="52" t="s">
+      <c r="O4" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="P4" s="52" t="s">
+      <c r="P4" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="Q4" s="52" t="s">
+      <c r="Q4" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="R4" s="52" t="s">
+      <c r="R4" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="S4" s="52" t="s">
+      <c r="S4" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="T4" s="52" t="s">
+      <c r="T4" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="U4" s="52" t="s">
+      <c r="U4" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="V4" s="52" t="s">
+      <c r="V4" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="W4" s="52" t="s">
+      <c r="W4" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="X4" s="52" t="s">
+      <c r="X4" s="53" t="s">
         <v>205</v>
       </c>
-      <c r="Y4" s="52" t="s">
+      <c r="Y4" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="Z4" s="52" t="s">
+      <c r="Z4" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="AA4" s="52" t="s">
+      <c r="AA4" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="AB4" s="52" t="s">
+      <c r="AB4" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="AC4" s="52" t="s">
+      <c r="AC4" s="53" t="s">
         <v>210</v>
       </c>
-      <c r="AD4" s="52" t="s">
+      <c r="AD4" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="AE4" s="52" t="s">
+      <c r="AE4" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="AF4" s="52" t="s">
+      <c r="AF4" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="AG4" s="52" t="s">
+      <c r="AG4" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="AH4" s="52" t="s">
+      <c r="AH4" s="53" t="s">
         <v>215</v>
       </c>
-      <c r="AI4" s="52" t="s">
+      <c r="AI4" s="53" t="s">
         <v>216</v>
       </c>
-      <c r="AJ4" s="52" t="s">
+      <c r="AJ4" s="53" t="s">
         <v>217</v>
       </c>
-      <c r="AK4" s="52" t="s">
+      <c r="AK4" s="53" t="s">
         <v>218</v>
       </c>
-      <c r="AL4" s="52" t="s">
+      <c r="AL4" s="53" t="s">
         <v>219</v>
       </c>
-      <c r="AM4" s="52" t="s">
+      <c r="AM4" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="AN4" s="52" t="s">
+      <c r="AN4" s="53" t="s">
         <v>221</v>
       </c>
-      <c r="AO4" s="52" t="s">
+      <c r="AO4" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="AP4" s="52" t="s">
+      <c r="AP4" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="AQ4" s="52" t="s">
+      <c r="AQ4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="AR4" s="52" t="s">
+      <c r="AR4" s="53" t="s">
         <v>224</v>
       </c>
-      <c r="AS4" s="52" t="s">
+      <c r="AS4" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="AT4" s="52" t="s">
+      <c r="AT4" s="53" t="s">
         <v>226</v>
       </c>
-      <c r="AU4" s="52" t="s">
+      <c r="AU4" s="53" t="s">
         <v>227</v>
       </c>
-      <c r="AV4" s="52" t="s">
+      <c r="AV4" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="AW4" s="52" t="s">
+      <c r="AW4" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="AX4" s="52" t="s">
+      <c r="AX4" s="53" t="s">
         <v>230</v>
       </c>
-      <c r="AY4" s="52" t="s">
+      <c r="AY4" s="53" t="s">
         <v>231</v>
       </c>
-      <c r="AZ4" s="52" t="s">
+      <c r="AZ4" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="BA4" s="52" t="s">
+      <c r="BA4" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="BB4" s="52" t="s">
+      <c r="BB4" s="53" t="s">
         <v>234</v>
       </c>
-      <c r="BC4" s="52" t="s">
+      <c r="BC4" s="53" t="s">
         <v>235</v>
       </c>
-      <c r="BD4" s="52" t="s">
+      <c r="BD4" s="53" t="s">
         <v>236</v>
       </c>
-      <c r="BE4" s="52" t="s">
+      <c r="BE4" s="53" t="s">
         <v>237</v>
       </c>
-      <c r="BF4" s="52" t="s">
+      <c r="BF4" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="BG4" s="52" t="s">
+      <c r="BG4" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="BH4" s="52" t="s">
+      <c r="BH4" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="BI4" s="52" t="s">
+      <c r="BI4" s="53" t="s">
         <v>240</v>
       </c>
-      <c r="BJ4" s="52" t="s">
+      <c r="BJ4" s="53" t="s">
         <v>241</v>
       </c>
-      <c r="BK4" s="52" t="s">
+      <c r="BK4" s="53" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:63">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="53" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="53" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="G5" s="53" t="s">
         <v>249</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="I5" s="52" t="s">
+      <c r="I5" s="53" t="s">
         <v>250</v>
       </c>
-      <c r="J5" s="52" t="s">
+      <c r="J5" s="53" t="s">
         <v>251</v>
       </c>
-      <c r="K5" s="52" t="s">
+      <c r="K5" s="53" t="s">
         <v>252</v>
       </c>
-      <c r="L5" s="52" t="s">
+      <c r="L5" s="53" t="s">
         <v>253</v>
       </c>
-      <c r="M5" s="52" t="s">
+      <c r="M5" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="N5" s="52" t="s">
+      <c r="N5" s="53" t="s">
         <v>255</v>
       </c>
-      <c r="O5" s="52" t="s">
+      <c r="O5" s="53" t="s">
         <v>256</v>
       </c>
-      <c r="P5" s="52" t="s">
+      <c r="P5" s="53" t="s">
         <v>257</v>
       </c>
-      <c r="Q5" s="52" t="s">
+      <c r="Q5" s="53" t="s">
         <v>258</v>
       </c>
-      <c r="R5" s="52" t="s">
+      <c r="R5" s="53" t="s">
         <v>259</v>
       </c>
-      <c r="S5" s="52" t="s">
+      <c r="S5" s="53" t="s">
         <v>260</v>
       </c>
-      <c r="T5" s="52" t="s">
+      <c r="T5" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="U5" s="52" t="s">
+      <c r="U5" s="53" t="s">
         <v>262</v>
       </c>
-      <c r="V5" s="52" t="s">
+      <c r="V5" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="W5" s="52" t="s">
+      <c r="W5" s="53" t="s">
         <v>263</v>
       </c>
-      <c r="X5" s="52" t="s">
+      <c r="X5" s="53" t="s">
         <v>264</v>
       </c>
-      <c r="Y5" s="52" t="s">
+      <c r="Y5" s="53" t="s">
         <v>265</v>
       </c>
-      <c r="Z5" s="52" t="s">
+      <c r="Z5" s="53" t="s">
         <v>266</v>
       </c>
-      <c r="AA5" s="52" t="s">
+      <c r="AA5" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="AB5" s="52" t="s">
+      <c r="AB5" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="AC5" s="52" t="s">
+      <c r="AC5" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="AD5" s="52" t="s">
+      <c r="AD5" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="AE5" s="52" t="s">
+      <c r="AE5" s="53" t="s">
         <v>270</v>
       </c>
-      <c r="AF5" s="52" t="s">
+      <c r="AF5" s="53" t="s">
         <v>271</v>
       </c>
-      <c r="AG5" s="52" t="s">
+      <c r="AG5" s="53" t="s">
         <v>272</v>
       </c>
-      <c r="AH5" s="52" t="s">
+      <c r="AH5" s="53" t="s">
         <v>273</v>
       </c>
-      <c r="AI5" s="52" t="s">
+      <c r="AI5" s="53" t="s">
         <v>274</v>
       </c>
-      <c r="AJ5" s="52" t="s">
+      <c r="AJ5" s="53" t="s">
         <v>275</v>
       </c>
-      <c r="AK5" s="52" t="s">
+      <c r="AK5" s="53" t="s">
         <v>276</v>
       </c>
-      <c r="AL5" s="52" t="s">
+      <c r="AL5" s="53" t="s">
         <v>277</v>
       </c>
-      <c r="AM5" s="52" t="s">
+      <c r="AM5" s="53" t="s">
         <v>278</v>
       </c>
-      <c r="AN5" s="52" t="s">
+      <c r="AN5" s="53" t="s">
         <v>279</v>
       </c>
-      <c r="AO5" s="52" t="s">
+      <c r="AO5" s="53" t="s">
         <v>280</v>
       </c>
-      <c r="AP5" s="52" t="s">
+      <c r="AP5" s="53" t="s">
         <v>281</v>
       </c>
-      <c r="AQ5" s="52" t="s">
+      <c r="AQ5" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="AR5" s="52" t="s">
+      <c r="AR5" s="53" t="s">
         <v>282</v>
       </c>
-      <c r="AS5" s="52" t="s">
+      <c r="AS5" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="AT5" s="52" t="s">
+      <c r="AT5" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="AU5" s="52" t="s">
+      <c r="AU5" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="AV5" s="52" t="s">
+      <c r="AV5" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="AW5" s="52" t="s">
+      <c r="AW5" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="AX5" s="52" t="s">
+      <c r="AX5" s="53" t="s">
         <v>287</v>
       </c>
-      <c r="AY5" s="52" t="s">
+      <c r="AY5" s="53" t="s">
         <v>288</v>
       </c>
-      <c r="AZ5" s="52" t="s">
+      <c r="AZ5" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="BA5" s="52" t="s">
+      <c r="BA5" s="53" t="s">
         <v>290</v>
       </c>
-      <c r="BB5" s="52" t="s">
+      <c r="BB5" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="BC5" s="52" t="s">
+      <c r="BC5" s="53" t="s">
         <v>292</v>
       </c>
-      <c r="BD5" s="52" t="s">
+      <c r="BD5" s="53" t="s">
         <v>293</v>
       </c>
-      <c r="BE5" s="52" t="s">
+      <c r="BE5" s="53" t="s">
         <v>294</v>
       </c>
-      <c r="BF5" s="52" t="s">
+      <c r="BF5" s="53" t="s">
         <v>295</v>
       </c>
-      <c r="BG5" s="52" t="s">
+      <c r="BG5" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="BH5" s="52" t="s">
+      <c r="BH5" s="53" t="s">
         <v>296</v>
       </c>
-      <c r="BI5" s="52" t="s">
+      <c r="BI5" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="BJ5" s="52" t="s">
+      <c r="BJ5" s="53" t="s">
         <v>298</v>
       </c>
-      <c r="BK5" s="52" t="s">
+      <c r="BK5" s="53" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:63">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="53" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:63">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="53" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:63">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="53" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:63">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="53" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:63">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="53" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:63">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="53" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:63">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="53" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:63">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="53" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:63">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="53" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:63">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="53" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:63">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="53" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="53" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="53" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="53" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="53" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="52" t="s">
+      <c r="A21" s="53" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="53" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="53" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="53" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="53" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="53" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="52" t="s">
+      <c r="A27" s="53" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="52" t="s">
+      <c r="A28" s="53" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="52" t="s">
+      <c r="A29" s="53" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="52" t="s">
+      <c r="A30" s="53" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="52" t="s">
+      <c r="A31" s="53" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="52" t="s">
+      <c r="A32" s="53" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="52" t="s">
+      <c r="A33" s="53" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="52" t="s">
+      <c r="A34" s="53" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="52" t="s">
+      <c r="A35" s="53" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="52" t="s">
+      <c r="A36" s="53" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="52" t="s">
+      <c r="A37" s="53" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="52" t="s">
+      <c r="A38" s="53" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="52" t="s">
+      <c r="A39" s="53" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="52" t="s">
+      <c r="A40" s="53" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="52" t="s">
+      <c r="A41" s="53" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="52" t="s">
+      <c r="A42" s="53" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="52" t="s">
+      <c r="A43" s="53" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="52" t="s">
+      <c r="A44" s="53" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="52" t="s">
+      <c r="A45" s="53" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="52" t="s">
+      <c r="A46" s="53" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="52" t="s">
+      <c r="A47" s="53" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="52" t="s">
+      <c r="A48" s="53" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="52" t="s">
+      <c r="A49" s="53" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="52" t="s">
+      <c r="A50" s="53" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="52" t="s">
+      <c r="A51" s="53" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="52" t="s">
+      <c r="A52" s="53" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="52" t="s">
+      <c r="A53" s="53" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="52" t="s">
+      <c r="A54" s="53" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="52" t="s">
+      <c r="A55" s="53" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="52" t="s">
+      <c r="A56" s="53" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="52" t="s">
+      <c r="A57" s="53" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="52" t="s">
+      <c r="A58" s="53" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="52" t="s">
+      <c r="A59" s="53" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="52" t="s">
+      <c r="A60" s="53" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="52" t="s">
+      <c r="A61" s="53" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="52" t="s">
+      <c r="A62" s="53" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="52" t="s">
+      <c r="A63" s="53" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="52" t="s">
+      <c r="A64" s="53" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="52" t="s">
+      <c r="A65" s="53" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="52" t="s">
+      <c r="A66" s="53" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="52" t="s">
+      <c r="A67" s="53" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="52" t="s">
+      <c r="A68" s="53" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="52" t="s">
+      <c r="A69" s="53" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="52" t="s">
+      <c r="A70" s="53" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="52" t="s">
+      <c r="A71" s="53" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="52" t="s">
+      <c r="A72" s="53" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="52" t="s">
+      <c r="A73" s="53" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="52" t="s">
+      <c r="A74" s="53" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="52" t="s">
+      <c r="A75" s="53" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="52" t="s">
+      <c r="A76" s="53" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="52" t="s">
+      <c r="A77" s="53" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="52" t="s">
+      <c r="A78" s="53" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="52" t="s">
+      <c r="A79" s="53" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="52" t="s">
+      <c r="A80" s="53" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="52" t="s">
+      <c r="A81" s="53" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="52" t="s">
+      <c r="A82" s="53" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="52" t="s">
+      <c r="A83" s="53" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="52" t="s">
+      <c r="A84" s="53" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="52" t="s">
+      <c r="A85" s="53" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="52" t="s">
+      <c r="A86" s="53" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="52" t="s">
+      <c r="A87" s="53" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="52" t="s">
+      <c r="A88" s="53" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="52" t="s">
+      <c r="A89" s="53" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="52" t="s">
+      <c r="A90" s="53" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="52" t="s">
+      <c r="A91" s="53" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="52" t="s">
+      <c r="A92" s="53" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="52" t="s">
+      <c r="A93" s="53" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="52" t="s">
+      <c r="A94" s="53" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="52" t="s">
+      <c r="A95" s="53" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="52" t="s">
+      <c r="A96" s="53" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="52" t="s">
+      <c r="A97" s="53" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="52" t="s">
+      <c r="A98" s="53" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="52" t="s">
+      <c r="A99" s="53" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="52" t="s">
+      <c r="A100" s="53" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="52" t="s">
+      <c r="A101" s="53" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="52" t="s">
+      <c r="A102" s="53" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="52" t="s">
+      <c r="A103" s="53" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="52" t="s">
+      <c r="A104" s="53" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="52" t="s">
+      <c r="A105" s="53" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="52" t="s">
+      <c r="A106" s="53" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="52" t="s">
+      <c r="A107" s="53" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="52" t="s">
+      <c r="A108" s="53" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="52" t="s">
+      <c r="A109" s="53" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="52" t="s">
+      <c r="A110" s="53" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="52" t="s">
+      <c r="A111" s="53" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="52" t="s">
+      <c r="A112" s="53" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="52" t="s">
+      <c r="A113" s="53" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="52" t="s">
+      <c r="A114" s="53" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="52" t="s">
+      <c r="A115" s="53" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="52" t="s">
+      <c r="A116" s="53" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="52" t="s">
+      <c r="A117" s="53" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="52" t="s">
+      <c r="A118" s="53" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="52" t="s">
+      <c r="A119" s="53" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="52" t="s">
+      <c r="A120" s="53" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="52" t="s">
+      <c r="A121" s="53" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="52" t="s">
+      <c r="A122" s="53" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="52" t="s">
+      <c r="A123" s="53" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="52" t="s">
+      <c r="A124" s="53" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="52" t="s">
+      <c r="A125" s="53" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="52" t="s">
+      <c r="A126" s="53" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="52" t="s">
+      <c r="A127" s="53" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="52" t="s">
+      <c r="A128" s="53" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="52" t="s">
+      <c r="A129" s="53" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="52" t="s">
+      <c r="A130" s="53" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="52" t="s">
+      <c r="A131" s="53" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="52" t="s">
+      <c r="A132" s="53" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="52" t="s">
+      <c r="A133" s="53" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="52" t="s">
+      <c r="A134" s="53" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="52" t="s">
+      <c r="A135" s="53" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="52" t="s">
+      <c r="A136" s="53" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="52" t="s">
+      <c r="A137" s="53" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="52" t="s">
+      <c r="A138" s="53" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="52" t="s">
+      <c r="A139" s="53" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="52" t="s">
+      <c r="A140" s="53" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="52" t="s">
+      <c r="A141" s="53" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="52" t="s">
+      <c r="A142" s="53" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="52" t="s">
+      <c r="A143" s="53" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="52" t="s">
+      <c r="A144" s="53" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="52" t="s">
+      <c r="A145" s="53" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="52" t="s">
+      <c r="A146" s="53" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="52" t="s">
+      <c r="A147" s="53" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="52" t="s">
+      <c r="A148" s="53" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="52" t="s">
+      <c r="A149" s="53" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="52" t="s">
+      <c r="A150" s="53" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="52" t="s">
+      <c r="A151" s="53" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="52" t="s">
+      <c r="A152" s="53" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="52" t="s">
+      <c r="A153" s="53" t="s">
         <v>447</v>
       </c>
     </row>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="484">
   <si>
     <t>_de</t>
   </si>
@@ -24,6 +24,114 @@
   </si>
   <si>
     <t>Euro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">32. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">33. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">36. </t>
   </si>
   <si>
     <t>AED</t>
@@ -1365,10 +1473,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mm-dd-yy"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -1694,7 +1803,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1827,9 +1936,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1864,6 +1970,21 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2159,7 +2280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:ALL20"/>
+  <dimension ref="A1:ALL31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.28515625" style="1" customWidth="1"/>
@@ -2232,10 +2353,6 @@
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="38">
-        <f>IF($E$2="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
-        <v>0</v>
-      </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -2244,7 +2361,7 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="39">
+      <c r="J4" s="38">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>0</v>
       </c>
@@ -2290,12 +2407,12 @@
         <v>0</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="40">
+      <c r="D8" s="39">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="40">
+      <c r="F8" s="39">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>0</v>
       </c>
@@ -2313,12 +2430,12 @@
         <v>0</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="40">
+      <c r="D9" s="39">
         <f>D8</f>
         <v>0</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="40">
+      <c r="F9" s="39">
         <f>F8</f>
         <v>0</v>
       </c>
@@ -2330,23 +2447,23 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="41">
+      <c r="D11" s="40">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="41">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="40">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="40">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>0</v>
       </c>
@@ -2362,7 +2479,7 @@
       <c r="R11" s="2"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="44">
+      <c r="B12" s="43">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>0</v>
       </c>
@@ -2374,7 +2491,7 @@
       <c r="H12" s="11"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="45">
+      <c r="B13" s="44">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>0</v>
       </c>
@@ -2384,33 +2501,33 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="11"/>
-      <c r="L13" s="46">
+      <c r="L13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
       <c r="M13" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="46">
+      <c r="N13" s="45">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="46">
+      <c r="O13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S13" s="46">
+      <c r="S13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
       <c r="T13" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="U13" s="46">
+      <c r="U13" s="45">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="46">
+      <c r="V13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
@@ -2423,9 +2540,37 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="11"/>
+      <c r="J14" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="54"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="56">
+        <f>IF(M14="","",N14/M14)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="54"/>
+      <c r="T14" s="55"/>
+      <c r="U14" s="55"/>
+      <c r="V14" s="56">
+        <f>IF(T14="","",U14/T14)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="47">
+      <c r="B15" s="46">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>0</v>
       </c>
@@ -2437,9 +2582,37 @@
       <c r="F15" s="27"/>
       <c r="G15" s="28"/>
       <c r="H15" s="29"/>
+      <c r="J15" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="54"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="56">
+        <f>IF(M15="","",N15/M15)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="R15" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="54"/>
+      <c r="T15" s="55"/>
+      <c r="U15" s="55"/>
+      <c r="V15" s="56">
+        <f>IF(T15="","",U15/T15)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="48">
+      <c r="B16" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>0</v>
       </c>
@@ -2449,14 +2622,42 @@
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
-      <c r="G16" s="49">
+      <c r="G16" s="48">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
       <c r="H16" s="29"/>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="48">
+      <c r="J16" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="54"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="56">
+        <f>IF(M16="","",N16/M16)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="54"/>
+      <c r="T16" s="55"/>
+      <c r="U16" s="55"/>
+      <c r="V16" s="56">
+        <f>IF(T16="","",U16/T16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22">
+      <c r="B17" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>0</v>
       </c>
@@ -2466,14 +2667,42 @@
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="27"/>
-      <c r="G17" s="49">
+      <c r="G17" s="48">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
       <c r="H17" s="29"/>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="48">
+      <c r="J17" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="54"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="56">
+        <f>IF(M17="","",N17/M17)</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="R17" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="54"/>
+      <c r="T17" s="55"/>
+      <c r="U17" s="55"/>
+      <c r="V17" s="56">
+        <f>IF(T17="","",U17/T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>0</v>
       </c>
@@ -2483,14 +2712,42 @@
       </c>
       <c r="E18" s="27"/>
       <c r="F18" s="27"/>
-      <c r="G18" s="49">
+      <c r="G18" s="48">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
       <c r="H18" s="29"/>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="48">
+      <c r="J18" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="54"/>
+      <c r="M18" s="55"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="56">
+        <f>IF(M18="","",N18/M18)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="R18" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="54"/>
+      <c r="T18" s="55"/>
+      <c r="U18" s="55"/>
+      <c r="V18" s="56">
+        <f>IF(T18="","",U18/T18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>0</v>
       </c>
@@ -2500,35 +2757,421 @@
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="49">
+      <c r="G19" s="48">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
       <c r="H19" s="29"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="50">
+      <c r="J19" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="54"/>
+      <c r="M19" s="55"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="56">
+        <f>IF(M19="","",N19/M19)</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="R19" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="54"/>
+      <c r="T19" s="55"/>
+      <c r="U19" s="55"/>
+      <c r="V19" s="56">
+        <f>IF(T19="","",U19/T19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="49">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>0</v>
       </c>
       <c r="C20" s="16"/>
-      <c r="D20" s="51">
+      <c r="D20" s="50">
         <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="50">
         <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="50">
         <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="51">
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v>0</v>
       </c>
       <c r="H20" s="30"/>
+      <c r="J20" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="54"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="56">
+        <f>IF(M20="","",N20/M20)</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="R20" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="54"/>
+      <c r="T20" s="55"/>
+      <c r="U20" s="55"/>
+      <c r="V20" s="56">
+        <f>IF(T20="","",U20/T20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="J21" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="54"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="56">
+        <f>IF(M21="","",N21/M21)</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="R21" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="54"/>
+      <c r="T21" s="55"/>
+      <c r="U21" s="55"/>
+      <c r="V21" s="56">
+        <f>IF(T21="","",U21/T21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="J22" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="54"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="56">
+        <f>IF(M22="","",N22/M22)</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="R22" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="54"/>
+      <c r="T22" s="55"/>
+      <c r="U22" s="55"/>
+      <c r="V22" s="56">
+        <f>IF(T22="","",U22/T22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="J23" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="54"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="56">
+        <f>IF(M23="","",N23/M23)</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="R23" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S23" s="54"/>
+      <c r="T23" s="55"/>
+      <c r="U23" s="55"/>
+      <c r="V23" s="56">
+        <f>IF(T23="","",U23/T23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="J24" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="54"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="56">
+        <f>IF(M24="","",N24/M24)</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="R24" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="54"/>
+      <c r="T24" s="55"/>
+      <c r="U24" s="55"/>
+      <c r="V24" s="56">
+        <f>IF(T24="","",U24/T24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="J25" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="54"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="56">
+        <f>IF(M25="","",N25/M25)</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="R25" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="54"/>
+      <c r="T25" s="55"/>
+      <c r="U25" s="55"/>
+      <c r="V25" s="56">
+        <f>IF(T25="","",U25/T25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="J26" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="54"/>
+      <c r="M26" s="55"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="56">
+        <f>IF(M26="","",N26/M26)</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="R26" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="54"/>
+      <c r="T26" s="55"/>
+      <c r="U26" s="55"/>
+      <c r="V26" s="56">
+        <f>IF(T26="","",U26/T26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="J27" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="54"/>
+      <c r="M27" s="55"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="56">
+        <f>IF(M27="","",N27/M27)</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="R27" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="54"/>
+      <c r="T27" s="55"/>
+      <c r="U27" s="55"/>
+      <c r="V27" s="56">
+        <f>IF(T27="","",U27/T27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="J28" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="54"/>
+      <c r="M28" s="55"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="56">
+        <f>IF(M28="","",N28/M28)</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S28" s="54"/>
+      <c r="T28" s="55"/>
+      <c r="U28" s="55"/>
+      <c r="V28" s="56">
+        <f>IF(T28="","",U28/T28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22">
+      <c r="J29" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="K29" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="54"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="56">
+        <f>IF(M29="","",N29/M29)</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="R29" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S29" s="54"/>
+      <c r="T29" s="55"/>
+      <c r="U29" s="55"/>
+      <c r="V29" s="56">
+        <f>IF(T29="","",U29/T29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22">
+      <c r="J30" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="54"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="56">
+        <f>IF(M30="","",N30/M30)</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="R30" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="54"/>
+      <c r="T30" s="55"/>
+      <c r="U30" s="55"/>
+      <c r="V30" s="56">
+        <f>IF(T30="","",U30/T30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22">
+      <c r="J31" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="K31" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="54"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="56">
+        <f>IF(M31="","",N31/M31)</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="R31" s="53">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="S31" s="54"/>
+      <c r="T31" s="55"/>
+      <c r="U31" s="55"/>
+      <c r="V31" s="56">
+        <f>IF(T31="","",U31/T31)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -2561,9 +3204,12 @@
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2">
       <formula1>Sprachversionen!$B$1:$B$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3">
+      <formula1>Sprachversionen!$A$1:$A$153</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2576,1698 +3222,1698 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:63">
-      <c r="A1" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="53" t="s">
+      <c r="A1" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="U1" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="V1" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="W1" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="X1" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y1" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB1" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD1" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE1" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF1" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG1" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH1" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI1" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ1" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK1" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL1" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM1" s="53" t="s">
+      <c r="C1" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="AN1" s="53" t="s">
+      <c r="D1" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="AO1" s="53" t="s">
+      <c r="E1" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AP1" s="53" t="s">
+      <c r="F1" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="AQ1" s="53" t="s">
+      <c r="G1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="AR1" s="53" t="s">
+      <c r="H1" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="AS1" s="53" t="s">
+      <c r="I1" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AT1" s="53" t="s">
+      <c r="J1" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="AU1" s="53" t="s">
+      <c r="K1" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="AV1" s="53" t="s">
+      <c r="L1" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="AW1" s="53" t="s">
+      <c r="M1" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="AX1" s="53" t="s">
+      <c r="N1" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="AY1" s="53" t="s">
+      <c r="O1" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="AZ1" s="53" t="s">
+      <c r="P1" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" s="53" t="s">
+      <c r="Q1" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="BB1" s="53" t="s">
+      <c r="R1" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="BC1" s="53" t="s">
+      <c r="S1" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="BD1" s="53" t="s">
+      <c r="T1" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="BE1" s="53" t="s">
+      <c r="U1" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="BF1" s="53" t="s">
+      <c r="V1" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="BG1" s="53" t="s">
+      <c r="W1" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="BH1" s="53" t="s">
+      <c r="X1" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="BI1" s="53" t="s">
+      <c r="Y1" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="BJ1" s="53" t="s">
+      <c r="Z1" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="BK1" s="53" t="s">
+      <c r="AA1" s="57" t="s">
         <v>64</v>
       </c>
+      <c r="AB1" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC1" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD1" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE1" s="57" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF1" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG1" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH1" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI1" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ1" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK1" s="57" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL1" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM1" s="57" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN1" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO1" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP1" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ1" s="57" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR1" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS1" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT1" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU1" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV1" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW1" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX1" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY1" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ1" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="BA1" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="BB1" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="BC1" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD1" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE1" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF1" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="BG1" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH1" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="BI1" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="BJ1" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="BK1" s="57" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="2" spans="1:63">
-      <c r="A2" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="K2" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="L2" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="M2" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="N2" s="53" t="s">
+      <c r="A2" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="J2" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="L2" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="M2" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="N2" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="O2" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="P2" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q2" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="R2" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="S2" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="T2" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="U2" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="V2" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="W2" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="X2" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y2" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z2" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA2" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB2" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD2" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE2" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF2" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG2" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="AH2" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI2" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="AJ2" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="AK2" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL2" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM2" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="AN2" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO2" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="O2" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="P2" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q2" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="R2" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="S2" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="T2" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="53" t="s">
+      <c r="AP2" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ2" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="AR2" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="AS2" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="AT2" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="AU2" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="AV2" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="V2" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="W2" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="X2" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y2" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z2" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA2" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB2" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC2" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD2" s="53" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE2" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="AF2" s="53" t="s">
-        <v>96</v>
-      </c>
-      <c r="AG2" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH2" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="AI2" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="AJ2" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK2" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL2" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="AM2" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN2" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO2" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP2" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="AQ2" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="AS2" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="AT2" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU2" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="AV2" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="AW2" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="AX2" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="AY2" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="AZ2" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="BA2" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="BB2" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="BC2" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="BD2" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="BE2" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF2" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="BG2" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="BH2" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="BI2" s="53" t="s">
+      <c r="AW2" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="AX2" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="AY2" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="AZ2" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="BA2" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="BB2" s="57" t="s">
+        <v>151</v>
+      </c>
+      <c r="BC2" s="57" t="s">
+        <v>152</v>
+      </c>
+      <c r="BD2" s="57" t="s">
+        <v>153</v>
+      </c>
+      <c r="BE2" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="BF2" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="BG2" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="BH2" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="BI2" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ2" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="BK2" s="57" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:63">
+      <c r="A3" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="F3" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="J3" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="K3" s="57" t="s">
+        <v>170</v>
+      </c>
+      <c r="L3" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="M3" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="N3" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="O3" s="57" t="s">
+        <v>174</v>
+      </c>
+      <c r="P3" s="57" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q3" s="57" t="s">
+        <v>176</v>
+      </c>
+      <c r="R3" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="S3" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="T3" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="U3" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="V3" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="W3" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="X3" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y3" s="57" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z3" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA3" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB3" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="AC3" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD3" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="AE3" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="AF3" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="AG3" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH3" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI3" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="AJ3" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK3" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="AL3" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM3" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="AN3" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO3" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP3" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="AQ3" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="AR3" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="AS3" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="AT3" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU3" s="57" t="s">
+        <v>202</v>
+      </c>
+      <c r="AV3" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="AW3" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="AX3" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="AY3" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="AZ3" s="57" t="s">
+        <v>207</v>
+      </c>
+      <c r="BA3" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="BB3" s="57" t="s">
+        <v>209</v>
+      </c>
+      <c r="BC3" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD3" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE3" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="BF3" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="BG3" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="BH3" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="BI3" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="BJ3" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="BK3" s="57" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:63">
+      <c r="A4" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="G4" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="J4" s="57" t="s">
+        <v>228</v>
+      </c>
+      <c r="K4" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="L4" s="57" t="s">
+        <v>230</v>
+      </c>
+      <c r="M4" s="57" t="s">
+        <v>231</v>
+      </c>
+      <c r="N4" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="O4" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="P4" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q4" s="57" t="s">
+        <v>235</v>
+      </c>
+      <c r="R4" s="57" t="s">
+        <v>236</v>
+      </c>
+      <c r="S4" s="57" t="s">
+        <v>237</v>
+      </c>
+      <c r="T4" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="U4" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="V4" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="W4" s="57" t="s">
+        <v>240</v>
+      </c>
+      <c r="X4" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y4" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z4" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA4" s="57" t="s">
+        <v>244</v>
+      </c>
+      <c r="AB4" s="57" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC4" s="57" t="s">
+        <v>246</v>
+      </c>
+      <c r="AD4" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="AE4" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="AF4" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="AG4" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="AH4" s="57" t="s">
+        <v>251</v>
+      </c>
+      <c r="AI4" s="57" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ4" s="57" t="s">
+        <v>253</v>
+      </c>
+      <c r="AK4" s="57" t="s">
+        <v>254</v>
+      </c>
+      <c r="AL4" s="57" t="s">
+        <v>255</v>
+      </c>
+      <c r="AM4" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="AN4" s="57" t="s">
+        <v>257</v>
+      </c>
+      <c r="AO4" s="57" t="s">
+        <v>258</v>
+      </c>
+      <c r="AP4" s="57" t="s">
+        <v>259</v>
+      </c>
+      <c r="AQ4" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="BJ2" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK2" s="53" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:63">
-      <c r="A3" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="G3" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="H3" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="I3" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="J3" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="K3" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="L3" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="M3" s="53" t="s">
-        <v>136</v>
-      </c>
-      <c r="N3" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="O3" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="P3" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q3" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="R3" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="S3" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="T3" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="U3" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="V3" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="W3" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="X3" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y3" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z3" s="53" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA3" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="AB3" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="AC3" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="AD3" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE3" s="53" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF3" s="53" t="s">
-        <v>154</v>
-      </c>
-      <c r="AG3" s="53" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH3" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="AI3" s="53" t="s">
-        <v>157</v>
-      </c>
-      <c r="AJ3" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="AK3" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="AL3" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="AM3" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="AN3" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO3" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP3" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="AQ3" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="AR3" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="AS3" s="53" t="s">
-        <v>164</v>
-      </c>
-      <c r="AT3" s="53" t="s">
-        <v>165</v>
-      </c>
-      <c r="AU3" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="AV3" s="53" t="s">
-        <v>167</v>
-      </c>
-      <c r="AW3" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="AX3" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="AY3" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="AZ3" s="53" t="s">
-        <v>171</v>
-      </c>
-      <c r="BA3" s="53" t="s">
-        <v>172</v>
-      </c>
-      <c r="BB3" s="53" t="s">
-        <v>173</v>
-      </c>
-      <c r="BC3" s="53" t="s">
-        <v>174</v>
-      </c>
-      <c r="BD3" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="BE3" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="BF3" s="53" t="s">
-        <v>177</v>
-      </c>
-      <c r="BG3" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="BH3" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="BI3" s="53" t="s">
-        <v>180</v>
-      </c>
-      <c r="BJ3" s="53" t="s">
+      <c r="AR4" s="57" t="s">
+        <v>260</v>
+      </c>
+      <c r="AS4" s="57" t="s">
+        <v>261</v>
+      </c>
+      <c r="AT4" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="AU4" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="AV4" s="57" t="s">
+        <v>264</v>
+      </c>
+      <c r="AW4" s="57" t="s">
+        <v>265</v>
+      </c>
+      <c r="AX4" s="57" t="s">
+        <v>266</v>
+      </c>
+      <c r="AY4" s="57" t="s">
+        <v>267</v>
+      </c>
+      <c r="AZ4" s="57" t="s">
+        <v>268</v>
+      </c>
+      <c r="BA4" s="57" t="s">
+        <v>269</v>
+      </c>
+      <c r="BB4" s="57" t="s">
+        <v>270</v>
+      </c>
+      <c r="BC4" s="57" t="s">
+        <v>271</v>
+      </c>
+      <c r="BD4" s="57" t="s">
+        <v>272</v>
+      </c>
+      <c r="BE4" s="57" t="s">
+        <v>273</v>
+      </c>
+      <c r="BF4" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="BG4" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="BH4" s="57" t="s">
+        <v>275</v>
+      </c>
+      <c r="BI4" s="57" t="s">
+        <v>276</v>
+      </c>
+      <c r="BJ4" s="57" t="s">
+        <v>277</v>
+      </c>
+      <c r="BK4" s="57" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:63">
+      <c r="A5" s="57" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>282</v>
+      </c>
+      <c r="E5" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="57" t="s">
+        <v>284</v>
+      </c>
+      <c r="G5" s="57" t="s">
+        <v>285</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="I5" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>287</v>
+      </c>
+      <c r="K5" s="57" t="s">
+        <v>288</v>
+      </c>
+      <c r="L5" s="57" t="s">
+        <v>289</v>
+      </c>
+      <c r="M5" s="57" t="s">
+        <v>290</v>
+      </c>
+      <c r="N5" s="57" t="s">
+        <v>291</v>
+      </c>
+      <c r="O5" s="57" t="s">
+        <v>292</v>
+      </c>
+      <c r="P5" s="57" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q5" s="57" t="s">
+        <v>294</v>
+      </c>
+      <c r="R5" s="57" t="s">
+        <v>295</v>
+      </c>
+      <c r="S5" s="57" t="s">
+        <v>296</v>
+      </c>
+      <c r="T5" s="57" t="s">
+        <v>297</v>
+      </c>
+      <c r="U5" s="57" t="s">
+        <v>298</v>
+      </c>
+      <c r="V5" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="BK3" s="53" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="4" spans="1:63">
-      <c r="A4" s="53" t="s">
-        <v>183</v>
-      </c>
-      <c r="B4" s="53" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="53" t="s">
-        <v>185</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>186</v>
-      </c>
-      <c r="E4" s="53" t="s">
-        <v>187</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="G4" s="53" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="I4" s="53" t="s">
-        <v>191</v>
-      </c>
-      <c r="J4" s="53" t="s">
-        <v>192</v>
-      </c>
-      <c r="K4" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="L4" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="M4" s="53" t="s">
-        <v>195</v>
-      </c>
-      <c r="N4" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="O4" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="P4" s="53" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q4" s="53" t="s">
-        <v>199</v>
-      </c>
-      <c r="R4" s="53" t="s">
-        <v>200</v>
-      </c>
-      <c r="S4" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="T4" s="53" t="s">
-        <v>202</v>
-      </c>
-      <c r="U4" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="V4" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="W4" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="X4" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y4" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z4" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA4" s="53" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB4" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC4" s="53" t="s">
-        <v>210</v>
-      </c>
-      <c r="AD4" s="53" t="s">
-        <v>211</v>
-      </c>
-      <c r="AE4" s="53" t="s">
-        <v>212</v>
-      </c>
-      <c r="AF4" s="53" t="s">
-        <v>213</v>
-      </c>
-      <c r="AG4" s="53" t="s">
+      <c r="W5" s="57" t="s">
+        <v>299</v>
+      </c>
+      <c r="X5" s="57" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y5" s="57" t="s">
+        <v>301</v>
+      </c>
+      <c r="Z5" s="57" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA5" s="57" t="s">
+        <v>303</v>
+      </c>
+      <c r="AB5" s="57" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC5" s="57" t="s">
+        <v>304</v>
+      </c>
+      <c r="AD5" s="57" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE5" s="57" t="s">
+        <v>306</v>
+      </c>
+      <c r="AF5" s="57" t="s">
+        <v>307</v>
+      </c>
+      <c r="AG5" s="57" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH5" s="57" t="s">
+        <v>309</v>
+      </c>
+      <c r="AI5" s="57" t="s">
+        <v>310</v>
+      </c>
+      <c r="AJ5" s="57" t="s">
+        <v>311</v>
+      </c>
+      <c r="AK5" s="57" t="s">
+        <v>312</v>
+      </c>
+      <c r="AL5" s="57" t="s">
+        <v>313</v>
+      </c>
+      <c r="AM5" s="57" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN5" s="57" t="s">
+        <v>315</v>
+      </c>
+      <c r="AO5" s="57" t="s">
+        <v>316</v>
+      </c>
+      <c r="AP5" s="57" t="s">
+        <v>317</v>
+      </c>
+      <c r="AQ5" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="AR5" s="57" t="s">
+        <v>318</v>
+      </c>
+      <c r="AS5" s="57" t="s">
+        <v>319</v>
+      </c>
+      <c r="AT5" s="57" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU5" s="57" t="s">
+        <v>321</v>
+      </c>
+      <c r="AV5" s="57" t="s">
+        <v>264</v>
+      </c>
+      <c r="AW5" s="57" t="s">
+        <v>322</v>
+      </c>
+      <c r="AX5" s="57" t="s">
+        <v>323</v>
+      </c>
+      <c r="AY5" s="57" t="s">
+        <v>324</v>
+      </c>
+      <c r="AZ5" s="57" t="s">
+        <v>325</v>
+      </c>
+      <c r="BA5" s="57" t="s">
+        <v>326</v>
+      </c>
+      <c r="BB5" s="57" t="s">
+        <v>327</v>
+      </c>
+      <c r="BC5" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="BD5" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="BE5" s="57" t="s">
+        <v>330</v>
+      </c>
+      <c r="BF5" s="57" t="s">
+        <v>331</v>
+      </c>
+      <c r="BG5" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="AH4" s="53" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI4" s="53" t="s">
-        <v>216</v>
-      </c>
-      <c r="AJ4" s="53" t="s">
-        <v>217</v>
-      </c>
-      <c r="AK4" s="53" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL4" s="53" t="s">
-        <v>219</v>
-      </c>
-      <c r="AM4" s="53" t="s">
-        <v>220</v>
-      </c>
-      <c r="AN4" s="53" t="s">
-        <v>221</v>
-      </c>
-      <c r="AO4" s="53" t="s">
-        <v>222</v>
-      </c>
-      <c r="AP4" s="53" t="s">
-        <v>223</v>
-      </c>
-      <c r="AQ4" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR4" s="53" t="s">
-        <v>224</v>
-      </c>
-      <c r="AS4" s="53" t="s">
-        <v>225</v>
-      </c>
-      <c r="AT4" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="AU4" s="53" t="s">
-        <v>227</v>
-      </c>
-      <c r="AV4" s="53" t="s">
-        <v>228</v>
-      </c>
-      <c r="AW4" s="53" t="s">
-        <v>229</v>
-      </c>
-      <c r="AX4" s="53" t="s">
-        <v>230</v>
-      </c>
-      <c r="AY4" s="53" t="s">
-        <v>231</v>
-      </c>
-      <c r="AZ4" s="53" t="s">
-        <v>232</v>
-      </c>
-      <c r="BA4" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="BB4" s="53" t="s">
-        <v>234</v>
-      </c>
-      <c r="BC4" s="53" t="s">
-        <v>235</v>
-      </c>
-      <c r="BD4" s="53" t="s">
-        <v>236</v>
-      </c>
-      <c r="BE4" s="53" t="s">
-        <v>237</v>
-      </c>
-      <c r="BF4" s="53" t="s">
-        <v>238</v>
-      </c>
-      <c r="BG4" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="BH4" s="53" t="s">
-        <v>239</v>
-      </c>
-      <c r="BI4" s="53" t="s">
-        <v>240</v>
-      </c>
-      <c r="BJ4" s="53" t="s">
-        <v>241</v>
-      </c>
-      <c r="BK4" s="53" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="5" spans="1:63">
-      <c r="A5" s="53" t="s">
-        <v>243</v>
-      </c>
-      <c r="B5" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="D5" s="53" t="s">
-        <v>246</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="F5" s="53" t="s">
-        <v>248</v>
-      </c>
-      <c r="G5" s="53" t="s">
-        <v>249</v>
-      </c>
-      <c r="H5" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="I5" s="53" t="s">
-        <v>250</v>
-      </c>
-      <c r="J5" s="53" t="s">
-        <v>251</v>
-      </c>
-      <c r="K5" s="53" t="s">
-        <v>252</v>
-      </c>
-      <c r="L5" s="53" t="s">
-        <v>253</v>
-      </c>
-      <c r="M5" s="53" t="s">
-        <v>254</v>
-      </c>
-      <c r="N5" s="53" t="s">
-        <v>255</v>
-      </c>
-      <c r="O5" s="53" t="s">
-        <v>256</v>
-      </c>
-      <c r="P5" s="53" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q5" s="53" t="s">
-        <v>258</v>
-      </c>
-      <c r="R5" s="53" t="s">
-        <v>259</v>
-      </c>
-      <c r="S5" s="53" t="s">
-        <v>260</v>
-      </c>
-      <c r="T5" s="53" t="s">
-        <v>261</v>
-      </c>
-      <c r="U5" s="53" t="s">
-        <v>262</v>
-      </c>
-      <c r="V5" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="W5" s="53" t="s">
-        <v>263</v>
-      </c>
-      <c r="X5" s="53" t="s">
-        <v>264</v>
-      </c>
-      <c r="Y5" s="53" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z5" s="53" t="s">
-        <v>266</v>
-      </c>
-      <c r="AA5" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="AB5" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC5" s="53" t="s">
-        <v>268</v>
-      </c>
-      <c r="AD5" s="53" t="s">
-        <v>269</v>
-      </c>
-      <c r="AE5" s="53" t="s">
-        <v>270</v>
-      </c>
-      <c r="AF5" s="53" t="s">
-        <v>271</v>
-      </c>
-      <c r="AG5" s="53" t="s">
-        <v>272</v>
-      </c>
-      <c r="AH5" s="53" t="s">
-        <v>273</v>
-      </c>
-      <c r="AI5" s="53" t="s">
-        <v>274</v>
-      </c>
-      <c r="AJ5" s="53" t="s">
-        <v>275</v>
-      </c>
-      <c r="AK5" s="53" t="s">
-        <v>276</v>
-      </c>
-      <c r="AL5" s="53" t="s">
-        <v>277</v>
-      </c>
-      <c r="AM5" s="53" t="s">
-        <v>278</v>
-      </c>
-      <c r="AN5" s="53" t="s">
-        <v>279</v>
-      </c>
-      <c r="AO5" s="53" t="s">
-        <v>280</v>
-      </c>
-      <c r="AP5" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="AQ5" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR5" s="53" t="s">
-        <v>282</v>
-      </c>
-      <c r="AS5" s="53" t="s">
-        <v>283</v>
-      </c>
-      <c r="AT5" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="AU5" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="AV5" s="53" t="s">
-        <v>228</v>
-      </c>
-      <c r="AW5" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="AX5" s="53" t="s">
-        <v>287</v>
-      </c>
-      <c r="AY5" s="53" t="s">
-        <v>288</v>
-      </c>
-      <c r="AZ5" s="53" t="s">
-        <v>289</v>
-      </c>
-      <c r="BA5" s="53" t="s">
-        <v>290</v>
-      </c>
-      <c r="BB5" s="53" t="s">
-        <v>291</v>
-      </c>
-      <c r="BC5" s="53" t="s">
-        <v>292</v>
-      </c>
-      <c r="BD5" s="53" t="s">
-        <v>293</v>
-      </c>
-      <c r="BE5" s="53" t="s">
-        <v>294</v>
-      </c>
-      <c r="BF5" s="53" t="s">
-        <v>295</v>
-      </c>
-      <c r="BG5" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="BH5" s="53" t="s">
-        <v>296</v>
-      </c>
-      <c r="BI5" s="53" t="s">
-        <v>297</v>
-      </c>
-      <c r="BJ5" s="53" t="s">
-        <v>298</v>
-      </c>
-      <c r="BK5" s="53" t="s">
-        <v>299</v>
+      <c r="BH5" s="57" t="s">
+        <v>332</v>
+      </c>
+      <c r="BI5" s="57" t="s">
+        <v>333</v>
+      </c>
+      <c r="BJ5" s="57" t="s">
+        <v>334</v>
+      </c>
+      <c r="BK5" s="57" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:63">
-      <c r="A6" s="53" t="s">
-        <v>300</v>
+      <c r="A6" s="57" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:63">
-      <c r="A7" s="53" t="s">
-        <v>301</v>
+      <c r="A7" s="57" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:63">
-      <c r="A8" s="53" t="s">
-        <v>302</v>
+      <c r="A8" s="57" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:63">
-      <c r="A9" s="53" t="s">
-        <v>303</v>
+      <c r="A9" s="57" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:63">
-      <c r="A10" s="53" t="s">
-        <v>304</v>
+      <c r="A10" s="57" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:63">
-      <c r="A11" s="53" t="s">
-        <v>305</v>
+      <c r="A11" s="57" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:63">
-      <c r="A12" s="53" t="s">
-        <v>306</v>
+      <c r="A12" s="57" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:63">
-      <c r="A13" s="53" t="s">
-        <v>307</v>
+      <c r="A13" s="57" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:63">
-      <c r="A14" s="53" t="s">
-        <v>308</v>
+      <c r="A14" s="57" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:63">
-      <c r="A15" s="53" t="s">
-        <v>309</v>
+      <c r="A15" s="57" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:63">
-      <c r="A16" s="53" t="s">
-        <v>310</v>
+      <c r="A16" s="57" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="53" t="s">
-        <v>311</v>
+      <c r="A17" s="57" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="53" t="s">
-        <v>312</v>
+      <c r="A18" s="57" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="53" t="s">
-        <v>313</v>
+      <c r="A19" s="57" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="53" t="s">
-        <v>314</v>
+      <c r="A20" s="57" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="53" t="s">
-        <v>315</v>
+      <c r="A21" s="57" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="53" t="s">
-        <v>316</v>
+      <c r="A22" s="57" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="53" t="s">
-        <v>317</v>
+      <c r="A23" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="53" t="s">
-        <v>318</v>
+      <c r="A24" s="57" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="53" t="s">
-        <v>319</v>
+      <c r="A25" s="57" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="53" t="s">
-        <v>320</v>
+      <c r="A26" s="57" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="53" t="s">
-        <v>321</v>
+      <c r="A27" s="57" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="53" t="s">
-        <v>322</v>
+      <c r="A28" s="57" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="53" t="s">
-        <v>323</v>
+      <c r="A29" s="57" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="53" t="s">
-        <v>324</v>
+      <c r="A30" s="57" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="53" t="s">
-        <v>325</v>
+      <c r="A31" s="57" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="53" t="s">
-        <v>326</v>
+      <c r="A32" s="57" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="53" t="s">
-        <v>327</v>
+      <c r="A33" s="57" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="53" t="s">
-        <v>328</v>
+      <c r="A34" s="57" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="53" t="s">
-        <v>329</v>
+      <c r="A35" s="57" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="53" t="s">
-        <v>330</v>
+      <c r="A36" s="57" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="53" t="s">
-        <v>331</v>
+      <c r="A37" s="57" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="53" t="s">
-        <v>332</v>
+      <c r="A38" s="57" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="53" t="s">
-        <v>333</v>
+      <c r="A39" s="57" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="53" t="s">
-        <v>334</v>
+      <c r="A40" s="57" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="53" t="s">
-        <v>335</v>
+      <c r="A41" s="57" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="53" t="s">
-        <v>336</v>
+      <c r="A42" s="57" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="53" t="s">
-        <v>337</v>
+      <c r="A43" s="57" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="53" t="s">
-        <v>338</v>
+      <c r="A44" s="57" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="53" t="s">
-        <v>339</v>
+      <c r="A45" s="57" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="53" t="s">
-        <v>340</v>
+      <c r="A46" s="57" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="53" t="s">
-        <v>341</v>
+      <c r="A47" s="57" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="53" t="s">
-        <v>342</v>
+      <c r="A48" s="57" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="53" t="s">
-        <v>343</v>
+      <c r="A49" s="57" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="53" t="s">
-        <v>344</v>
+      <c r="A50" s="57" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="53" t="s">
-        <v>345</v>
+      <c r="A51" s="57" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="53" t="s">
-        <v>346</v>
+      <c r="A52" s="57" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="53" t="s">
-        <v>347</v>
+      <c r="A53" s="57" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="53" t="s">
-        <v>348</v>
+      <c r="A54" s="57" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="53" t="s">
-        <v>349</v>
+      <c r="A55" s="57" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="53" t="s">
-        <v>350</v>
+      <c r="A56" s="57" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="53" t="s">
-        <v>351</v>
+      <c r="A57" s="57" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="53" t="s">
-        <v>352</v>
+      <c r="A58" s="57" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="53" t="s">
-        <v>353</v>
+      <c r="A59" s="57" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="53" t="s">
-        <v>354</v>
+      <c r="A60" s="57" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="53" t="s">
-        <v>355</v>
+      <c r="A61" s="57" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="53" t="s">
-        <v>356</v>
+      <c r="A62" s="57" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="53" t="s">
-        <v>357</v>
+      <c r="A63" s="57" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="53" t="s">
-        <v>358</v>
+      <c r="A64" s="57" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="53" t="s">
-        <v>359</v>
+      <c r="A65" s="57" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="53" t="s">
-        <v>360</v>
+      <c r="A66" s="57" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="53" t="s">
-        <v>361</v>
+      <c r="A67" s="57" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="53" t="s">
-        <v>362</v>
+      <c r="A68" s="57" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="53" t="s">
-        <v>363</v>
+      <c r="A69" s="57" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="53" t="s">
-        <v>364</v>
+      <c r="A70" s="57" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="53" t="s">
-        <v>365</v>
+      <c r="A71" s="57" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="53" t="s">
-        <v>366</v>
+      <c r="A72" s="57" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="53" t="s">
-        <v>367</v>
+      <c r="A73" s="57" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="53" t="s">
-        <v>368</v>
+      <c r="A74" s="57" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="53" t="s">
-        <v>369</v>
+      <c r="A75" s="57" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="53" t="s">
-        <v>370</v>
+      <c r="A76" s="57" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="53" t="s">
-        <v>371</v>
+      <c r="A77" s="57" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="53" t="s">
-        <v>372</v>
+      <c r="A78" s="57" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="53" t="s">
-        <v>373</v>
+      <c r="A79" s="57" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="53" t="s">
-        <v>374</v>
+      <c r="A80" s="57" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="53" t="s">
-        <v>375</v>
+      <c r="A81" s="57" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="53" t="s">
-        <v>376</v>
+      <c r="A82" s="57" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="53" t="s">
-        <v>377</v>
+      <c r="A83" s="57" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="53" t="s">
-        <v>378</v>
+      <c r="A84" s="57" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="53" t="s">
-        <v>379</v>
+      <c r="A85" s="57" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="53" t="s">
-        <v>380</v>
+      <c r="A86" s="57" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="53" t="s">
-        <v>381</v>
+      <c r="A87" s="57" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="53" t="s">
-        <v>382</v>
+      <c r="A88" s="57" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="53" t="s">
-        <v>383</v>
+      <c r="A89" s="57" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="53" t="s">
-        <v>384</v>
+      <c r="A90" s="57" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="53" t="s">
-        <v>385</v>
+      <c r="A91" s="57" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="53" t="s">
-        <v>386</v>
+      <c r="A92" s="57" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="53" t="s">
-        <v>387</v>
+      <c r="A93" s="57" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="53" t="s">
-        <v>388</v>
+      <c r="A94" s="57" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="53" t="s">
-        <v>389</v>
+      <c r="A95" s="57" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="53" t="s">
-        <v>390</v>
+      <c r="A96" s="57" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="53" t="s">
-        <v>391</v>
+      <c r="A97" s="57" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="53" t="s">
-        <v>392</v>
+      <c r="A98" s="57" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="53" t="s">
-        <v>393</v>
+      <c r="A99" s="57" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="53" t="s">
-        <v>394</v>
+      <c r="A100" s="57" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="53" t="s">
-        <v>395</v>
+      <c r="A101" s="57" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="53" t="s">
-        <v>396</v>
+      <c r="A102" s="57" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="53" t="s">
-        <v>397</v>
+      <c r="A103" s="57" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="53" t="s">
-        <v>398</v>
+      <c r="A104" s="57" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="53" t="s">
-        <v>399</v>
+      <c r="A105" s="57" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="53" t="s">
-        <v>400</v>
+      <c r="A106" s="57" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="53" t="s">
-        <v>401</v>
+      <c r="A107" s="57" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="53" t="s">
-        <v>402</v>
+      <c r="A108" s="57" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="53" t="s">
-        <v>403</v>
+      <c r="A109" s="57" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="53" t="s">
-        <v>404</v>
+      <c r="A110" s="57" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="53" t="s">
-        <v>405</v>
+      <c r="A111" s="57" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="53" t="s">
-        <v>406</v>
+      <c r="A112" s="57" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="53" t="s">
-        <v>407</v>
+      <c r="A113" s="57" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="53" t="s">
-        <v>408</v>
+      <c r="A114" s="57" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="53" t="s">
-        <v>409</v>
+      <c r="A115" s="57" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="53" t="s">
-        <v>410</v>
+      <c r="A116" s="57" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="53" t="s">
-        <v>411</v>
+      <c r="A117" s="57" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="53" t="s">
-        <v>412</v>
+      <c r="A118" s="57" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="53" t="s">
-        <v>413</v>
+      <c r="A119" s="57" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="53" t="s">
-        <v>414</v>
+      <c r="A120" s="57" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="53" t="s">
-        <v>415</v>
+      <c r="A121" s="57" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="53" t="s">
-        <v>416</v>
+      <c r="A122" s="57" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="53" t="s">
-        <v>417</v>
+      <c r="A123" s="57" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="53" t="s">
-        <v>418</v>
+      <c r="A124" s="57" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="53" t="s">
-        <v>419</v>
+      <c r="A125" s="57" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="53" t="s">
-        <v>420</v>
+      <c r="A126" s="57" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="53" t="s">
-        <v>421</v>
+      <c r="A127" s="57" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="53" t="s">
-        <v>422</v>
+      <c r="A128" s="57" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="53" t="s">
-        <v>423</v>
+      <c r="A129" s="57" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="53" t="s">
-        <v>424</v>
+      <c r="A130" s="57" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="53" t="s">
-        <v>425</v>
+      <c r="A131" s="57" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="53" t="s">
-        <v>426</v>
+      <c r="A132" s="57" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="53" t="s">
-        <v>427</v>
+      <c r="A133" s="57" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="53" t="s">
-        <v>428</v>
+      <c r="A134" s="57" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="53" t="s">
-        <v>429</v>
+      <c r="A135" s="57" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="53" t="s">
-        <v>430</v>
+      <c r="A136" s="57" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="53" t="s">
-        <v>431</v>
+      <c r="A137" s="57" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="53" t="s">
-        <v>432</v>
+      <c r="A138" s="57" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="53" t="s">
-        <v>433</v>
+      <c r="A139" s="57" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="53" t="s">
-        <v>434</v>
+      <c r="A140" s="57" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="53" t="s">
-        <v>435</v>
+      <c r="A141" s="57" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="53" t="s">
-        <v>436</v>
+      <c r="A142" s="57" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="53" t="s">
-        <v>437</v>
+      <c r="A143" s="57" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="53" t="s">
-        <v>438</v>
+      <c r="A144" s="57" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="53" t="s">
-        <v>439</v>
+      <c r="A145" s="57" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="53" t="s">
-        <v>440</v>
+      <c r="A146" s="57" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="53" t="s">
-        <v>441</v>
+      <c r="A147" s="57" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="53" t="s">
-        <v>442</v>
+      <c r="A148" s="57" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="53" t="s">
-        <v>443</v>
+      <c r="A149" s="57" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="53" t="s">
-        <v>444</v>
+      <c r="A150" s="57" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="53" t="s">
-        <v>445</v>
+      <c r="A151" s="57" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="53" t="s">
-        <v>446</v>
+      <c r="A152" s="57" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="53" t="s">
-        <v>447</v>
+      <c r="A153" s="57" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -15,15 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="483">
   <si>
     <t>_de</t>
   </si>
   <si>
     <t>deutsch</t>
-  </si>
-  <si>
-    <t>Euro</t>
   </si>
   <si>
     <t xml:space="preserve">1. </t>
@@ -1545,7 +1542,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1799,11 +1796,84 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1970,17 +2040,53 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2431,12 +2537,12 @@
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="39">
-        <f>D8</f>
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>0</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="39">
-        <f>F8</f>
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>0</v>
       </c>
       <c r="G9" s="8"/>
@@ -2467,16 +2573,18 @@
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="34">
-        <f>B18</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="Q11" s="34">
-        <f>B18</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="2"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="54"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="53"/>
+      <c r="T11" s="53"/>
+      <c r="U11" s="53"/>
+      <c r="V11" s="54"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="43">
@@ -2489,6 +2597,18 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="11"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="56"/>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="56"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="44">
@@ -2501,36 +2621,18 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="11"/>
-      <c r="L13" s="45">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="N13" s="45">
-        <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="45">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="S13" s="45">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="T13" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="U13" s="45">
-        <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="45">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
-        <v>0</v>
-      </c>
+      <c r="J13" s="55"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="56"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="56"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="25"/>
@@ -2540,31 +2642,31 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="11"/>
-      <c r="J14" s="52" t="s">
+      <c r="J14" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="58">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="59"/>
+      <c r="M14" s="60"/>
+      <c r="N14" s="60"/>
+      <c r="O14" s="61">
+        <f>IF(M14="","",N14/M14)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="53">
+      <c r="R14" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L14" s="54"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="56">
-        <f>IF(M14="","",N14/M14)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="52" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="53">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="S14" s="54"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="55"/>
-      <c r="V14" s="56">
+      <c r="S14" s="59"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="61">
         <f>IF(T14="","",U14/T14)</f>
         <v>0</v>
       </c>
@@ -2582,31 +2684,31 @@
       <c r="F15" s="27"/>
       <c r="G15" s="28"/>
       <c r="H15" s="29"/>
-      <c r="J15" s="52" t="s">
+      <c r="J15" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="K15" s="58">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+      <c r="N15" s="60"/>
+      <c r="O15" s="61">
+        <f>IF(M15="","",N15/M15)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="53">
+      <c r="R15" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L15" s="54"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="56">
-        <f>IF(M15="","",N15/M15)</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="R15" s="53">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="S15" s="54"/>
-      <c r="T15" s="55"/>
-      <c r="U15" s="55"/>
-      <c r="V15" s="56">
+      <c r="S15" s="59"/>
+      <c r="T15" s="60"/>
+      <c r="U15" s="60"/>
+      <c r="V15" s="61">
         <f>IF(T15="","",U15/T15)</f>
         <v>0</v>
       </c>
@@ -2627,31 +2729,31 @@
         <v>0</v>
       </c>
       <c r="H16" s="29"/>
-      <c r="J16" s="52" t="s">
+      <c r="J16" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="58">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="59"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="61">
+        <f>IF(M16="","",N16/M16)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="53">
+      <c r="R16" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L16" s="54"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="56">
-        <f>IF(M16="","",N16/M16)</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="52" t="s">
-        <v>8</v>
-      </c>
-      <c r="R16" s="53">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="S16" s="54"/>
-      <c r="T16" s="55"/>
-      <c r="U16" s="55"/>
-      <c r="V16" s="56">
+      <c r="S16" s="59"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="61">
         <f>IF(T16="","",U16/T16)</f>
         <v>0</v>
       </c>
@@ -2672,31 +2774,31 @@
         <v>0</v>
       </c>
       <c r="H17" s="29"/>
-      <c r="J17" s="52" t="s">
+      <c r="J17" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="58">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="59"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="61">
+        <f>IF(M17="","",N17/M17)</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="K17" s="53">
+      <c r="R17" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L17" s="54"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="56">
-        <f>IF(M17="","",N17/M17)</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="R17" s="53">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="S17" s="54"/>
-      <c r="T17" s="55"/>
-      <c r="U17" s="55"/>
-      <c r="V17" s="56">
+      <c r="S17" s="59"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="61">
         <f>IF(T17="","",U17/T17)</f>
         <v>0</v>
       </c>
@@ -2717,31 +2819,31 @@
         <v>0</v>
       </c>
       <c r="H18" s="29"/>
-      <c r="J18" s="52" t="s">
+      <c r="J18" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="58">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="59"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="61">
+        <f>IF(M18="","",N18/M18)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="53">
+      <c r="R18" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L18" s="54"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="56">
-        <f>IF(M18="","",N18/M18)</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="R18" s="53">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="54"/>
-      <c r="T18" s="55"/>
-      <c r="U18" s="55"/>
-      <c r="V18" s="56">
+      <c r="S18" s="59"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="61">
         <f>IF(T18="","",U18/T18)</f>
         <v>0</v>
       </c>
@@ -2762,31 +2864,31 @@
         <v>0</v>
       </c>
       <c r="H19" s="29"/>
-      <c r="J19" s="52" t="s">
+      <c r="J19" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="58">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="59"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="61">
+        <f>IF(M19="","",N19/M19)</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="53">
+      <c r="R19" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L19" s="54"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="56">
-        <f>IF(M19="","",N19/M19)</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="R19" s="53">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="54"/>
-      <c r="T19" s="55"/>
-      <c r="U19" s="55"/>
-      <c r="V19" s="56">
+      <c r="S19" s="59"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="61">
         <f>IF(T19="","",U19/T19)</f>
         <v>0</v>
       </c>
@@ -2814,361 +2916,361 @@
         <v>0</v>
       </c>
       <c r="H20" s="30"/>
-      <c r="J20" s="52" t="s">
+      <c r="J20" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20" s="58">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="59"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="61">
+        <f>IF(M20="","",N20/M20)</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="K20" s="53">
+      <c r="R20" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L20" s="54"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="56">
-        <f>IF(M20="","",N20/M20)</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="52" t="s">
+      <c r="S20" s="59"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="61">
+        <f>IF(T20="","",U20/T20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="J21" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="R20" s="53">
+      <c r="K21" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S20" s="54"/>
-      <c r="T20" s="55"/>
-      <c r="U20" s="55"/>
-      <c r="V20" s="56">
-        <f>IF(T20="","",U20/T20)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:22">
-      <c r="J21" s="52" t="s">
+      <c r="L21" s="59"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="61">
+        <f>IF(M21="","",N21/M21)</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="K21" s="53">
+      <c r="R21" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L21" s="54"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="56">
-        <f>IF(M21="","",N21/M21)</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="52" t="s">
+      <c r="S21" s="59"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="61">
+        <f>IF(T21="","",U21/T21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="J22" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="R21" s="53">
+      <c r="K22" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S21" s="54"/>
-      <c r="T21" s="55"/>
-      <c r="U21" s="55"/>
-      <c r="V21" s="56">
-        <f>IF(T21="","",U21/T21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:22">
-      <c r="J22" s="52" t="s">
+      <c r="L22" s="59"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="61">
+        <f>IF(M22="","",N22/M22)</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="K22" s="53">
+      <c r="R22" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L22" s="54"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="56">
-        <f>IF(M22="","",N22/M22)</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="52" t="s">
+      <c r="S22" s="59"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="61">
+        <f>IF(T22="","",U22/T22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="J23" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="R22" s="53">
+      <c r="K23" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S22" s="54"/>
-      <c r="T22" s="55"/>
-      <c r="U22" s="55"/>
-      <c r="V22" s="56">
-        <f>IF(T22="","",U22/T22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:22">
-      <c r="J23" s="52" t="s">
+      <c r="L23" s="59"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="61">
+        <f>IF(M23="","",N23/M23)</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="K23" s="53">
+      <c r="R23" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L23" s="54"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="56">
-        <f>IF(M23="","",N23/M23)</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="52" t="s">
+      <c r="S23" s="59"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="61">
+        <f>IF(T23="","",U23/T23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="J24" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="R23" s="53">
+      <c r="K24" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S23" s="54"/>
-      <c r="T23" s="55"/>
-      <c r="U23" s="55"/>
-      <c r="V23" s="56">
-        <f>IF(T23="","",U23/T23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:22">
-      <c r="J24" s="52" t="s">
+      <c r="L24" s="59"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="61">
+        <f>IF(M24="","",N24/M24)</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="K24" s="53">
+      <c r="R24" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L24" s="54"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="56">
-        <f>IF(M24="","",N24/M24)</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="52" t="s">
+      <c r="S24" s="59"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="61">
+        <f>IF(T24="","",U24/T24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="J25" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="R24" s="53">
+      <c r="K25" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S24" s="54"/>
-      <c r="T24" s="55"/>
-      <c r="U24" s="55"/>
-      <c r="V24" s="56">
-        <f>IF(T24="","",U24/T24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:22">
-      <c r="J25" s="52" t="s">
+      <c r="L25" s="59"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="61">
+        <f>IF(M25="","",N25/M25)</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="53">
+      <c r="R25" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L25" s="54"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="56">
-        <f>IF(M25="","",N25/M25)</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="52" t="s">
+      <c r="S25" s="59"/>
+      <c r="T25" s="60"/>
+      <c r="U25" s="60"/>
+      <c r="V25" s="61">
+        <f>IF(T25="","",U25/T25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="J26" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="R25" s="53">
+      <c r="K26" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S25" s="54"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="55"/>
-      <c r="V25" s="56">
-        <f>IF(T25="","",U25/T25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:22">
-      <c r="J26" s="52" t="s">
+      <c r="L26" s="59"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="61">
+        <f>IF(M26="","",N26/M26)</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="K26" s="53">
+      <c r="R26" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L26" s="54"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="56">
-        <f>IF(M26="","",N26/M26)</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="52" t="s">
+      <c r="S26" s="59"/>
+      <c r="T26" s="60"/>
+      <c r="U26" s="60"/>
+      <c r="V26" s="61">
+        <f>IF(T26="","",U26/T26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="J27" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="R26" s="53">
+      <c r="K27" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S26" s="54"/>
-      <c r="T26" s="55"/>
-      <c r="U26" s="55"/>
-      <c r="V26" s="56">
-        <f>IF(T26="","",U26/T26)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:22">
-      <c r="J27" s="52" t="s">
+      <c r="L27" s="59"/>
+      <c r="M27" s="60"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="61">
+        <f>IF(M27="","",N27/M27)</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="K27" s="53">
+      <c r="R27" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L27" s="54"/>
-      <c r="M27" s="55"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="56">
-        <f>IF(M27="","",N27/M27)</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="52" t="s">
+      <c r="S27" s="59"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="60"/>
+      <c r="V27" s="61">
+        <f>IF(T27="","",U27/T27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="J28" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="R27" s="53">
+      <c r="K28" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S27" s="54"/>
-      <c r="T27" s="55"/>
-      <c r="U27" s="55"/>
-      <c r="V27" s="56">
-        <f>IF(T27="","",U27/T27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:22">
-      <c r="J28" s="52" t="s">
+      <c r="L28" s="59"/>
+      <c r="M28" s="60"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="61">
+        <f>IF(M28="","",N28/M28)</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="K28" s="53">
+      <c r="R28" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="54"/>
-      <c r="M28" s="55"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="56">
-        <f>IF(M28="","",N28/M28)</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="52" t="s">
+      <c r="S28" s="59"/>
+      <c r="T28" s="60"/>
+      <c r="U28" s="60"/>
+      <c r="V28" s="61">
+        <f>IF(T28="","",U28/T28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22">
+      <c r="J29" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="R28" s="53">
+      <c r="K29" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S28" s="54"/>
-      <c r="T28" s="55"/>
-      <c r="U28" s="55"/>
-      <c r="V28" s="56">
-        <f>IF(T28="","",U28/T28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:22">
-      <c r="J29" s="52" t="s">
+      <c r="L29" s="59"/>
+      <c r="M29" s="60"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="61">
+        <f>IF(M29="","",N29/M29)</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="K29" s="53">
+      <c r="R29" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L29" s="54"/>
-      <c r="M29" s="55"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="56">
-        <f>IF(M29="","",N29/M29)</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="52" t="s">
+      <c r="S29" s="59"/>
+      <c r="T29" s="60"/>
+      <c r="U29" s="60"/>
+      <c r="V29" s="61">
+        <f>IF(T29="","",U29/T29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22">
+      <c r="J30" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="R29" s="53">
+      <c r="K30" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S29" s="54"/>
-      <c r="T29" s="55"/>
-      <c r="U29" s="55"/>
-      <c r="V29" s="56">
-        <f>IF(T29="","",U29/T29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:22">
-      <c r="J30" s="52" t="s">
+      <c r="L30" s="59"/>
+      <c r="M30" s="60"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="61">
+        <f>IF(M30="","",N30/M30)</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="K30" s="53">
+      <c r="R30" s="58">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L30" s="54"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="56">
-        <f>IF(M30="","",N30/M30)</f>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="52" t="s">
+      <c r="S30" s="59"/>
+      <c r="T30" s="60"/>
+      <c r="U30" s="60"/>
+      <c r="V30" s="61">
+        <f>IF(T30="","",U30/T30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22">
+      <c r="J31" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="R30" s="53">
+      <c r="K31" s="63">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S30" s="54"/>
-      <c r="T30" s="55"/>
-      <c r="U30" s="55"/>
-      <c r="V30" s="56">
-        <f>IF(T30="","",U30/T30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:22">
-      <c r="J31" s="52" t="s">
+      <c r="L31" s="64"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="65"/>
+      <c r="O31" s="66">
+        <f>IF(M31="","",N31/M31)</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="K31" s="53">
+      <c r="R31" s="63">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L31" s="54"/>
-      <c r="M31" s="55"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="56">
-        <f>IF(M31="","",N31/M31)</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="R31" s="53">
-        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="S31" s="54"/>
-      <c r="T31" s="55"/>
-      <c r="U31" s="55"/>
-      <c r="V31" s="56">
+      <c r="S31" s="64"/>
+      <c r="T31" s="65"/>
+      <c r="U31" s="65"/>
+      <c r="V31" s="66">
         <f>IF(T31="","",U31/T31)</f>
         <v>0</v>
       </c>
@@ -3222,1698 +3324,1698 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:63">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="57" t="s">
+      <c r="D1" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="E1" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="F1" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="57" t="s">
+      <c r="G1" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="57" t="s">
+      <c r="H1" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="57" t="s">
+      <c r="I1" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="57" t="s">
+      <c r="J1" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="57" t="s">
+      <c r="K1" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="57" t="s">
+      <c r="L1" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="L1" s="57" t="s">
+      <c r="M1" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="57" t="s">
+      <c r="N1" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="N1" s="57" t="s">
+      <c r="O1" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="O1" s="57" t="s">
+      <c r="P1" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="P1" s="57" t="s">
+      <c r="Q1" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="57" t="s">
+      <c r="R1" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="R1" s="57" t="s">
+      <c r="S1" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="S1" s="57" t="s">
+      <c r="T1" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="T1" s="57" t="s">
+      <c r="U1" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="U1" s="57" t="s">
+      <c r="V1" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="V1" s="57" t="s">
+      <c r="W1" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="W1" s="57" t="s">
+      <c r="X1" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="X1" s="57" t="s">
+      <c r="Y1" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="Y1" s="57" t="s">
+      <c r="Z1" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="Z1" s="57" t="s">
+      <c r="AA1" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="AA1" s="57" t="s">
+      <c r="AB1" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="AB1" s="57" t="s">
+      <c r="AC1" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="57" t="s">
+      <c r="AD1" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="AD1" s="57" t="s">
+      <c r="AE1" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="AE1" s="57" t="s">
+      <c r="AF1" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="AF1" s="57" t="s">
+      <c r="AG1" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="AG1" s="57" t="s">
+      <c r="AH1" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="AH1" s="57" t="s">
+      <c r="AI1" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="AI1" s="57" t="s">
+      <c r="AJ1" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="AJ1" s="57" t="s">
+      <c r="AK1" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="AK1" s="57" t="s">
+      <c r="AL1" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="AL1" s="57" t="s">
+      <c r="AM1" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="AM1" s="57" t="s">
+      <c r="AN1" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="AN1" s="57" t="s">
+      <c r="AO1" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="AO1" s="57" t="s">
+      <c r="AP1" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="AP1" s="57" t="s">
+      <c r="AQ1" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="AQ1" s="57" t="s">
+      <c r="AR1" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="AR1" s="57" t="s">
+      <c r="AS1" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="AS1" s="57" t="s">
+      <c r="AT1" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="AT1" s="57" t="s">
+      <c r="AU1" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="AU1" s="57" t="s">
+      <c r="AV1" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="AV1" s="57" t="s">
+      <c r="AW1" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="AW1" s="57" t="s">
+      <c r="AX1" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AX1" s="57" t="s">
+      <c r="AY1" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AY1" s="57" t="s">
+      <c r="AZ1" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="AZ1" s="57" t="s">
+      <c r="BA1" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="BA1" s="57" t="s">
+      <c r="BB1" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="BB1" s="57" t="s">
+      <c r="BC1" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="BC1" s="57" t="s">
+      <c r="BD1" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="BD1" s="57" t="s">
+      <c r="BE1" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="BE1" s="57" t="s">
+      <c r="BF1" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="BF1" s="57" t="s">
+      <c r="BG1" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="BG1" s="57" t="s">
+      <c r="BH1" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="BH1" s="57" t="s">
+      <c r="BI1" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="BI1" s="57" t="s">
+      <c r="BJ1" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="BJ1" s="57" t="s">
+      <c r="BK1" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="BK1" s="57" t="s">
+    </row>
+    <row r="2" spans="1:63">
+      <c r="A2" s="67" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" spans="1:63">
-      <c r="A2" s="57" t="s">
+      <c r="B2" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="C2" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="D2" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="E2" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="F2" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="G2" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="H2" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="I2" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="J2" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="57" t="s">
+      <c r="K2" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="L2" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="L2" s="57" t="s">
+      <c r="M2" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="M2" s="57" t="s">
+      <c r="N2" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="N2" s="57" t="s">
+      <c r="O2" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="57" t="s">
+      <c r="P2" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="P2" s="57" t="s">
+      <c r="Q2" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="Q2" s="57" t="s">
+      <c r="R2" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="R2" s="57" t="s">
+      <c r="S2" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="S2" s="57" t="s">
+      <c r="T2" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="T2" s="57" t="s">
+      <c r="U2" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="U2" s="57" t="s">
+      <c r="V2" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="V2" s="57" t="s">
+      <c r="W2" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="W2" s="57" t="s">
+      <c r="X2" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="X2" s="57" t="s">
+      <c r="Y2" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="57" t="s">
+      <c r="Z2" s="67" t="s">
         <v>125</v>
       </c>
-      <c r="Z2" s="57" t="s">
+      <c r="AA2" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="AA2" s="57" t="s">
+      <c r="AB2" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="AB2" s="57" t="s">
+      <c r="AC2" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="AC2" s="57" t="s">
+      <c r="AD2" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="AD2" s="57" t="s">
+      <c r="AE2" s="67" t="s">
         <v>130</v>
       </c>
-      <c r="AE2" s="57" t="s">
+      <c r="AF2" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="AF2" s="57" t="s">
+      <c r="AG2" s="67" t="s">
         <v>132</v>
       </c>
-      <c r="AG2" s="57" t="s">
+      <c r="AH2" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="AH2" s="57" t="s">
+      <c r="AI2" s="67" t="s">
         <v>134</v>
       </c>
-      <c r="AI2" s="57" t="s">
+      <c r="AJ2" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="AJ2" s="57" t="s">
+      <c r="AK2" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="AK2" s="57" t="s">
+      <c r="AL2" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="57" t="s">
+      <c r="AM2" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="AM2" s="57" t="s">
+      <c r="AN2" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="AN2" s="57" t="s">
+      <c r="AO2" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP2" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="AO2" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="AP2" s="57" t="s">
+      <c r="AQ2" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR2" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AQ2" s="57" t="s">
+      <c r="AS2" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="AT2" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="AU2" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="AV2" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW2" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX2" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="AY2" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="AZ2" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="BA2" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="BB2" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="BC2" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="BD2" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="BE2" s="67" t="s">
+        <v>153</v>
+      </c>
+      <c r="BF2" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="BG2" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="BH2" s="67" t="s">
+        <v>156</v>
+      </c>
+      <c r="BI2" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="BJ2" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="BK2" s="67" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:63">
+      <c r="A3" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="H3" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="I3" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="J3" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="K3" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="L3" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="M3" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="N3" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="O3" s="67" t="s">
+        <v>173</v>
+      </c>
+      <c r="P3" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q3" s="67" t="s">
+        <v>175</v>
+      </c>
+      <c r="R3" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="S3" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="T3" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="U3" s="67" t="s">
+        <v>179</v>
+      </c>
+      <c r="V3" s="67" t="s">
+        <v>180</v>
+      </c>
+      <c r="W3" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="AR2" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS2" s="57" t="s">
-        <v>143</v>
-      </c>
-      <c r="AT2" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="AU2" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="AV2" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW2" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="AX2" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="AY2" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="AZ2" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="BA2" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="BB2" s="57" t="s">
-        <v>151</v>
-      </c>
-      <c r="BC2" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="BD2" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="BE2" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="BF2" s="57" t="s">
-        <v>155</v>
-      </c>
-      <c r="BG2" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="BH2" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="BI2" s="57" t="s">
-        <v>158</v>
-      </c>
-      <c r="BJ2" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="BK2" s="57" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:63">
-      <c r="A3" s="57" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="57" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="G3" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="57" t="s">
-        <v>168</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>168</v>
-      </c>
-      <c r="J3" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="K3" s="57" t="s">
-        <v>170</v>
-      </c>
-      <c r="L3" s="57" t="s">
-        <v>171</v>
-      </c>
-      <c r="M3" s="57" t="s">
-        <v>172</v>
-      </c>
-      <c r="N3" s="57" t="s">
-        <v>173</v>
-      </c>
-      <c r="O3" s="57" t="s">
-        <v>174</v>
-      </c>
-      <c r="P3" s="57" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q3" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="R3" s="57" t="s">
-        <v>177</v>
-      </c>
-      <c r="S3" s="57" t="s">
-        <v>178</v>
-      </c>
-      <c r="T3" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="U3" s="57" t="s">
+      <c r="X3" s="67" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y3" s="67" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z3" s="67" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA3" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB3" s="67" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC3" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD3" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="AE3" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="AF3" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="AG3" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="AH3" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="AI3" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="AJ3" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="AK3" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="AL3" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="AM3" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN3" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO3" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP3" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ3" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="V3" s="57" t="s">
-        <v>181</v>
-      </c>
-      <c r="W3" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="X3" s="57" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y3" s="57" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z3" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA3" s="57" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB3" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="AC3" s="57" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD3" s="57" t="s">
-        <v>188</v>
-      </c>
-      <c r="AE3" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="AF3" s="57" t="s">
-        <v>190</v>
-      </c>
-      <c r="AG3" s="57" t="s">
-        <v>191</v>
-      </c>
-      <c r="AH3" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="AI3" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="AJ3" s="57" t="s">
-        <v>194</v>
-      </c>
-      <c r="AK3" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="AL3" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="AM3" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="AN3" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="AO3" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="AP3" s="57" t="s">
+      <c r="AR3" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="AQ3" s="57" t="s">
-        <v>181</v>
-      </c>
-      <c r="AR3" s="57" t="s">
+      <c r="AS3" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="AS3" s="57" t="s">
+      <c r="AT3" s="67" t="s">
         <v>200</v>
       </c>
-      <c r="AT3" s="57" t="s">
+      <c r="AU3" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="AU3" s="57" t="s">
+      <c r="AV3" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="AV3" s="57" t="s">
+      <c r="AW3" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="AW3" s="57" t="s">
+      <c r="AX3" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="AX3" s="57" t="s">
+      <c r="AY3" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="AY3" s="57" t="s">
+      <c r="AZ3" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="AZ3" s="57" t="s">
+      <c r="BA3" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="BA3" s="57" t="s">
+      <c r="BB3" s="67" t="s">
         <v>208</v>
       </c>
-      <c r="BB3" s="57" t="s">
+      <c r="BC3" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="BC3" s="57" t="s">
+      <c r="BD3" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="BD3" s="57" t="s">
+      <c r="BE3" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="BE3" s="57" t="s">
+      <c r="BF3" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="BF3" s="57" t="s">
+      <c r="BG3" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="BG3" s="57" t="s">
+      <c r="BH3" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="BH3" s="57" t="s">
+      <c r="BI3" s="67" t="s">
         <v>215</v>
       </c>
-      <c r="BI3" s="57" t="s">
+      <c r="BJ3" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="BJ3" s="57" t="s">
+      <c r="BK3" s="67" t="s">
         <v>217</v>
       </c>
-      <c r="BK3" s="57" t="s">
+    </row>
+    <row r="4" spans="1:63">
+      <c r="A4" s="67" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="4" spans="1:63">
-      <c r="A4" s="57" t="s">
+      <c r="B4" s="67" t="s">
         <v>219</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="C4" s="67" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="D4" s="67" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="E4" s="67" t="s">
         <v>222</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="F4" s="67" t="s">
         <v>223</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="G4" s="67" t="s">
         <v>224</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="H4" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="H4" s="57" t="s">
+      <c r="I4" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="I4" s="57" t="s">
+      <c r="J4" s="67" t="s">
         <v>227</v>
       </c>
-      <c r="J4" s="57" t="s">
+      <c r="K4" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="K4" s="57" t="s">
+      <c r="L4" s="67" t="s">
         <v>229</v>
       </c>
-      <c r="L4" s="57" t="s">
+      <c r="M4" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="M4" s="57" t="s">
+      <c r="N4" s="67" t="s">
         <v>231</v>
       </c>
-      <c r="N4" s="57" t="s">
+      <c r="O4" s="67" t="s">
         <v>232</v>
       </c>
-      <c r="O4" s="57" t="s">
+      <c r="P4" s="67" t="s">
         <v>233</v>
       </c>
-      <c r="P4" s="57" t="s">
+      <c r="Q4" s="67" t="s">
         <v>234</v>
       </c>
-      <c r="Q4" s="57" t="s">
+      <c r="R4" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="R4" s="57" t="s">
+      <c r="S4" s="67" t="s">
         <v>236</v>
       </c>
-      <c r="S4" s="57" t="s">
+      <c r="T4" s="67" t="s">
         <v>237</v>
       </c>
-      <c r="T4" s="57" t="s">
+      <c r="U4" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="U4" s="57" t="s">
+      <c r="V4" s="67" t="s">
+        <v>180</v>
+      </c>
+      <c r="W4" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="V4" s="57" t="s">
-        <v>181</v>
-      </c>
-      <c r="W4" s="57" t="s">
+      <c r="X4" s="67" t="s">
         <v>240</v>
       </c>
-      <c r="X4" s="57" t="s">
+      <c r="Y4" s="67" t="s">
         <v>241</v>
       </c>
-      <c r="Y4" s="57" t="s">
+      <c r="Z4" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="Z4" s="57" t="s">
+      <c r="AA4" s="67" t="s">
         <v>243</v>
       </c>
-      <c r="AA4" s="57" t="s">
+      <c r="AB4" s="67" t="s">
         <v>244</v>
       </c>
-      <c r="AB4" s="57" t="s">
+      <c r="AC4" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="AC4" s="57" t="s">
+      <c r="AD4" s="67" t="s">
         <v>246</v>
       </c>
-      <c r="AD4" s="57" t="s">
+      <c r="AE4" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="AE4" s="57" t="s">
+      <c r="AF4" s="67" t="s">
         <v>248</v>
       </c>
-      <c r="AF4" s="57" t="s">
+      <c r="AG4" s="67" t="s">
         <v>249</v>
       </c>
-      <c r="AG4" s="57" t="s">
+      <c r="AH4" s="67" t="s">
         <v>250</v>
       </c>
-      <c r="AH4" s="57" t="s">
+      <c r="AI4" s="67" t="s">
         <v>251</v>
       </c>
-      <c r="AI4" s="57" t="s">
+      <c r="AJ4" s="67" t="s">
         <v>252</v>
       </c>
-      <c r="AJ4" s="57" t="s">
+      <c r="AK4" s="67" t="s">
         <v>253</v>
       </c>
-      <c r="AK4" s="57" t="s">
+      <c r="AL4" s="67" t="s">
         <v>254</v>
       </c>
-      <c r="AL4" s="57" t="s">
+      <c r="AM4" s="67" t="s">
         <v>255</v>
       </c>
-      <c r="AM4" s="57" t="s">
+      <c r="AN4" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="AN4" s="57" t="s">
+      <c r="AO4" s="67" t="s">
         <v>257</v>
       </c>
-      <c r="AO4" s="57" t="s">
+      <c r="AP4" s="67" t="s">
         <v>258</v>
       </c>
-      <c r="AP4" s="57" t="s">
+      <c r="AQ4" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR4" s="67" t="s">
         <v>259</v>
       </c>
-      <c r="AQ4" s="57" t="s">
-        <v>122</v>
-      </c>
-      <c r="AR4" s="57" t="s">
+      <c r="AS4" s="67" t="s">
         <v>260</v>
       </c>
-      <c r="AS4" s="57" t="s">
+      <c r="AT4" s="67" t="s">
         <v>261</v>
       </c>
-      <c r="AT4" s="57" t="s">
+      <c r="AU4" s="67" t="s">
         <v>262</v>
       </c>
-      <c r="AU4" s="57" t="s">
+      <c r="AV4" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="AV4" s="57" t="s">
+      <c r="AW4" s="67" t="s">
         <v>264</v>
       </c>
-      <c r="AW4" s="57" t="s">
+      <c r="AX4" s="67" t="s">
         <v>265</v>
       </c>
-      <c r="AX4" s="57" t="s">
+      <c r="AY4" s="67" t="s">
         <v>266</v>
       </c>
-      <c r="AY4" s="57" t="s">
+      <c r="AZ4" s="67" t="s">
         <v>267</v>
       </c>
-      <c r="AZ4" s="57" t="s">
+      <c r="BA4" s="67" t="s">
         <v>268</v>
       </c>
-      <c r="BA4" s="57" t="s">
+      <c r="BB4" s="67" t="s">
         <v>269</v>
       </c>
-      <c r="BB4" s="57" t="s">
+      <c r="BC4" s="67" t="s">
         <v>270</v>
       </c>
-      <c r="BC4" s="57" t="s">
+      <c r="BD4" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="BD4" s="57" t="s">
+      <c r="BE4" s="67" t="s">
         <v>272</v>
       </c>
-      <c r="BE4" s="57" t="s">
+      <c r="BF4" s="67" t="s">
         <v>273</v>
       </c>
-      <c r="BF4" s="57" t="s">
+      <c r="BG4" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="BH4" s="67" t="s">
         <v>274</v>
       </c>
-      <c r="BG4" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="BH4" s="57" t="s">
+      <c r="BI4" s="67" t="s">
         <v>275</v>
       </c>
-      <c r="BI4" s="57" t="s">
+      <c r="BJ4" s="67" t="s">
         <v>276</v>
       </c>
-      <c r="BJ4" s="57" t="s">
+      <c r="BK4" s="67" t="s">
         <v>277</v>
       </c>
-      <c r="BK4" s="57" t="s">
+    </row>
+    <row r="5" spans="1:63">
+      <c r="A5" s="67" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="5" spans="1:63">
-      <c r="A5" s="57" t="s">
+      <c r="B5" s="67" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="C5" s="67" t="s">
         <v>280</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="D5" s="67" t="s">
         <v>281</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="E5" s="67" t="s">
         <v>282</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="F5" s="67" t="s">
         <v>283</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="G5" s="67" t="s">
         <v>284</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="H5" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="I5" s="67" t="s">
         <v>285</v>
       </c>
-      <c r="H5" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="I5" s="57" t="s">
+      <c r="J5" s="67" t="s">
         <v>286</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="K5" s="67" t="s">
         <v>287</v>
       </c>
-      <c r="K5" s="57" t="s">
+      <c r="L5" s="67" t="s">
         <v>288</v>
       </c>
-      <c r="L5" s="57" t="s">
+      <c r="M5" s="67" t="s">
         <v>289</v>
       </c>
-      <c r="M5" s="57" t="s">
+      <c r="N5" s="67" t="s">
         <v>290</v>
       </c>
-      <c r="N5" s="57" t="s">
+      <c r="O5" s="67" t="s">
         <v>291</v>
       </c>
-      <c r="O5" s="57" t="s">
+      <c r="P5" s="67" t="s">
         <v>292</v>
       </c>
-      <c r="P5" s="57" t="s">
+      <c r="Q5" s="67" t="s">
         <v>293</v>
       </c>
-      <c r="Q5" s="57" t="s">
+      <c r="R5" s="67" t="s">
         <v>294</v>
       </c>
-      <c r="R5" s="57" t="s">
+      <c r="S5" s="67" t="s">
         <v>295</v>
       </c>
-      <c r="S5" s="57" t="s">
+      <c r="T5" s="67" t="s">
         <v>296</v>
       </c>
-      <c r="T5" s="57" t="s">
+      <c r="U5" s="67" t="s">
         <v>297</v>
       </c>
-      <c r="U5" s="57" t="s">
+      <c r="V5" s="67" t="s">
+        <v>180</v>
+      </c>
+      <c r="W5" s="67" t="s">
         <v>298</v>
       </c>
-      <c r="V5" s="57" t="s">
-        <v>181</v>
-      </c>
-      <c r="W5" s="57" t="s">
+      <c r="X5" s="67" t="s">
         <v>299</v>
       </c>
-      <c r="X5" s="57" t="s">
+      <c r="Y5" s="67" t="s">
         <v>300</v>
       </c>
-      <c r="Y5" s="57" t="s">
+      <c r="Z5" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="Z5" s="57" t="s">
+      <c r="AA5" s="67" t="s">
         <v>302</v>
       </c>
-      <c r="AA5" s="57" t="s">
+      <c r="AB5" s="67" t="s">
+        <v>244</v>
+      </c>
+      <c r="AC5" s="67" t="s">
         <v>303</v>
       </c>
-      <c r="AB5" s="57" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC5" s="57" t="s">
+      <c r="AD5" s="67" t="s">
         <v>304</v>
       </c>
-      <c r="AD5" s="57" t="s">
+      <c r="AE5" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="AE5" s="57" t="s">
+      <c r="AF5" s="67" t="s">
         <v>306</v>
       </c>
-      <c r="AF5" s="57" t="s">
+      <c r="AG5" s="67" t="s">
         <v>307</v>
       </c>
-      <c r="AG5" s="57" t="s">
+      <c r="AH5" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="AH5" s="57" t="s">
+      <c r="AI5" s="67" t="s">
         <v>309</v>
       </c>
-      <c r="AI5" s="57" t="s">
+      <c r="AJ5" s="67" t="s">
         <v>310</v>
       </c>
-      <c r="AJ5" s="57" t="s">
+      <c r="AK5" s="67" t="s">
         <v>311</v>
       </c>
-      <c r="AK5" s="57" t="s">
+      <c r="AL5" s="67" t="s">
         <v>312</v>
       </c>
-      <c r="AL5" s="57" t="s">
+      <c r="AM5" s="67" t="s">
         <v>313</v>
       </c>
-      <c r="AM5" s="57" t="s">
+      <c r="AN5" s="67" t="s">
         <v>314</v>
       </c>
-      <c r="AN5" s="57" t="s">
+      <c r="AO5" s="67" t="s">
         <v>315</v>
       </c>
-      <c r="AO5" s="57" t="s">
+      <c r="AP5" s="67" t="s">
         <v>316</v>
       </c>
-      <c r="AP5" s="57" t="s">
+      <c r="AQ5" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR5" s="67" t="s">
         <v>317</v>
       </c>
-      <c r="AQ5" s="57" t="s">
-        <v>122</v>
-      </c>
-      <c r="AR5" s="57" t="s">
+      <c r="AS5" s="67" t="s">
         <v>318</v>
       </c>
-      <c r="AS5" s="57" t="s">
+      <c r="AT5" s="67" t="s">
         <v>319</v>
       </c>
-      <c r="AT5" s="57" t="s">
+      <c r="AU5" s="67" t="s">
         <v>320</v>
       </c>
-      <c r="AU5" s="57" t="s">
+      <c r="AV5" s="67" t="s">
+        <v>263</v>
+      </c>
+      <c r="AW5" s="67" t="s">
         <v>321</v>
       </c>
-      <c r="AV5" s="57" t="s">
-        <v>264</v>
-      </c>
-      <c r="AW5" s="57" t="s">
+      <c r="AX5" s="67" t="s">
         <v>322</v>
       </c>
-      <c r="AX5" s="57" t="s">
+      <c r="AY5" s="67" t="s">
         <v>323</v>
       </c>
-      <c r="AY5" s="57" t="s">
+      <c r="AZ5" s="67" t="s">
         <v>324</v>
       </c>
-      <c r="AZ5" s="57" t="s">
+      <c r="BA5" s="67" t="s">
         <v>325</v>
       </c>
-      <c r="BA5" s="57" t="s">
+      <c r="BB5" s="67" t="s">
         <v>326</v>
       </c>
-      <c r="BB5" s="57" t="s">
+      <c r="BC5" s="67" t="s">
         <v>327</v>
       </c>
-      <c r="BC5" s="57" t="s">
+      <c r="BD5" s="67" t="s">
         <v>328</v>
       </c>
-      <c r="BD5" s="57" t="s">
+      <c r="BE5" s="67" t="s">
         <v>329</v>
       </c>
-      <c r="BE5" s="57" t="s">
+      <c r="BF5" s="67" t="s">
         <v>330</v>
       </c>
-      <c r="BF5" s="57" t="s">
+      <c r="BG5" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="BH5" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="BG5" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="BH5" s="57" t="s">
+      <c r="BI5" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="BI5" s="57" t="s">
+      <c r="BJ5" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="BJ5" s="57" t="s">
+      <c r="BK5" s="67" t="s">
         <v>334</v>
       </c>
-      <c r="BK5" s="57" t="s">
+    </row>
+    <row r="6" spans="1:63">
+      <c r="A6" s="67" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="6" spans="1:63">
-      <c r="A6" s="57" t="s">
+    <row r="7" spans="1:63">
+      <c r="A7" s="67" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="7" spans="1:63">
-      <c r="A7" s="57" t="s">
+    <row r="8" spans="1:63">
+      <c r="A8" s="67" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="8" spans="1:63">
-      <c r="A8" s="57" t="s">
+    <row r="9" spans="1:63">
+      <c r="A9" s="67" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="9" spans="1:63">
-      <c r="A9" s="57" t="s">
+    <row r="10" spans="1:63">
+      <c r="A10" s="67" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:63">
-      <c r="A10" s="57" t="s">
+    <row r="11" spans="1:63">
+      <c r="A11" s="67" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="11" spans="1:63">
-      <c r="A11" s="57" t="s">
+    <row r="12" spans="1:63">
+      <c r="A12" s="67" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:63">
-      <c r="A12" s="57" t="s">
+    <row r="13" spans="1:63">
+      <c r="A13" s="67" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="13" spans="1:63">
-      <c r="A13" s="57" t="s">
+    <row r="14" spans="1:63">
+      <c r="A14" s="67" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="14" spans="1:63">
-      <c r="A14" s="57" t="s">
+    <row r="15" spans="1:63">
+      <c r="A15" s="67" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="15" spans="1:63">
-      <c r="A15" s="57" t="s">
+    <row r="16" spans="1:63">
+      <c r="A16" s="67" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="16" spans="1:63">
-      <c r="A16" s="57" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="67" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="57" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="67" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="57" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="67" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="57" t="s">
+    <row r="20" spans="1:1">
+      <c r="A20" s="67" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="57" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="67" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="57" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" s="67" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="57" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="67" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="57" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" s="67" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="57" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="67" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="57" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" s="67" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="57" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" s="67" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="57" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" s="67" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="57" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" s="67" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="57" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" s="67" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="57" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" s="67" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="57" t="s">
+    <row r="32" spans="1:1">
+      <c r="A32" s="67" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="57" t="s">
+    <row r="33" spans="1:1">
+      <c r="A33" s="67" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="57" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" s="67" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="57" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" s="67" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="57" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" s="67" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="57" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" s="67" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="57" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" s="67" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="57" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" s="67" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="57" t="s">
+    <row r="40" spans="1:1">
+      <c r="A40" s="67" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="57" t="s">
+    <row r="41" spans="1:1">
+      <c r="A41" s="67" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="57" t="s">
+    <row r="42" spans="1:1">
+      <c r="A42" s="67" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="57" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="67" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="57" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="67" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="57" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="67" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="57" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" s="67" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="57" t="s">
+    <row r="47" spans="1:1">
+      <c r="A47" s="67" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="57" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="67" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="57" t="s">
+    <row r="49" spans="1:1">
+      <c r="A49" s="67" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="57" t="s">
+    <row r="50" spans="1:1">
+      <c r="A50" s="67" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="57" t="s">
+    <row r="51" spans="1:1">
+      <c r="A51" s="67" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="57" t="s">
+    <row r="52" spans="1:1">
+      <c r="A52" s="67" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="57" t="s">
+    <row r="53" spans="1:1">
+      <c r="A53" s="67" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="57" t="s">
+    <row r="54" spans="1:1">
+      <c r="A54" s="67" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="57" t="s">
+    <row r="55" spans="1:1">
+      <c r="A55" s="67" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="57" t="s">
+    <row r="56" spans="1:1">
+      <c r="A56" s="67" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="57" t="s">
+    <row r="57" spans="1:1">
+      <c r="A57" s="67" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="57" t="s">
+    <row r="58" spans="1:1">
+      <c r="A58" s="67" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="57" t="s">
+    <row r="59" spans="1:1">
+      <c r="A59" s="67" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="57" t="s">
+    <row r="60" spans="1:1">
+      <c r="A60" s="67" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="57" t="s">
+    <row r="61" spans="1:1">
+      <c r="A61" s="67" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="57" t="s">
+    <row r="62" spans="1:1">
+      <c r="A62" s="67" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="57" t="s">
+    <row r="63" spans="1:1">
+      <c r="A63" s="67" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="57" t="s">
+    <row r="64" spans="1:1">
+      <c r="A64" s="67" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="57" t="s">
+    <row r="65" spans="1:1">
+      <c r="A65" s="67" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="57" t="s">
+    <row r="66" spans="1:1">
+      <c r="A66" s="67" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="57" t="s">
+    <row r="67" spans="1:1">
+      <c r="A67" s="67" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="57" t="s">
+    <row r="68" spans="1:1">
+      <c r="A68" s="67" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="57" t="s">
+    <row r="69" spans="1:1">
+      <c r="A69" s="67" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="57" t="s">
+    <row r="70" spans="1:1">
+      <c r="A70" s="67" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="57" t="s">
+    <row r="71" spans="1:1">
+      <c r="A71" s="67" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="57" t="s">
+    <row r="72" spans="1:1">
+      <c r="A72" s="67" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="57" t="s">
+    <row r="73" spans="1:1">
+      <c r="A73" s="67" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="57" t="s">
+    <row r="74" spans="1:1">
+      <c r="A74" s="67" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="57" t="s">
+    <row r="75" spans="1:1">
+      <c r="A75" s="67" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="57" t="s">
+    <row r="76" spans="1:1">
+      <c r="A76" s="67" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="57" t="s">
+    <row r="77" spans="1:1">
+      <c r="A77" s="67" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="57" t="s">
+    <row r="78" spans="1:1">
+      <c r="A78" s="67" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="57" t="s">
+    <row r="79" spans="1:1">
+      <c r="A79" s="67" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="57" t="s">
+    <row r="80" spans="1:1">
+      <c r="A80" s="67" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="57" t="s">
+    <row r="81" spans="1:1">
+      <c r="A81" s="67" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="57" t="s">
+    <row r="82" spans="1:1">
+      <c r="A82" s="67" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="57" t="s">
+    <row r="83" spans="1:1">
+      <c r="A83" s="67" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="57" t="s">
+    <row r="84" spans="1:1">
+      <c r="A84" s="67" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="57" t="s">
+    <row r="85" spans="1:1">
+      <c r="A85" s="67" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="57" t="s">
+    <row r="86" spans="1:1">
+      <c r="A86" s="67" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="57" t="s">
+    <row r="87" spans="1:1">
+      <c r="A87" s="67" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="57" t="s">
+    <row r="88" spans="1:1">
+      <c r="A88" s="67" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="57" t="s">
+    <row r="89" spans="1:1">
+      <c r="A89" s="67" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="57" t="s">
+    <row r="90" spans="1:1">
+      <c r="A90" s="67" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="57" t="s">
+    <row r="91" spans="1:1">
+      <c r="A91" s="67" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="57" t="s">
+    <row r="92" spans="1:1">
+      <c r="A92" s="67" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="57" t="s">
+    <row r="93" spans="1:1">
+      <c r="A93" s="67" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="57" t="s">
+    <row r="94" spans="1:1">
+      <c r="A94" s="67" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="57" t="s">
+    <row r="95" spans="1:1">
+      <c r="A95" s="67" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="57" t="s">
+    <row r="96" spans="1:1">
+      <c r="A96" s="67" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="57" t="s">
+    <row r="97" spans="1:1">
+      <c r="A97" s="67" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="57" t="s">
+    <row r="98" spans="1:1">
+      <c r="A98" s="67" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="57" t="s">
+    <row r="99" spans="1:1">
+      <c r="A99" s="67" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="57" t="s">
+    <row r="100" spans="1:1">
+      <c r="A100" s="67" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="57" t="s">
+    <row r="101" spans="1:1">
+      <c r="A101" s="67" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="57" t="s">
+    <row r="102" spans="1:1">
+      <c r="A102" s="67" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="57" t="s">
+    <row r="103" spans="1:1">
+      <c r="A103" s="67" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="57" t="s">
+    <row r="104" spans="1:1">
+      <c r="A104" s="67" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="57" t="s">
+    <row r="105" spans="1:1">
+      <c r="A105" s="67" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="57" t="s">
+    <row r="106" spans="1:1">
+      <c r="A106" s="67" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="57" t="s">
+    <row r="107" spans="1:1">
+      <c r="A107" s="67" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="57" t="s">
+    <row r="108" spans="1:1">
+      <c r="A108" s="67" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="57" t="s">
+    <row r="109" spans="1:1">
+      <c r="A109" s="67" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="57" t="s">
+    <row r="110" spans="1:1">
+      <c r="A110" s="67" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="57" t="s">
+    <row r="111" spans="1:1">
+      <c r="A111" s="67" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="57" t="s">
+    <row r="112" spans="1:1">
+      <c r="A112" s="67" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="57" t="s">
+    <row r="113" spans="1:1">
+      <c r="A113" s="67" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="57" t="s">
+    <row r="114" spans="1:1">
+      <c r="A114" s="67" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="57" t="s">
+    <row r="115" spans="1:1">
+      <c r="A115" s="67" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="57" t="s">
+    <row r="116" spans="1:1">
+      <c r="A116" s="67" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="57" t="s">
+    <row r="117" spans="1:1">
+      <c r="A117" s="67" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="57" t="s">
+    <row r="118" spans="1:1">
+      <c r="A118" s="67" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="57" t="s">
+    <row r="119" spans="1:1">
+      <c r="A119" s="67" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="57" t="s">
+    <row r="120" spans="1:1">
+      <c r="A120" s="67" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="57" t="s">
+    <row r="121" spans="1:1">
+      <c r="A121" s="67" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="57" t="s">
+    <row r="122" spans="1:1">
+      <c r="A122" s="67" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="57" t="s">
+    <row r="123" spans="1:1">
+      <c r="A123" s="67" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="57" t="s">
+    <row r="124" spans="1:1">
+      <c r="A124" s="67" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="57" t="s">
+    <row r="125" spans="1:1">
+      <c r="A125" s="67" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="57" t="s">
+    <row r="126" spans="1:1">
+      <c r="A126" s="67" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="57" t="s">
+    <row r="127" spans="1:1">
+      <c r="A127" s="67" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="57" t="s">
+    <row r="128" spans="1:1">
+      <c r="A128" s="67" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="57" t="s">
+    <row r="129" spans="1:1">
+      <c r="A129" s="67" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="57" t="s">
+    <row r="130" spans="1:1">
+      <c r="A130" s="67" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="57" t="s">
+    <row r="131" spans="1:1">
+      <c r="A131" s="67" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="57" t="s">
+    <row r="132" spans="1:1">
+      <c r="A132" s="67" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="57" t="s">
+    <row r="133" spans="1:1">
+      <c r="A133" s="67" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="57" t="s">
+    <row r="134" spans="1:1">
+      <c r="A134" s="67" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="57" t="s">
+    <row r="135" spans="1:1">
+      <c r="A135" s="67" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="57" t="s">
+    <row r="136" spans="1:1">
+      <c r="A136" s="67" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="57" t="s">
+    <row r="137" spans="1:1">
+      <c r="A137" s="67" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="57" t="s">
+    <row r="138" spans="1:1">
+      <c r="A138" s="67" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="57" t="s">
+    <row r="139" spans="1:1">
+      <c r="A139" s="67" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="57" t="s">
+    <row r="140" spans="1:1">
+      <c r="A140" s="67" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="57" t="s">
+    <row r="141" spans="1:1">
+      <c r="A141" s="67" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="57" t="s">
+    <row r="142" spans="1:1">
+      <c r="A142" s="67" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="57" t="s">
+    <row r="143" spans="1:1">
+      <c r="A143" s="67" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="57" t="s">
+    <row r="144" spans="1:1">
+      <c r="A144" s="67" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="57" t="s">
+    <row r="145" spans="1:1">
+      <c r="A145" s="67" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="57" t="s">
+    <row r="146" spans="1:1">
+      <c r="A146" s="67" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="57" t="s">
+    <row r="147" spans="1:1">
+      <c r="A147" s="67" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="57" t="s">
+    <row r="148" spans="1:1">
+      <c r="A148" s="67" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="57" t="s">
+    <row r="149" spans="1:1">
+      <c r="A149" s="67" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="57" t="s">
+    <row r="150" spans="1:1">
+      <c r="A150" s="67" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="57" t="s">
+    <row r="151" spans="1:1">
+      <c r="A151" s="67" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="57" t="s">
+    <row r="152" spans="1:1">
+      <c r="A152" s="67" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="57" t="s">
+    <row r="153" spans="1:1">
+      <c r="A153" s="67" t="s">
         <v>482</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="57" t="s">
-        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1587,6 +1587,17 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1782,29 +1793,27 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1832,15 +1841,6 @@
         <color auto="1"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1906,58 +1906,58 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1965,39 +1965,39 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2010,56 +2010,55 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2077,21 +2076,20 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2421,11 +2419,11 @@
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="2:22">
       <c r="B2" s="3" t="s">
@@ -2436,7 +2434,7 @@
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="32" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="37">
@@ -2483,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="19"/>
+      <c r="D5" s="20"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="36">
@@ -2505,7 +2503,7 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="J7" s="20"/>
+      <c r="J7" s="21"/>
     </row>
     <row r="8" spans="2:22">
       <c r="B8" s="36">
@@ -2524,7 +2522,7 @@
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-      <c r="J8" s="21"/>
+      <c r="J8" s="22"/>
       <c r="K8" s="1">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,59,FALSE))</f>
         <v>0</v>
@@ -2547,730 +2545,736 @@
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-      <c r="J9" s="22"/>
+      <c r="J9" s="23"/>
     </row>
     <row r="10" spans="2:22" ht="13.5" customHeight="1"/>
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="40">
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="41">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="41">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="41">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="43">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="52"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="54"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="53"/>
-      <c r="S11" s="53"/>
-      <c r="T11" s="53"/>
-      <c r="U11" s="53"/>
-      <c r="V11" s="54"/>
+      <c r="J11" s="40">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="55"/>
+      <c r="Q11" s="40">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="9"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="55"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="43">
+      <c r="B12" s="44">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="11"/>
-      <c r="J12" s="55"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="12"/>
+      <c r="J12" s="56"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="56"/>
-      <c r="Q12" s="55"/>
+      <c r="O12" s="57"/>
+      <c r="Q12" s="56"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-      <c r="V12" s="56"/>
+      <c r="V12" s="57"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="44">
+      <c r="B13" s="45">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="11"/>
-      <c r="J13" s="55"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="12"/>
+      <c r="J13" s="56"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="56"/>
-      <c r="Q13" s="55"/>
+      <c r="O13" s="57"/>
+      <c r="Q13" s="56"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
-      <c r="V13" s="56"/>
+      <c r="V13" s="57"/>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="11"/>
-      <c r="J14" s="57" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="12"/>
+      <c r="J14" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="58">
+      <c r="K14" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L14" s="59"/>
-      <c r="M14" s="60"/>
-      <c r="N14" s="60"/>
-      <c r="O14" s="61">
+      <c r="L14" s="60"/>
+      <c r="M14" s="61"/>
+      <c r="N14" s="61"/>
+      <c r="O14" s="62">
         <f>IF(M14="","",N14/M14)</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="57" t="s">
+      <c r="Q14" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="58">
+      <c r="R14" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S14" s="59"/>
-      <c r="T14" s="60"/>
-      <c r="U14" s="60"/>
-      <c r="V14" s="61">
+      <c r="S14" s="60"/>
+      <c r="T14" s="61"/>
+      <c r="U14" s="61"/>
+      <c r="V14" s="62">
         <f>IF(T14="","",U14/T14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="46">
+      <c r="B15" s="48">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C15" s="14"/>
+      <c r="C15" s="15"/>
       <c r="D15" s="33">
         <v>0</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
-      <c r="J15" s="57" t="s">
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="30"/>
+      <c r="J15" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="K15" s="58">
+      <c r="K15" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L15" s="59"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="61">
+      <c r="L15" s="60"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="61"/>
+      <c r="O15" s="62">
         <f>IF(M15="","",N15/M15)</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="57" t="s">
+      <c r="Q15" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="R15" s="58">
+      <c r="R15" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S15" s="59"/>
-      <c r="T15" s="60"/>
-      <c r="U15" s="60"/>
-      <c r="V15" s="61">
+      <c r="S15" s="60"/>
+      <c r="T15" s="61"/>
+      <c r="U15" s="61"/>
+      <c r="V15" s="62">
         <f>IF(T15="","",U15/T15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="47">
+      <c r="B16" s="49">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C16" s="15"/>
+      <c r="C16" s="16"/>
       <c r="D16" s="33">
         <v>0</v>
       </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="48">
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="50">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="29"/>
-      <c r="J16" s="57" t="s">
+      <c r="H16" s="30"/>
+      <c r="J16" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="58">
+      <c r="K16" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L16" s="59"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="61">
+      <c r="L16" s="60"/>
+      <c r="M16" s="61"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="62">
         <f>IF(M16="","",N16/M16)</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="57" t="s">
+      <c r="Q16" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="R16" s="58">
+      <c r="R16" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S16" s="59"/>
-      <c r="T16" s="60"/>
-      <c r="U16" s="60"/>
-      <c r="V16" s="61">
+      <c r="S16" s="60"/>
+      <c r="T16" s="61"/>
+      <c r="U16" s="61"/>
+      <c r="V16" s="62">
         <f>IF(T16="","",U16/T16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="47">
+      <c r="B17" s="49">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C17" s="15"/>
+      <c r="C17" s="16"/>
       <c r="D17" s="33">
         <v>0</v>
       </c>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="48">
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="50">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="29"/>
-      <c r="J17" s="57" t="s">
+      <c r="H17" s="30"/>
+      <c r="J17" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="58">
+      <c r="K17" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L17" s="59"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="61">
+      <c r="L17" s="60"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="62">
         <f>IF(M17="","",N17/M17)</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="57" t="s">
+      <c r="Q17" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="R17" s="58">
+      <c r="R17" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S17" s="59"/>
-      <c r="T17" s="60"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="61">
+      <c r="S17" s="60"/>
+      <c r="T17" s="61"/>
+      <c r="U17" s="61"/>
+      <c r="V17" s="62">
         <f>IF(T17="","",U17/T17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="47">
+      <c r="B18" s="49">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C18" s="15"/>
+      <c r="C18" s="16"/>
       <c r="D18" s="33">
         <v>0</v>
       </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="48">
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="50">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="29"/>
-      <c r="J18" s="57" t="s">
+      <c r="H18" s="30"/>
+      <c r="J18" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="58">
+      <c r="K18" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L18" s="59"/>
-      <c r="M18" s="60"/>
-      <c r="N18" s="60"/>
-      <c r="O18" s="61">
+      <c r="L18" s="60"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="62">
         <f>IF(M18="","",N18/M18)</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="57" t="s">
+      <c r="Q18" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="R18" s="58">
+      <c r="R18" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S18" s="59"/>
-      <c r="T18" s="60"/>
-      <c r="U18" s="60"/>
-      <c r="V18" s="61">
+      <c r="S18" s="60"/>
+      <c r="T18" s="61"/>
+      <c r="U18" s="61"/>
+      <c r="V18" s="62">
         <f>IF(T18="","",U18/T18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="47">
+      <c r="B19" s="49">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C19" s="15"/>
+      <c r="C19" s="16"/>
       <c r="D19" s="33">
         <v>0</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="48">
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="50">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="29"/>
-      <c r="J19" s="57" t="s">
+      <c r="H19" s="30"/>
+      <c r="J19" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="58">
+      <c r="K19" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L19" s="59"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="61">
+      <c r="L19" s="60"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="62">
         <f>IF(M19="","",N19/M19)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="57" t="s">
+      <c r="Q19" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="R19" s="58">
+      <c r="R19" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S19" s="59"/>
-      <c r="T19" s="60"/>
-      <c r="U19" s="60"/>
-      <c r="V19" s="61">
+      <c r="S19" s="60"/>
+      <c r="T19" s="61"/>
+      <c r="U19" s="61"/>
+      <c r="V19" s="62">
         <f>IF(T19="","",U19/T19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="49">
+      <c r="B20" s="51">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="50">
+      <c r="C20" s="17"/>
+      <c r="D20" s="52">
         <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="52">
         <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="53">
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="30"/>
-      <c r="J20" s="57" t="s">
+      <c r="H20" s="31"/>
+      <c r="J20" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="K20" s="58">
+      <c r="K20" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L20" s="59"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="60"/>
-      <c r="O20" s="61">
+      <c r="L20" s="60"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="62">
         <f>IF(M20="","",N20/M20)</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="57" t="s">
+      <c r="Q20" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="R20" s="58">
+      <c r="R20" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S20" s="59"/>
-      <c r="T20" s="60"/>
-      <c r="U20" s="60"/>
-      <c r="V20" s="61">
+      <c r="S20" s="60"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
+      <c r="V20" s="62">
         <f>IF(T20="","",U20/T20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:22">
-      <c r="J21" s="57" t="s">
+      <c r="J21" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="K21" s="58">
+      <c r="K21" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L21" s="59"/>
-      <c r="M21" s="60"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="61">
+      <c r="L21" s="60"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="62">
         <f>IF(M21="","",N21/M21)</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="57" t="s">
+      <c r="Q21" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="R21" s="58">
+      <c r="R21" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S21" s="59"/>
-      <c r="T21" s="60"/>
-      <c r="U21" s="60"/>
-      <c r="V21" s="61">
+      <c r="S21" s="60"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="61"/>
+      <c r="V21" s="62">
         <f>IF(T21="","",U21/T21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:22">
-      <c r="J22" s="57" t="s">
+      <c r="J22" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="58">
+      <c r="K22" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L22" s="59"/>
-      <c r="M22" s="60"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="61">
+      <c r="L22" s="60"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="62">
         <f>IF(M22="","",N22/M22)</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="57" t="s">
+      <c r="Q22" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="R22" s="58">
+      <c r="R22" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S22" s="59"/>
-      <c r="T22" s="60"/>
-      <c r="U22" s="60"/>
-      <c r="V22" s="61">
+      <c r="S22" s="60"/>
+      <c r="T22" s="61"/>
+      <c r="U22" s="61"/>
+      <c r="V22" s="62">
         <f>IF(T22="","",U22/T22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:22">
-      <c r="J23" s="57" t="s">
+      <c r="J23" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="58">
+      <c r="K23" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L23" s="59"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="61">
+      <c r="L23" s="60"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="62">
         <f>IF(M23="","",N23/M23)</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="57" t="s">
+      <c r="Q23" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="58">
+      <c r="R23" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S23" s="59"/>
-      <c r="T23" s="60"/>
-      <c r="U23" s="60"/>
-      <c r="V23" s="61">
+      <c r="S23" s="60"/>
+      <c r="T23" s="61"/>
+      <c r="U23" s="61"/>
+      <c r="V23" s="62">
         <f>IF(T23="","",U23/T23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:22">
-      <c r="J24" s="57" t="s">
+      <c r="J24" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="58">
+      <c r="K24" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L24" s="59"/>
-      <c r="M24" s="60"/>
-      <c r="N24" s="60"/>
-      <c r="O24" s="61">
+      <c r="L24" s="60"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="62">
         <f>IF(M24="","",N24/M24)</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="57" t="s">
+      <c r="Q24" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="R24" s="58">
+      <c r="R24" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S24" s="59"/>
-      <c r="T24" s="60"/>
-      <c r="U24" s="60"/>
-      <c r="V24" s="61">
+      <c r="S24" s="60"/>
+      <c r="T24" s="61"/>
+      <c r="U24" s="61"/>
+      <c r="V24" s="62">
         <f>IF(T24="","",U24/T24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:22">
-      <c r="J25" s="57" t="s">
+      <c r="J25" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="58">
+      <c r="K25" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L25" s="59"/>
-      <c r="M25" s="60"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="61">
+      <c r="L25" s="60"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="61"/>
+      <c r="O25" s="62">
         <f>IF(M25="","",N25/M25)</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="57" t="s">
+      <c r="Q25" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="R25" s="58">
+      <c r="R25" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S25" s="59"/>
-      <c r="T25" s="60"/>
-      <c r="U25" s="60"/>
-      <c r="V25" s="61">
+      <c r="S25" s="60"/>
+      <c r="T25" s="61"/>
+      <c r="U25" s="61"/>
+      <c r="V25" s="62">
         <f>IF(T25="","",U25/T25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:22">
-      <c r="J26" s="57" t="s">
+      <c r="J26" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="58">
+      <c r="K26" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L26" s="59"/>
-      <c r="M26" s="60"/>
-      <c r="N26" s="60"/>
-      <c r="O26" s="61">
+      <c r="L26" s="60"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="62">
         <f>IF(M26="","",N26/M26)</f>
         <v>0</v>
       </c>
-      <c r="Q26" s="57" t="s">
+      <c r="Q26" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="R26" s="58">
+      <c r="R26" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S26" s="59"/>
-      <c r="T26" s="60"/>
-      <c r="U26" s="60"/>
-      <c r="V26" s="61">
+      <c r="S26" s="60"/>
+      <c r="T26" s="61"/>
+      <c r="U26" s="61"/>
+      <c r="V26" s="62">
         <f>IF(T26="","",U26/T26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:22">
-      <c r="J27" s="57" t="s">
+      <c r="J27" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="K27" s="58">
+      <c r="K27" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L27" s="59"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="61">
+      <c r="L27" s="60"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="61"/>
+      <c r="O27" s="62">
         <f>IF(M27="","",N27/M27)</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="57" t="s">
+      <c r="Q27" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="58">
+      <c r="R27" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S27" s="59"/>
-      <c r="T27" s="60"/>
-      <c r="U27" s="60"/>
-      <c r="V27" s="61">
+      <c r="S27" s="60"/>
+      <c r="T27" s="61"/>
+      <c r="U27" s="61"/>
+      <c r="V27" s="62">
         <f>IF(T27="","",U27/T27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:22">
-      <c r="J28" s="57" t="s">
+      <c r="J28" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="58">
+      <c r="K28" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="59"/>
-      <c r="M28" s="60"/>
-      <c r="N28" s="60"/>
-      <c r="O28" s="61">
+      <c r="L28" s="60"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="61"/>
+      <c r="O28" s="62">
         <f>IF(M28="","",N28/M28)</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="57" t="s">
+      <c r="Q28" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="R28" s="58">
+      <c r="R28" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S28" s="59"/>
-      <c r="T28" s="60"/>
-      <c r="U28" s="60"/>
-      <c r="V28" s="61">
+      <c r="S28" s="60"/>
+      <c r="T28" s="61"/>
+      <c r="U28" s="61"/>
+      <c r="V28" s="62">
         <f>IF(T28="","",U28/T28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:22">
-      <c r="J29" s="57" t="s">
+      <c r="J29" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="K29" s="58">
+      <c r="K29" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L29" s="59"/>
-      <c r="M29" s="60"/>
-      <c r="N29" s="60"/>
-      <c r="O29" s="61">
+      <c r="L29" s="60"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="61"/>
+      <c r="O29" s="62">
         <f>IF(M29="","",N29/M29)</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="57" t="s">
+      <c r="Q29" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="R29" s="58">
+      <c r="R29" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S29" s="59"/>
-      <c r="T29" s="60"/>
-      <c r="U29" s="60"/>
-      <c r="V29" s="61">
+      <c r="S29" s="60"/>
+      <c r="T29" s="61"/>
+      <c r="U29" s="61"/>
+      <c r="V29" s="62">
         <f>IF(T29="","",U29/T29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:22">
-      <c r="J30" s="57" t="s">
+      <c r="J30" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="58">
+      <c r="K30" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L30" s="59"/>
-      <c r="M30" s="60"/>
-      <c r="N30" s="60"/>
-      <c r="O30" s="61">
+      <c r="L30" s="60"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="62">
         <f>IF(M30="","",N30/M30)</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="57" t="s">
+      <c r="Q30" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="58">
+      <c r="R30" s="59">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S30" s="59"/>
-      <c r="T30" s="60"/>
-      <c r="U30" s="60"/>
-      <c r="V30" s="61">
+      <c r="S30" s="60"/>
+      <c r="T30" s="61"/>
+      <c r="U30" s="61"/>
+      <c r="V30" s="62">
         <f>IF(T30="","",U30/T30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:22">
-      <c r="J31" s="62" t="s">
+      <c r="J31" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="K31" s="63">
+      <c r="K31" s="64">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L31" s="64"/>
-      <c r="M31" s="65"/>
-      <c r="N31" s="65"/>
-      <c r="O31" s="66">
+      <c r="L31" s="65"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="67">
         <f>IF(M31="","",N31/M31)</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="62" t="s">
+      <c r="Q31" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="R31" s="63">
+      <c r="R31" s="64">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S31" s="64"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="66">
+      <c r="S31" s="65"/>
+      <c r="T31" s="66"/>
+      <c r="U31" s="66"/>
+      <c r="V31" s="67">
         <f>IF(T31="","",U31/T31)</f>
         <v>0</v>
       </c>
@@ -3324,1697 +3328,1697 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:63">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="67" t="s">
+      <c r="K1" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="67" t="s">
+      <c r="L1" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="67" t="s">
+      <c r="M1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="N1" s="67" t="s">
+      <c r="N1" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="O1" s="67" t="s">
+      <c r="O1" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="67" t="s">
+      <c r="P1" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="67" t="s">
+      <c r="Q1" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="R1" s="67" t="s">
+      <c r="R1" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="S1" s="67" t="s">
+      <c r="S1" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="T1" s="67" t="s">
+      <c r="T1" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="U1" s="67" t="s">
+      <c r="U1" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="V1" s="67" t="s">
+      <c r="V1" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="W1" s="67" t="s">
+      <c r="W1" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="X1" s="67" t="s">
+      <c r="X1" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="Y1" s="67" t="s">
+      <c r="Y1" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="Z1" s="67" t="s">
+      <c r="Z1" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="AA1" s="67" t="s">
+      <c r="AA1" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="AB1" s="67" t="s">
+      <c r="AB1" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="AC1" s="67" t="s">
+      <c r="AC1" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="AD1" s="67" t="s">
+      <c r="AD1" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="AE1" s="67" t="s">
+      <c r="AE1" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="AF1" s="67" t="s">
+      <c r="AF1" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="AG1" s="67" t="s">
+      <c r="AG1" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="AH1" s="67" t="s">
+      <c r="AH1" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="AI1" s="67" t="s">
+      <c r="AI1" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="AJ1" s="67" t="s">
+      <c r="AJ1" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="AK1" s="67" t="s">
+      <c r="AK1" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="AL1" s="67" t="s">
+      <c r="AL1" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="AM1" s="67" t="s">
+      <c r="AM1" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="AN1" s="67" t="s">
+      <c r="AN1" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="AO1" s="67" t="s">
+      <c r="AO1" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="AP1" s="67" t="s">
+      <c r="AP1" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="AQ1" s="67" t="s">
+      <c r="AQ1" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="AR1" s="67" t="s">
+      <c r="AR1" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="AS1" s="67" t="s">
+      <c r="AS1" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="AT1" s="67" t="s">
+      <c r="AT1" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="AU1" s="67" t="s">
+      <c r="AU1" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="AV1" s="67" t="s">
+      <c r="AV1" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="AW1" s="67" t="s">
+      <c r="AW1" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="AX1" s="67" t="s">
+      <c r="AX1" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="AY1" s="67" t="s">
+      <c r="AY1" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="AZ1" s="67" t="s">
+      <c r="AZ1" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="BA1" s="67" t="s">
+      <c r="BA1" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="BB1" s="67" t="s">
+      <c r="BB1" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="BC1" s="67" t="s">
+      <c r="BC1" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="BD1" s="67" t="s">
+      <c r="BD1" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="BE1" s="67" t="s">
+      <c r="BE1" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="BF1" s="67" t="s">
+      <c r="BF1" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="BG1" s="67" t="s">
+      <c r="BG1" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="BH1" s="67" t="s">
+      <c r="BH1" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="BI1" s="67" t="s">
+      <c r="BI1" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="BJ1" s="67" t="s">
+      <c r="BJ1" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="BK1" s="67" t="s">
+      <c r="BK1" s="46" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:63">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="46" t="s">
         <v>106</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="67" t="s">
+      <c r="J2" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="67" t="s">
+      <c r="K2" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="L2" s="67" t="s">
+      <c r="L2" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="M2" s="67" t="s">
+      <c r="M2" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="N2" s="67" t="s">
+      <c r="N2" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="O2" s="67" t="s">
+      <c r="O2" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="P2" s="67" t="s">
+      <c r="P2" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="Q2" s="67" t="s">
+      <c r="Q2" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="R2" s="67" t="s">
+      <c r="R2" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="S2" s="67" t="s">
+      <c r="S2" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="T2" s="67" t="s">
+      <c r="T2" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="U2" s="67" t="s">
+      <c r="U2" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="V2" s="67" t="s">
+      <c r="V2" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="W2" s="67" t="s">
+      <c r="W2" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="X2" s="67" t="s">
+      <c r="X2" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="Y2" s="67" t="s">
+      <c r="Y2" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="Z2" s="67" t="s">
+      <c r="Z2" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="AA2" s="67" t="s">
+      <c r="AA2" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="AB2" s="67" t="s">
+      <c r="AB2" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="AC2" s="67" t="s">
+      <c r="AC2" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="AD2" s="67" t="s">
+      <c r="AD2" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="AE2" s="67" t="s">
+      <c r="AE2" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="AF2" s="67" t="s">
+      <c r="AF2" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="AG2" s="67" t="s">
+      <c r="AG2" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="AH2" s="67" t="s">
+      <c r="AH2" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="AI2" s="67" t="s">
+      <c r="AI2" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="AJ2" s="67" t="s">
+      <c r="AJ2" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="AK2" s="67" t="s">
+      <c r="AK2" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="AL2" s="67" t="s">
+      <c r="AL2" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="AM2" s="67" t="s">
+      <c r="AM2" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="67" t="s">
+      <c r="AN2" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="AO2" s="67" t="s">
+      <c r="AO2" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="AP2" s="67" t="s">
+      <c r="AP2" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="67" t="s">
+      <c r="AQ2" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="AR2" s="67" t="s">
+      <c r="AR2" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="AS2" s="67" t="s">
+      <c r="AS2" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="AT2" s="67" t="s">
+      <c r="AT2" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="AU2" s="67" t="s">
+      <c r="AU2" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="AV2" s="67" t="s">
+      <c r="AV2" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="AW2" s="67" t="s">
+      <c r="AW2" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="AX2" s="67" t="s">
+      <c r="AX2" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="AY2" s="67" t="s">
+      <c r="AY2" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="AZ2" s="67" t="s">
+      <c r="AZ2" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="BA2" s="67" t="s">
+      <c r="BA2" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="BB2" s="67" t="s">
+      <c r="BB2" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="BC2" s="67" t="s">
+      <c r="BC2" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="BD2" s="67" t="s">
+      <c r="BD2" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="BE2" s="67" t="s">
+      <c r="BE2" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="BF2" s="67" t="s">
+      <c r="BF2" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="BG2" s="67" t="s">
+      <c r="BG2" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="BH2" s="67" t="s">
+      <c r="BH2" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="BI2" s="67" t="s">
+      <c r="BI2" s="46" t="s">
         <v>157</v>
       </c>
-      <c r="BJ2" s="67" t="s">
+      <c r="BJ2" s="46" t="s">
         <v>158</v>
       </c>
-      <c r="BK2" s="67" t="s">
+      <c r="BK2" s="46" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:63">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="46" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="46" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="I3" s="67" t="s">
+      <c r="I3" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="J3" s="67" t="s">
+      <c r="J3" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="K3" s="67" t="s">
+      <c r="K3" s="46" t="s">
         <v>169</v>
       </c>
-      <c r="L3" s="67" t="s">
+      <c r="L3" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="M3" s="67" t="s">
+      <c r="M3" s="46" t="s">
         <v>171</v>
       </c>
-      <c r="N3" s="67" t="s">
+      <c r="N3" s="46" t="s">
         <v>172</v>
       </c>
-      <c r="O3" s="67" t="s">
+      <c r="O3" s="46" t="s">
         <v>173</v>
       </c>
-      <c r="P3" s="67" t="s">
+      <c r="P3" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="Q3" s="67" t="s">
+      <c r="Q3" s="46" t="s">
         <v>175</v>
       </c>
-      <c r="R3" s="67" t="s">
+      <c r="R3" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="S3" s="67" t="s">
+      <c r="S3" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="T3" s="67" t="s">
+      <c r="T3" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="U3" s="67" t="s">
+      <c r="U3" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="V3" s="67" t="s">
+      <c r="V3" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="W3" s="67" t="s">
+      <c r="W3" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="X3" s="67" t="s">
+      <c r="X3" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="Y3" s="67" t="s">
+      <c r="Y3" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="Z3" s="67" t="s">
+      <c r="Z3" s="46" t="s">
         <v>183</v>
       </c>
-      <c r="AA3" s="67" t="s">
+      <c r="AA3" s="46" t="s">
         <v>184</v>
       </c>
-      <c r="AB3" s="67" t="s">
+      <c r="AB3" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="AC3" s="67" t="s">
+      <c r="AC3" s="46" t="s">
         <v>186</v>
       </c>
-      <c r="AD3" s="67" t="s">
+      <c r="AD3" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="AE3" s="67" t="s">
+      <c r="AE3" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="AF3" s="67" t="s">
+      <c r="AF3" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="AG3" s="67" t="s">
+      <c r="AG3" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="AH3" s="67" t="s">
+      <c r="AH3" s="46" t="s">
         <v>191</v>
       </c>
-      <c r="AI3" s="67" t="s">
+      <c r="AI3" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="AJ3" s="67" t="s">
+      <c r="AJ3" s="46" t="s">
         <v>193</v>
       </c>
-      <c r="AK3" s="67" t="s">
+      <c r="AK3" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="AL3" s="67" t="s">
+      <c r="AL3" s="46" t="s">
         <v>195</v>
       </c>
-      <c r="AM3" s="67" t="s">
+      <c r="AM3" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="AN3" s="67" t="s">
+      <c r="AN3" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="AO3" s="67" t="s">
+      <c r="AO3" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="AP3" s="67" t="s">
+      <c r="AP3" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="AQ3" s="67" t="s">
+      <c r="AQ3" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="AR3" s="67" t="s">
+      <c r="AR3" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="AS3" s="67" t="s">
+      <c r="AS3" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="AT3" s="67" t="s">
+      <c r="AT3" s="46" t="s">
         <v>200</v>
       </c>
-      <c r="AU3" s="67" t="s">
+      <c r="AU3" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="AV3" s="67" t="s">
+      <c r="AV3" s="46" t="s">
         <v>202</v>
       </c>
-      <c r="AW3" s="67" t="s">
+      <c r="AW3" s="46" t="s">
         <v>203</v>
       </c>
-      <c r="AX3" s="67" t="s">
+      <c r="AX3" s="46" t="s">
         <v>204</v>
       </c>
-      <c r="AY3" s="67" t="s">
+      <c r="AY3" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="AZ3" s="67" t="s">
+      <c r="AZ3" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="BA3" s="67" t="s">
+      <c r="BA3" s="46" t="s">
         <v>207</v>
       </c>
-      <c r="BB3" s="67" t="s">
+      <c r="BB3" s="46" t="s">
         <v>208</v>
       </c>
-      <c r="BC3" s="67" t="s">
+      <c r="BC3" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="BD3" s="67" t="s">
+      <c r="BD3" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="BE3" s="67" t="s">
+      <c r="BE3" s="46" t="s">
         <v>211</v>
       </c>
-      <c r="BF3" s="67" t="s">
+      <c r="BF3" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="BG3" s="67" t="s">
+      <c r="BG3" s="46" t="s">
         <v>213</v>
       </c>
-      <c r="BH3" s="67" t="s">
+      <c r="BH3" s="46" t="s">
         <v>214</v>
       </c>
-      <c r="BI3" s="67" t="s">
+      <c r="BI3" s="46" t="s">
         <v>215</v>
       </c>
-      <c r="BJ3" s="67" t="s">
+      <c r="BJ3" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="BK3" s="67" t="s">
+      <c r="BK3" s="46" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:63">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="46" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="46" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="46" t="s">
         <v>220</v>
       </c>
-      <c r="D4" s="67" t="s">
+      <c r="D4" s="46" t="s">
         <v>221</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="E4" s="46" t="s">
         <v>222</v>
       </c>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="46" t="s">
         <v>223</v>
       </c>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="46" t="s">
         <v>224</v>
       </c>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="46" t="s">
         <v>225</v>
       </c>
-      <c r="I4" s="67" t="s">
+      <c r="I4" s="46" t="s">
         <v>226</v>
       </c>
-      <c r="J4" s="67" t="s">
+      <c r="J4" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="K4" s="67" t="s">
+      <c r="K4" s="46" t="s">
         <v>228</v>
       </c>
-      <c r="L4" s="67" t="s">
+      <c r="L4" s="46" t="s">
         <v>229</v>
       </c>
-      <c r="M4" s="67" t="s">
+      <c r="M4" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="N4" s="67" t="s">
+      <c r="N4" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="O4" s="67" t="s">
+      <c r="O4" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="P4" s="67" t="s">
+      <c r="P4" s="46" t="s">
         <v>233</v>
       </c>
-      <c r="Q4" s="67" t="s">
+      <c r="Q4" s="46" t="s">
         <v>234</v>
       </c>
-      <c r="R4" s="67" t="s">
+      <c r="R4" s="46" t="s">
         <v>235</v>
       </c>
-      <c r="S4" s="67" t="s">
+      <c r="S4" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="T4" s="67" t="s">
+      <c r="T4" s="46" t="s">
         <v>237</v>
       </c>
-      <c r="U4" s="67" t="s">
+      <c r="U4" s="46" t="s">
         <v>238</v>
       </c>
-      <c r="V4" s="67" t="s">
+      <c r="V4" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="W4" s="67" t="s">
+      <c r="W4" s="46" t="s">
         <v>239</v>
       </c>
-      <c r="X4" s="67" t="s">
+      <c r="X4" s="46" t="s">
         <v>240</v>
       </c>
-      <c r="Y4" s="67" t="s">
+      <c r="Y4" s="46" t="s">
         <v>241</v>
       </c>
-      <c r="Z4" s="67" t="s">
+      <c r="Z4" s="46" t="s">
         <v>242</v>
       </c>
-      <c r="AA4" s="67" t="s">
+      <c r="AA4" s="46" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="67" t="s">
+      <c r="AB4" s="46" t="s">
         <v>244</v>
       </c>
-      <c r="AC4" s="67" t="s">
+      <c r="AC4" s="46" t="s">
         <v>245</v>
       </c>
-      <c r="AD4" s="67" t="s">
+      <c r="AD4" s="46" t="s">
         <v>246</v>
       </c>
-      <c r="AE4" s="67" t="s">
+      <c r="AE4" s="46" t="s">
         <v>247</v>
       </c>
-      <c r="AF4" s="67" t="s">
+      <c r="AF4" s="46" t="s">
         <v>248</v>
       </c>
-      <c r="AG4" s="67" t="s">
+      <c r="AG4" s="46" t="s">
         <v>249</v>
       </c>
-      <c r="AH4" s="67" t="s">
+      <c r="AH4" s="46" t="s">
         <v>250</v>
       </c>
-      <c r="AI4" s="67" t="s">
+      <c r="AI4" s="46" t="s">
         <v>251</v>
       </c>
-      <c r="AJ4" s="67" t="s">
+      <c r="AJ4" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="AK4" s="67" t="s">
+      <c r="AK4" s="46" t="s">
         <v>253</v>
       </c>
-      <c r="AL4" s="67" t="s">
+      <c r="AL4" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="AM4" s="67" t="s">
+      <c r="AM4" s="46" t="s">
         <v>255</v>
       </c>
-      <c r="AN4" s="67" t="s">
+      <c r="AN4" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="AO4" s="67" t="s">
+      <c r="AO4" s="46" t="s">
         <v>257</v>
       </c>
-      <c r="AP4" s="67" t="s">
+      <c r="AP4" s="46" t="s">
         <v>258</v>
       </c>
-      <c r="AQ4" s="67" t="s">
+      <c r="AQ4" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="AR4" s="67" t="s">
+      <c r="AR4" s="46" t="s">
         <v>259</v>
       </c>
-      <c r="AS4" s="67" t="s">
+      <c r="AS4" s="46" t="s">
         <v>260</v>
       </c>
-      <c r="AT4" s="67" t="s">
+      <c r="AT4" s="46" t="s">
         <v>261</v>
       </c>
-      <c r="AU4" s="67" t="s">
+      <c r="AU4" s="46" t="s">
         <v>262</v>
       </c>
-      <c r="AV4" s="67" t="s">
+      <c r="AV4" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="AW4" s="67" t="s">
+      <c r="AW4" s="46" t="s">
         <v>264</v>
       </c>
-      <c r="AX4" s="67" t="s">
+      <c r="AX4" s="46" t="s">
         <v>265</v>
       </c>
-      <c r="AY4" s="67" t="s">
+      <c r="AY4" s="46" t="s">
         <v>266</v>
       </c>
-      <c r="AZ4" s="67" t="s">
+      <c r="AZ4" s="46" t="s">
         <v>267</v>
       </c>
-      <c r="BA4" s="67" t="s">
+      <c r="BA4" s="46" t="s">
         <v>268</v>
       </c>
-      <c r="BB4" s="67" t="s">
+      <c r="BB4" s="46" t="s">
         <v>269</v>
       </c>
-      <c r="BC4" s="67" t="s">
+      <c r="BC4" s="46" t="s">
         <v>270</v>
       </c>
-      <c r="BD4" s="67" t="s">
+      <c r="BD4" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="BE4" s="67" t="s">
+      <c r="BE4" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="BF4" s="67" t="s">
+      <c r="BF4" s="46" t="s">
         <v>273</v>
       </c>
-      <c r="BG4" s="67" t="s">
+      <c r="BG4" s="46" t="s">
         <v>213</v>
       </c>
-      <c r="BH4" s="67" t="s">
+      <c r="BH4" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="BI4" s="67" t="s">
+      <c r="BI4" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="BJ4" s="67" t="s">
+      <c r="BJ4" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="BK4" s="67" t="s">
+      <c r="BK4" s="46" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:63">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="46" t="s">
         <v>278</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="46" t="s">
         <v>279</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="46" t="s">
         <v>280</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="46" t="s">
         <v>281</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="46" t="s">
         <v>282</v>
       </c>
-      <c r="F5" s="67" t="s">
+      <c r="F5" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="G5" s="67" t="s">
+      <c r="G5" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="H5" s="67" t="s">
+      <c r="H5" s="46" t="s">
         <v>225</v>
       </c>
-      <c r="I5" s="67" t="s">
+      <c r="I5" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="J5" s="67" t="s">
+      <c r="J5" s="46" t="s">
         <v>286</v>
       </c>
-      <c r="K5" s="67" t="s">
+      <c r="K5" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="L5" s="67" t="s">
+      <c r="L5" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="M5" s="67" t="s">
+      <c r="M5" s="46" t="s">
         <v>289</v>
       </c>
-      <c r="N5" s="67" t="s">
+      <c r="N5" s="46" t="s">
         <v>290</v>
       </c>
-      <c r="O5" s="67" t="s">
+      <c r="O5" s="46" t="s">
         <v>291</v>
       </c>
-      <c r="P5" s="67" t="s">
+      <c r="P5" s="46" t="s">
         <v>292</v>
       </c>
-      <c r="Q5" s="67" t="s">
+      <c r="Q5" s="46" t="s">
         <v>293</v>
       </c>
-      <c r="R5" s="67" t="s">
+      <c r="R5" s="46" t="s">
         <v>294</v>
       </c>
-      <c r="S5" s="67" t="s">
+      <c r="S5" s="46" t="s">
         <v>295</v>
       </c>
-      <c r="T5" s="67" t="s">
+      <c r="T5" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="U5" s="67" t="s">
+      <c r="U5" s="46" t="s">
         <v>297</v>
       </c>
-      <c r="V5" s="67" t="s">
+      <c r="V5" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="W5" s="67" t="s">
+      <c r="W5" s="46" t="s">
         <v>298</v>
       </c>
-      <c r="X5" s="67" t="s">
+      <c r="X5" s="46" t="s">
         <v>299</v>
       </c>
-      <c r="Y5" s="67" t="s">
+      <c r="Y5" s="46" t="s">
         <v>300</v>
       </c>
-      <c r="Z5" s="67" t="s">
+      <c r="Z5" s="46" t="s">
         <v>301</v>
       </c>
-      <c r="AA5" s="67" t="s">
+      <c r="AA5" s="46" t="s">
         <v>302</v>
       </c>
-      <c r="AB5" s="67" t="s">
+      <c r="AB5" s="46" t="s">
         <v>244</v>
       </c>
-      <c r="AC5" s="67" t="s">
+      <c r="AC5" s="46" t="s">
         <v>303</v>
       </c>
-      <c r="AD5" s="67" t="s">
+      <c r="AD5" s="46" t="s">
         <v>304</v>
       </c>
-      <c r="AE5" s="67" t="s">
+      <c r="AE5" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="AF5" s="67" t="s">
+      <c r="AF5" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="AG5" s="67" t="s">
+      <c r="AG5" s="46" t="s">
         <v>307</v>
       </c>
-      <c r="AH5" s="67" t="s">
+      <c r="AH5" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="AI5" s="67" t="s">
+      <c r="AI5" s="46" t="s">
         <v>309</v>
       </c>
-      <c r="AJ5" s="67" t="s">
+      <c r="AJ5" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="AK5" s="67" t="s">
+      <c r="AK5" s="46" t="s">
         <v>311</v>
       </c>
-      <c r="AL5" s="67" t="s">
+      <c r="AL5" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="AM5" s="67" t="s">
+      <c r="AM5" s="46" t="s">
         <v>313</v>
       </c>
-      <c r="AN5" s="67" t="s">
+      <c r="AN5" s="46" t="s">
         <v>314</v>
       </c>
-      <c r="AO5" s="67" t="s">
+      <c r="AO5" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="AP5" s="67" t="s">
+      <c r="AP5" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="AQ5" s="67" t="s">
+      <c r="AQ5" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="AR5" s="67" t="s">
+      <c r="AR5" s="46" t="s">
         <v>317</v>
       </c>
-      <c r="AS5" s="67" t="s">
+      <c r="AS5" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="AT5" s="67" t="s">
+      <c r="AT5" s="46" t="s">
         <v>319</v>
       </c>
-      <c r="AU5" s="67" t="s">
+      <c r="AU5" s="46" t="s">
         <v>320</v>
       </c>
-      <c r="AV5" s="67" t="s">
+      <c r="AV5" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="AW5" s="67" t="s">
+      <c r="AW5" s="46" t="s">
         <v>321</v>
       </c>
-      <c r="AX5" s="67" t="s">
+      <c r="AX5" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="AY5" s="67" t="s">
+      <c r="AY5" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="AZ5" s="67" t="s">
+      <c r="AZ5" s="46" t="s">
         <v>324</v>
       </c>
-      <c r="BA5" s="67" t="s">
+      <c r="BA5" s="46" t="s">
         <v>325</v>
       </c>
-      <c r="BB5" s="67" t="s">
+      <c r="BB5" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="BC5" s="67" t="s">
+      <c r="BC5" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="BD5" s="67" t="s">
+      <c r="BD5" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="BE5" s="67" t="s">
+      <c r="BE5" s="46" t="s">
         <v>329</v>
       </c>
-      <c r="BF5" s="67" t="s">
+      <c r="BF5" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="BG5" s="67" t="s">
+      <c r="BG5" s="46" t="s">
         <v>213</v>
       </c>
-      <c r="BH5" s="67" t="s">
+      <c r="BH5" s="46" t="s">
         <v>331</v>
       </c>
-      <c r="BI5" s="67" t="s">
+      <c r="BI5" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="BJ5" s="67" t="s">
+      <c r="BJ5" s="46" t="s">
         <v>333</v>
       </c>
-      <c r="BK5" s="67" t="s">
+      <c r="BK5" s="46" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:63">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="46" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:63">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="46" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:63">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="46" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="9" spans="1:63">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="46" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:63">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="46" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:63">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="46" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:63">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="46" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:63">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="46" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:63">
-      <c r="A14" s="67" t="s">
+      <c r="A14" s="46" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:63">
-      <c r="A15" s="67" t="s">
+      <c r="A15" s="46" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:63">
-      <c r="A16" s="67" t="s">
+      <c r="A16" s="46" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="46" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="46" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="46" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="46" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="67" t="s">
+      <c r="A21" s="46" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="46" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="46" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="46" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="67" t="s">
+      <c r="A25" s="46" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="67" t="s">
+      <c r="A26" s="46" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="67" t="s">
+      <c r="A27" s="46" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="67" t="s">
+      <c r="A28" s="46" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="67" t="s">
+      <c r="A29" s="46" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="67" t="s">
+      <c r="A30" s="46" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="67" t="s">
+      <c r="A31" s="46" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="67" t="s">
+      <c r="A32" s="46" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="67" t="s">
+      <c r="A33" s="46" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="67" t="s">
+      <c r="A34" s="46" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="67" t="s">
+      <c r="A35" s="46" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="67" t="s">
+      <c r="A36" s="46" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="67" t="s">
+      <c r="A37" s="46" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="67" t="s">
+      <c r="A38" s="46" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="67" t="s">
+      <c r="A39" s="46" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="67" t="s">
+      <c r="A40" s="46" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="67" t="s">
+      <c r="A41" s="46" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="46" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="67" t="s">
+      <c r="A43" s="46" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="67" t="s">
+      <c r="A44" s="46" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="67" t="s">
+      <c r="A45" s="46" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="67" t="s">
+      <c r="A46" s="46" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="67" t="s">
+      <c r="A47" s="46" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="67" t="s">
+      <c r="A48" s="46" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="67" t="s">
+      <c r="A49" s="46" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="67" t="s">
+      <c r="A50" s="46" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="67" t="s">
+      <c r="A51" s="46" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="67" t="s">
+      <c r="A52" s="46" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="67" t="s">
+      <c r="A53" s="46" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="67" t="s">
+      <c r="A54" s="46" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="46" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="46" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="67" t="s">
+      <c r="A57" s="46" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="67" t="s">
+      <c r="A58" s="46" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="67" t="s">
+      <c r="A59" s="46" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="67" t="s">
+      <c r="A60" s="46" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="46" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="67" t="s">
+      <c r="A62" s="46" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="67" t="s">
+      <c r="A63" s="46" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="67" t="s">
+      <c r="A64" s="46" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="67" t="s">
+      <c r="A65" s="46" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="67" t="s">
+      <c r="A66" s="46" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="67" t="s">
+      <c r="A67" s="46" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="46" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="67" t="s">
+      <c r="A69" s="46" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="67" t="s">
+      <c r="A70" s="46" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="67" t="s">
+      <c r="A71" s="46" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="67" t="s">
+      <c r="A72" s="46" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="67" t="s">
+      <c r="A73" s="46" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="67" t="s">
+      <c r="A74" s="46" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="67" t="s">
+      <c r="A75" s="46" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="67" t="s">
+      <c r="A76" s="46" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="67" t="s">
+      <c r="A77" s="46" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="67" t="s">
+      <c r="A78" s="46" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="67" t="s">
+      <c r="A79" s="46" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="46" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="67" t="s">
+      <c r="A81" s="46" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="67" t="s">
+      <c r="A82" s="46" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="67" t="s">
+      <c r="A83" s="46" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="67" t="s">
+      <c r="A84" s="46" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="67" t="s">
+      <c r="A85" s="46" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="67" t="s">
+      <c r="A86" s="46" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="67" t="s">
+      <c r="A87" s="46" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="67" t="s">
+      <c r="A88" s="46" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="67" t="s">
+      <c r="A89" s="46" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="67" t="s">
+      <c r="A90" s="46" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="67" t="s">
+      <c r="A91" s="46" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="67" t="s">
+      <c r="A92" s="46" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="67" t="s">
+      <c r="A93" s="46" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="67" t="s">
+      <c r="A94" s="46" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="67" t="s">
+      <c r="A95" s="46" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="67" t="s">
+      <c r="A96" s="46" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="67" t="s">
+      <c r="A97" s="46" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="67" t="s">
+      <c r="A98" s="46" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="46" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="67" t="s">
+      <c r="A100" s="46" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="67" t="s">
+      <c r="A101" s="46" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="67" t="s">
+      <c r="A102" s="46" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="67" t="s">
+      <c r="A103" s="46" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="67" t="s">
+      <c r="A104" s="46" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="67" t="s">
+      <c r="A105" s="46" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="67" t="s">
+      <c r="A106" s="46" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="67" t="s">
+      <c r="A107" s="46" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="67" t="s">
+      <c r="A108" s="46" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="67" t="s">
+      <c r="A109" s="46" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="67" t="s">
+      <c r="A110" s="46" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="67" t="s">
+      <c r="A111" s="46" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="67" t="s">
+      <c r="A112" s="46" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="67" t="s">
+      <c r="A113" s="46" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="67" t="s">
+      <c r="A114" s="46" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="67" t="s">
+      <c r="A115" s="46" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="67" t="s">
+      <c r="A116" s="46" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="67" t="s">
+      <c r="A117" s="46" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="67" t="s">
+      <c r="A118" s="46" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="67" t="s">
+      <c r="A119" s="46" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="67" t="s">
+      <c r="A120" s="46" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="67" t="s">
+      <c r="A121" s="46" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="67" t="s">
+      <c r="A122" s="46" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="67" t="s">
+      <c r="A123" s="46" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="67" t="s">
+      <c r="A124" s="46" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="67" t="s">
+      <c r="A125" s="46" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="67" t="s">
+      <c r="A126" s="46" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="67" t="s">
+      <c r="A127" s="46" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="67" t="s">
+      <c r="A128" s="46" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="67" t="s">
+      <c r="A129" s="46" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="67" t="s">
+      <c r="A130" s="46" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="67" t="s">
+      <c r="A131" s="46" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="67" t="s">
+      <c r="A132" s="46" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="67" t="s">
+      <c r="A133" s="46" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="67" t="s">
+      <c r="A134" s="46" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="67" t="s">
+      <c r="A135" s="46" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="67" t="s">
+      <c r="A136" s="46" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="67" t="s">
+      <c r="A137" s="46" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="67" t="s">
+      <c r="A138" s="46" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="67" t="s">
+      <c r="A139" s="46" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="67" t="s">
+      <c r="A140" s="46" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="67" t="s">
+      <c r="A141" s="46" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="67" t="s">
+      <c r="A142" s="46" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="67" t="s">
+      <c r="A143" s="46" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="67" t="s">
+      <c r="A144" s="46" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="67" t="s">
+      <c r="A145" s="46" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="67" t="s">
+      <c r="A146" s="46" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="67" t="s">
+      <c r="A147" s="46" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="67" t="s">
+      <c r="A148" s="46" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="67" t="s">
+      <c r="A149" s="46" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="67" t="s">
+      <c r="A150" s="46" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="67" t="s">
+      <c r="A151" s="46" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="67" t="s">
+      <c r="A152" s="46" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="67" t="s">
+      <c r="A153" s="46" t="s">
         <v>482</v>
       </c>
     </row>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1680,6 +1680,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="dotted">
         <color auto="1"/>
       </left>
@@ -1779,15 +1788,6 @@
         <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="dashed">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1948,20 +1948,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1969,35 +1969,35 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2036,7 +2036,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2076,18 +2076,18 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2434,7 +2434,7 @@
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="37">
@@ -2457,6 +2457,7 @@
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>0</v>
       </c>
+      <c r="E3" s="20"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -2481,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="20"/>
+      <c r="D5" s="21"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="36">
@@ -2503,7 +2504,7 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="J7" s="21"/>
+      <c r="J7" s="22"/>
     </row>
     <row r="8" spans="2:22">
       <c r="B8" s="36">
@@ -2522,7 +2523,7 @@
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-      <c r="J8" s="22"/>
+      <c r="J8" s="23"/>
       <c r="K8" s="1">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,59,FALSE))</f>
         <v>0</v>
@@ -2545,12 +2546,12 @@
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-      <c r="J9" s="23"/>
+      <c r="J9" s="24"/>
     </row>
     <row r="10" spans="2:22" ht="13.5" customHeight="1"/>
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B11" s="24"/>
-      <c r="C11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="41">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>0</v>
@@ -2639,8 +2640,8 @@
       <c r="V13" s="57"/>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="28"/>
       <c r="D14" s="10"/>
       <c r="E14" s="11"/>
       <c r="F14" s="10"/>
@@ -2684,10 +2685,10 @@
       <c r="D15" s="33">
         <v>0</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="30"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="31"/>
       <c r="J15" s="58" t="s">
         <v>4</v>
       </c>
@@ -2726,13 +2727,13 @@
       <c r="D16" s="33">
         <v>0</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
       <c r="G16" s="50">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="30"/>
+      <c r="H16" s="31"/>
       <c r="J16" s="58" t="s">
         <v>6</v>
       </c>
@@ -2771,13 +2772,13 @@
       <c r="D17" s="33">
         <v>0</v>
       </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
       <c r="G17" s="50">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="30"/>
+      <c r="H17" s="31"/>
       <c r="J17" s="58" t="s">
         <v>8</v>
       </c>
@@ -2816,13 +2817,13 @@
       <c r="D18" s="33">
         <v>0</v>
       </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
       <c r="G18" s="50">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="30"/>
+      <c r="H18" s="31"/>
       <c r="J18" s="58" t="s">
         <v>10</v>
       </c>
@@ -2861,13 +2862,13 @@
       <c r="D19" s="33">
         <v>0</v>
       </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
       <c r="G19" s="50">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="30"/>
+      <c r="H19" s="31"/>
       <c r="J19" s="58" t="s">
         <v>12</v>
       </c>
@@ -2919,7 +2920,7 @@
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="31"/>
+      <c r="H20" s="32"/>
       <c r="J20" s="58" t="s">
         <v>14</v>
       </c>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2917,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="53">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>
       <c r="H20" s="32"/>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2410,14 +2410,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="34">
+      <c r="B1" s="34" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
-        <v>0</v>
+        <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="J1" s="35">
+      <c r="J1" s="35" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
-        <v>0</v>
+        <v>Tipp:</v>
       </c>
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
@@ -2430,16 +2430,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="36">
+      <c r="D2" s="36" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
-        <v>0</v>
+        <v>Sprache</v>
       </c>
       <c r="E2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="37">
+      <c r="J2" s="37" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
-        <v>0</v>
+        <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -2448,14 +2448,14 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="34">
+      <c r="B3" s="34" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
-        <v>0</v>
+        <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="36">
+      <c r="D3" s="36" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
-        <v>0</v>
+        <v>Lokalwährung</v>
       </c>
       <c r="E3" s="20"/>
       <c r="J3" s="4"/>
@@ -2466,9 +2466,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="38">
+      <c r="J4" s="38" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
-        <v>0</v>
+        <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -2477,17 +2477,17 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="36">
+      <c r="B5" s="36" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
-        <v>0</v>
+        <v>Projektnummer</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="21"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="36">
+      <c r="B6" s="36" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
-        <v>0</v>
+        <v>Projekttitel</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="7"/>
@@ -2507,42 +2507,42 @@
       <c r="J7" s="22"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="36">
+      <c r="B8" s="36" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
-        <v>0</v>
+        <v>Projektlaufzeit</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="39">
+      <c r="D8" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
-        <v>0</v>
+        <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="39">
+      <c r="F8" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
-        <v>0</v>
+        <v>bis (TT MM JJJJ):</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="J8" s="23"/>
-      <c r="K8" s="1">
+      <c r="K8" s="1" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,59,FALSE))</f>
-        <v>0</v>
+        <v>Ausfüllbare Felder sind in den Farben links</v>
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="36">
+      <c r="B9" s="36" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
-        <v>0</v>
+        <v>Aktueller Berichtszeitraum</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="39">
+      <c r="D9" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
-        <v>0</v>
+        <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="39">
+      <c r="F9" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
-        <v>0</v>
+        <v>bis (TT MM JJJJ):</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -2552,38 +2552,38 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="25"/>
       <c r="C11" s="26"/>
-      <c r="D11" s="41">
+      <c r="D11" s="41" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="42">
+        <v>Bewilligtes Budget</v>
+      </c>
+      <c r="E11" s="42" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="41">
+        <v>Einnahmen im Berichtszeitraum</v>
+      </c>
+      <c r="F11" s="41" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="41">
+        <v>Einnahmen der gesamten Projektlaufzeit</v>
+      </c>
+      <c r="G11" s="41" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="43">
+        <v>% erhaltene Einnahmen</v>
+      </c>
+      <c r="H11" s="43" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="40">
+        <v>Begründung der Budgetüber- oder unterschreitung</v>
+      </c>
+      <c r="J11" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
-        <v>0</v>
+        <v>KMW Mittel*</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="54"/>
       <c r="M11" s="54"/>
       <c r="N11" s="54"/>
       <c r="O11" s="55"/>
-      <c r="Q11" s="40">
+      <c r="Q11" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
-        <v>0</v>
+        <v>KMW Mittel*</v>
       </c>
       <c r="R11" s="9"/>
       <c r="S11" s="54"/>
@@ -2592,9 +2592,9 @@
       <c r="V11" s="55"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="44">
+      <c r="B12" s="44" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
-        <v>0</v>
+        <v>EINNAHMEN</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="10"/>
@@ -2616,9 +2616,9 @@
       <c r="V12" s="57"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="45">
+      <c r="B13" s="45" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
-        <v>0</v>
+        <v>(in lokaler Währung)</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="10"/>
@@ -2650,9 +2650,9 @@
       <c r="J14" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="59">
+      <c r="K14" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L14" s="60"/>
       <c r="M14" s="61"/>
@@ -2664,9 +2664,9 @@
       <c r="Q14" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="59">
+      <c r="R14" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S14" s="60"/>
       <c r="T14" s="61"/>
@@ -2677,9 +2677,9 @@
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="48">
+      <c r="B15" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
-        <v>0</v>
+        <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="33">
@@ -2692,9 +2692,9 @@
       <c r="J15" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="K15" s="59">
+      <c r="K15" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L15" s="60"/>
       <c r="M15" s="61"/>
@@ -2706,9 +2706,9 @@
       <c r="Q15" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="R15" s="59">
+      <c r="R15" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S15" s="60"/>
       <c r="T15" s="61"/>
@@ -2719,9 +2719,9 @@
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="49">
+      <c r="B16" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
-        <v>0</v>
+        <v>Lokale Eigenleistung</v>
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="33">
@@ -2737,9 +2737,9 @@
       <c r="J16" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="59">
+      <c r="K16" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L16" s="60"/>
       <c r="M16" s="61"/>
@@ -2751,9 +2751,9 @@
       <c r="Q16" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="R16" s="59">
+      <c r="R16" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S16" s="60"/>
       <c r="T16" s="61"/>
@@ -2764,9 +2764,9 @@
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="49">
+      <c r="B17" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
-        <v>0</v>
+        <v>Beiträge von dritter Seite</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="33">
@@ -2782,9 +2782,9 @@
       <c r="J17" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="59">
+      <c r="K17" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L17" s="60"/>
       <c r="M17" s="61"/>
@@ -2796,9 +2796,9 @@
       <c r="Q17" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="R17" s="59">
+      <c r="R17" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S17" s="60"/>
       <c r="T17" s="61"/>
@@ -2809,9 +2809,9 @@
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="49">
+      <c r="B18" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
-        <v>0</v>
+        <v>KMW Mittel*</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="33">
@@ -2827,9 +2827,9 @@
       <c r="J18" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="59">
+      <c r="K18" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L18" s="60"/>
       <c r="M18" s="61"/>
@@ -2841,9 +2841,9 @@
       <c r="Q18" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="R18" s="59">
+      <c r="R18" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S18" s="60"/>
       <c r="T18" s="61"/>
@@ -2854,9 +2854,9 @@
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="49">
+      <c r="B19" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
-        <v>0</v>
+        <v>Zinserträge</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="33">
@@ -2872,9 +2872,9 @@
       <c r="J19" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="59">
+      <c r="K19" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L19" s="60"/>
       <c r="M19" s="61"/>
@@ -2886,9 +2886,9 @@
       <c r="Q19" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="R19" s="59">
+      <c r="R19" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S19" s="60"/>
       <c r="T19" s="61"/>
@@ -2899,9 +2899,9 @@
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="51">
+      <c r="B20" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
-        <v>0</v>
+        <v>GESAMT</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="52">
@@ -2924,9 +2924,9 @@
       <c r="J20" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="K20" s="59">
+      <c r="K20" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L20" s="60"/>
       <c r="M20" s="61"/>
@@ -2938,9 +2938,9 @@
       <c r="Q20" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="R20" s="59">
+      <c r="R20" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S20" s="60"/>
       <c r="T20" s="61"/>
@@ -2954,9 +2954,9 @@
       <c r="J21" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="K21" s="59">
+      <c r="K21" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L21" s="60"/>
       <c r="M21" s="61"/>
@@ -2968,9 +2968,9 @@
       <c r="Q21" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="R21" s="59">
+      <c r="R21" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S21" s="60"/>
       <c r="T21" s="61"/>
@@ -2984,9 +2984,9 @@
       <c r="J22" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="59">
+      <c r="K22" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L22" s="60"/>
       <c r="M22" s="61"/>
@@ -2998,9 +2998,9 @@
       <c r="Q22" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="R22" s="59">
+      <c r="R22" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S22" s="60"/>
       <c r="T22" s="61"/>
@@ -3014,9 +3014,9 @@
       <c r="J23" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="59">
+      <c r="K23" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L23" s="60"/>
       <c r="M23" s="61"/>
@@ -3028,9 +3028,9 @@
       <c r="Q23" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="59">
+      <c r="R23" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S23" s="60"/>
       <c r="T23" s="61"/>
@@ -3044,9 +3044,9 @@
       <c r="J24" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="59">
+      <c r="K24" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L24" s="60"/>
       <c r="M24" s="61"/>
@@ -3058,9 +3058,9 @@
       <c r="Q24" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="R24" s="59">
+      <c r="R24" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S24" s="60"/>
       <c r="T24" s="61"/>
@@ -3074,9 +3074,9 @@
       <c r="J25" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="59">
+      <c r="K25" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L25" s="60"/>
       <c r="M25" s="61"/>
@@ -3088,9 +3088,9 @@
       <c r="Q25" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="R25" s="59">
+      <c r="R25" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S25" s="60"/>
       <c r="T25" s="61"/>
@@ -3104,9 +3104,9 @@
       <c r="J26" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="59">
+      <c r="K26" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L26" s="60"/>
       <c r="M26" s="61"/>
@@ -3118,9 +3118,9 @@
       <c r="Q26" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="R26" s="59">
+      <c r="R26" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S26" s="60"/>
       <c r="T26" s="61"/>
@@ -3134,9 +3134,9 @@
       <c r="J27" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="K27" s="59">
+      <c r="K27" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L27" s="60"/>
       <c r="M27" s="61"/>
@@ -3148,9 +3148,9 @@
       <c r="Q27" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="59">
+      <c r="R27" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S27" s="60"/>
       <c r="T27" s="61"/>
@@ -3164,9 +3164,9 @@
       <c r="J28" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="59">
+      <c r="K28" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L28" s="60"/>
       <c r="M28" s="61"/>
@@ -3178,9 +3178,9 @@
       <c r="Q28" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="R28" s="59">
+      <c r="R28" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S28" s="60"/>
       <c r="T28" s="61"/>
@@ -3194,9 +3194,9 @@
       <c r="J29" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="K29" s="59">
+      <c r="K29" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L29" s="60"/>
       <c r="M29" s="61"/>
@@ -3208,9 +3208,9 @@
       <c r="Q29" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="R29" s="59">
+      <c r="R29" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S29" s="60"/>
       <c r="T29" s="61"/>
@@ -3224,9 +3224,9 @@
       <c r="J30" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="59">
+      <c r="K30" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L30" s="60"/>
       <c r="M30" s="61"/>
@@ -3238,9 +3238,9 @@
       <c r="Q30" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="59">
+      <c r="R30" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S30" s="60"/>
       <c r="T30" s="61"/>
@@ -3254,9 +3254,9 @@
       <c r="J31" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="K31" s="64">
+      <c r="K31" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="L31" s="65"/>
       <c r="M31" s="66"/>
@@ -3268,9 +3268,9 @@
       <c r="Q31" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="R31" s="64">
+      <c r="R31" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
-        <v>0</v>
+        <v>Rate</v>
       </c>
       <c r="S31" s="65"/>
       <c r="T31" s="66"/>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="484">
   <si>
     <t>_de</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>https://www.kindermissionswerk.org/fuer-partner/service</t>
+  </si>
+  <si>
+    <t>Euro</t>
   </si>
   <si>
     <t>AFN</t>
@@ -1793,6 +1796,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -1811,50 +1858,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1873,7 +1876,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1991,6 +1994,10 @@
     <xf numFmtId="165" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="165" fontId="1" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -2028,8 +2035,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2040,8 +2048,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -2051,14 +2062,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2090,6 +2098,7 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2410,12 +2419,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="34" t="str">
+      <c r="B1" s="35" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="J1" s="35" t="str">
+      <c r="J1" s="36" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
@@ -2430,14 +2439,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="36" t="str">
+      <c r="D2" s="37" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
       <c r="E2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="37" t="str">
+      <c r="J2" s="38" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2448,12 +2457,12 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="34" t="str">
+      <c r="B3" s="35" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="36" t="str">
+      <c r="D3" s="37" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
@@ -2466,7 +2475,7 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="38" t="str">
+      <c r="J4" s="39" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2477,7 +2486,7 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="36" t="str">
+      <c r="B5" s="37" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
@@ -2485,7 +2494,7 @@
       <c r="D5" s="21"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="36" t="str">
+      <c r="B6" s="37" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
@@ -2507,17 +2516,17 @@
       <c r="J7" s="22"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="36" t="str">
+      <c r="B8" s="37" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="39" t="str">
+      <c r="D8" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="39" t="str">
+      <c r="F8" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2530,17 +2539,17 @@
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="36" t="str">
+      <c r="B9" s="37" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="39" t="str">
+      <c r="D9" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="39" t="str">
+      <c r="F9" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2552,27 +2561,27 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="25"/>
       <c r="C11" s="26"/>
-      <c r="D11" s="41" t="str">
+      <c r="D11" s="42" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="42" t="str">
+      <c r="E11" s="43" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="41" t="str">
+      <c r="F11" s="42" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="41" t="str">
+      <c r="G11" s="42" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="43" t="str">
+      <c r="H11" s="44" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="40" t="str">
+      <c r="J11" s="41" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2581,7 +2590,7 @@
       <c r="M11" s="54"/>
       <c r="N11" s="54"/>
       <c r="O11" s="55"/>
-      <c r="Q11" s="40" t="str">
+      <c r="Q11" s="41" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2592,7 +2601,7 @@
       <c r="V11" s="55"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="44" t="str">
+      <c r="B12" s="45" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
@@ -2616,7 +2625,7 @@
       <c r="V12" s="57"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="45" t="str">
+      <c r="B13" s="46" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
@@ -2628,16 +2637,40 @@
       <c r="H13" s="12"/>
       <c r="J13" s="56"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="57"/>
+      <c r="L13" s="47" t="str">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
+        <v>Datum</v>
+      </c>
+      <c r="M13" s="47" t="str">
+        <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE)</f>
+        <v>Euro</v>
+      </c>
+      <c r="N13" s="47" t="str">
+        <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
+        <v>Lokalwährung</v>
+      </c>
+      <c r="O13" s="47" t="str">
+        <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE)</f>
+        <v>WK</v>
+      </c>
       <c r="Q13" s="56"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="57"/>
+      <c r="S13" s="47" t="str">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
+        <v>Datum</v>
+      </c>
+      <c r="T13" s="47" t="str">
+        <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE)</f>
+        <v>Euro</v>
+      </c>
+      <c r="U13" s="47" t="str">
+        <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
+        <v>Lokalwährung</v>
+      </c>
+      <c r="V13" s="47" t="str">
+        <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE)</f>
+        <v>WK</v>
+      </c>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="27"/>
@@ -2682,7 +2715,7 @@
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
       <c r="C15" s="15"/>
-      <c r="D15" s="33">
+      <c r="D15" s="34">
         <v>0</v>
       </c>
       <c r="E15" s="29"/>
@@ -2724,7 +2757,7 @@
         <v>Lokale Eigenleistung</v>
       </c>
       <c r="C16" s="16"/>
-      <c r="D16" s="33">
+      <c r="D16" s="34">
         <v>0</v>
       </c>
       <c r="E16" s="29"/>
@@ -2769,7 +2802,7 @@
         <v>Beiträge von dritter Seite</v>
       </c>
       <c r="C17" s="16"/>
-      <c r="D17" s="33">
+      <c r="D17" s="34">
         <v>0</v>
       </c>
       <c r="E17" s="29"/>
@@ -2814,7 +2847,7 @@
         <v>KMW Mittel*</v>
       </c>
       <c r="C18" s="16"/>
-      <c r="D18" s="33">
+      <c r="D18" s="34">
         <v>0</v>
       </c>
       <c r="E18" s="29"/>
@@ -2859,7 +2892,7 @@
         <v>Zinserträge</v>
       </c>
       <c r="C19" s="16"/>
-      <c r="D19" s="33">
+      <c r="D19" s="34">
         <v>0</v>
       </c>
       <c r="E19" s="29"/>
@@ -3325,1702 +3358,1717 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BK153"/>
+  <dimension ref="A1:BL153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:63">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:64">
+      <c r="A1" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="46" t="s">
+      <c r="H1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="46" t="s">
+      <c r="L1" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="N1" s="46" t="s">
+      <c r="N1" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="O1" s="46" t="s">
+      <c r="O1" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="46" t="s">
+      <c r="P1" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="46" t="s">
+      <c r="Q1" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="R1" s="46" t="s">
+      <c r="R1" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="S1" s="46" t="s">
+      <c r="S1" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="U1" s="46" t="s">
+      <c r="U1" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="V1" s="46" t="s">
+      <c r="V1" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="W1" s="46" t="s">
+      <c r="W1" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="X1" s="46" t="s">
+      <c r="X1" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="Y1" s="46" t="s">
+      <c r="Y1" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="Z1" s="46" t="s">
+      <c r="Z1" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="AA1" s="46" t="s">
+      <c r="AA1" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="AB1" s="46" t="s">
+      <c r="AB1" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="AC1" s="46" t="s">
+      <c r="AC1" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="AD1" s="46" t="s">
+      <c r="AD1" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="AE1" s="46" t="s">
+      <c r="AE1" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="AF1" s="46" t="s">
+      <c r="AF1" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="AG1" s="46" t="s">
+      <c r="AG1" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="AH1" s="46" t="s">
+      <c r="AH1" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="AI1" s="46" t="s">
+      <c r="AI1" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="AJ1" s="46" t="s">
+      <c r="AJ1" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="AK1" s="46" t="s">
+      <c r="AK1" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="AL1" s="46" t="s">
+      <c r="AL1" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="AM1" s="46" t="s">
+      <c r="AM1" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="AN1" s="46" t="s">
+      <c r="AN1" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="AO1" s="46" t="s">
+      <c r="AO1" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="AP1" s="46" t="s">
+      <c r="AP1" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="AQ1" s="46" t="s">
+      <c r="AQ1" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="AR1" s="46" t="s">
+      <c r="AR1" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="AS1" s="46" t="s">
+      <c r="AS1" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="AT1" s="46" t="s">
+      <c r="AT1" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="AU1" s="46" t="s">
+      <c r="AU1" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="AV1" s="46" t="s">
+      <c r="AV1" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="AW1" s="46" t="s">
+      <c r="AW1" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="AX1" s="46" t="s">
+      <c r="AX1" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="AY1" s="46" t="s">
+      <c r="AY1" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="AZ1" s="46" t="s">
+      <c r="AZ1" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="BA1" s="46" t="s">
+      <c r="BA1" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="BB1" s="46" t="s">
+      <c r="BB1" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="BC1" s="46" t="s">
+      <c r="BC1" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="BD1" s="46" t="s">
+      <c r="BD1" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="BE1" s="46" t="s">
+      <c r="BE1" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="BF1" s="46" t="s">
+      <c r="BF1" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="BG1" s="46" t="s">
+      <c r="BG1" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="BH1" s="46" t="s">
+      <c r="BH1" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="BI1" s="46" t="s">
+      <c r="BI1" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="BJ1" s="46" t="s">
+      <c r="BJ1" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="BK1" s="46" t="s">
+      <c r="BK1" s="68" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" spans="1:63">
-      <c r="A2" s="46" t="s">
+      <c r="BL1" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="46" t="s">
+    </row>
+    <row r="2" spans="1:64">
+      <c r="A2" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="B2" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="C2" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="D2" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="E2" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="F2" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="H2" s="46" t="s">
+      <c r="G2" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="46" t="s">
+      <c r="H2" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="46" t="s">
+      <c r="I2" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="46" t="s">
+      <c r="J2" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="L2" s="46" t="s">
+      <c r="K2" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="M2" s="46" t="s">
+      <c r="L2" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="N2" s="46" t="s">
+      <c r="M2" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="O2" s="46" t="s">
+      <c r="N2" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="Q2" s="46" t="s">
+      <c r="P2" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="R2" s="46" t="s">
+      <c r="Q2" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="S2" s="46" t="s">
+      <c r="R2" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="T2" s="46" t="s">
+      <c r="S2" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="U2" s="46" t="s">
+      <c r="T2" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="V2" s="46" t="s">
+      <c r="U2" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="W2" s="46" t="s">
+      <c r="V2" s="68" t="s">
         <v>122</v>
       </c>
-      <c r="X2" s="46" t="s">
+      <c r="W2" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="Y2" s="46" t="s">
+      <c r="X2" s="68" t="s">
         <v>124</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="Y2" s="68" t="s">
         <v>125</v>
       </c>
-      <c r="AA2" s="46" t="s">
+      <c r="Z2" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="AB2" s="46" t="s">
+      <c r="AA2" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="AC2" s="46" t="s">
+      <c r="AB2" s="68" t="s">
         <v>128</v>
       </c>
-      <c r="AD2" s="46" t="s">
+      <c r="AC2" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="AE2" s="46" t="s">
+      <c r="AD2" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="AF2" s="46" t="s">
+      <c r="AE2" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="AG2" s="46" t="s">
+      <c r="AF2" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="AH2" s="46" t="s">
+      <c r="AG2" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="AI2" s="46" t="s">
+      <c r="AH2" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="AJ2" s="46" t="s">
+      <c r="AI2" s="68" t="s">
         <v>135</v>
       </c>
-      <c r="AK2" s="46" t="s">
+      <c r="AJ2" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="AL2" s="46" t="s">
+      <c r="AK2" s="68" t="s">
         <v>137</v>
       </c>
-      <c r="AM2" s="46" t="s">
+      <c r="AL2" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="AN2" s="46" t="s">
+      <c r="AM2" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="AO2" s="46" t="s">
+      <c r="AN2" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO2" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="AP2" s="46" t="s">
+      <c r="AP2" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ2" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="AR2" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="AS2" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="AT2" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="AU2" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="AV2" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW2" s="68" t="s">
+        <v>146</v>
+      </c>
+      <c r="AX2" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="AY2" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="AZ2" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="BA2" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="BB2" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="BC2" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="BD2" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="BE2" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="BF2" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="BG2" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="BH2" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="BI2" s="68" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ2" s="68" t="s">
+        <v>159</v>
+      </c>
+      <c r="BK2" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="BL2" s="68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:64">
+      <c r="A3" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="F3" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="J3" s="68" t="s">
+        <v>169</v>
+      </c>
+      <c r="K3" s="68" t="s">
+        <v>170</v>
+      </c>
+      <c r="L3" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="M3" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="N3" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="O3" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="P3" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q3" s="68" t="s">
+        <v>176</v>
+      </c>
+      <c r="R3" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="S3" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="T3" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="U3" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="V3" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="W3" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="X3" s="68" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y3" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z3" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA3" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB3" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="AC3" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD3" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="AE3" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="AF3" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="AG3" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH3" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI3" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="AJ3" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK3" s="68" t="s">
+        <v>195</v>
+      </c>
+      <c r="AL3" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM3" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AN3" s="68" t="s">
         <v>140</v>
       </c>
-      <c r="AQ2" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="AR2" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="AS2" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="AT2" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="AU2" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="AV2" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW2" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="AX2" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="AY2" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="AZ2" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="BA2" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="BB2" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="BC2" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="BD2" s="46" t="s">
-        <v>152</v>
-      </c>
-      <c r="BE2" s="46" t="s">
-        <v>153</v>
-      </c>
-      <c r="BF2" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="BG2" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="BH2" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="BI2" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="BJ2" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="BK2" s="46" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="3" spans="1:63">
-      <c r="A3" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="D3" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="E3" s="46" t="s">
-        <v>164</v>
-      </c>
-      <c r="F3" s="46" t="s">
-        <v>165</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="H3" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="I3" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="J3" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="K3" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="L3" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="M3" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="N3" s="46" t="s">
-        <v>172</v>
-      </c>
-      <c r="O3" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="P3" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q3" s="46" t="s">
-        <v>175</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>177</v>
-      </c>
-      <c r="T3" s="46" t="s">
-        <v>178</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="V3" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="W3" s="46" t="s">
+      <c r="AO3" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP3" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="AQ3" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="AR3" s="68" t="s">
+        <v>199</v>
+      </c>
+      <c r="AS3" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="AT3" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU3" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="AV3" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="AW3" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="AX3" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="AY3" s="68" t="s">
+        <v>206</v>
+      </c>
+      <c r="AZ3" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="BA3" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="BB3" s="68" t="s">
+        <v>209</v>
+      </c>
+      <c r="BC3" s="68" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD3" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE3" s="68" t="s">
+        <v>212</v>
+      </c>
+      <c r="BF3" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="BG3" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="BH3" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="BI3" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="BJ3" s="68" t="s">
+        <v>217</v>
+      </c>
+      <c r="BK3" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="BL3" s="68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:64">
+      <c r="A4" s="68" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="68" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="G4" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="H4" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="I4" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="J4" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="K4" s="68" t="s">
+        <v>229</v>
+      </c>
+      <c r="L4" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="M4" s="68" t="s">
+        <v>231</v>
+      </c>
+      <c r="N4" s="68" t="s">
+        <v>232</v>
+      </c>
+      <c r="O4" s="68" t="s">
+        <v>233</v>
+      </c>
+      <c r="P4" s="68" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q4" s="68" t="s">
+        <v>235</v>
+      </c>
+      <c r="R4" s="68" t="s">
+        <v>236</v>
+      </c>
+      <c r="S4" s="68" t="s">
+        <v>237</v>
+      </c>
+      <c r="T4" s="68" t="s">
+        <v>238</v>
+      </c>
+      <c r="U4" s="68" t="s">
+        <v>239</v>
+      </c>
+      <c r="V4" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="W4" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="X4" s="68" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y4" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z4" s="68" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA4" s="68" t="s">
+        <v>244</v>
+      </c>
+      <c r="AB4" s="68" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC4" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="AD4" s="68" t="s">
+        <v>247</v>
+      </c>
+      <c r="AE4" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="AF4" s="68" t="s">
+        <v>249</v>
+      </c>
+      <c r="AG4" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="AH4" s="68" t="s">
+        <v>251</v>
+      </c>
+      <c r="AI4" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ4" s="68" t="s">
+        <v>253</v>
+      </c>
+      <c r="AK4" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="AL4" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="AM4" s="68" t="s">
+        <v>256</v>
+      </c>
+      <c r="AN4" s="68" t="s">
+        <v>257</v>
+      </c>
+      <c r="AO4" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="AP4" s="68" t="s">
+        <v>259</v>
+      </c>
+      <c r="AQ4" s="68" t="s">
         <v>122</v>
       </c>
-      <c r="X3" s="46" t="s">
+      <c r="AR4" s="68" t="s">
+        <v>260</v>
+      </c>
+      <c r="AS4" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="AT4" s="68" t="s">
+        <v>262</v>
+      </c>
+      <c r="AU4" s="68" t="s">
+        <v>263</v>
+      </c>
+      <c r="AV4" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="AW4" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="AX4" s="68" t="s">
+        <v>266</v>
+      </c>
+      <c r="AY4" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="AZ4" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="BA4" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="BB4" s="68" t="s">
+        <v>270</v>
+      </c>
+      <c r="BC4" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="BD4" s="68" t="s">
+        <v>272</v>
+      </c>
+      <c r="BE4" s="68" t="s">
+        <v>273</v>
+      </c>
+      <c r="BF4" s="68" t="s">
+        <v>274</v>
+      </c>
+      <c r="BG4" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="BH4" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="BI4" s="68" t="s">
+        <v>276</v>
+      </c>
+      <c r="BJ4" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="BK4" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="BL4" s="68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:64">
+      <c r="A5" s="68" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>282</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="G5" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="H5" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="I5" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" s="68" t="s">
+        <v>287</v>
+      </c>
+      <c r="K5" s="68" t="s">
+        <v>288</v>
+      </c>
+      <c r="L5" s="68" t="s">
+        <v>289</v>
+      </c>
+      <c r="M5" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="N5" s="68" t="s">
+        <v>291</v>
+      </c>
+      <c r="O5" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="P5" s="68" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q5" s="68" t="s">
+        <v>294</v>
+      </c>
+      <c r="R5" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="S5" s="68" t="s">
+        <v>296</v>
+      </c>
+      <c r="T5" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="U5" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="V5" s="68" t="s">
         <v>181</v>
       </c>
-      <c r="Y3" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA3" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="AB3" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="AC3" s="46" t="s">
-        <v>186</v>
-      </c>
-      <c r="AD3" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="AE3" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="AF3" s="46" t="s">
-        <v>189</v>
-      </c>
-      <c r="AG3" s="46" t="s">
-        <v>190</v>
-      </c>
-      <c r="AH3" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AI3" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="AJ3" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK3" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="AL3" s="46" t="s">
-        <v>195</v>
-      </c>
-      <c r="AM3" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="AN3" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="AO3" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="AP3" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="AQ3" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="AR3" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="AS3" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="AT3" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="AU3" s="46" t="s">
-        <v>201</v>
-      </c>
-      <c r="AV3" s="46" t="s">
-        <v>202</v>
-      </c>
-      <c r="AW3" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AX3" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="AY3" s="46" t="s">
-        <v>205</v>
-      </c>
-      <c r="AZ3" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="BA3" s="46" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB3" s="46" t="s">
-        <v>208</v>
-      </c>
-      <c r="BC3" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="BD3" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE3" s="46" t="s">
-        <v>211</v>
-      </c>
-      <c r="BF3" s="46" t="s">
-        <v>212</v>
-      </c>
-      <c r="BG3" s="46" t="s">
-        <v>213</v>
-      </c>
-      <c r="BH3" s="46" t="s">
+      <c r="W5" s="68" t="s">
+        <v>299</v>
+      </c>
+      <c r="X5" s="68" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y5" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="Z5" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA5" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="AB5" s="68" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC5" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="AD5" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE5" s="68" t="s">
+        <v>306</v>
+      </c>
+      <c r="AF5" s="68" t="s">
+        <v>307</v>
+      </c>
+      <c r="AG5" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH5" s="68" t="s">
+        <v>309</v>
+      </c>
+      <c r="AI5" s="68" t="s">
+        <v>310</v>
+      </c>
+      <c r="AJ5" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="AK5" s="68" t="s">
+        <v>312</v>
+      </c>
+      <c r="AL5" s="68" t="s">
+        <v>313</v>
+      </c>
+      <c r="AM5" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN5" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="AO5" s="68" t="s">
+        <v>316</v>
+      </c>
+      <c r="AP5" s="68" t="s">
+        <v>317</v>
+      </c>
+      <c r="AQ5" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="AR5" s="68" t="s">
+        <v>318</v>
+      </c>
+      <c r="AS5" s="68" t="s">
+        <v>319</v>
+      </c>
+      <c r="AT5" s="68" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU5" s="68" t="s">
+        <v>321</v>
+      </c>
+      <c r="AV5" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="AW5" s="68" t="s">
+        <v>322</v>
+      </c>
+      <c r="AX5" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="AY5" s="68" t="s">
+        <v>324</v>
+      </c>
+      <c r="AZ5" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="BA5" s="68" t="s">
+        <v>326</v>
+      </c>
+      <c r="BB5" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="BC5" s="68" t="s">
+        <v>328</v>
+      </c>
+      <c r="BD5" s="68" t="s">
+        <v>329</v>
+      </c>
+      <c r="BE5" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="BF5" s="68" t="s">
+        <v>331</v>
+      </c>
+      <c r="BG5" s="68" t="s">
         <v>214</v>
       </c>
-      <c r="BI3" s="46" t="s">
-        <v>215</v>
-      </c>
-      <c r="BJ3" s="46" t="s">
-        <v>216</v>
-      </c>
-      <c r="BK3" s="46" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:63">
-      <c r="A4" s="46" t="s">
-        <v>218</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>219</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="E4" s="46" t="s">
-        <v>222</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>223</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>224</v>
-      </c>
-      <c r="H4" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="I4" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="J4" s="46" t="s">
-        <v>227</v>
-      </c>
-      <c r="K4" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="L4" s="46" t="s">
-        <v>229</v>
-      </c>
-      <c r="M4" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="N4" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="O4" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="P4" s="46" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q4" s="46" t="s">
-        <v>234</v>
-      </c>
-      <c r="R4" s="46" t="s">
-        <v>235</v>
-      </c>
-      <c r="S4" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="T4" s="46" t="s">
-        <v>237</v>
-      </c>
-      <c r="U4" s="46" t="s">
-        <v>238</v>
-      </c>
-      <c r="V4" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="W4" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="X4" s="46" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y4" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z4" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="AA4" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="AB4" s="46" t="s">
-        <v>244</v>
-      </c>
-      <c r="AC4" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="AD4" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="AE4" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="AF4" s="46" t="s">
-        <v>248</v>
-      </c>
-      <c r="AG4" s="46" t="s">
-        <v>249</v>
-      </c>
-      <c r="AH4" s="46" t="s">
-        <v>250</v>
-      </c>
-      <c r="AI4" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="AJ4" s="46" t="s">
-        <v>252</v>
-      </c>
-      <c r="AK4" s="46" t="s">
-        <v>253</v>
-      </c>
-      <c r="AL4" s="46" t="s">
-        <v>254</v>
-      </c>
-      <c r="AM4" s="46" t="s">
-        <v>255</v>
-      </c>
-      <c r="AN4" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="AO4" s="46" t="s">
-        <v>257</v>
-      </c>
-      <c r="AP4" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="AQ4" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="AR4" s="46" t="s">
-        <v>259</v>
-      </c>
-      <c r="AS4" s="46" t="s">
-        <v>260</v>
-      </c>
-      <c r="AT4" s="46" t="s">
-        <v>261</v>
-      </c>
-      <c r="AU4" s="46" t="s">
-        <v>262</v>
-      </c>
-      <c r="AV4" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="AW4" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="AX4" s="46" t="s">
-        <v>265</v>
-      </c>
-      <c r="AY4" s="46" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ4" s="46" t="s">
-        <v>267</v>
-      </c>
-      <c r="BA4" s="46" t="s">
-        <v>268</v>
-      </c>
-      <c r="BB4" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="BC4" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="BD4" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="BE4" s="46" t="s">
-        <v>272</v>
-      </c>
-      <c r="BF4" s="46" t="s">
-        <v>273</v>
-      </c>
-      <c r="BG4" s="46" t="s">
-        <v>213</v>
-      </c>
-      <c r="BH4" s="46" t="s">
-        <v>274</v>
-      </c>
-      <c r="BI4" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="BJ4" s="46" t="s">
-        <v>276</v>
-      </c>
-      <c r="BK4" s="46" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="5" spans="1:63">
-      <c r="A5" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>279</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>280</v>
-      </c>
-      <c r="D5" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>282</v>
-      </c>
-      <c r="F5" s="46" t="s">
-        <v>283</v>
-      </c>
-      <c r="G5" s="46" t="s">
-        <v>284</v>
-      </c>
-      <c r="H5" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="I5" s="46" t="s">
-        <v>285</v>
-      </c>
-      <c r="J5" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="K5" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="L5" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="M5" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="N5" s="46" t="s">
-        <v>290</v>
-      </c>
-      <c r="O5" s="46" t="s">
-        <v>291</v>
-      </c>
-      <c r="P5" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q5" s="46" t="s">
-        <v>293</v>
-      </c>
-      <c r="R5" s="46" t="s">
-        <v>294</v>
-      </c>
-      <c r="S5" s="46" t="s">
-        <v>295</v>
-      </c>
-      <c r="T5" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="U5" s="46" t="s">
-        <v>297</v>
-      </c>
-      <c r="V5" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="W5" s="46" t="s">
-        <v>298</v>
-      </c>
-      <c r="X5" s="46" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y5" s="46" t="s">
-        <v>300</v>
-      </c>
-      <c r="Z5" s="46" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA5" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="AB5" s="46" t="s">
-        <v>244</v>
-      </c>
-      <c r="AC5" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="AD5" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="AE5" s="46" t="s">
-        <v>305</v>
-      </c>
-      <c r="AF5" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="AG5" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="AH5" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="AI5" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="AJ5" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="AK5" s="46" t="s">
-        <v>311</v>
-      </c>
-      <c r="AL5" s="46" t="s">
-        <v>312</v>
-      </c>
-      <c r="AM5" s="46" t="s">
-        <v>313</v>
-      </c>
-      <c r="AN5" s="46" t="s">
-        <v>314</v>
-      </c>
-      <c r="AO5" s="46" t="s">
-        <v>315</v>
-      </c>
-      <c r="AP5" s="46" t="s">
-        <v>316</v>
-      </c>
-      <c r="AQ5" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="AR5" s="46" t="s">
-        <v>317</v>
-      </c>
-      <c r="AS5" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="AT5" s="46" t="s">
-        <v>319</v>
-      </c>
-      <c r="AU5" s="46" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV5" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="AW5" s="46" t="s">
-        <v>321</v>
-      </c>
-      <c r="AX5" s="46" t="s">
-        <v>322</v>
-      </c>
-      <c r="AY5" s="46" t="s">
-        <v>323</v>
-      </c>
-      <c r="AZ5" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="BA5" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="BB5" s="46" t="s">
-        <v>326</v>
-      </c>
-      <c r="BC5" s="46" t="s">
-        <v>327</v>
-      </c>
-      <c r="BD5" s="46" t="s">
-        <v>328</v>
-      </c>
-      <c r="BE5" s="46" t="s">
-        <v>329</v>
-      </c>
-      <c r="BF5" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="BG5" s="46" t="s">
-        <v>213</v>
-      </c>
-      <c r="BH5" s="46" t="s">
-        <v>331</v>
-      </c>
-      <c r="BI5" s="46" t="s">
+      <c r="BH5" s="68" t="s">
         <v>332</v>
       </c>
-      <c r="BJ5" s="46" t="s">
+      <c r="BI5" s="68" t="s">
         <v>333</v>
       </c>
-      <c r="BK5" s="46" t="s">
+      <c r="BJ5" s="68" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="6" spans="1:63">
-      <c r="A6" s="46" t="s">
+      <c r="BK5" s="68" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="7" spans="1:63">
-      <c r="A7" s="46" t="s">
+      <c r="BL5" s="68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:64">
+      <c r="A6" s="68" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="8" spans="1:63">
-      <c r="A8" s="46" t="s">
+    <row r="7" spans="1:64">
+      <c r="A7" s="68" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="9" spans="1:63">
-      <c r="A9" s="46" t="s">
+    <row r="8" spans="1:64">
+      <c r="A8" s="68" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="10" spans="1:63">
-      <c r="A10" s="46" t="s">
+    <row r="9" spans="1:64">
+      <c r="A9" s="68" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="11" spans="1:63">
-      <c r="A11" s="46" t="s">
+    <row r="10" spans="1:64">
+      <c r="A10" s="68" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="12" spans="1:63">
-      <c r="A12" s="46" t="s">
+    <row r="11" spans="1:64">
+      <c r="A11" s="68" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="13" spans="1:63">
-      <c r="A13" s="46" t="s">
+    <row r="12" spans="1:64">
+      <c r="A12" s="68" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="14" spans="1:63">
-      <c r="A14" s="46" t="s">
+    <row r="13" spans="1:64">
+      <c r="A13" s="68" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="15" spans="1:63">
-      <c r="A15" s="46" t="s">
+    <row r="14" spans="1:64">
+      <c r="A14" s="68" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="16" spans="1:63">
-      <c r="A16" s="46" t="s">
+    <row r="15" spans="1:64">
+      <c r="A15" s="68" t="s">
         <v>345</v>
       </c>
     </row>
+    <row r="16" spans="1:64">
+      <c r="A16" s="68" t="s">
+        <v>346</v>
+      </c>
+    </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="46" t="s">
-        <v>346</v>
+      <c r="A17" s="68" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="46" t="s">
-        <v>347</v>
+      <c r="A18" s="68" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="46" t="s">
-        <v>348</v>
+      <c r="A19" s="68" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="46" t="s">
-        <v>349</v>
+      <c r="A20" s="68" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="46" t="s">
-        <v>350</v>
+      <c r="A21" s="68" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="46" t="s">
-        <v>351</v>
+      <c r="A22" s="68" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="46" t="s">
-        <v>352</v>
+      <c r="A23" s="68" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="46" t="s">
-        <v>353</v>
+      <c r="A24" s="68" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="46" t="s">
-        <v>354</v>
+      <c r="A25" s="68" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="46" t="s">
-        <v>355</v>
+      <c r="A26" s="68" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="46" t="s">
-        <v>356</v>
+      <c r="A27" s="68" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="46" t="s">
-        <v>357</v>
+      <c r="A28" s="68" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="46" t="s">
-        <v>358</v>
+      <c r="A29" s="68" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="46" t="s">
-        <v>359</v>
+      <c r="A30" s="68" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="46" t="s">
-        <v>360</v>
+      <c r="A31" s="68" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="46" t="s">
-        <v>361</v>
+      <c r="A32" s="68" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="46" t="s">
-        <v>362</v>
+      <c r="A33" s="68" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="46" t="s">
-        <v>363</v>
+      <c r="A34" s="68" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="46" t="s">
-        <v>364</v>
+      <c r="A35" s="68" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="46" t="s">
-        <v>365</v>
+      <c r="A36" s="68" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="46" t="s">
-        <v>366</v>
+      <c r="A37" s="68" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="46" t="s">
-        <v>367</v>
+      <c r="A38" s="68" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="46" t="s">
-        <v>368</v>
+      <c r="A39" s="68" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="46" t="s">
-        <v>369</v>
+      <c r="A40" s="68" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="46" t="s">
-        <v>370</v>
+      <c r="A41" s="68" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="46" t="s">
-        <v>371</v>
+      <c r="A42" s="68" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="46" t="s">
-        <v>372</v>
+      <c r="A43" s="68" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="46" t="s">
-        <v>373</v>
+      <c r="A44" s="68" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="46" t="s">
-        <v>374</v>
+      <c r="A45" s="68" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="46" t="s">
-        <v>375</v>
+      <c r="A46" s="68" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="46" t="s">
-        <v>376</v>
+      <c r="A47" s="68" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="46" t="s">
-        <v>377</v>
+      <c r="A48" s="68" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="46" t="s">
-        <v>378</v>
+      <c r="A49" s="68" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="46" t="s">
-        <v>379</v>
+      <c r="A50" s="68" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="46" t="s">
-        <v>380</v>
+      <c r="A51" s="68" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="46" t="s">
-        <v>381</v>
+      <c r="A52" s="68" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="46" t="s">
-        <v>382</v>
+      <c r="A53" s="68" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="46" t="s">
-        <v>383</v>
+      <c r="A54" s="68" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="46" t="s">
-        <v>384</v>
+      <c r="A55" s="68" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="46" t="s">
-        <v>385</v>
+      <c r="A56" s="68" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="46" t="s">
-        <v>386</v>
+      <c r="A57" s="68" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="46" t="s">
-        <v>387</v>
+      <c r="A58" s="68" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="46" t="s">
-        <v>388</v>
+      <c r="A59" s="68" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="46" t="s">
-        <v>389</v>
+      <c r="A60" s="68" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="46" t="s">
-        <v>390</v>
+      <c r="A61" s="68" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="46" t="s">
-        <v>391</v>
+      <c r="A62" s="68" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="46" t="s">
-        <v>392</v>
+      <c r="A63" s="68" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="46" t="s">
-        <v>393</v>
+      <c r="A64" s="68" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="46" t="s">
-        <v>394</v>
+      <c r="A65" s="68" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="46" t="s">
-        <v>395</v>
+      <c r="A66" s="68" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="46" t="s">
-        <v>396</v>
+      <c r="A67" s="68" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="46" t="s">
-        <v>397</v>
+      <c r="A68" s="68" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="46" t="s">
-        <v>398</v>
+      <c r="A69" s="68" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="46" t="s">
-        <v>399</v>
+      <c r="A70" s="68" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="46" t="s">
-        <v>400</v>
+      <c r="A71" s="68" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="46" t="s">
-        <v>401</v>
+      <c r="A72" s="68" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="46" t="s">
-        <v>402</v>
+      <c r="A73" s="68" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="46" t="s">
-        <v>403</v>
+      <c r="A74" s="68" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="46" t="s">
-        <v>404</v>
+      <c r="A75" s="68" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="46" t="s">
-        <v>405</v>
+      <c r="A76" s="68" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="46" t="s">
-        <v>406</v>
+      <c r="A77" s="68" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="46" t="s">
-        <v>407</v>
+      <c r="A78" s="68" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="46" t="s">
-        <v>408</v>
+      <c r="A79" s="68" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="46" t="s">
-        <v>409</v>
+      <c r="A80" s="68" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="46" t="s">
-        <v>410</v>
+      <c r="A81" s="68" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="46" t="s">
-        <v>411</v>
+      <c r="A82" s="68" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="46" t="s">
-        <v>412</v>
+      <c r="A83" s="68" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="46" t="s">
-        <v>413</v>
+      <c r="A84" s="68" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="46" t="s">
-        <v>414</v>
+      <c r="A85" s="68" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="46" t="s">
-        <v>415</v>
+      <c r="A86" s="68" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="46" t="s">
-        <v>416</v>
+      <c r="A87" s="68" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="46" t="s">
-        <v>417</v>
+      <c r="A88" s="68" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="46" t="s">
-        <v>418</v>
+      <c r="A89" s="68" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="46" t="s">
-        <v>419</v>
+      <c r="A90" s="68" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="46" t="s">
-        <v>420</v>
+      <c r="A91" s="68" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="46" t="s">
-        <v>421</v>
+      <c r="A92" s="68" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="46" t="s">
-        <v>422</v>
+      <c r="A93" s="68" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="46" t="s">
-        <v>423</v>
+      <c r="A94" s="68" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="46" t="s">
-        <v>424</v>
+      <c r="A95" s="68" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="46" t="s">
-        <v>425</v>
+      <c r="A96" s="68" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="46" t="s">
-        <v>426</v>
+      <c r="A97" s="68" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="46" t="s">
-        <v>427</v>
+      <c r="A98" s="68" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="46" t="s">
-        <v>428</v>
+      <c r="A99" s="68" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="46" t="s">
-        <v>429</v>
+      <c r="A100" s="68" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="46" t="s">
-        <v>430</v>
+      <c r="A101" s="68" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="46" t="s">
-        <v>431</v>
+      <c r="A102" s="68" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="46" t="s">
-        <v>432</v>
+      <c r="A103" s="68" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="46" t="s">
-        <v>433</v>
+      <c r="A104" s="68" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="46" t="s">
-        <v>434</v>
+      <c r="A105" s="68" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="46" t="s">
-        <v>435</v>
+      <c r="A106" s="68" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="46" t="s">
-        <v>436</v>
+      <c r="A107" s="68" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="46" t="s">
-        <v>437</v>
+      <c r="A108" s="68" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="46" t="s">
-        <v>438</v>
+      <c r="A109" s="68" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="46" t="s">
-        <v>439</v>
+      <c r="A110" s="68" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="46" t="s">
-        <v>440</v>
+      <c r="A111" s="68" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="46" t="s">
-        <v>441</v>
+      <c r="A112" s="68" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="46" t="s">
-        <v>442</v>
+      <c r="A113" s="68" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="46" t="s">
-        <v>443</v>
+      <c r="A114" s="68" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="46" t="s">
-        <v>444</v>
+      <c r="A115" s="68" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="46" t="s">
-        <v>445</v>
+      <c r="A116" s="68" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="46" t="s">
-        <v>446</v>
+      <c r="A117" s="68" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="46" t="s">
-        <v>447</v>
+      <c r="A118" s="68" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="46" t="s">
-        <v>448</v>
+      <c r="A119" s="68" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="46" t="s">
-        <v>449</v>
+      <c r="A120" s="68" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="46" t="s">
-        <v>450</v>
+      <c r="A121" s="68" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="46" t="s">
-        <v>451</v>
+      <c r="A122" s="68" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="46" t="s">
-        <v>452</v>
+      <c r="A123" s="68" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="46" t="s">
-        <v>453</v>
+      <c r="A124" s="68" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="46" t="s">
-        <v>454</v>
+      <c r="A125" s="68" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="46" t="s">
-        <v>455</v>
+      <c r="A126" s="68" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="46" t="s">
-        <v>456</v>
+      <c r="A127" s="68" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="46" t="s">
-        <v>457</v>
+      <c r="A128" s="68" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="46" t="s">
-        <v>458</v>
+      <c r="A129" s="68" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="46" t="s">
-        <v>459</v>
+      <c r="A130" s="68" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="46" t="s">
-        <v>460</v>
+      <c r="A131" s="68" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="46" t="s">
-        <v>461</v>
+      <c r="A132" s="68" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="46" t="s">
-        <v>462</v>
+      <c r="A133" s="68" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="46" t="s">
-        <v>463</v>
+      <c r="A134" s="68" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="46" t="s">
-        <v>464</v>
+      <c r="A135" s="68" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="46" t="s">
-        <v>465</v>
+      <c r="A136" s="68" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="46" t="s">
-        <v>466</v>
+      <c r="A137" s="68" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="46" t="s">
-        <v>467</v>
+      <c r="A138" s="68" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="46" t="s">
-        <v>468</v>
+      <c r="A139" s="68" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="46" t="s">
-        <v>469</v>
+      <c r="A140" s="68" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="46" t="s">
-        <v>470</v>
+      <c r="A141" s="68" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="46" t="s">
-        <v>471</v>
+      <c r="A142" s="68" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="46" t="s">
-        <v>472</v>
+      <c r="A143" s="68" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="46" t="s">
-        <v>473</v>
+      <c r="A144" s="68" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="46" t="s">
-        <v>474</v>
+      <c r="A145" s="68" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="46" t="s">
-        <v>475</v>
+      <c r="A146" s="68" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="46" t="s">
-        <v>476</v>
+      <c r="A147" s="68" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="46" t="s">
-        <v>477</v>
+      <c r="A148" s="68" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="46" t="s">
-        <v>478</v>
+      <c r="A149" s="68" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="46" t="s">
-        <v>479</v>
+      <c r="A150" s="68" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="46" t="s">
-        <v>480</v>
+      <c r="A151" s="68" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="46" t="s">
-        <v>481</v>
+      <c r="A152" s="68" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="46" t="s">
-        <v>482</v>
+      <c r="A153" s="68" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1528,12 +1528,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1541,6 +1535,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1587,82 +1587,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1718,8 +1642,23 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
@@ -1732,9 +1671,48 @@
       <left style="medium">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1744,6 +1722,17 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -1799,15 +1788,11 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1868,6 +1853,21 @@
       <right/>
       <top/>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1909,102 +1909,146 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2017,87 +2061,42 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2419,34 +2418,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="35" t="str">
+      <c r="B1" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="J1" s="36" t="str">
+      <c r="J1" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="19"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="10"/>
     </row>
     <row r="2" spans="2:22">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="37" t="str">
+      <c r="D2" s="50" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="38" t="str">
+      <c r="J2" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2457,16 +2456,16 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="35" t="str">
+      <c r="B3" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="37" t="str">
+      <c r="D3" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="E3" s="20"/>
+      <c r="E3" s="11"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -2475,7 +2474,7 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="39" t="str">
+      <c r="J4" s="52" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2486,15 +2485,15 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="37" t="str">
+      <c r="B5" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="37" t="str">
+      <c r="B6" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
@@ -2513,809 +2512,809 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="J7" s="22"/>
+      <c r="J7" s="13"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="37" t="str">
+      <c r="B8" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="40" t="str">
+      <c r="D8" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="40" t="str">
+      <c r="F8" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-      <c r="J8" s="23"/>
+      <c r="J8" s="14"/>
       <c r="K8" s="1" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,59,FALSE))</f>
         <v>Ausfüllbare Felder sind in den Farben links</v>
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="37" t="str">
+      <c r="B9" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="40" t="str">
+      <c r="D9" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="40" t="str">
+      <c r="F9" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-      <c r="J9" s="24"/>
+      <c r="J9" s="15"/>
     </row>
     <row r="10" spans="2:22" ht="13.5" customHeight="1"/>
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B11" s="25"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="26"/>
-      <c r="D11" s="42" t="str">
+      <c r="D11" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="43" t="str">
+      <c r="E11" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="42" t="str">
+      <c r="F11" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="42" t="str">
+      <c r="G11" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="44" t="str">
+      <c r="H11" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="41" t="str">
+      <c r="J11" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="55"/>
-      <c r="Q11" s="41" t="str">
+      <c r="K11" s="33"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="35"/>
+      <c r="Q11" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
-      <c r="R11" s="9"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="55"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="34"/>
+      <c r="V11" s="35"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="45" t="str">
+      <c r="B12" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="12"/>
-      <c r="J12" s="56"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="19"/>
+      <c r="J12" s="36"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="57"/>
-      <c r="Q12" s="56"/>
+      <c r="O12" s="37"/>
+      <c r="Q12" s="36"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-      <c r="V12" s="57"/>
+      <c r="V12" s="37"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="46" t="str">
+      <c r="B13" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="12"/>
-      <c r="J13" s="56"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="19"/>
+      <c r="J13" s="36"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="47" t="str">
+      <c r="L13" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="47" t="str">
+      <c r="M13" s="60" t="str">
         <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE)</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="47" t="str">
+      <c r="N13" s="60" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="47" t="str">
+      <c r="O13" s="61" t="str">
         <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE)</f>
         <v>WK</v>
       </c>
-      <c r="Q13" s="56"/>
+      <c r="Q13" s="36"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="47" t="str">
+      <c r="S13" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="47" t="str">
+      <c r="T13" s="60" t="str">
         <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE)</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="47" t="str">
+      <c r="U13" s="60" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="47" t="str">
+      <c r="V13" s="61" t="str">
         <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE)</f>
         <v>WK</v>
       </c>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="27"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="12"/>
-      <c r="J14" s="58" t="s">
+      <c r="B14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="19"/>
+      <c r="J14" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="59" t="str">
+      <c r="K14" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L14" s="60"/>
-      <c r="M14" s="61"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="62">
+      <c r="L14" s="40"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="42">
         <f>IF(M14="","",N14/M14)</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="58" t="s">
+      <c r="Q14" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="59" t="str">
+      <c r="R14" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S14" s="60"/>
-      <c r="T14" s="61"/>
-      <c r="U14" s="61"/>
-      <c r="V14" s="62">
+      <c r="S14" s="40"/>
+      <c r="T14" s="41"/>
+      <c r="U14" s="41"/>
+      <c r="V14" s="42">
         <f>IF(T14="","",U14/T14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="48" t="str">
+      <c r="B15" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="34">
+      <c r="C15" s="23"/>
+      <c r="D15" s="32">
         <v>0</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="31"/>
-      <c r="J15" s="58" t="s">
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="30"/>
+      <c r="J15" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="K15" s="59" t="str">
+      <c r="K15" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="62">
+      <c r="L15" s="40"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="42">
         <f>IF(M15="","",N15/M15)</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="58" t="s">
+      <c r="Q15" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="R15" s="59" t="str">
+      <c r="R15" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S15" s="60"/>
-      <c r="T15" s="61"/>
-      <c r="U15" s="61"/>
-      <c r="V15" s="62">
+      <c r="S15" s="40"/>
+      <c r="T15" s="41"/>
+      <c r="U15" s="41"/>
+      <c r="V15" s="42">
         <f>IF(T15="","",U15/T15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="49" t="str">
+      <c r="B16" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>Lokale Eigenleistung</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="34">
+      <c r="C16" s="24"/>
+      <c r="D16" s="32">
         <v>0</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="50">
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="64">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="31"/>
-      <c r="J16" s="58" t="s">
+      <c r="H16" s="30"/>
+      <c r="J16" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="59" t="str">
+      <c r="K16" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L16" s="60"/>
-      <c r="M16" s="61"/>
-      <c r="N16" s="61"/>
-      <c r="O16" s="62">
+      <c r="L16" s="40"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="42">
         <f>IF(M16="","",N16/M16)</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="58" t="s">
+      <c r="Q16" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="R16" s="59" t="str">
+      <c r="R16" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S16" s="60"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="61"/>
-      <c r="V16" s="62">
+      <c r="S16" s="40"/>
+      <c r="T16" s="41"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="42">
         <f>IF(T16="","",U16/T16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="49" t="str">
+      <c r="B17" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>Beiträge von dritter Seite</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="34">
+      <c r="C17" s="24"/>
+      <c r="D17" s="32">
         <v>0</v>
       </c>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="50">
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="64">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="31"/>
-      <c r="J17" s="58" t="s">
+      <c r="H17" s="30"/>
+      <c r="J17" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="59" t="str">
+      <c r="K17" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L17" s="60"/>
-      <c r="M17" s="61"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="62">
+      <c r="L17" s="40"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="42">
         <f>IF(M17="","",N17/M17)</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="58" t="s">
+      <c r="Q17" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="R17" s="59" t="str">
+      <c r="R17" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S17" s="60"/>
-      <c r="T17" s="61"/>
-      <c r="U17" s="61"/>
-      <c r="V17" s="62">
+      <c r="S17" s="40"/>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="42">
         <f>IF(T17="","",U17/T17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="49" t="str">
+      <c r="B18" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="34">
+      <c r="C18" s="24"/>
+      <c r="D18" s="32">
         <v>0</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="50">
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="64">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="31"/>
-      <c r="J18" s="58" t="s">
+      <c r="H18" s="30"/>
+      <c r="J18" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="59" t="str">
+      <c r="K18" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L18" s="60"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="62">
+      <c r="L18" s="40"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="42">
         <f>IF(M18="","",N18/M18)</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="58" t="s">
+      <c r="Q18" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="R18" s="59" t="str">
+      <c r="R18" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S18" s="60"/>
-      <c r="T18" s="61"/>
-      <c r="U18" s="61"/>
-      <c r="V18" s="62">
+      <c r="S18" s="40"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="42">
         <f>IF(T18="","",U18/T18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="49" t="str">
+      <c r="B19" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>Zinserträge</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="34">
+      <c r="C19" s="24"/>
+      <c r="D19" s="32">
         <v>0</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="50">
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="64">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="31"/>
-      <c r="J19" s="58" t="s">
+      <c r="H19" s="30"/>
+      <c r="J19" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="59" t="str">
+      <c r="K19" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L19" s="60"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="62">
+      <c r="L19" s="40"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="42">
         <f>IF(M19="","",N19/M19)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="58" t="s">
+      <c r="Q19" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="R19" s="59" t="str">
+      <c r="R19" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S19" s="60"/>
-      <c r="T19" s="61"/>
-      <c r="U19" s="61"/>
-      <c r="V19" s="62">
+      <c r="S19" s="40"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="42">
         <f>IF(T19="","",U19/T19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="51" t="str">
+      <c r="B20" s="65" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="52">
+      <c r="C20" s="25"/>
+      <c r="D20" s="66">
         <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="66">
         <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="66">
         <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="67">
         <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="32"/>
-      <c r="J20" s="58" t="s">
+      <c r="H20" s="31"/>
+      <c r="J20" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="K20" s="59" t="str">
+      <c r="K20" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L20" s="60"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="62">
+      <c r="L20" s="40"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="42">
         <f>IF(M20="","",N20/M20)</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="58" t="s">
+      <c r="Q20" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R20" s="59" t="str">
+      <c r="R20" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S20" s="60"/>
-      <c r="T20" s="61"/>
-      <c r="U20" s="61"/>
-      <c r="V20" s="62">
+      <c r="S20" s="40"/>
+      <c r="T20" s="41"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="42">
         <f>IF(T20="","",U20/T20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:22">
-      <c r="J21" s="58" t="s">
+      <c r="J21" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="K21" s="59" t="str">
+      <c r="K21" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L21" s="60"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="61"/>
-      <c r="O21" s="62">
+      <c r="L21" s="40"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="42">
         <f>IF(M21="","",N21/M21)</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="58" t="s">
+      <c r="Q21" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="R21" s="59" t="str">
+      <c r="R21" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S21" s="60"/>
-      <c r="T21" s="61"/>
-      <c r="U21" s="61"/>
-      <c r="V21" s="62">
+      <c r="S21" s="40"/>
+      <c r="T21" s="41"/>
+      <c r="U21" s="41"/>
+      <c r="V21" s="42">
         <f>IF(T21="","",U21/T21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:22">
-      <c r="J22" s="58" t="s">
+      <c r="J22" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="59" t="str">
+      <c r="K22" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L22" s="60"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="61"/>
-      <c r="O22" s="62">
+      <c r="L22" s="40"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="42">
         <f>IF(M22="","",N22/M22)</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="58" t="s">
+      <c r="Q22" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="R22" s="59" t="str">
+      <c r="R22" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S22" s="60"/>
-      <c r="T22" s="61"/>
-      <c r="U22" s="61"/>
-      <c r="V22" s="62">
+      <c r="S22" s="40"/>
+      <c r="T22" s="41"/>
+      <c r="U22" s="41"/>
+      <c r="V22" s="42">
         <f>IF(T22="","",U22/T22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:22">
-      <c r="J23" s="58" t="s">
+      <c r="J23" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="59" t="str">
+      <c r="K23" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L23" s="60"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="62">
+      <c r="L23" s="40"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="42">
         <f>IF(M23="","",N23/M23)</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="58" t="s">
+      <c r="Q23" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="59" t="str">
+      <c r="R23" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S23" s="60"/>
-      <c r="T23" s="61"/>
-      <c r="U23" s="61"/>
-      <c r="V23" s="62">
+      <c r="S23" s="40"/>
+      <c r="T23" s="41"/>
+      <c r="U23" s="41"/>
+      <c r="V23" s="42">
         <f>IF(T23="","",U23/T23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:22">
-      <c r="J24" s="58" t="s">
+      <c r="J24" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="59" t="str">
+      <c r="K24" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L24" s="60"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="61"/>
-      <c r="O24" s="62">
+      <c r="L24" s="40"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="42">
         <f>IF(M24="","",N24/M24)</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="58" t="s">
+      <c r="Q24" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="R24" s="59" t="str">
+      <c r="R24" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S24" s="60"/>
-      <c r="T24" s="61"/>
-      <c r="U24" s="61"/>
-      <c r="V24" s="62">
+      <c r="S24" s="40"/>
+      <c r="T24" s="41"/>
+      <c r="U24" s="41"/>
+      <c r="V24" s="42">
         <f>IF(T24="","",U24/T24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:22">
-      <c r="J25" s="58" t="s">
+      <c r="J25" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="59" t="str">
+      <c r="K25" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L25" s="60"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="61"/>
-      <c r="O25" s="62">
+      <c r="L25" s="40"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="42">
         <f>IF(M25="","",N25/M25)</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="58" t="s">
+      <c r="Q25" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="R25" s="59" t="str">
+      <c r="R25" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S25" s="60"/>
-      <c r="T25" s="61"/>
-      <c r="U25" s="61"/>
-      <c r="V25" s="62">
+      <c r="S25" s="40"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="42">
         <f>IF(T25="","",U25/T25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:22">
-      <c r="J26" s="58" t="s">
+      <c r="J26" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="59" t="str">
+      <c r="K26" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L26" s="60"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="61"/>
-      <c r="O26" s="62">
+      <c r="L26" s="40"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="42">
         <f>IF(M26="","",N26/M26)</f>
         <v>0</v>
       </c>
-      <c r="Q26" s="58" t="s">
+      <c r="Q26" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="R26" s="59" t="str">
+      <c r="R26" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S26" s="60"/>
-      <c r="T26" s="61"/>
-      <c r="U26" s="61"/>
-      <c r="V26" s="62">
+      <c r="S26" s="40"/>
+      <c r="T26" s="41"/>
+      <c r="U26" s="41"/>
+      <c r="V26" s="42">
         <f>IF(T26="","",U26/T26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:22">
-      <c r="J27" s="58" t="s">
+      <c r="J27" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="K27" s="59" t="str">
+      <c r="K27" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L27" s="60"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="61"/>
-      <c r="O27" s="62">
+      <c r="L27" s="40"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="42">
         <f>IF(M27="","",N27/M27)</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="58" t="s">
+      <c r="Q27" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="59" t="str">
+      <c r="R27" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S27" s="60"/>
-      <c r="T27" s="61"/>
-      <c r="U27" s="61"/>
-      <c r="V27" s="62">
+      <c r="S27" s="40"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="42">
         <f>IF(T27="","",U27/T27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:22">
-      <c r="J28" s="58" t="s">
+      <c r="J28" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="59" t="str">
+      <c r="K28" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L28" s="60"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="61"/>
-      <c r="O28" s="62">
+      <c r="L28" s="40"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="42">
         <f>IF(M28="","",N28/M28)</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="58" t="s">
+      <c r="Q28" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="R28" s="59" t="str">
+      <c r="R28" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S28" s="60"/>
-      <c r="T28" s="61"/>
-      <c r="U28" s="61"/>
-      <c r="V28" s="62">
+      <c r="S28" s="40"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="42">
         <f>IF(T28="","",U28/T28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:22">
-      <c r="J29" s="58" t="s">
+      <c r="J29" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="K29" s="59" t="str">
+      <c r="K29" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L29" s="60"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="61"/>
-      <c r="O29" s="62">
+      <c r="L29" s="40"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="42">
         <f>IF(M29="","",N29/M29)</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="58" t="s">
+      <c r="Q29" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="R29" s="59" t="str">
+      <c r="R29" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S29" s="60"/>
-      <c r="T29" s="61"/>
-      <c r="U29" s="61"/>
-      <c r="V29" s="62">
+      <c r="S29" s="40"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="42">
         <f>IF(T29="","",U29/T29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:22">
-      <c r="J30" s="58" t="s">
+      <c r="J30" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="59" t="str">
+      <c r="K30" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L30" s="60"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="62">
+      <c r="L30" s="40"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="42">
         <f>IF(M30="","",N30/M30)</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="58" t="s">
+      <c r="Q30" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="59" t="str">
+      <c r="R30" s="39" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S30" s="60"/>
-      <c r="T30" s="61"/>
-      <c r="U30" s="61"/>
-      <c r="V30" s="62">
+      <c r="S30" s="40"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="42">
         <f>IF(T30="","",U30/T30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:22">
-      <c r="J31" s="63" t="s">
+      <c r="J31" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="K31" s="64" t="str">
+      <c r="K31" s="44" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L31" s="65"/>
-      <c r="M31" s="66"/>
-      <c r="N31" s="66"/>
-      <c r="O31" s="67">
+      <c r="L31" s="45"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="47">
         <f>IF(M31="","",N31/M31)</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="63" t="s">
+      <c r="Q31" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="R31" s="64" t="str">
+      <c r="R31" s="44" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S31" s="65"/>
-      <c r="T31" s="66"/>
-      <c r="U31" s="66"/>
-      <c r="V31" s="67">
+      <c r="S31" s="45"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="47">
         <f>IF(T31="","",U31/T31)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="27">
+  <mergeCells count="29">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="J2:O3"/>
@@ -3328,8 +3327,7 @@
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:D14"/>
     <mergeCell ref="E11:E14"/>
     <mergeCell ref="F11:F14"/>
@@ -3337,12 +3335,15 @@
     <mergeCell ref="H11:H14"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="Q11:R11"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2">

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2045,58 +2045,58 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2418,12 +2418,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="48" t="str">
+      <c r="B1" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="J1" s="49" t="str">
+      <c r="J1" s="65" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
@@ -2438,14 +2438,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="50" t="str">
+      <c r="D2" s="55" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="51" t="str">
+      <c r="J2" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2456,12 +2456,12 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="48" t="str">
+      <c r="B3" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="50" t="str">
+      <c r="D3" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
@@ -2474,7 +2474,7 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="52" t="str">
+      <c r="J4" s="64" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2485,7 +2485,7 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="50" t="str">
+      <c r="B5" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="D5" s="12"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="50" t="str">
+      <c r="B6" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
@@ -2515,17 +2515,17 @@
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="50" t="str">
+      <c r="B8" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="53" t="str">
+      <c r="D8" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="53" t="str">
+      <c r="F8" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2538,17 +2538,17 @@
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="50" t="str">
+      <c r="B9" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="53" t="str">
+      <c r="D9" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="53" t="str">
+      <c r="F9" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2560,27 +2560,27 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="16"/>
       <c r="C11" s="26"/>
-      <c r="D11" s="55" t="str">
+      <c r="D11" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="56" t="str">
+      <c r="E11" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="55" t="str">
+      <c r="F11" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="55" t="str">
+      <c r="G11" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="57" t="str">
+      <c r="H11" s="67" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="54" t="str">
+      <c r="J11" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2589,7 +2589,7 @@
       <c r="M11" s="34"/>
       <c r="N11" s="34"/>
       <c r="O11" s="35"/>
-      <c r="Q11" s="54" t="str">
+      <c r="Q11" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2600,7 +2600,7 @@
       <c r="V11" s="35"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="58" t="str">
+      <c r="B12" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="V12" s="37"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="59" t="str">
+      <c r="B13" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
@@ -2636,38 +2636,38 @@
       <c r="H13" s="19"/>
       <c r="J13" s="36"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="60" t="str">
+      <c r="L13" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="60" t="str">
-        <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE)</f>
+      <c r="M13" s="52" t="str">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="60" t="str">
+      <c r="N13" s="52" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="61" t="str">
-        <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE)</f>
+      <c r="O13" s="57" t="str">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
       <c r="Q13" s="36"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="60" t="str">
+      <c r="S13" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="60" t="str">
-        <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE)</f>
+      <c r="T13" s="52" t="str">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="60" t="str">
+      <c r="U13" s="52" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="61" t="str">
-        <f>VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE)</f>
+      <c r="V13" s="57" t="str">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="62" t="str">
+      <c r="B15" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="63" t="str">
+      <c r="B16" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>Lokale Eigenleistung</v>
       </c>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="64">
+      <c r="G16" s="48">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
@@ -2796,7 +2796,7 @@
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="63" t="str">
+      <c r="B17" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>Beiträge von dritter Seite</v>
       </c>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
-      <c r="G17" s="64">
+      <c r="G17" s="48">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
@@ -2841,7 +2841,7 @@
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="63" t="str">
+      <c r="B18" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
-      <c r="G18" s="64">
+      <c r="G18" s="48">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
@@ -2886,7 +2886,7 @@
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="63" t="str">
+      <c r="B19" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>Zinserträge</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="28"/>
-      <c r="G19" s="64">
+      <c r="G19" s="48">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
@@ -2931,24 +2931,24 @@
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="65" t="str">
+      <c r="B20" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
       <c r="C20" s="25"/>
-      <c r="D20" s="66">
-        <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
+      <c r="D20" s="49">
+        <f>SUMPRODUCT(ROUND(D15:D19,2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="66">
-        <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
+      <c r="E20" s="49">
+        <f>SUMPRODUCT(ROUND(E15:E19,2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="66">
-        <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
+      <c r="F20" s="49">
+        <f>SUMPRODUCT(ROUND(F15:F19,2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="67">
+      <c r="G20" s="66">
         <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2045,57 +2045,57 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2418,12 +2418,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="62" t="str">
+      <c r="B1" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="J1" s="65" t="str">
+      <c r="J1" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
@@ -2438,14 +2438,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="55" t="str">
+      <c r="D2" s="51" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="54" t="str">
+      <c r="J2" s="67" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2456,12 +2456,12 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="62" t="str">
+      <c r="B3" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="55" t="str">
+      <c r="D3" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
@@ -2474,7 +2474,7 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="64" t="str">
+      <c r="J4" s="65" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2485,7 +2485,7 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="55" t="str">
+      <c r="B5" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="D5" s="12"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="55" t="str">
+      <c r="B6" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
@@ -2515,7 +2515,7 @@
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="55" t="str">
+      <c r="B8" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
@@ -2538,7 +2538,7 @@
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="55" t="str">
+      <c r="B9" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
@@ -2560,27 +2560,27 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="16"/>
       <c r="C11" s="26"/>
-      <c r="D11" s="60" t="str">
+      <c r="D11" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="50" t="str">
+      <c r="E11" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="60" t="str">
+      <c r="F11" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="60" t="str">
+      <c r="G11" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="67" t="str">
+      <c r="H11" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="61" t="str">
+      <c r="J11" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2589,7 +2589,7 @@
       <c r="M11" s="34"/>
       <c r="N11" s="34"/>
       <c r="O11" s="35"/>
-      <c r="Q11" s="61" t="str">
+      <c r="Q11" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="V12" s="37"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="51" t="str">
+      <c r="B13" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
@@ -2636,37 +2636,37 @@
       <c r="H13" s="19"/>
       <c r="J13" s="36"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="52" t="str">
+      <c r="L13" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="52" t="str">
+      <c r="M13" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="52" t="str">
+      <c r="N13" s="55" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="57" t="str">
+      <c r="O13" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
       <c r="Q13" s="36"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="52" t="str">
+      <c r="S13" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="52" t="str">
+      <c r="T13" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="52" t="str">
+      <c r="U13" s="55" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="57" t="str">
+      <c r="V13" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
@@ -2709,7 +2709,7 @@
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="63" t="str">
+      <c r="B15" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="53" t="str">
+      <c r="B16" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>Lokale Eigenleistung</v>
       </c>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="48">
+      <c r="G16" s="52">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
@@ -2796,7 +2796,7 @@
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="53" t="str">
+      <c r="B17" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>Beiträge von dritter Seite</v>
       </c>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
-      <c r="G17" s="48">
+      <c r="G17" s="52">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
@@ -2841,7 +2841,7 @@
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="53" t="str">
+      <c r="B18" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
-      <c r="G18" s="48">
+      <c r="G18" s="52">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
@@ -2886,7 +2886,7 @@
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="53" t="str">
+      <c r="B19" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>Zinserträge</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="28"/>
-      <c r="G19" s="48">
+      <c r="G19" s="52">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
@@ -2931,20 +2931,20 @@
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="59" t="str">
+      <c r="B20" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
       <c r="C20" s="25"/>
-      <c r="D20" s="49">
+      <c r="D20" s="59">
         <f>SUMPRODUCT(ROUND(D15:D19,2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="59">
         <f>SUMPRODUCT(ROUND(E15:E19,2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="59">
         <f>SUMPRODUCT(ROUND(F15:F19,2))</f>
         <v>0</v>
       </c>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2045,57 +2045,57 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2418,12 +2418,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="61" t="str">
+      <c r="B1" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="J1" s="57" t="str">
+      <c r="J1" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
@@ -2438,14 +2438,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="51" t="str">
+      <c r="D2" s="55" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="67" t="str">
+      <c r="J2" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2456,12 +2456,12 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="61" t="str">
+      <c r="B3" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="51" t="str">
+      <c r="D3" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
@@ -2474,7 +2474,7 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="65" t="str">
+      <c r="J4" s="56" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2485,7 +2485,7 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="51" t="str">
+      <c r="B5" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="D5" s="12"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="51" t="str">
+      <c r="B6" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
@@ -2515,17 +2515,17 @@
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="51" t="str">
+      <c r="B8" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="58" t="str">
+      <c r="D8" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="58" t="str">
+      <c r="F8" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2538,17 +2538,17 @@
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="51" t="str">
+      <c r="B9" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="58" t="str">
+      <c r="D9" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="58" t="str">
+      <c r="F9" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2560,27 +2560,27 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="16"/>
       <c r="C11" s="26"/>
-      <c r="D11" s="49" t="str">
+      <c r="D11" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="62" t="str">
+      <c r="E11" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="49" t="str">
+      <c r="F11" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="49" t="str">
+      <c r="G11" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="64" t="str">
+      <c r="H11" s="66" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="53" t="str">
+      <c r="J11" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2589,7 +2589,7 @@
       <c r="M11" s="34"/>
       <c r="N11" s="34"/>
       <c r="O11" s="35"/>
-      <c r="Q11" s="53" t="str">
+      <c r="Q11" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2600,7 +2600,7 @@
       <c r="V11" s="35"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="56" t="str">
+      <c r="B12" s="67" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="V12" s="37"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="63" t="str">
+      <c r="B13" s="65" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
@@ -2636,37 +2636,37 @@
       <c r="H13" s="19"/>
       <c r="J13" s="36"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="55" t="str">
+      <c r="L13" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="55" t="str">
+      <c r="M13" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="55" t="str">
+      <c r="N13" s="49" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="60" t="str">
+      <c r="O13" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
       <c r="Q13" s="36"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="55" t="str">
+      <c r="S13" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="55" t="str">
+      <c r="T13" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="55" t="str">
+      <c r="U13" s="49" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="60" t="str">
+      <c r="V13" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
@@ -2709,7 +2709,7 @@
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="48" t="str">
+      <c r="B15" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="50" t="str">
+      <c r="B16" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>Lokale Eigenleistung</v>
       </c>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="52">
+      <c r="G16" s="58">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
@@ -2796,7 +2796,7 @@
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="50" t="str">
+      <c r="B17" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>Beiträge von dritter Seite</v>
       </c>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
-      <c r="G17" s="52">
+      <c r="G17" s="58">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
@@ -2841,7 +2841,7 @@
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="50" t="str">
+      <c r="B18" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
-      <c r="G18" s="52">
+      <c r="G18" s="58">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
@@ -2886,7 +2886,7 @@
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="50" t="str">
+      <c r="B19" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>Zinserträge</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="28"/>
-      <c r="G19" s="52">
+      <c r="G19" s="58">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
@@ -2931,24 +2931,24 @@
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="54" t="str">
+      <c r="B20" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
       <c r="C20" s="25"/>
-      <c r="D20" s="59">
+      <c r="D20" s="51">
         <f>SUMPRODUCT(ROUND(D15:D19,2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="59">
+      <c r="E20" s="51">
         <f>SUMPRODUCT(ROUND(E15:E19,2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="59">
+      <c r="F20" s="51">
         <f>SUMPRODUCT(ROUND(F15:F19,2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G20" s="60">
         <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2045,57 +2045,57 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2418,12 +2418,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="57" t="str">
+      <c r="B1" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="J1" s="61" t="str">
+      <c r="J1" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
@@ -2438,14 +2438,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="55" t="str">
+      <c r="D2" s="62" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="48" t="str">
+      <c r="J2" s="66" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2456,12 +2456,12 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="57" t="str">
+      <c r="B3" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="55" t="str">
+      <c r="D3" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
@@ -2474,7 +2474,7 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="56" t="str">
+      <c r="J4" s="61" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2485,7 +2485,7 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="55" t="str">
+      <c r="B5" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="D5" s="12"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="55" t="str">
+      <c r="B6" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
@@ -2515,7 +2515,7 @@
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="55" t="str">
+      <c r="B8" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
@@ -2538,7 +2538,7 @@
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="55" t="str">
+      <c r="B9" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
@@ -2560,27 +2560,27 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="16"/>
       <c r="C11" s="26"/>
-      <c r="D11" s="50" t="str">
+      <c r="D11" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="64" t="str">
+      <c r="E11" s="67" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="50" t="str">
+      <c r="F11" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="50" t="str">
+      <c r="G11" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="66" t="str">
+      <c r="H11" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="59" t="str">
+      <c r="J11" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2589,7 +2589,7 @@
       <c r="M11" s="34"/>
       <c r="N11" s="34"/>
       <c r="O11" s="35"/>
-      <c r="Q11" s="59" t="str">
+      <c r="Q11" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2600,7 +2600,7 @@
       <c r="V11" s="35"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="67" t="str">
+      <c r="B12" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="V12" s="37"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="65" t="str">
+      <c r="B13" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
@@ -2636,37 +2636,37 @@
       <c r="H13" s="19"/>
       <c r="J13" s="36"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="49" t="str">
+      <c r="L13" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="49" t="str">
+      <c r="M13" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="49" t="str">
+      <c r="N13" s="50" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="53" t="str">
+      <c r="O13" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
       <c r="Q13" s="36"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="49" t="str">
+      <c r="S13" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="49" t="str">
+      <c r="T13" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="49" t="str">
+      <c r="U13" s="50" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="53" t="str">
+      <c r="V13" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
@@ -2709,7 +2709,7 @@
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="62" t="str">
+      <c r="B15" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="58">
+      <c r="G16" s="56">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
-      <c r="G17" s="58">
+      <c r="G17" s="56">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
-      <c r="G18" s="58">
+      <c r="G18" s="56">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="28"/>
-      <c r="G19" s="58">
+      <c r="G19" s="56">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
@@ -2931,24 +2931,24 @@
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="63" t="str">
+      <c r="B20" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
       <c r="C20" s="25"/>
-      <c r="D20" s="51">
+      <c r="D20" s="55">
         <f>SUMPRODUCT(ROUND(D15:D19,2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="55">
         <f>SUMPRODUCT(ROUND(E15:E19,2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="55">
         <f>SUMPRODUCT(ROUND(F15:F19,2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="60">
+      <c r="G20" s="65">
         <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2046,56 +2046,56 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2418,12 +2418,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="48" t="str">
+      <c r="B1" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="J1" s="49" t="str">
+      <c r="J1" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
@@ -2438,14 +2438,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="62" t="str">
+      <c r="D2" s="57" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="66" t="str">
+      <c r="J2" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2456,12 +2456,12 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="48" t="str">
+      <c r="B3" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="62" t="str">
+      <c r="D3" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
@@ -2474,7 +2474,7 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="61" t="str">
+      <c r="J4" s="60" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2485,7 +2485,7 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="62" t="str">
+      <c r="B5" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="D5" s="12"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="62" t="str">
+      <c r="B6" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
@@ -2515,17 +2515,17 @@
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="62" t="str">
+      <c r="B8" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="52" t="str">
+      <c r="D8" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="52" t="str">
+      <c r="F8" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2538,17 +2538,17 @@
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="62" t="str">
+      <c r="B9" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="52" t="str">
+      <c r="D9" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="52" t="str">
+      <c r="F9" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2560,27 +2560,27 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="16"/>
       <c r="C11" s="26"/>
-      <c r="D11" s="51" t="str">
+      <c r="D11" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="67" t="str">
+      <c r="E11" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="51" t="str">
+      <c r="F11" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="51" t="str">
+      <c r="G11" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="53" t="str">
+      <c r="H11" s="66" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="58" t="str">
+      <c r="J11" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2589,7 +2589,7 @@
       <c r="M11" s="34"/>
       <c r="N11" s="34"/>
       <c r="O11" s="35"/>
-      <c r="Q11" s="58" t="str">
+      <c r="Q11" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2600,7 +2600,7 @@
       <c r="V11" s="35"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="59" t="str">
+      <c r="B12" s="67" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="V12" s="37"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="60" t="str">
+      <c r="B13" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
@@ -2636,37 +2636,37 @@
       <c r="H13" s="19"/>
       <c r="J13" s="36"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="50" t="str">
+      <c r="L13" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="50" t="str">
+      <c r="M13" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="50" t="str">
+      <c r="N13" s="48" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="63" t="str">
+      <c r="O13" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
       <c r="Q13" s="36"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="50" t="str">
+      <c r="S13" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="50" t="str">
+      <c r="T13" s="48" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="50" t="str">
+      <c r="U13" s="48" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="63" t="str">
+      <c r="V13" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
@@ -2709,7 +2709,7 @@
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="57" t="str">
+      <c r="B15" s="65" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="54" t="str">
+      <c r="B16" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>Lokale Eigenleistung</v>
       </c>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="56">
+      <c r="G16" s="59">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
@@ -2796,7 +2796,7 @@
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="54" t="str">
+      <c r="B17" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>Beiträge von dritter Seite</v>
       </c>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
-      <c r="G17" s="56">
+      <c r="G17" s="59">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
@@ -2841,7 +2841,7 @@
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="54" t="str">
+      <c r="B18" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
-      <c r="G18" s="56">
+      <c r="G18" s="59">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
@@ -2886,7 +2886,7 @@
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="54" t="str">
+      <c r="B19" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>Zinserträge</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="28"/>
-      <c r="G19" s="56">
+      <c r="G19" s="59">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
@@ -2931,24 +2931,24 @@
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="64" t="str">
+      <c r="B20" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
       <c r="C20" s="25"/>
-      <c r="D20" s="55">
+      <c r="D20" s="53">
         <f>SUMPRODUCT(ROUND(D15:D19,2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="53">
         <f>SUMPRODUCT(ROUND(E15:E19,2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="53">
         <f>SUMPRODUCT(ROUND(F15:F19,2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="65">
+      <c r="G20" s="62">
         <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -1479,13 +1479,20 @@
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1507,8 +1514,9 @@
       <family val="2"/>
     </font>
     <font>
+      <u/>
       <sz val="10"/>
-      <color rgb="FF0563C1"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1873,69 +1881,70 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1943,163 +1952,168 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2395,919 +2409,919 @@
   <dimension ref="A1:ALL31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="56.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" style="1" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="10" width="4.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
-    <col min="13" max="15" width="15.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="4.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.85546875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.5703125" style="1" customWidth="1"/>
-    <col min="20" max="22" width="15.7109375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="4.7109375" style="1" customWidth="1"/>
-    <col min="24" max="24" width="37.42578125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="11.5703125" style="1" customWidth="1"/>
-    <col min="26" max="1000" width="9.140625" style="1"/>
+    <col min="1" max="1" width="3.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="56.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
+    <col min="5" max="6" width="18.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" style="2" customWidth="1"/>
+    <col min="9" max="10" width="4.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="2" customWidth="1"/>
+    <col min="13" max="15" width="15.7109375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="19.85546875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="11.5703125" style="2" customWidth="1"/>
+    <col min="20" max="22" width="15.7109375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="4.7109375" style="2" customWidth="1"/>
+    <col min="24" max="24" width="37.42578125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="11.5703125" style="2" customWidth="1"/>
+    <col min="26" max="1000" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="58" t="str">
+      <c r="B1" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="3"/>
       <c r="J1" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="11"/>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="57" t="str">
+      <c r="C2" s="4"/>
+      <c r="D2" s="58" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="55" t="str">
+      <c r="J2" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="58" t="str">
+      <c r="B3" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="57" t="str">
+      <c r="C3" s="3"/>
+      <c r="D3" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="E3" s="12"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="60" t="str">
+      <c r="J4" s="67" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="57" t="str">
+      <c r="B5" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="12"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="13"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="57" t="str">
+      <c r="B6" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" spans="2:22">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="J7" s="13"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="57" t="str">
+      <c r="B8" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="50" t="str">
+      <c r="C8" s="7"/>
+      <c r="D8" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="50" t="str">
+      <c r="E8" s="9"/>
+      <c r="F8" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="1" t="str">
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="2" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,59,FALSE))</f>
         <v>Ausfüllbare Felder sind in den Farben links</v>
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="57" t="str">
+      <c r="B9" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="50" t="str">
+      <c r="C9" s="7"/>
+      <c r="D9" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="50" t="str">
+      <c r="E9" s="9"/>
+      <c r="F9" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="J9" s="15"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="J9" s="16"/>
     </row>
     <row r="10" spans="2:22" ht="13.5" customHeight="1"/>
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B11" s="16"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="52" t="str">
+      <c r="B11" s="17"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="63" t="str">
+      <c r="E11" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="52" t="str">
+      <c r="F11" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="52" t="str">
+      <c r="G11" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="66" t="str">
+      <c r="H11" s="65" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="49" t="str">
+      <c r="J11" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
-      <c r="K11" s="33"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="35"/>
-      <c r="Q11" s="49" t="str">
+      <c r="K11" s="34"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="36"/>
+      <c r="Q11" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
-      <c r="R11" s="33"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="35"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="36"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="67" t="str">
+      <c r="B12" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="19"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="37"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="37"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="20"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="38"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="38"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="61" t="str">
+      <c r="B13" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="19"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="48" t="str">
+      <c r="C13" s="22"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="20"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="48" t="str">
+      <c r="M13" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="48" t="str">
+      <c r="N13" s="54" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="56" t="str">
+      <c r="O13" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="48" t="str">
+      <c r="Q13" s="37"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="48" t="str">
+      <c r="T13" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="48" t="str">
+      <c r="U13" s="54" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="56" t="str">
+      <c r="V13" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="22"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="19"/>
-      <c r="J14" s="38" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="20"/>
+      <c r="J14" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="39" t="str">
+      <c r="K14" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L14" s="40"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="42">
+      <c r="L14" s="41"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="43">
         <f>IF(M14="","",N14/M14)</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="38" t="s">
+      <c r="Q14" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="39" t="str">
+      <c r="R14" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S14" s="40"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="42">
+      <c r="S14" s="41"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="43">
         <f>IF(T14="","",U14/T14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="65" t="str">
+      <c r="B15" s="66" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="32">
+      <c r="C15" s="24"/>
+      <c r="D15" s="33">
         <v>0</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="30"/>
-      <c r="J15" s="38" t="s">
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="31"/>
+      <c r="J15" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="K15" s="39" t="str">
+      <c r="K15" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L15" s="40"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="42">
+      <c r="L15" s="41"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="43">
         <f>IF(M15="","",N15/M15)</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="38" t="s">
+      <c r="Q15" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="R15" s="39" t="str">
+      <c r="R15" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S15" s="40"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="42">
+      <c r="S15" s="41"/>
+      <c r="T15" s="42"/>
+      <c r="U15" s="42"/>
+      <c r="V15" s="43">
         <f>IF(T15="","",U15/T15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="51" t="str">
+      <c r="B16" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>Lokale Eigenleistung</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="32">
+      <c r="C16" s="25"/>
+      <c r="D16" s="33">
         <v>0</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="59">
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="51">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="30"/>
-      <c r="J16" s="38" t="s">
+      <c r="H16" s="31"/>
+      <c r="J16" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="39" t="str">
+      <c r="K16" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L16" s="40"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="42">
+      <c r="L16" s="41"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="43">
         <f>IF(M16="","",N16/M16)</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="38" t="s">
+      <c r="Q16" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="R16" s="39" t="str">
+      <c r="R16" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S16" s="40"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="42">
+      <c r="S16" s="41"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="42"/>
+      <c r="V16" s="43">
         <f>IF(T16="","",U16/T16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="51" t="str">
+      <c r="B17" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>Beiträge von dritter Seite</v>
       </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="32">
+      <c r="C17" s="25"/>
+      <c r="D17" s="33">
         <v>0</v>
       </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="59">
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="51">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="30"/>
-      <c r="J17" s="38" t="s">
+      <c r="H17" s="31"/>
+      <c r="J17" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="39" t="str">
+      <c r="K17" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L17" s="40"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="42">
+      <c r="L17" s="41"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="43">
         <f>IF(M17="","",N17/M17)</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="38" t="s">
+      <c r="Q17" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R17" s="39" t="str">
+      <c r="R17" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S17" s="40"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="42">
+      <c r="S17" s="41"/>
+      <c r="T17" s="42"/>
+      <c r="U17" s="42"/>
+      <c r="V17" s="43">
         <f>IF(T17="","",U17/T17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="51" t="str">
+      <c r="B18" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="32">
+      <c r="C18" s="25"/>
+      <c r="D18" s="33">
         <v>0</v>
       </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="59">
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="51">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="30"/>
-      <c r="J18" s="38" t="s">
+      <c r="H18" s="31"/>
+      <c r="J18" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="39" t="str">
+      <c r="K18" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L18" s="40"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="42">
+      <c r="L18" s="41"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="43">
         <f>IF(M18="","",N18/M18)</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="38" t="s">
+      <c r="Q18" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="R18" s="39" t="str">
+      <c r="R18" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S18" s="40"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="42">
+      <c r="S18" s="41"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="43">
         <f>IF(T18="","",U18/T18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="51" t="str">
+      <c r="B19" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>Zinserträge</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="32">
+      <c r="C19" s="25"/>
+      <c r="D19" s="33">
         <v>0</v>
       </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="59">
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="51">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="30"/>
-      <c r="J19" s="38" t="s">
+      <c r="H19" s="31"/>
+      <c r="J19" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="39" t="str">
+      <c r="K19" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L19" s="40"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="42">
+      <c r="L19" s="41"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="43">
         <f>IF(M19="","",N19/M19)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="38" t="s">
+      <c r="Q19" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="R19" s="39" t="str">
+      <c r="R19" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S19" s="40"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
-      <c r="V19" s="42">
+      <c r="S19" s="41"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="42"/>
+      <c r="V19" s="43">
         <f>IF(T19="","",U19/T19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="54" t="str">
+      <c r="B20" s="68" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="53">
+      <c r="C20" s="26"/>
+      <c r="D20" s="50">
         <f>SUMPRODUCT(ROUND(D15:D19,2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="50">
         <f>SUMPRODUCT(ROUND(E15:E19,2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="50">
         <f>SUMPRODUCT(ROUND(F15:F19,2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="62">
+      <c r="G20" s="53">
         <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="31"/>
-      <c r="J20" s="38" t="s">
+      <c r="H20" s="32"/>
+      <c r="J20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="K20" s="39" t="str">
+      <c r="K20" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L20" s="40"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="42">
+      <c r="L20" s="41"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="43">
         <f>IF(M20="","",N20/M20)</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="38" t="s">
+      <c r="Q20" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="R20" s="39" t="str">
+      <c r="R20" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S20" s="40"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="V20" s="42">
+      <c r="S20" s="41"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="43">
         <f>IF(T20="","",U20/T20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:22">
-      <c r="J21" s="38" t="s">
+      <c r="J21" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K21" s="39" t="str">
+      <c r="K21" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L21" s="40"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="42">
+      <c r="L21" s="41"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="43">
         <f>IF(M21="","",N21/M21)</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="38" t="s">
+      <c r="Q21" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="R21" s="39" t="str">
+      <c r="R21" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S21" s="40"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="42">
+      <c r="S21" s="41"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="42"/>
+      <c r="V21" s="43">
         <f>IF(T21="","",U21/T21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:22">
-      <c r="J22" s="38" t="s">
+      <c r="J22" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="39" t="str">
+      <c r="K22" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L22" s="40"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="42">
+      <c r="L22" s="41"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="43">
         <f>IF(M22="","",N22/M22)</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="38" t="s">
+      <c r="Q22" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="R22" s="39" t="str">
+      <c r="R22" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S22" s="40"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="41"/>
-      <c r="V22" s="42">
+      <c r="S22" s="41"/>
+      <c r="T22" s="42"/>
+      <c r="U22" s="42"/>
+      <c r="V22" s="43">
         <f>IF(T22="","",U22/T22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:22">
-      <c r="J23" s="38" t="s">
+      <c r="J23" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="39" t="str">
+      <c r="K23" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L23" s="40"/>
-      <c r="M23" s="41"/>
-      <c r="N23" s="41"/>
-      <c r="O23" s="42">
+      <c r="L23" s="41"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="43">
         <f>IF(M23="","",N23/M23)</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="38" t="s">
+      <c r="Q23" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="39" t="str">
+      <c r="R23" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S23" s="40"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="41"/>
-      <c r="V23" s="42">
+      <c r="S23" s="41"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="42"/>
+      <c r="V23" s="43">
         <f>IF(T23="","",U23/T23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:22">
-      <c r="J24" s="38" t="s">
+      <c r="J24" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="39" t="str">
+      <c r="K24" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L24" s="40"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="42">
+      <c r="L24" s="41"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="43">
         <f>IF(M24="","",N24/M24)</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="38" t="s">
+      <c r="Q24" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="R24" s="39" t="str">
+      <c r="R24" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S24" s="40"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="42">
+      <c r="S24" s="41"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="42"/>
+      <c r="V24" s="43">
         <f>IF(T24="","",U24/T24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:22">
-      <c r="J25" s="38" t="s">
+      <c r="J25" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="39" t="str">
+      <c r="K25" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L25" s="40"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="42">
+      <c r="L25" s="41"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="43">
         <f>IF(M25="","",N25/M25)</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="38" t="s">
+      <c r="Q25" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="R25" s="39" t="str">
+      <c r="R25" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S25" s="40"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="41"/>
-      <c r="V25" s="42">
+      <c r="S25" s="41"/>
+      <c r="T25" s="42"/>
+      <c r="U25" s="42"/>
+      <c r="V25" s="43">
         <f>IF(T25="","",U25/T25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:22">
-      <c r="J26" s="38" t="s">
+      <c r="J26" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="39" t="str">
+      <c r="K26" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L26" s="40"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="42">
+      <c r="L26" s="41"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="43">
         <f>IF(M26="","",N26/M26)</f>
         <v>0</v>
       </c>
-      <c r="Q26" s="38" t="s">
+      <c r="Q26" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="R26" s="39" t="str">
+      <c r="R26" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S26" s="40"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="42">
+      <c r="S26" s="41"/>
+      <c r="T26" s="42"/>
+      <c r="U26" s="42"/>
+      <c r="V26" s="43">
         <f>IF(T26="","",U26/T26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:22">
-      <c r="J27" s="38" t="s">
+      <c r="J27" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K27" s="39" t="str">
+      <c r="K27" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L27" s="40"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="42">
+      <c r="L27" s="41"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="43">
         <f>IF(M27="","",N27/M27)</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="38" t="s">
+      <c r="Q27" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="39" t="str">
+      <c r="R27" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S27" s="40"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="41"/>
-      <c r="V27" s="42">
+      <c r="S27" s="41"/>
+      <c r="T27" s="42"/>
+      <c r="U27" s="42"/>
+      <c r="V27" s="43">
         <f>IF(T27="","",U27/T27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:22">
-      <c r="J28" s="38" t="s">
+      <c r="J28" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="39" t="str">
+      <c r="K28" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L28" s="40"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="42">
+      <c r="L28" s="41"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="43">
         <f>IF(M28="","",N28/M28)</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="38" t="s">
+      <c r="Q28" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="R28" s="39" t="str">
+      <c r="R28" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S28" s="40"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="42">
+      <c r="S28" s="41"/>
+      <c r="T28" s="42"/>
+      <c r="U28" s="42"/>
+      <c r="V28" s="43">
         <f>IF(T28="","",U28/T28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:22">
-      <c r="J29" s="38" t="s">
+      <c r="J29" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="K29" s="39" t="str">
+      <c r="K29" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L29" s="40"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="42">
+      <c r="L29" s="41"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="43">
         <f>IF(M29="","",N29/M29)</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="38" t="s">
+      <c r="Q29" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="R29" s="39" t="str">
+      <c r="R29" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S29" s="40"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="42">
+      <c r="S29" s="41"/>
+      <c r="T29" s="42"/>
+      <c r="U29" s="42"/>
+      <c r="V29" s="43">
         <f>IF(T29="","",U29/T29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:22">
-      <c r="J30" s="38" t="s">
+      <c r="J30" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="39" t="str">
+      <c r="K30" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L30" s="40"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="42">
+      <c r="L30" s="41"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="43">
         <f>IF(M30="","",N30/M30)</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="38" t="s">
+      <c r="Q30" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="39" t="str">
+      <c r="R30" s="40" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S30" s="40"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="42">
+      <c r="S30" s="41"/>
+      <c r="T30" s="42"/>
+      <c r="U30" s="42"/>
+      <c r="V30" s="43">
         <f>IF(T30="","",U30/T30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:22">
-      <c r="J31" s="43" t="s">
+      <c r="J31" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="K31" s="44" t="str">
+      <c r="K31" s="45" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="L31" s="45"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
-      <c r="O31" s="47">
+      <c r="L31" s="46"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="47"/>
+      <c r="O31" s="48">
         <f>IF(M31="","",N31/M31)</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="43" t="s">
+      <c r="Q31" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="R31" s="44" t="str">
+      <c r="R31" s="45" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>Rate</v>
       </c>
-      <c r="S31" s="45"/>
-      <c r="T31" s="46"/>
-      <c r="U31" s="46"/>
-      <c r="V31" s="47">
+      <c r="S31" s="46"/>
+      <c r="T31" s="47"/>
+      <c r="U31" s="47"/>
+      <c r="V31" s="48">
         <f>IF(T31="","",U31/T31)</f>
         <v>0</v>
       </c>
@@ -3363,1712 +3377,1712 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:64">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="68" t="s">
+      <c r="J1" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="68" t="s">
+      <c r="K1" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="68" t="s">
+      <c r="L1" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="68" t="s">
+      <c r="M1" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="N1" s="68" t="s">
+      <c r="N1" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="O1" s="68" t="s">
+      <c r="O1" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="68" t="s">
+      <c r="P1" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="68" t="s">
+      <c r="Q1" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="R1" s="68" t="s">
+      <c r="R1" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="S1" s="68" t="s">
+      <c r="S1" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="T1" s="68" t="s">
+      <c r="T1" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="U1" s="68" t="s">
+      <c r="U1" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="V1" s="68" t="s">
+      <c r="V1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="W1" s="68" t="s">
+      <c r="W1" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="X1" s="68" t="s">
+      <c r="X1" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="Y1" s="68" t="s">
+      <c r="Y1" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="Z1" s="68" t="s">
+      <c r="Z1" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="AA1" s="68" t="s">
+      <c r="AA1" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="AB1" s="68" t="s">
+      <c r="AB1" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="AC1" s="68" t="s">
+      <c r="AC1" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="AD1" s="68" t="s">
+      <c r="AD1" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="AE1" s="68" t="s">
+      <c r="AE1" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="AF1" s="68" t="s">
+      <c r="AF1" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="AG1" s="68" t="s">
+      <c r="AG1" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="AH1" s="68" t="s">
+      <c r="AH1" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="AI1" s="68" t="s">
+      <c r="AI1" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="AJ1" s="68" t="s">
+      <c r="AJ1" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="AK1" s="68" t="s">
+      <c r="AK1" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="AL1" s="68" t="s">
+      <c r="AL1" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="AM1" s="68" t="s">
+      <c r="AM1" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="AN1" s="68" t="s">
+      <c r="AN1" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="AO1" s="68" t="s">
+      <c r="AO1" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="AP1" s="68" t="s">
+      <c r="AP1" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="AQ1" s="68" t="s">
+      <c r="AQ1" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="AR1" s="68" t="s">
+      <c r="AR1" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="AS1" s="68" t="s">
+      <c r="AS1" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="AT1" s="68" t="s">
+      <c r="AT1" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="AU1" s="68" t="s">
+      <c r="AU1" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="AV1" s="68" t="s">
+      <c r="AV1" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="AW1" s="68" t="s">
+      <c r="AW1" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="AX1" s="68" t="s">
+      <c r="AX1" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="AY1" s="68" t="s">
+      <c r="AY1" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="AZ1" s="68" t="s">
+      <c r="AZ1" s="69" t="s">
         <v>88</v>
       </c>
-      <c r="BA1" s="68" t="s">
+      <c r="BA1" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="BB1" s="68" t="s">
+      <c r="BB1" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="BC1" s="68" t="s">
+      <c r="BC1" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="BD1" s="68" t="s">
+      <c r="BD1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="BE1" s="68" t="s">
+      <c r="BE1" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="BF1" s="68" t="s">
+      <c r="BF1" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="BG1" s="68" t="s">
+      <c r="BG1" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="BH1" s="68" t="s">
+      <c r="BH1" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="BI1" s="68" t="s">
+      <c r="BI1" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="BJ1" s="68" t="s">
+      <c r="BJ1" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="BK1" s="68" t="s">
+      <c r="BK1" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="BL1" s="68" t="s">
+      <c r="BL1" s="69" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:64">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="68" t="s">
+      <c r="G2" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="68" t="s">
+      <c r="H2" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="68" t="s">
+      <c r="J2" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="68" t="s">
+      <c r="K2" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="L2" s="68" t="s">
+      <c r="L2" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="M2" s="68" t="s">
+      <c r="M2" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="N2" s="68" t="s">
+      <c r="N2" s="69" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="68" t="s">
+      <c r="O2" s="69" t="s">
         <v>115</v>
       </c>
-      <c r="P2" s="68" t="s">
+      <c r="P2" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="Q2" s="68" t="s">
+      <c r="Q2" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="R2" s="68" t="s">
+      <c r="R2" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="S2" s="68" t="s">
+      <c r="S2" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="T2" s="68" t="s">
+      <c r="T2" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="U2" s="68" t="s">
+      <c r="U2" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="V2" s="68" t="s">
+      <c r="V2" s="69" t="s">
         <v>122</v>
       </c>
-      <c r="W2" s="68" t="s">
+      <c r="W2" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="X2" s="68" t="s">
+      <c r="X2" s="69" t="s">
         <v>124</v>
       </c>
-      <c r="Y2" s="68" t="s">
+      <c r="Y2" s="69" t="s">
         <v>125</v>
       </c>
-      <c r="Z2" s="68" t="s">
+      <c r="Z2" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="AA2" s="68" t="s">
+      <c r="AA2" s="69" t="s">
         <v>127</v>
       </c>
-      <c r="AB2" s="68" t="s">
+      <c r="AB2" s="69" t="s">
         <v>128</v>
       </c>
-      <c r="AC2" s="68" t="s">
+      <c r="AC2" s="69" t="s">
         <v>129</v>
       </c>
-      <c r="AD2" s="68" t="s">
+      <c r="AD2" s="69" t="s">
         <v>130</v>
       </c>
-      <c r="AE2" s="68" t="s">
+      <c r="AE2" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="AF2" s="68" t="s">
+      <c r="AF2" s="69" t="s">
         <v>132</v>
       </c>
-      <c r="AG2" s="68" t="s">
+      <c r="AG2" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="AH2" s="68" t="s">
+      <c r="AH2" s="69" t="s">
         <v>134</v>
       </c>
-      <c r="AI2" s="68" t="s">
+      <c r="AI2" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="AJ2" s="68" t="s">
+      <c r="AJ2" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="AK2" s="68" t="s">
+      <c r="AK2" s="69" t="s">
         <v>137</v>
       </c>
-      <c r="AL2" s="68" t="s">
+      <c r="AL2" s="69" t="s">
         <v>138</v>
       </c>
-      <c r="AM2" s="68" t="s">
+      <c r="AM2" s="69" t="s">
         <v>139</v>
       </c>
-      <c r="AN2" s="68" t="s">
+      <c r="AN2" s="69" t="s">
         <v>140</v>
       </c>
-      <c r="AO2" s="68" t="s">
+      <c r="AO2" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="AP2" s="68" t="s">
+      <c r="AP2" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AQ2" s="68" t="s">
+      <c r="AQ2" s="69" t="s">
         <v>122</v>
       </c>
-      <c r="AR2" s="68" t="s">
+      <c r="AR2" s="69" t="s">
         <v>142</v>
       </c>
-      <c r="AS2" s="68" t="s">
+      <c r="AS2" s="69" t="s">
         <v>143</v>
       </c>
-      <c r="AT2" s="68" t="s">
+      <c r="AT2" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="AU2" s="68" t="s">
+      <c r="AU2" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AV2" s="68" t="s">
+      <c r="AV2" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="AW2" s="68" t="s">
+      <c r="AW2" s="69" t="s">
         <v>146</v>
       </c>
-      <c r="AX2" s="68" t="s">
+      <c r="AX2" s="69" t="s">
         <v>147</v>
       </c>
-      <c r="AY2" s="68" t="s">
+      <c r="AY2" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="AZ2" s="68" t="s">
+      <c r="AZ2" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="BA2" s="68" t="s">
+      <c r="BA2" s="69" t="s">
         <v>150</v>
       </c>
-      <c r="BB2" s="68" t="s">
+      <c r="BB2" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="BC2" s="68" t="s">
+      <c r="BC2" s="69" t="s">
         <v>152</v>
       </c>
-      <c r="BD2" s="68" t="s">
+      <c r="BD2" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="BE2" s="68" t="s">
+      <c r="BE2" s="69" t="s">
         <v>154</v>
       </c>
-      <c r="BF2" s="68" t="s">
+      <c r="BF2" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="BG2" s="68" t="s">
+      <c r="BG2" s="69" t="s">
         <v>156</v>
       </c>
-      <c r="BH2" s="68" t="s">
+      <c r="BH2" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="BI2" s="68" t="s">
+      <c r="BI2" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="BJ2" s="68" t="s">
+      <c r="BJ2" s="69" t="s">
         <v>159</v>
       </c>
-      <c r="BK2" s="68" t="s">
+      <c r="BK2" s="69" t="s">
         <v>160</v>
       </c>
-      <c r="BL2" s="68" t="s">
+      <c r="BL2" s="69" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:64">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="69" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="69" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="69" t="s">
         <v>163</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="69" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="69" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="68" t="s">
+      <c r="F3" s="69" t="s">
         <v>166</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="69" t="s">
         <v>167</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="69" t="s">
         <v>168</v>
       </c>
-      <c r="I3" s="68" t="s">
+      <c r="I3" s="69" t="s">
         <v>168</v>
       </c>
-      <c r="J3" s="68" t="s">
+      <c r="J3" s="69" t="s">
         <v>169</v>
       </c>
-      <c r="K3" s="68" t="s">
+      <c r="K3" s="69" t="s">
         <v>170</v>
       </c>
-      <c r="L3" s="68" t="s">
+      <c r="L3" s="69" t="s">
         <v>171</v>
       </c>
-      <c r="M3" s="68" t="s">
+      <c r="M3" s="69" t="s">
         <v>172</v>
       </c>
-      <c r="N3" s="68" t="s">
+      <c r="N3" s="69" t="s">
         <v>173</v>
       </c>
-      <c r="O3" s="68" t="s">
+      <c r="O3" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="P3" s="68" t="s">
+      <c r="P3" s="69" t="s">
         <v>175</v>
       </c>
-      <c r="Q3" s="68" t="s">
+      <c r="Q3" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="R3" s="68" t="s">
+      <c r="R3" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="S3" s="68" t="s">
+      <c r="S3" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="T3" s="68" t="s">
+      <c r="T3" s="69" t="s">
         <v>179</v>
       </c>
-      <c r="U3" s="68" t="s">
+      <c r="U3" s="69" t="s">
         <v>180</v>
       </c>
-      <c r="V3" s="68" t="s">
+      <c r="V3" s="69" t="s">
         <v>181</v>
       </c>
-      <c r="W3" s="68" t="s">
+      <c r="W3" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="69" t="s">
         <v>182</v>
       </c>
-      <c r="Y3" s="68" t="s">
+      <c r="Y3" s="69" t="s">
         <v>183</v>
       </c>
-      <c r="Z3" s="68" t="s">
+      <c r="Z3" s="69" t="s">
         <v>184</v>
       </c>
-      <c r="AA3" s="68" t="s">
+      <c r="AA3" s="69" t="s">
         <v>185</v>
       </c>
-      <c r="AB3" s="68" t="s">
+      <c r="AB3" s="69" t="s">
         <v>186</v>
       </c>
-      <c r="AC3" s="68" t="s">
+      <c r="AC3" s="69" t="s">
         <v>187</v>
       </c>
-      <c r="AD3" s="68" t="s">
+      <c r="AD3" s="69" t="s">
         <v>188</v>
       </c>
-      <c r="AE3" s="68" t="s">
+      <c r="AE3" s="69" t="s">
         <v>189</v>
       </c>
-      <c r="AF3" s="68" t="s">
+      <c r="AF3" s="69" t="s">
         <v>190</v>
       </c>
-      <c r="AG3" s="68" t="s">
+      <c r="AG3" s="69" t="s">
         <v>191</v>
       </c>
-      <c r="AH3" s="68" t="s">
+      <c r="AH3" s="69" t="s">
         <v>192</v>
       </c>
-      <c r="AI3" s="68" t="s">
+      <c r="AI3" s="69" t="s">
         <v>193</v>
       </c>
-      <c r="AJ3" s="68" t="s">
+      <c r="AJ3" s="69" t="s">
         <v>194</v>
       </c>
-      <c r="AK3" s="68" t="s">
+      <c r="AK3" s="69" t="s">
         <v>195</v>
       </c>
-      <c r="AL3" s="68" t="s">
+      <c r="AL3" s="69" t="s">
         <v>196</v>
       </c>
-      <c r="AM3" s="68" t="s">
+      <c r="AM3" s="69" t="s">
         <v>197</v>
       </c>
-      <c r="AN3" s="68" t="s">
+      <c r="AN3" s="69" t="s">
         <v>140</v>
       </c>
-      <c r="AO3" s="68" t="s">
+      <c r="AO3" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="AP3" s="68" t="s">
+      <c r="AP3" s="69" t="s">
         <v>198</v>
       </c>
-      <c r="AQ3" s="68" t="s">
+      <c r="AQ3" s="69" t="s">
         <v>181</v>
       </c>
-      <c r="AR3" s="68" t="s">
+      <c r="AR3" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="AS3" s="68" t="s">
+      <c r="AS3" s="69" t="s">
         <v>200</v>
       </c>
-      <c r="AT3" s="68" t="s">
+      <c r="AT3" s="69" t="s">
         <v>201</v>
       </c>
-      <c r="AU3" s="68" t="s">
+      <c r="AU3" s="69" t="s">
         <v>202</v>
       </c>
-      <c r="AV3" s="68" t="s">
+      <c r="AV3" s="69" t="s">
         <v>203</v>
       </c>
-      <c r="AW3" s="68" t="s">
+      <c r="AW3" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="AX3" s="68" t="s">
+      <c r="AX3" s="69" t="s">
         <v>205</v>
       </c>
-      <c r="AY3" s="68" t="s">
+      <c r="AY3" s="69" t="s">
         <v>206</v>
       </c>
-      <c r="AZ3" s="68" t="s">
+      <c r="AZ3" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="BA3" s="68" t="s">
+      <c r="BA3" s="69" t="s">
         <v>208</v>
       </c>
-      <c r="BB3" s="68" t="s">
+      <c r="BB3" s="69" t="s">
         <v>209</v>
       </c>
-      <c r="BC3" s="68" t="s">
+      <c r="BC3" s="69" t="s">
         <v>210</v>
       </c>
-      <c r="BD3" s="68" t="s">
+      <c r="BD3" s="69" t="s">
         <v>211</v>
       </c>
-      <c r="BE3" s="68" t="s">
+      <c r="BE3" s="69" t="s">
         <v>212</v>
       </c>
-      <c r="BF3" s="68" t="s">
+      <c r="BF3" s="69" t="s">
         <v>213</v>
       </c>
-      <c r="BG3" s="68" t="s">
+      <c r="BG3" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="BH3" s="68" t="s">
+      <c r="BH3" s="69" t="s">
         <v>215</v>
       </c>
-      <c r="BI3" s="68" t="s">
+      <c r="BI3" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="BJ3" s="68" t="s">
+      <c r="BJ3" s="69" t="s">
         <v>217</v>
       </c>
-      <c r="BK3" s="68" t="s">
+      <c r="BK3" s="69" t="s">
         <v>218</v>
       </c>
-      <c r="BL3" s="68" t="s">
+      <c r="BL3" s="69" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:64">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="69" t="s">
         <v>219</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="69" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="69" t="s">
         <v>222</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="F4" s="68" t="s">
+      <c r="F4" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="69" t="s">
         <v>225</v>
       </c>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="69" t="s">
         <v>226</v>
       </c>
-      <c r="I4" s="68" t="s">
+      <c r="I4" s="69" t="s">
         <v>227</v>
       </c>
-      <c r="J4" s="68" t="s">
+      <c r="J4" s="69" t="s">
         <v>228</v>
       </c>
-      <c r="K4" s="68" t="s">
+      <c r="K4" s="69" t="s">
         <v>229</v>
       </c>
-      <c r="L4" s="68" t="s">
+      <c r="L4" s="69" t="s">
         <v>230</v>
       </c>
-      <c r="M4" s="68" t="s">
+      <c r="M4" s="69" t="s">
         <v>231</v>
       </c>
-      <c r="N4" s="68" t="s">
+      <c r="N4" s="69" t="s">
         <v>232</v>
       </c>
-      <c r="O4" s="68" t="s">
+      <c r="O4" s="69" t="s">
         <v>233</v>
       </c>
-      <c r="P4" s="68" t="s">
+      <c r="P4" s="69" t="s">
         <v>234</v>
       </c>
-      <c r="Q4" s="68" t="s">
+      <c r="Q4" s="69" t="s">
         <v>235</v>
       </c>
-      <c r="R4" s="68" t="s">
+      <c r="R4" s="69" t="s">
         <v>236</v>
       </c>
-      <c r="S4" s="68" t="s">
+      <c r="S4" s="69" t="s">
         <v>237</v>
       </c>
-      <c r="T4" s="68" t="s">
+      <c r="T4" s="69" t="s">
         <v>238</v>
       </c>
-      <c r="U4" s="68" t="s">
+      <c r="U4" s="69" t="s">
         <v>239</v>
       </c>
-      <c r="V4" s="68" t="s">
+      <c r="V4" s="69" t="s">
         <v>181</v>
       </c>
-      <c r="W4" s="68" t="s">
+      <c r="W4" s="69" t="s">
         <v>240</v>
       </c>
-      <c r="X4" s="68" t="s">
+      <c r="X4" s="69" t="s">
         <v>241</v>
       </c>
-      <c r="Y4" s="68" t="s">
+      <c r="Y4" s="69" t="s">
         <v>242</v>
       </c>
-      <c r="Z4" s="68" t="s">
+      <c r="Z4" s="69" t="s">
         <v>243</v>
       </c>
-      <c r="AA4" s="68" t="s">
+      <c r="AA4" s="69" t="s">
         <v>244</v>
       </c>
-      <c r="AB4" s="68" t="s">
+      <c r="AB4" s="69" t="s">
         <v>245</v>
       </c>
-      <c r="AC4" s="68" t="s">
+      <c r="AC4" s="69" t="s">
         <v>246</v>
       </c>
-      <c r="AD4" s="68" t="s">
+      <c r="AD4" s="69" t="s">
         <v>247</v>
       </c>
-      <c r="AE4" s="68" t="s">
+      <c r="AE4" s="69" t="s">
         <v>248</v>
       </c>
-      <c r="AF4" s="68" t="s">
+      <c r="AF4" s="69" t="s">
         <v>249</v>
       </c>
-      <c r="AG4" s="68" t="s">
+      <c r="AG4" s="69" t="s">
         <v>250</v>
       </c>
-      <c r="AH4" s="68" t="s">
+      <c r="AH4" s="69" t="s">
         <v>251</v>
       </c>
-      <c r="AI4" s="68" t="s">
+      <c r="AI4" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="AJ4" s="68" t="s">
+      <c r="AJ4" s="69" t="s">
         <v>253</v>
       </c>
-      <c r="AK4" s="68" t="s">
+      <c r="AK4" s="69" t="s">
         <v>254</v>
       </c>
-      <c r="AL4" s="68" t="s">
+      <c r="AL4" s="69" t="s">
         <v>255</v>
       </c>
-      <c r="AM4" s="68" t="s">
+      <c r="AM4" s="69" t="s">
         <v>256</v>
       </c>
-      <c r="AN4" s="68" t="s">
+      <c r="AN4" s="69" t="s">
         <v>257</v>
       </c>
-      <c r="AO4" s="68" t="s">
+      <c r="AO4" s="69" t="s">
         <v>258</v>
       </c>
-      <c r="AP4" s="68" t="s">
+      <c r="AP4" s="69" t="s">
         <v>259</v>
       </c>
-      <c r="AQ4" s="68" t="s">
+      <c r="AQ4" s="69" t="s">
         <v>122</v>
       </c>
-      <c r="AR4" s="68" t="s">
+      <c r="AR4" s="69" t="s">
         <v>260</v>
       </c>
-      <c r="AS4" s="68" t="s">
+      <c r="AS4" s="69" t="s">
         <v>261</v>
       </c>
-      <c r="AT4" s="68" t="s">
+      <c r="AT4" s="69" t="s">
         <v>262</v>
       </c>
-      <c r="AU4" s="68" t="s">
+      <c r="AU4" s="69" t="s">
         <v>263</v>
       </c>
-      <c r="AV4" s="68" t="s">
+      <c r="AV4" s="69" t="s">
         <v>264</v>
       </c>
-      <c r="AW4" s="68" t="s">
+      <c r="AW4" s="69" t="s">
         <v>265</v>
       </c>
-      <c r="AX4" s="68" t="s">
+      <c r="AX4" s="69" t="s">
         <v>266</v>
       </c>
-      <c r="AY4" s="68" t="s">
+      <c r="AY4" s="69" t="s">
         <v>267</v>
       </c>
-      <c r="AZ4" s="68" t="s">
+      <c r="AZ4" s="69" t="s">
         <v>268</v>
       </c>
-      <c r="BA4" s="68" t="s">
+      <c r="BA4" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="BB4" s="68" t="s">
+      <c r="BB4" s="69" t="s">
         <v>270</v>
       </c>
-      <c r="BC4" s="68" t="s">
+      <c r="BC4" s="69" t="s">
         <v>271</v>
       </c>
-      <c r="BD4" s="68" t="s">
+      <c r="BD4" s="69" t="s">
         <v>272</v>
       </c>
-      <c r="BE4" s="68" t="s">
+      <c r="BE4" s="69" t="s">
         <v>273</v>
       </c>
-      <c r="BF4" s="68" t="s">
+      <c r="BF4" s="69" t="s">
         <v>274</v>
       </c>
-      <c r="BG4" s="68" t="s">
+      <c r="BG4" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="BH4" s="68" t="s">
+      <c r="BH4" s="69" t="s">
         <v>275</v>
       </c>
-      <c r="BI4" s="68" t="s">
+      <c r="BI4" s="69" t="s">
         <v>276</v>
       </c>
-      <c r="BJ4" s="68" t="s">
+      <c r="BJ4" s="69" t="s">
         <v>277</v>
       </c>
-      <c r="BK4" s="68" t="s">
+      <c r="BK4" s="69" t="s">
         <v>278</v>
       </c>
-      <c r="BL4" s="68" t="s">
+      <c r="BL4" s="69" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:64">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="69" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="69" t="s">
         <v>280</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="69" t="s">
         <v>281</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="69" t="s">
         <v>282</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="69" t="s">
         <v>283</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="69" t="s">
         <v>284</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="69" t="s">
         <v>285</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="69" t="s">
         <v>226</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="I5" s="69" t="s">
         <v>286</v>
       </c>
-      <c r="J5" s="68" t="s">
+      <c r="J5" s="69" t="s">
         <v>287</v>
       </c>
-      <c r="K5" s="68" t="s">
+      <c r="K5" s="69" t="s">
         <v>288</v>
       </c>
-      <c r="L5" s="68" t="s">
+      <c r="L5" s="69" t="s">
         <v>289</v>
       </c>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="69" t="s">
         <v>290</v>
       </c>
-      <c r="N5" s="68" t="s">
+      <c r="N5" s="69" t="s">
         <v>291</v>
       </c>
-      <c r="O5" s="68" t="s">
+      <c r="O5" s="69" t="s">
         <v>292</v>
       </c>
-      <c r="P5" s="68" t="s">
+      <c r="P5" s="69" t="s">
         <v>293</v>
       </c>
-      <c r="Q5" s="68" t="s">
+      <c r="Q5" s="69" t="s">
         <v>294</v>
       </c>
-      <c r="R5" s="68" t="s">
+      <c r="R5" s="69" t="s">
         <v>295</v>
       </c>
-      <c r="S5" s="68" t="s">
+      <c r="S5" s="69" t="s">
         <v>296</v>
       </c>
-      <c r="T5" s="68" t="s">
+      <c r="T5" s="69" t="s">
         <v>297</v>
       </c>
-      <c r="U5" s="68" t="s">
+      <c r="U5" s="69" t="s">
         <v>298</v>
       </c>
-      <c r="V5" s="68" t="s">
+      <c r="V5" s="69" t="s">
         <v>181</v>
       </c>
-      <c r="W5" s="68" t="s">
+      <c r="W5" s="69" t="s">
         <v>299</v>
       </c>
-      <c r="X5" s="68" t="s">
+      <c r="X5" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="Y5" s="68" t="s">
+      <c r="Y5" s="69" t="s">
         <v>301</v>
       </c>
-      <c r="Z5" s="68" t="s">
+      <c r="Z5" s="69" t="s">
         <v>302</v>
       </c>
-      <c r="AA5" s="68" t="s">
+      <c r="AA5" s="69" t="s">
         <v>303</v>
       </c>
-      <c r="AB5" s="68" t="s">
+      <c r="AB5" s="69" t="s">
         <v>245</v>
       </c>
-      <c r="AC5" s="68" t="s">
+      <c r="AC5" s="69" t="s">
         <v>304</v>
       </c>
-      <c r="AD5" s="68" t="s">
+      <c r="AD5" s="69" t="s">
         <v>305</v>
       </c>
-      <c r="AE5" s="68" t="s">
+      <c r="AE5" s="69" t="s">
         <v>306</v>
       </c>
-      <c r="AF5" s="68" t="s">
+      <c r="AF5" s="69" t="s">
         <v>307</v>
       </c>
-      <c r="AG5" s="68" t="s">
+      <c r="AG5" s="69" t="s">
         <v>308</v>
       </c>
-      <c r="AH5" s="68" t="s">
+      <c r="AH5" s="69" t="s">
         <v>309</v>
       </c>
-      <c r="AI5" s="68" t="s">
+      <c r="AI5" s="69" t="s">
         <v>310</v>
       </c>
-      <c r="AJ5" s="68" t="s">
+      <c r="AJ5" s="69" t="s">
         <v>311</v>
       </c>
-      <c r="AK5" s="68" t="s">
+      <c r="AK5" s="69" t="s">
         <v>312</v>
       </c>
-      <c r="AL5" s="68" t="s">
+      <c r="AL5" s="69" t="s">
         <v>313</v>
       </c>
-      <c r="AM5" s="68" t="s">
+      <c r="AM5" s="69" t="s">
         <v>314</v>
       </c>
-      <c r="AN5" s="68" t="s">
+      <c r="AN5" s="69" t="s">
         <v>315</v>
       </c>
-      <c r="AO5" s="68" t="s">
+      <c r="AO5" s="69" t="s">
         <v>316</v>
       </c>
-      <c r="AP5" s="68" t="s">
+      <c r="AP5" s="69" t="s">
         <v>317</v>
       </c>
-      <c r="AQ5" s="68" t="s">
+      <c r="AQ5" s="69" t="s">
         <v>122</v>
       </c>
-      <c r="AR5" s="68" t="s">
+      <c r="AR5" s="69" t="s">
         <v>318</v>
       </c>
-      <c r="AS5" s="68" t="s">
+      <c r="AS5" s="69" t="s">
         <v>319</v>
       </c>
-      <c r="AT5" s="68" t="s">
+      <c r="AT5" s="69" t="s">
         <v>320</v>
       </c>
-      <c r="AU5" s="68" t="s">
+      <c r="AU5" s="69" t="s">
         <v>321</v>
       </c>
-      <c r="AV5" s="68" t="s">
+      <c r="AV5" s="69" t="s">
         <v>264</v>
       </c>
-      <c r="AW5" s="68" t="s">
+      <c r="AW5" s="69" t="s">
         <v>322</v>
       </c>
-      <c r="AX5" s="68" t="s">
+      <c r="AX5" s="69" t="s">
         <v>323</v>
       </c>
-      <c r="AY5" s="68" t="s">
+      <c r="AY5" s="69" t="s">
         <v>324</v>
       </c>
-      <c r="AZ5" s="68" t="s">
+      <c r="AZ5" s="69" t="s">
         <v>325</v>
       </c>
-      <c r="BA5" s="68" t="s">
+      <c r="BA5" s="69" t="s">
         <v>326</v>
       </c>
-      <c r="BB5" s="68" t="s">
+      <c r="BB5" s="69" t="s">
         <v>327</v>
       </c>
-      <c r="BC5" s="68" t="s">
+      <c r="BC5" s="69" t="s">
         <v>328</v>
       </c>
-      <c r="BD5" s="68" t="s">
+      <c r="BD5" s="69" t="s">
         <v>329</v>
       </c>
-      <c r="BE5" s="68" t="s">
+      <c r="BE5" s="69" t="s">
         <v>330</v>
       </c>
-      <c r="BF5" s="68" t="s">
+      <c r="BF5" s="69" t="s">
         <v>331</v>
       </c>
-      <c r="BG5" s="68" t="s">
+      <c r="BG5" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="BH5" s="68" t="s">
+      <c r="BH5" s="69" t="s">
         <v>332</v>
       </c>
-      <c r="BI5" s="68" t="s">
+      <c r="BI5" s="69" t="s">
         <v>333</v>
       </c>
-      <c r="BJ5" s="68" t="s">
+      <c r="BJ5" s="69" t="s">
         <v>334</v>
       </c>
-      <c r="BK5" s="68" t="s">
+      <c r="BK5" s="69" t="s">
         <v>335</v>
       </c>
-      <c r="BL5" s="68" t="s">
+      <c r="BL5" s="69" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:64">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="69" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:64">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="69" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:64">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="69" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:64">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="69" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:64">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="69" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:64">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="69" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:64">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="69" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:64">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="69" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:64">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="69" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:64">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="69" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:64">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="69" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="69" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="69" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="69" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="69" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="69" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="69" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="69" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="68" t="s">
+      <c r="A24" s="69" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="68" t="s">
+      <c r="A25" s="69" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="68" t="s">
+      <c r="A26" s="69" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="68" t="s">
+      <c r="A27" s="69" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="68" t="s">
+      <c r="A28" s="69" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="68" t="s">
+      <c r="A29" s="69" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="68" t="s">
+      <c r="A30" s="69" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="69" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="68" t="s">
+      <c r="A32" s="69" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="68" t="s">
+      <c r="A33" s="69" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="68" t="s">
+      <c r="A34" s="69" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="68" t="s">
+      <c r="A35" s="69" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="68" t="s">
+      <c r="A36" s="69" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="68" t="s">
+      <c r="A37" s="69" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="68" t="s">
+      <c r="A38" s="69" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="68" t="s">
+      <c r="A39" s="69" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="68" t="s">
+      <c r="A40" s="69" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="68" t="s">
+      <c r="A41" s="69" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="68" t="s">
+      <c r="A42" s="69" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="68" t="s">
+      <c r="A43" s="69" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="68" t="s">
+      <c r="A44" s="69" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="68" t="s">
+      <c r="A45" s="69" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="68" t="s">
+      <c r="A46" s="69" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="68" t="s">
+      <c r="A47" s="69" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="68" t="s">
+      <c r="A48" s="69" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="68" t="s">
+      <c r="A49" s="69" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="68" t="s">
+      <c r="A50" s="69" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="68" t="s">
+      <c r="A51" s="69" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="68" t="s">
+      <c r="A52" s="69" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="68" t="s">
+      <c r="A53" s="69" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="68" t="s">
+      <c r="A54" s="69" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="68" t="s">
+      <c r="A55" s="69" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="68" t="s">
+      <c r="A56" s="69" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="68" t="s">
+      <c r="A57" s="69" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="68" t="s">
+      <c r="A58" s="69" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="68" t="s">
+      <c r="A59" s="69" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="68" t="s">
+      <c r="A60" s="69" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="68" t="s">
+      <c r="A61" s="69" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="68" t="s">
+      <c r="A62" s="69" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="68" t="s">
+      <c r="A63" s="69" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="68" t="s">
+      <c r="A64" s="69" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="68" t="s">
+      <c r="A65" s="69" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="68" t="s">
+      <c r="A66" s="69" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="68" t="s">
+      <c r="A67" s="69" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="68" t="s">
+      <c r="A68" s="69" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="68" t="s">
+      <c r="A69" s="69" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="68" t="s">
+      <c r="A70" s="69" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="68" t="s">
+      <c r="A71" s="69" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="68" t="s">
+      <c r="A72" s="69" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="68" t="s">
+      <c r="A73" s="69" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="68" t="s">
+      <c r="A74" s="69" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="68" t="s">
+      <c r="A75" s="69" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="68" t="s">
+      <c r="A76" s="69" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="68" t="s">
+      <c r="A77" s="69" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="68" t="s">
+      <c r="A78" s="69" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="68" t="s">
+      <c r="A79" s="69" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="68" t="s">
+      <c r="A80" s="69" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="68" t="s">
+      <c r="A81" s="69" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="68" t="s">
+      <c r="A82" s="69" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="68" t="s">
+      <c r="A83" s="69" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="68" t="s">
+      <c r="A84" s="69" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="68" t="s">
+      <c r="A85" s="69" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="68" t="s">
+      <c r="A86" s="69" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="68" t="s">
+      <c r="A87" s="69" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="68" t="s">
+      <c r="A88" s="69" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="68" t="s">
+      <c r="A89" s="69" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="68" t="s">
+      <c r="A90" s="69" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="68" t="s">
+      <c r="A91" s="69" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="68" t="s">
+      <c r="A92" s="69" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="68" t="s">
+      <c r="A93" s="69" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="68" t="s">
+      <c r="A94" s="69" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="68" t="s">
+      <c r="A95" s="69" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="68" t="s">
+      <c r="A96" s="69" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="68" t="s">
+      <c r="A97" s="69" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="68" t="s">
+      <c r="A98" s="69" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="68" t="s">
+      <c r="A99" s="69" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="68" t="s">
+      <c r="A100" s="69" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="68" t="s">
+      <c r="A101" s="69" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="68" t="s">
+      <c r="A102" s="69" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="68" t="s">
+      <c r="A103" s="69" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="68" t="s">
+      <c r="A104" s="69" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="68" t="s">
+      <c r="A105" s="69" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="68" t="s">
+      <c r="A106" s="69" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="68" t="s">
+      <c r="A107" s="69" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="68" t="s">
+      <c r="A108" s="69" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="68" t="s">
+      <c r="A109" s="69" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="68" t="s">
+      <c r="A110" s="69" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="68" t="s">
+      <c r="A111" s="69" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="68" t="s">
+      <c r="A112" s="69" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="68" t="s">
+      <c r="A113" s="69" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="68" t="s">
+      <c r="A114" s="69" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="68" t="s">
+      <c r="A115" s="69" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="68" t="s">
+      <c r="A116" s="69" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="68" t="s">
+      <c r="A117" s="69" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="68" t="s">
+      <c r="A118" s="69" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="68" t="s">
+      <c r="A119" s="69" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="68" t="s">
+      <c r="A120" s="69" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="68" t="s">
+      <c r="A121" s="69" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="68" t="s">
+      <c r="A122" s="69" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="68" t="s">
+      <c r="A123" s="69" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="68" t="s">
+      <c r="A124" s="69" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="68" t="s">
+      <c r="A125" s="69" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="68" t="s">
+      <c r="A126" s="69" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="68" t="s">
+      <c r="A127" s="69" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="68" t="s">
+      <c r="A128" s="69" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="68" t="s">
+      <c r="A129" s="69" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="68" t="s">
+      <c r="A130" s="69" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="68" t="s">
+      <c r="A131" s="69" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="68" t="s">
+      <c r="A132" s="69" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="68" t="s">
+      <c r="A133" s="69" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="68" t="s">
+      <c r="A134" s="69" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="68" t="s">
+      <c r="A135" s="69" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="68" t="s">
+      <c r="A136" s="69" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="68" t="s">
+      <c r="A137" s="69" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="68" t="s">
+      <c r="A138" s="69" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="68" t="s">
+      <c r="A139" s="69" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="68" t="s">
+      <c r="A140" s="69" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="68" t="s">
+      <c r="A141" s="69" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="68" t="s">
+      <c r="A142" s="69" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="68" t="s">
+      <c r="A143" s="69" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="68" t="s">
+      <c r="A144" s="69" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="68" t="s">
+      <c r="A145" s="69" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="68" t="s">
+      <c r="A146" s="69" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="68" t="s">
+      <c r="A147" s="69" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="68" t="s">
+      <c r="A148" s="69" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="68" t="s">
+      <c r="A149" s="69" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="68" t="s">
+      <c r="A150" s="69" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="68" t="s">
+      <c r="A151" s="69" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="68" t="s">
+      <c r="A152" s="69" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="68" t="s">
+      <c r="A153" s="69" t="s">
         <v>483</v>
       </c>
     </row>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2058,57 +2058,57 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2432,12 +2432,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="57" t="str">
+      <c r="B1" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="J1" s="64" t="str">
+      <c r="J1" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
@@ -2452,14 +2452,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="58" t="str">
+      <c r="D2" s="49" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="62" t="str">
+      <c r="J2" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2470,12 +2470,12 @@
       <c r="O2" s="5"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="57" t="str">
+      <c r="B3" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="58" t="str">
+      <c r="D3" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
@@ -2488,7 +2488,7 @@
       <c r="O3" s="5"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="67" t="str">
+      <c r="J4" s="50" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2499,7 +2499,7 @@
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="58" t="str">
+      <c r="B5" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
@@ -2507,7 +2507,7 @@
       <c r="D5" s="13"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="58" t="str">
+      <c r="B6" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
@@ -2529,7 +2529,7 @@
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="58" t="str">
+      <c r="B8" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
@@ -2552,7 +2552,7 @@
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="58" t="str">
+      <c r="B9" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
@@ -2574,27 +2574,27 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="17"/>
       <c r="C11" s="27"/>
-      <c r="D11" s="61" t="str">
+      <c r="D11" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="52" t="str">
+      <c r="E11" s="66" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="61" t="str">
+      <c r="F11" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="61" t="str">
+      <c r="G11" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="65" t="str">
+      <c r="H11" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="63" t="str">
+      <c r="J11" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2603,7 +2603,7 @@
       <c r="M11" s="35"/>
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
-      <c r="Q11" s="63" t="str">
+      <c r="Q11" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2614,7 +2614,7 @@
       <c r="V11" s="36"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="56" t="str">
+      <c r="B12" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
@@ -2638,7 +2638,7 @@
       <c r="V12" s="38"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="59" t="str">
+      <c r="B13" s="68" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
@@ -2650,37 +2650,37 @@
       <c r="H13" s="20"/>
       <c r="J13" s="37"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="54" t="str">
+      <c r="L13" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="54" t="str">
+      <c r="M13" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="54" t="str">
+      <c r="N13" s="51" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="49" t="str">
+      <c r="O13" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
       <c r="Q13" s="37"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="54" t="str">
+      <c r="S13" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="54" t="str">
+      <c r="T13" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="54" t="str">
+      <c r="U13" s="51" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="49" t="str">
+      <c r="V13" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
@@ -2723,7 +2723,7 @@
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="66" t="str">
+      <c r="B15" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
@@ -2765,7 +2765,7 @@
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="60" t="str">
+      <c r="B16" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>Lokale Eigenleistung</v>
       </c>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="29"/>
-      <c r="G16" s="51">
+      <c r="G16" s="56">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
@@ -2810,7 +2810,7 @@
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="60" t="str">
+      <c r="B17" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>Beiträge von dritter Seite</v>
       </c>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E17" s="29"/>
       <c r="F17" s="29"/>
-      <c r="G17" s="51">
+      <c r="G17" s="56">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
@@ -2855,7 +2855,7 @@
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="60" t="str">
+      <c r="B18" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E18" s="29"/>
       <c r="F18" s="29"/>
-      <c r="G18" s="51">
+      <c r="G18" s="56">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
@@ -2900,7 +2900,7 @@
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="60" t="str">
+      <c r="B19" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>Zinserträge</v>
       </c>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E19" s="29"/>
       <c r="F19" s="29"/>
-      <c r="G19" s="51">
+      <c r="G19" s="56">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
@@ -2945,24 +2945,24 @@
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="68" t="str">
+      <c r="B20" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
       <c r="C20" s="26"/>
-      <c r="D20" s="50">
+      <c r="D20" s="67">
         <f>SUMPRODUCT(ROUND(D15:D19,2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="67">
         <f>SUMPRODUCT(ROUND(E15:E19,2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="67">
         <f>SUMPRODUCT(ROUND(F15:F19,2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="65">
         <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2061,54 +2061,54 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2432,12 +2432,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="52" t="str">
+      <c r="B1" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="J1" s="60" t="str">
+      <c r="J1" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
@@ -2459,7 +2459,7 @@
       <c r="E2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="61" t="str">
+      <c r="J2" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2470,7 +2470,7 @@
       <c r="O2" s="5"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="52" t="str">
+      <c r="B3" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
@@ -2488,7 +2488,7 @@
       <c r="O3" s="5"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="50" t="str">
+      <c r="J4" s="59" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2534,12 +2534,12 @@
         <v>Projektlaufzeit</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="55" t="str">
+      <c r="D8" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E8" s="9"/>
-      <c r="F8" s="55" t="str">
+      <c r="F8" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2557,12 +2557,12 @@
         <v>Aktueller Berichtszeitraum</v>
       </c>
       <c r="C9" s="7"/>
-      <c r="D9" s="55" t="str">
+      <c r="D9" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E9" s="9"/>
-      <c r="F9" s="55" t="str">
+      <c r="F9" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2574,27 +2574,27 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="17"/>
       <c r="C11" s="27"/>
-      <c r="D11" s="58" t="str">
+      <c r="D11" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="66" t="str">
+      <c r="E11" s="61" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="58" t="str">
+      <c r="F11" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="58" t="str">
+      <c r="G11" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="62" t="str">
+      <c r="H11" s="66" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="57" t="str">
+      <c r="J11" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2603,7 +2603,7 @@
       <c r="M11" s="35"/>
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
-      <c r="Q11" s="57" t="str">
+      <c r="Q11" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2614,7 +2614,7 @@
       <c r="V11" s="36"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="64" t="str">
+      <c r="B12" s="67" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
@@ -2638,7 +2638,7 @@
       <c r="V12" s="38"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="68" t="str">
+      <c r="B13" s="65" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
@@ -2650,37 +2650,37 @@
       <c r="H13" s="20"/>
       <c r="J13" s="37"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="51" t="str">
+      <c r="L13" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="51" t="str">
+      <c r="M13" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="51" t="str">
+      <c r="N13" s="52" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="59" t="str">
+      <c r="O13" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
       <c r="Q13" s="37"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="51" t="str">
+      <c r="S13" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="51" t="str">
+      <c r="T13" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="51" t="str">
+      <c r="U13" s="52" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="59" t="str">
+      <c r="V13" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
@@ -2723,7 +2723,7 @@
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="54" t="str">
+      <c r="B15" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
@@ -2765,7 +2765,7 @@
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="53" t="str">
+      <c r="B16" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>Lokale Eigenleistung</v>
       </c>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="29"/>
-      <c r="G16" s="56">
+      <c r="G16" s="57">
         <f>IFERROR(F16/D16,0)</f>
         <v>0</v>
       </c>
@@ -2810,7 +2810,7 @@
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="53" t="str">
+      <c r="B17" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>Beiträge von dritter Seite</v>
       </c>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E17" s="29"/>
       <c r="F17" s="29"/>
-      <c r="G17" s="56">
+      <c r="G17" s="57">
         <f>IFERROR(F17/D17,0)</f>
         <v>0</v>
       </c>
@@ -2855,7 +2855,7 @@
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="53" t="str">
+      <c r="B18" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E18" s="29"/>
       <c r="F18" s="29"/>
-      <c r="G18" s="56">
+      <c r="G18" s="57">
         <f>IFERROR(F18/D18,0)</f>
         <v>0</v>
       </c>
@@ -2900,7 +2900,7 @@
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="53" t="str">
+      <c r="B19" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>Zinserträge</v>
       </c>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E19" s="29"/>
       <c r="F19" s="29"/>
-      <c r="G19" s="56">
+      <c r="G19" s="57">
         <f>IFERROR(F19/D19,0)</f>
         <v>0</v>
       </c>
@@ -2945,24 +2945,24 @@
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="63" t="str">
+      <c r="B20" s="68" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
       <c r="C20" s="26"/>
-      <c r="D20" s="67">
+      <c r="D20" s="53">
         <f>SUMPRODUCT(ROUND(D15:D19,2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="67">
+      <c r="E20" s="53">
         <f>SUMPRODUCT(ROUND(E15:E19,2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="67">
+      <c r="F20" s="53">
         <f>SUMPRODUCT(ROUND(F15:F19,2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="65">
+      <c r="G20" s="51">
         <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>

--- a/src/v2/tests/header_test.xlsx
+++ b/src/v2/tests/header_test.xlsx
@@ -2058,56 +2058,56 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2432,12 +2432,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
-      <c r="B1" s="63" t="str">
+      <c r="B1" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,2,FALSE))</f>
         <v>F I N A N Z B E R I C H T</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="J1" s="58" t="str">
+      <c r="J1" s="60" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,60,FALSE))</f>
         <v>Tipp:</v>
       </c>
@@ -2452,14 +2452,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="49" t="str">
+      <c r="D2" s="52" t="str">
         <f>IF($E$2="","Chose your language",VLOOKUP($E$2,Sprachversionen!$B:$BN,27,FALSE))</f>
         <v>Sprache</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="56" t="str">
+      <c r="J2" s="49" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,61,FALSE))</f>
         <v>Bitte nutzen Sie zum ausfüllen des Finanzberichts unsere Ausfüllhilfe auf unserer Webseite:</v>
       </c>
@@ -2470,12 +2470,12 @@
       <c r="O2" s="5"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="63" t="str">
+      <c r="B3" s="54" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,3,FALSE))</f>
         <v>ÜBERSICHT ÜBER EINNAHMEN UND AUSGABEN</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="49" t="str">
+      <c r="D3" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>Lokalwährung</v>
       </c>
@@ -2488,7 +2488,7 @@
       <c r="O3" s="5"/>
     </row>
     <row r="4" spans="2:22" ht="12" customHeight="1">
-      <c r="J4" s="59" t="str">
+      <c r="J4" s="67" t="str">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>https://www.kindermissionswerk.org/fuer-partner/service</v>
       </c>
@@ -2499,7 +2499,7 @@
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="49" t="str">
+      <c r="B5" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,4,FALSE))</f>
         <v>Projektnummer</v>
       </c>
@@ -2507,7 +2507,7 @@
       <c r="D5" s="13"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="49" t="str">
+      <c r="B6" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,26,FALSE))</f>
         <v>Projekttitel</v>
       </c>
@@ -2529,17 +2529,17 @@
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="49" t="str">
+      <c r="B8" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,5,FALSE))</f>
         <v>Projektlaufzeit</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="60" t="str">
+      <c r="D8" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E8" s="9"/>
-      <c r="F8" s="60" t="str">
+      <c r="F8" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2552,17 +2552,17 @@
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="49" t="str">
+      <c r="B9" s="52" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,6,FALSE))</f>
         <v>Aktueller Berichtszeitraum</v>
       </c>
       <c r="C9" s="7"/>
-      <c r="D9" s="60" t="str">
+      <c r="D9" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>von (TT MM JJJJ):</v>
       </c>
       <c r="E9" s="9"/>
-      <c r="F9" s="60" t="str">
+      <c r="F9" s="62" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>bis (TT MM JJJJ):</v>
       </c>
@@ -2574,27 +2574,27 @@
     <row r="11" spans="2:22" ht="12.75" customHeight="1">
       <c r="B11" s="17"/>
       <c r="C11" s="27"/>
-      <c r="D11" s="62" t="str">
+      <c r="D11" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>Bewilligtes Budget</v>
       </c>
-      <c r="E11" s="61" t="str">
+      <c r="E11" s="65" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>Einnahmen im Berichtszeitraum</v>
       </c>
-      <c r="F11" s="62" t="str">
+      <c r="F11" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>Einnahmen der gesamten Projektlaufzeit</v>
       </c>
-      <c r="G11" s="62" t="str">
+      <c r="G11" s="59" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>% erhaltene Einnahmen</v>
       </c>
-      <c r="H11" s="66" t="str">
+      <c r="H11" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>Begründung der Budgetüber- oder unterschreitung</v>
       </c>
-      <c r="J11" s="54" t="str">
+      <c r="J11" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2603,7 +2603,7 @@
       <c r="M11" s="35"/>
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
-      <c r="Q11" s="54" t="str">
+      <c r="Q11" s="51" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2614,7 +2614,7 @@
       <c r="V11" s="36"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="67" t="str">
+      <c r="B12" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>EINNAHMEN</v>
       </c>
@@ -2638,7 +2638,7 @@
       <c r="V12" s="38"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="65" t="str">
+      <c r="B13" s="55" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>(in lokaler Währung)</v>
       </c>
@@ -2650,37 +2650,37 @@
       <c r="H13" s="20"/>
       <c r="J13" s="37"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="52" t="str">
+      <c r="L13" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="M13" s="52" t="str">
+      <c r="M13" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="N13" s="52" t="str">
+      <c r="N13" s="56" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="O13" s="64" t="str">
+      <c r="O13" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
       <c r="Q13" s="37"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="52" t="str">
+      <c r="S13" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>Datum</v>
       </c>
-      <c r="T13" s="52" t="str">
+      <c r="T13" s="56" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,63,FALSE))</f>
         <v>Euro</v>
       </c>
-      <c r="U13" s="52" t="str">
+      <c r="U13" s="56" t="str">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>Lokalwährung</v>
       </c>
-      <c r="V13" s="64" t="str">
+      <c r="V13" s="53" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>WK</v>
       </c>
@@ -2723,7 +2723,7 @@
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="50" t="str">
+      <c r="B15" s="68" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>Saldovortrag (aus vorherigem Berichtszeitraum)</v>
       </c>
@@ -2765,7 +2765,7 @@
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="55" t="str">
+      <c r="B16" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>Lokale Eigenleistung</v>
       </c>
@@ -2810,7 +2810,7 @@
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="55" t="str">
+      <c r="B17" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>Beiträge von dritter Seite</v>
       </c>
@@ -2855,7 +2855,7 @@
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="55" t="str">
+      <c r="B18" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>KMW Mittel*</v>
       </c>
@@ -2900,7 +2900,7 @@
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="55" t="str">
+      <c r="B19" s="50" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>Zinserträge</v>
       </c>
@@ -2945,24 +2945,24 @@
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="68" t="str">
+      <c r="B20" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>GESAMT</v>
       </c>
       <c r="C20" s="26"/>
-      <c r="D20" s="53">
+      <c r="D20" s="66">
         <f>SUMPRODUCT(ROUND(D15:D19,2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="66">
         <f>SUMPRODUCT(ROUND(E15:E19,2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="66">
         <f>SUMPRODUCT(ROUND(F15:F19,2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="61">
         <f>IFERROR(F20/D20,0)</f>
         <v>0</v>
       </c>
